--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2765,6 +2765,9974 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Technique 11 Armor Penetration</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>16</v>
+      </c>
+      <c r="G42" t="n">
+        <v>15</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 62%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Technique 11 Armor Penetration</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>18</v>
+      </c>
+      <c r="G43" t="n">
+        <v>17</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 62%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>C003</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Technique 11 Armor Penetration</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" t="n">
+        <v>20</v>
+      </c>
+      <c r="G44" t="n">
+        <v>18</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 62%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>C004</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Technique 11 Armor Penetration</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" t="n">
+        <v>22</v>
+      </c>
+      <c r="G45" t="n">
+        <v>20</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 62%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>C005</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Technique 11 Armor Penetration</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6</v>
+      </c>
+      <c r="F46" t="n">
+        <v>24</v>
+      </c>
+      <c r="G46" t="n">
+        <v>22</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 62%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>C006</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Technique 11 Armor Penetration</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>7</v>
+      </c>
+      <c r="F47" t="n">
+        <v>26</v>
+      </c>
+      <c r="G47" t="n">
+        <v>23</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 62%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>C007</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Technique 11 Armor Penetration</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>8</v>
+      </c>
+      <c r="F48" t="n">
+        <v>28</v>
+      </c>
+      <c r="G48" t="n">
+        <v>25</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 62%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>C008</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Technique 11 Armor Penetration</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>9</v>
+      </c>
+      <c r="F49" t="n">
+        <v>30</v>
+      </c>
+      <c r="G49" t="n">
+        <v>26</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 62%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>C009</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Technique 11 Armor Penetration</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>10</v>
+      </c>
+      <c r="F50" t="n">
+        <v>32</v>
+      </c>
+      <c r="G50" t="n">
+        <v>28</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 62%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C010</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Technique 48 Arrow Rain</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" t="n">
+        <v>23</v>
+      </c>
+      <c r="G51" t="n">
+        <v>22</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 57%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>C011</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Technique 48 Arrow Rain</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" t="n">
+        <v>27</v>
+      </c>
+      <c r="G52" t="n">
+        <v>24</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 57%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>C012</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Technique 48 Arrow Rain</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" t="n">
+        <v>30</v>
+      </c>
+      <c r="G53" t="n">
+        <v>26</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 57%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>C013</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Technique 48 Arrow Rain</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" t="n">
+        <v>33</v>
+      </c>
+      <c r="G54" t="n">
+        <v>28</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 57%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>C014</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Technique 48 Arrow Rain</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6</v>
+      </c>
+      <c r="F55" t="n">
+        <v>36</v>
+      </c>
+      <c r="G55" t="n">
+        <v>30</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 57%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>C015</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Technique 48 Arrow Rain</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>7</v>
+      </c>
+      <c r="F56" t="n">
+        <v>39</v>
+      </c>
+      <c r="G56" t="n">
+        <v>32</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 57%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>C016</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Technique 48 Arrow Rain</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>8</v>
+      </c>
+      <c r="F57" t="n">
+        <v>42</v>
+      </c>
+      <c r="G57" t="n">
+        <v>35</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 57%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>C017</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Technique 48 Arrow Rain</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>9</v>
+      </c>
+      <c r="F58" t="n">
+        <v>45</v>
+      </c>
+      <c r="G58" t="n">
+        <v>37</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 57%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>C018</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Technique 48 Arrow Rain</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F59" t="n">
+        <v>48</v>
+      </c>
+      <c r="G59" t="n">
+        <v>39</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 57%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>C019</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Technique 94 Beast Binder</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" t="n">
+        <v>20</v>
+      </c>
+      <c r="G60" t="n">
+        <v>19</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 58%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>C020</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Technique 94 Beast Binder</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>3</v>
+      </c>
+      <c r="F61" t="n">
+        <v>22</v>
+      </c>
+      <c r="G61" t="n">
+        <v>20</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 58%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C021</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Technique 94 Beast Binder</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4</v>
+      </c>
+      <c r="F62" t="n">
+        <v>24</v>
+      </c>
+      <c r="G62" t="n">
+        <v>22</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 58%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C022</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Technique 94 Beast Binder</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>26</v>
+      </c>
+      <c r="G63" t="n">
+        <v>23</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 58%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>C023</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Technique 94 Beast Binder</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6</v>
+      </c>
+      <c r="F64" t="n">
+        <v>28</v>
+      </c>
+      <c r="G64" t="n">
+        <v>24</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 58%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>C024</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Technique 94 Beast Binder</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>7</v>
+      </c>
+      <c r="F65" t="n">
+        <v>31</v>
+      </c>
+      <c r="G65" t="n">
+        <v>26</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 58%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>C025</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Technique 94 Beast Binder</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>8</v>
+      </c>
+      <c r="F66" t="n">
+        <v>34</v>
+      </c>
+      <c r="G66" t="n">
+        <v>28</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 58%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>C026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Technique 94 Beast Binder</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>9</v>
+      </c>
+      <c r="F67" t="n">
+        <v>37</v>
+      </c>
+      <c r="G67" t="n">
+        <v>30</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 58%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>C027</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Technique 94 Beast Binder</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>10</v>
+      </c>
+      <c r="F68" t="n">
+        <v>40</v>
+      </c>
+      <c r="G68" t="n">
+        <v>32</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 58%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>C028</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Technique 14 Blood Drain</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" t="n">
+        <v>15</v>
+      </c>
+      <c r="G69" t="n">
+        <v>13</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>C029</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Technique 14 Blood Drain</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" t="n">
+        <v>18</v>
+      </c>
+      <c r="G70" t="n">
+        <v>15</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>C030</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Technique 14 Blood Drain</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>4</v>
+      </c>
+      <c r="F71" t="n">
+        <v>21</v>
+      </c>
+      <c r="G71" t="n">
+        <v>17</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>C031</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Technique 14 Blood Drain</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>5</v>
+      </c>
+      <c r="F72" t="n">
+        <v>24</v>
+      </c>
+      <c r="G72" t="n">
+        <v>18</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>C032</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Technique 14 Blood Drain</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6</v>
+      </c>
+      <c r="F73" t="n">
+        <v>27</v>
+      </c>
+      <c r="G73" t="n">
+        <v>21</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>C033</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Technique 14 Blood Drain</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>7</v>
+      </c>
+      <c r="F74" t="n">
+        <v>30</v>
+      </c>
+      <c r="G74" t="n">
+        <v>23</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>C034</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Technique 14 Blood Drain</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>8</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32</v>
+      </c>
+      <c r="G75" t="n">
+        <v>24</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>C035</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Technique 14 Blood Drain</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>9</v>
+      </c>
+      <c r="F76" t="n">
+        <v>34</v>
+      </c>
+      <c r="G76" t="n">
+        <v>26</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>C036</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Technique 14 Blood Drain</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>10</v>
+      </c>
+      <c r="F77" t="n">
+        <v>36</v>
+      </c>
+      <c r="G77" t="n">
+        <v>27</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>C037</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Technique 21 Cross Slash</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" t="n">
+        <v>15</v>
+      </c>
+      <c r="G78" t="n">
+        <v>13</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 53%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>C038</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Technique 21 Cross Slash</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>3</v>
+      </c>
+      <c r="F79" t="n">
+        <v>18</v>
+      </c>
+      <c r="G79" t="n">
+        <v>15</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 53%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>C039</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Technique 21 Cross Slash</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>4</v>
+      </c>
+      <c r="F80" t="n">
+        <v>21</v>
+      </c>
+      <c r="G80" t="n">
+        <v>17</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 53%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>C040</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Technique 21 Cross Slash</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>5</v>
+      </c>
+      <c r="F81" t="n">
+        <v>24</v>
+      </c>
+      <c r="G81" t="n">
+        <v>19</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 53%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>C041</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Technique 21 Cross Slash</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6</v>
+      </c>
+      <c r="F82" t="n">
+        <v>27</v>
+      </c>
+      <c r="G82" t="n">
+        <v>21</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 53%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>C042</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Technique 21 Cross Slash</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>7</v>
+      </c>
+      <c r="F83" t="n">
+        <v>30</v>
+      </c>
+      <c r="G83" t="n">
+        <v>23</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 53%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>C043</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Technique 21 Cross Slash</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>8</v>
+      </c>
+      <c r="F84" t="n">
+        <v>33</v>
+      </c>
+      <c r="G84" t="n">
+        <v>25</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 53%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>C044</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Technique 21 Cross Slash</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>9</v>
+      </c>
+      <c r="F85" t="n">
+        <v>36</v>
+      </c>
+      <c r="G85" t="n">
+        <v>27</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 53%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>C045</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Technique 21 Cross Slash</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>10</v>
+      </c>
+      <c r="F86" t="n">
+        <v>39</v>
+      </c>
+      <c r="G86" t="n">
+        <v>30</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 53%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>C046</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Technique 26 Daedalus Attack</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>2</v>
+      </c>
+      <c r="F87" t="n">
+        <v>39</v>
+      </c>
+      <c r="G87" t="n">
+        <v>38</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 66%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>C047</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Technique 26 Daedalus Attack</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>3</v>
+      </c>
+      <c r="F88" t="n">
+        <v>42</v>
+      </c>
+      <c r="G88" t="n">
+        <v>41</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 66%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>C048</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Technique 26 Daedalus Attack</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>4</v>
+      </c>
+      <c r="F89" t="n">
+        <v>45</v>
+      </c>
+      <c r="G89" t="n">
+        <v>44</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 66%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>C049</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Technique 26 Daedalus Attack</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>5</v>
+      </c>
+      <c r="F90" t="n">
+        <v>48</v>
+      </c>
+      <c r="G90" t="n">
+        <v>46</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 66%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>C050</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Technique 26 Daedalus Attack</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6</v>
+      </c>
+      <c r="F91" t="n">
+        <v>51</v>
+      </c>
+      <c r="G91" t="n">
+        <v>49</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 66%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>C051</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Technique 26 Daedalus Attack</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>7</v>
+      </c>
+      <c r="F92" t="n">
+        <v>55</v>
+      </c>
+      <c r="G92" t="n">
+        <v>53</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 66%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>C052</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Technique 26 Daedalus Attack</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>8</v>
+      </c>
+      <c r="F93" t="n">
+        <v>59</v>
+      </c>
+      <c r="G93" t="n">
+        <v>56</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 66%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>C053</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Technique 26 Daedalus Attack</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>9</v>
+      </c>
+      <c r="F94" t="n">
+        <v>65</v>
+      </c>
+      <c r="G94" t="n">
+        <v>62</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 66%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>C054</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Technique 26 Daedalus Attack</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>10</v>
+      </c>
+      <c r="F95" t="n">
+        <v>71</v>
+      </c>
+      <c r="G95" t="n">
+        <v>67</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 66%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>C055</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Technique 79 Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" t="n">
+        <v>30</v>
+      </c>
+      <c r="G96" t="n">
+        <v>29</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>C056</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Technique 79 Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>3</v>
+      </c>
+      <c r="F97" t="n">
+        <v>33</v>
+      </c>
+      <c r="G97" t="n">
+        <v>31</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>C057</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Technique 79 Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>4</v>
+      </c>
+      <c r="F98" t="n">
+        <v>36</v>
+      </c>
+      <c r="G98" t="n">
+        <v>33</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>C058</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Technique 79 Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>5</v>
+      </c>
+      <c r="F99" t="n">
+        <v>40</v>
+      </c>
+      <c r="G99" t="n">
+        <v>36</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>C059</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Technique 79 Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6</v>
+      </c>
+      <c r="F100" t="n">
+        <v>44</v>
+      </c>
+      <c r="G100" t="n">
+        <v>39</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>C060</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Technique 79 Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>7</v>
+      </c>
+      <c r="F101" t="n">
+        <v>48</v>
+      </c>
+      <c r="G101" t="n">
+        <v>41</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>C061</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Technique 79 Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>8</v>
+      </c>
+      <c r="F102" t="n">
+        <v>52</v>
+      </c>
+      <c r="G102" t="n">
+        <v>44</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>C062</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Technique 79 Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>9</v>
+      </c>
+      <c r="F103" t="n">
+        <v>56</v>
+      </c>
+      <c r="G103" t="n">
+        <v>47</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>C063</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Technique 79 Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>10</v>
+      </c>
+      <c r="F104" t="n">
+        <v>60</v>
+      </c>
+      <c r="G104" t="n">
+        <v>50</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>C064</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Magic 223 Earth Scroll</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F105" t="n">
+        <v>25</v>
+      </c>
+      <c r="G105" t="n">
+        <v>22</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>C065</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Magic 223 Earth Scroll</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>3</v>
+      </c>
+      <c r="F106" t="n">
+        <v>30</v>
+      </c>
+      <c r="G106" t="n">
+        <v>24</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>C066</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Magic 223 Earth Scroll</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>4</v>
+      </c>
+      <c r="F107" t="n">
+        <v>35</v>
+      </c>
+      <c r="G107" t="n">
+        <v>27</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>C067</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Magic 223 Earth Scroll</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>5</v>
+      </c>
+      <c r="F108" t="n">
+        <v>40</v>
+      </c>
+      <c r="G108" t="n">
+        <v>30</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>C068</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Magic 219 Fire Scroll</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>2</v>
+      </c>
+      <c r="F109" t="n">
+        <v>25</v>
+      </c>
+      <c r="G109" t="n">
+        <v>22</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>C069</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Magic 219 Fire Scroll</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>3</v>
+      </c>
+      <c r="F110" t="n">
+        <v>30</v>
+      </c>
+      <c r="G110" t="n">
+        <v>24</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>C070</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Magic 219 Fire Scroll</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>4</v>
+      </c>
+      <c r="F111" t="n">
+        <v>35</v>
+      </c>
+      <c r="G111" t="n">
+        <v>27</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>C071</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Magic 219 Fire Scroll</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>5</v>
+      </c>
+      <c r="F112" t="n">
+        <v>40</v>
+      </c>
+      <c r="G112" t="n">
+        <v>30</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>C072</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Technique 42 Guided Shot</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>2</v>
+      </c>
+      <c r="F113" t="n">
+        <v>10</v>
+      </c>
+      <c r="G113" t="n">
+        <v>9</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 57%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>C073</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Technique 42 Guided Shot</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>3</v>
+      </c>
+      <c r="F114" t="n">
+        <v>12</v>
+      </c>
+      <c r="G114" t="n">
+        <v>10</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 57%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>C074</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Technique 42 Guided Shot</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>4</v>
+      </c>
+      <c r="F115" t="n">
+        <v>14</v>
+      </c>
+      <c r="G115" t="n">
+        <v>11</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 57%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>C075</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Technique 42 Guided Shot</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>5</v>
+      </c>
+      <c r="F116" t="n">
+        <v>16</v>
+      </c>
+      <c r="G116" t="n">
+        <v>13</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 57%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>C076</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Technique 76 Hard Whipping</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>2</v>
+      </c>
+      <c r="F117" t="n">
+        <v>25</v>
+      </c>
+      <c r="G117" t="n">
+        <v>24</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>C077</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Technique 76 Hard Whipping</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>3</v>
+      </c>
+      <c r="F118" t="n">
+        <v>28</v>
+      </c>
+      <c r="G118" t="n">
+        <v>26</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>C078</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Technique 76 Hard Whipping</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>4</v>
+      </c>
+      <c r="F119" t="n">
+        <v>31</v>
+      </c>
+      <c r="G119" t="n">
+        <v>28</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>C079</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Technique 76 Hard Whipping</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>5</v>
+      </c>
+      <c r="F120" t="n">
+        <v>34</v>
+      </c>
+      <c r="G120" t="n">
+        <v>30</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>C080</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Technique 76 Hard Whipping</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6</v>
+      </c>
+      <c r="F121" t="n">
+        <v>37</v>
+      </c>
+      <c r="G121" t="n">
+        <v>32</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>C081</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Technique 76 Hard Whipping</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>7</v>
+      </c>
+      <c r="F122" t="n">
+        <v>40</v>
+      </c>
+      <c r="G122" t="n">
+        <v>34</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>C082</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Technique 76 Hard Whipping</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>8</v>
+      </c>
+      <c r="F123" t="n">
+        <v>43</v>
+      </c>
+      <c r="G123" t="n">
+        <v>36</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>C083</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Technique 76 Hard Whipping</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>9</v>
+      </c>
+      <c r="F124" t="n">
+        <v>46</v>
+      </c>
+      <c r="G124" t="n">
+        <v>39</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>C084</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Technique 76 Hard Whipping</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>10</v>
+      </c>
+      <c r="F125" t="n">
+        <v>50</v>
+      </c>
+      <c r="G125" t="n">
+        <v>41</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>C085</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Magic 221 Lightning Scroll</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>2</v>
+      </c>
+      <c r="F126" t="n">
+        <v>25</v>
+      </c>
+      <c r="G126" t="n">
+        <v>22</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>C086</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Magic 221 Lightning Scroll</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>3</v>
+      </c>
+      <c r="F127" t="n">
+        <v>30</v>
+      </c>
+      <c r="G127" t="n">
+        <v>24</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>C087</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Magic 221 Lightning Scroll</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>4</v>
+      </c>
+      <c r="F128" t="n">
+        <v>35</v>
+      </c>
+      <c r="G128" t="n">
+        <v>27</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>C088</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Magic 221 Lightning Scroll</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>5</v>
+      </c>
+      <c r="F129" t="n">
+        <v>40</v>
+      </c>
+      <c r="G129" t="n">
+        <v>30</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>C089</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Technique 57 Magical Slash</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>2</v>
+      </c>
+      <c r="F130" t="n">
+        <v>40</v>
+      </c>
+      <c r="G130" t="n">
+        <v>39</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 61%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>C090</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Technique 57 Magical Slash</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>3</v>
+      </c>
+      <c r="F131" t="n">
+        <v>44</v>
+      </c>
+      <c r="G131" t="n">
+        <v>42</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 61%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>C091</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Technique 57 Magical Slash</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>4</v>
+      </c>
+      <c r="F132" t="n">
+        <v>48</v>
+      </c>
+      <c r="G132" t="n">
+        <v>45</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 61%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>C092</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Technique 57 Magical Slash</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>5</v>
+      </c>
+      <c r="F133" t="n">
+        <v>52</v>
+      </c>
+      <c r="G133" t="n">
+        <v>48</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 61%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>C093</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Technique 57 Magical Slash</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>6</v>
+      </c>
+      <c r="F134" t="n">
+        <v>57</v>
+      </c>
+      <c r="G134" t="n">
+        <v>51</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 61%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>C094</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Technique 57 Magical Slash</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>7</v>
+      </c>
+      <c r="F135" t="n">
+        <v>62</v>
+      </c>
+      <c r="G135" t="n">
+        <v>55</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 61%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>C095</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Technique 57 Magical Slash</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>8</v>
+      </c>
+      <c r="F136" t="n">
+        <v>67</v>
+      </c>
+      <c r="G136" t="n">
+        <v>59</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 61%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>C096</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Technique 57 Magical Slash</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>9</v>
+      </c>
+      <c r="F137" t="n">
+        <v>73</v>
+      </c>
+      <c r="G137" t="n">
+        <v>64</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 61%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>C097</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Technique 57 Magical Slash</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>10</v>
+      </c>
+      <c r="F138" t="n">
+        <v>79</v>
+      </c>
+      <c r="G138" t="n">
+        <v>68</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 61%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>C098</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Technique 60 Magical Spark</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>2</v>
+      </c>
+      <c r="F139" t="n">
+        <v>16</v>
+      </c>
+      <c r="G139" t="n">
+        <v>14</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 46%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>C099</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Technique 60 Magical Spark</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>3</v>
+      </c>
+      <c r="F140" t="n">
+        <v>19</v>
+      </c>
+      <c r="G140" t="n">
+        <v>16</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 46%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>C100</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Technique 60 Magical Spark</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>4</v>
+      </c>
+      <c r="F141" t="n">
+        <v>22</v>
+      </c>
+      <c r="G141" t="n">
+        <v>17</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 46%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>C101</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Technique 60 Magical Spark</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>5</v>
+      </c>
+      <c r="F142" t="n">
+        <v>25</v>
+      </c>
+      <c r="G142" t="n">
+        <v>19</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 46%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>C102</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Technique 60 Magical Spark</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>6</v>
+      </c>
+      <c r="F143" t="n">
+        <v>29</v>
+      </c>
+      <c r="G143" t="n">
+        <v>22</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 46%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>C103</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Technique 60 Magical Spark</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>7</v>
+      </c>
+      <c r="F144" t="n">
+        <v>33</v>
+      </c>
+      <c r="G144" t="n">
+        <v>25</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 46%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>C104</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Technique 60 Magical Spark</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>8</v>
+      </c>
+      <c r="F145" t="n">
+        <v>37</v>
+      </c>
+      <c r="G145" t="n">
+        <v>28</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 46%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>C105</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Technique 60 Magical Spark</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>9</v>
+      </c>
+      <c r="F146" t="n">
+        <v>41</v>
+      </c>
+      <c r="G146" t="n">
+        <v>31</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 46%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>C106</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Technique 60 Magical Spark</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>10</v>
+      </c>
+      <c r="F147" t="n">
+        <v>45</v>
+      </c>
+      <c r="G147" t="n">
+        <v>34</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 46%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>C107</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Technique 12 Onikagura</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>2</v>
+      </c>
+      <c r="F148" t="n">
+        <v>26</v>
+      </c>
+      <c r="G148" t="n">
+        <v>24</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 51%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>C108</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Technique 12 Onikagura</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>3</v>
+      </c>
+      <c r="F149" t="n">
+        <v>30</v>
+      </c>
+      <c r="G149" t="n">
+        <v>26</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 51%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>C109</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Technique 12 Onikagura</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>4</v>
+      </c>
+      <c r="F150" t="n">
+        <v>34</v>
+      </c>
+      <c r="G150" t="n">
+        <v>28</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 51%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>C110</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Technique 12 Onikagura</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>5</v>
+      </c>
+      <c r="F151" t="n">
+        <v>38</v>
+      </c>
+      <c r="G151" t="n">
+        <v>31</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 51%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>C111</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Technique 12 Onikagura</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>6</v>
+      </c>
+      <c r="F152" t="n">
+        <v>42</v>
+      </c>
+      <c r="G152" t="n">
+        <v>33</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 51%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>C112</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Technique 12 Onikagura</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>7</v>
+      </c>
+      <c r="F153" t="n">
+        <v>46</v>
+      </c>
+      <c r="G153" t="n">
+        <v>35</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 51%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>C113</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Technique 12 Onikagura</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>8</v>
+      </c>
+      <c r="F154" t="n">
+        <v>50</v>
+      </c>
+      <c r="G154" t="n">
+        <v>38</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 51%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>C114</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Technique 12 Onikagura</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>9</v>
+      </c>
+      <c r="F155" t="n">
+        <v>54</v>
+      </c>
+      <c r="G155" t="n">
+        <v>41</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 51%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>C115</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Technique 12 Onikagura</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>10</v>
+      </c>
+      <c r="F156" t="n">
+        <v>58</v>
+      </c>
+      <c r="G156" t="n">
+        <v>44</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 51%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>C116</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Technique 51 Phoenix</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>2</v>
+      </c>
+      <c r="F157" t="n">
+        <v>27</v>
+      </c>
+      <c r="G157" t="n">
+        <v>26</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 66%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>C117</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Technique 51 Phoenix</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>3</v>
+      </c>
+      <c r="F158" t="n">
+        <v>30</v>
+      </c>
+      <c r="G158" t="n">
+        <v>29</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 66%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>C118</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Technique 51 Phoenix</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>4</v>
+      </c>
+      <c r="F159" t="n">
+        <v>33</v>
+      </c>
+      <c r="G159" t="n">
+        <v>32</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 66%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>C119</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Technique 51 Phoenix</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>5</v>
+      </c>
+      <c r="F160" t="n">
+        <v>36</v>
+      </c>
+      <c r="G160" t="n">
+        <v>34</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 66%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>C120</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Technique 51 Phoenix</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>6</v>
+      </c>
+      <c r="F161" t="n">
+        <v>39</v>
+      </c>
+      <c r="G161" t="n">
+        <v>37</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 66%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>C121</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Technique 51 Phoenix</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>7</v>
+      </c>
+      <c r="F162" t="n">
+        <v>42</v>
+      </c>
+      <c r="G162" t="n">
+        <v>40</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 66%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>C122</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Technique 51 Phoenix</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>8</v>
+      </c>
+      <c r="F163" t="n">
+        <v>45</v>
+      </c>
+      <c r="G163" t="n">
+        <v>42</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 66%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>C123</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Technique 51 Phoenix</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>9</v>
+      </c>
+      <c r="F164" t="n">
+        <v>48</v>
+      </c>
+      <c r="G164" t="n">
+        <v>45</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 66%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>C124</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Technique 51 Phoenix</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>10</v>
+      </c>
+      <c r="F165" t="n">
+        <v>50</v>
+      </c>
+      <c r="G165" t="n">
+        <v>47</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 66%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>C125</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Technique 3 Raging Smash</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>2</v>
+      </c>
+      <c r="F166" t="n">
+        <v>8</v>
+      </c>
+      <c r="G166" t="n">
+        <v>6</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 29%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>C126</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Technique 3 Raging Smash</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>3</v>
+      </c>
+      <c r="F167" t="n">
+        <v>11</v>
+      </c>
+      <c r="G167" t="n">
+        <v>9</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 29%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>C127</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Technique 3 Raging Smash</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>4</v>
+      </c>
+      <c r="F168" t="n">
+        <v>14</v>
+      </c>
+      <c r="G168" t="n">
+        <v>11</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 29%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>C128</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Technique 3 Raging Smash</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>5</v>
+      </c>
+      <c r="F169" t="n">
+        <v>17</v>
+      </c>
+      <c r="G169" t="n">
+        <v>13</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 29%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>C129</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Technique 3 Raging Smash</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>6</v>
+      </c>
+      <c r="F170" t="n">
+        <v>20</v>
+      </c>
+      <c r="G170" t="n">
+        <v>15</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 29%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>C130</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Technique 3 Raging Smash</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>7</v>
+      </c>
+      <c r="F171" t="n">
+        <v>22</v>
+      </c>
+      <c r="G171" t="n">
+        <v>17</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 29%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>C131</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Technique 3 Raging Smash</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>8</v>
+      </c>
+      <c r="F172" t="n">
+        <v>24</v>
+      </c>
+      <c r="G172" t="n">
+        <v>18</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 29%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>C132</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Technique 3 Raging Smash</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>9</v>
+      </c>
+      <c r="F173" t="n">
+        <v>26</v>
+      </c>
+      <c r="G173" t="n">
+        <v>20</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 29%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>C133</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Technique 3 Raging Smash</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>10</v>
+      </c>
+      <c r="F174" t="n">
+        <v>28</v>
+      </c>
+      <c r="G174" t="n">
+        <v>21</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 29%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>C134</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Magic 224 Rainbow Flash</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>2</v>
+      </c>
+      <c r="F175" t="n">
+        <v>28</v>
+      </c>
+      <c r="G175" t="n">
+        <v>27</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 69%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>C135</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Magic 224 Rainbow Flash</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>3</v>
+      </c>
+      <c r="F176" t="n">
+        <v>34</v>
+      </c>
+      <c r="G176" t="n">
+        <v>33</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 69%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>C136</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Magic 224 Rainbow Flash</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>4</v>
+      </c>
+      <c r="F177" t="n">
+        <v>40</v>
+      </c>
+      <c r="G177" t="n">
+        <v>39</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 69%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>C137</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Magic 224 Rainbow Flash</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>5</v>
+      </c>
+      <c r="F178" t="n">
+        <v>46</v>
+      </c>
+      <c r="G178" t="n">
+        <v>45</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 69%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>C138</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Magic 224 Rainbow Flash</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>6</v>
+      </c>
+      <c r="F179" t="n">
+        <v>50</v>
+      </c>
+      <c r="G179" t="n">
+        <v>49</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 69%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>C139</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Magic 224 Rainbow Flash</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>7</v>
+      </c>
+      <c r="F180" t="n">
+        <v>54</v>
+      </c>
+      <c r="G180" t="n">
+        <v>53</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 69%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>C140</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Magic 224 Rainbow Flash</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>8</v>
+      </c>
+      <c r="F181" t="n">
+        <v>58</v>
+      </c>
+      <c r="G181" t="n">
+        <v>56</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 69%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>C141</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Magic 224 Rainbow Flash</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>9</v>
+      </c>
+      <c r="F182" t="n">
+        <v>62</v>
+      </c>
+      <c r="G182" t="n">
+        <v>60</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 69%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>C142</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Magic 224 Rainbow Flash</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>10</v>
+      </c>
+      <c r="F183" t="n">
+        <v>66</v>
+      </c>
+      <c r="G183" t="n">
+        <v>64</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 69%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>C143</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Technique 31 Sharp Stab</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>2</v>
+      </c>
+      <c r="F184" t="n">
+        <v>8</v>
+      </c>
+      <c r="G184" t="n">
+        <v>6</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 20%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>C144</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Technique 31 Sharp Stab</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>3</v>
+      </c>
+      <c r="F185" t="n">
+        <v>11</v>
+      </c>
+      <c r="G185" t="n">
+        <v>9</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 20%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>C145</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Technique 31 Sharp Stab</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>4</v>
+      </c>
+      <c r="F186" t="n">
+        <v>14</v>
+      </c>
+      <c r="G186" t="n">
+        <v>11</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 20%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>C146</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Technique 31 Sharp Stab</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>5</v>
+      </c>
+      <c r="F187" t="n">
+        <v>17</v>
+      </c>
+      <c r="G187" t="n">
+        <v>13</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 20%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>C147</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Technique 31 Sharp Stab</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>6</v>
+      </c>
+      <c r="F188" t="n">
+        <v>20</v>
+      </c>
+      <c r="G188" t="n">
+        <v>15</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 20%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>C148</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Technique 31 Sharp Stab</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>7</v>
+      </c>
+      <c r="F189" t="n">
+        <v>23</v>
+      </c>
+      <c r="G189" t="n">
+        <v>18</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 20%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>C149</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Technique 31 Sharp Stab</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>8</v>
+      </c>
+      <c r="F190" t="n">
+        <v>26</v>
+      </c>
+      <c r="G190" t="n">
+        <v>20</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 20%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>C150</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Technique 31 Sharp Stab</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>9</v>
+      </c>
+      <c r="F191" t="n">
+        <v>28</v>
+      </c>
+      <c r="G191" t="n">
+        <v>21</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 20%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>C151</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Technique 31 Sharp Stab</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>10</v>
+      </c>
+      <c r="F192" t="n">
+        <v>30</v>
+      </c>
+      <c r="G192" t="n">
+        <v>23</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 20%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>C152</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Technique 15 Soul Drain</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>2</v>
+      </c>
+      <c r="F193" t="n">
+        <v>8</v>
+      </c>
+      <c r="G193" t="n">
+        <v>6</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 38%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>C153</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Technique 15 Soul Drain</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>3</v>
+      </c>
+      <c r="F194" t="n">
+        <v>10</v>
+      </c>
+      <c r="G194" t="n">
+        <v>8</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 38%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>C154</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Technique 15 Soul Drain</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>4</v>
+      </c>
+      <c r="F195" t="n">
+        <v>12</v>
+      </c>
+      <c r="G195" t="n">
+        <v>9</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 38%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>C155</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Technique 15 Soul Drain</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>5</v>
+      </c>
+      <c r="F196" t="n">
+        <v>14</v>
+      </c>
+      <c r="G196" t="n">
+        <v>11</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 38%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>C156</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Technique 15 Soul Drain</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>6</v>
+      </c>
+      <c r="F197" t="n">
+        <v>16</v>
+      </c>
+      <c r="G197" t="n">
+        <v>12</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 38%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>C157</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Technique 15 Soul Drain</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>7</v>
+      </c>
+      <c r="F198" t="n">
+        <v>18</v>
+      </c>
+      <c r="G198" t="n">
+        <v>14</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 38%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>C158</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Technique 15 Soul Drain</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>8</v>
+      </c>
+      <c r="F199" t="n">
+        <v>20</v>
+      </c>
+      <c r="G199" t="n">
+        <v>15</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 38%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>C159</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Technique 15 Soul Drain</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>9</v>
+      </c>
+      <c r="F200" t="n">
+        <v>22</v>
+      </c>
+      <c r="G200" t="n">
+        <v>17</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 38%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>C160</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Technique 15 Soul Drain</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>10</v>
+      </c>
+      <c r="F201" t="n">
+        <v>24</v>
+      </c>
+      <c r="G201" t="n">
+        <v>18</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 38%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>C161</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Magic 220 Water Scroll</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>2</v>
+      </c>
+      <c r="F202" t="n">
+        <v>25</v>
+      </c>
+      <c r="G202" t="n">
+        <v>22</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>C162</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Magic 220 Water Scroll</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>3</v>
+      </c>
+      <c r="F203" t="n">
+        <v>30</v>
+      </c>
+      <c r="G203" t="n">
+        <v>24</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>C163</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Magic 220 Water Scroll</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>4</v>
+      </c>
+      <c r="F204" t="n">
+        <v>35</v>
+      </c>
+      <c r="G204" t="n">
+        <v>27</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>C164</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Magic 220 Water Scroll</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>5</v>
+      </c>
+      <c r="F205" t="n">
+        <v>40</v>
+      </c>
+      <c r="G205" t="n">
+        <v>30</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>C165</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Magic 222 Wind Scroll</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>2</v>
+      </c>
+      <c r="F206" t="n">
+        <v>25</v>
+      </c>
+      <c r="G206" t="n">
+        <v>22</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>C166</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Magic 222 Wind Scroll</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>3</v>
+      </c>
+      <c r="F207" t="n">
+        <v>30</v>
+      </c>
+      <c r="G207" t="n">
+        <v>24</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>C167</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Magic 222 Wind Scroll</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>4</v>
+      </c>
+      <c r="F208" t="n">
+        <v>35</v>
+      </c>
+      <c r="G208" t="n">
+        <v>27</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>C168</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Magic 222 Wind Scroll</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>5</v>
+      </c>
+      <c r="F209" t="n">
+        <v>40</v>
+      </c>
+      <c r="G209" t="n">
+        <v>30</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>J03, J10</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 50%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>R001.1</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Passive 256 Auto-Refresh</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>TP per turn (effect 247)</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>1</v>
+      </c>
+      <c r="F210" t="n">
+        <v>3</v>
+      </c>
+      <c r="G210" t="n">
+        <v>4</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>J05, F26</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>A little more TP outside the Maid line, which keeps Cook, Self-Sacrifice and Generous Heart as its own; measured: Actim without a Maid 7.0 to 6.4 of 20 battles (no real change), with one 15.6 to 16.9</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>R001.2</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Passive 256 Auto-Refresh</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>TP per turn (effect 247)</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>2</v>
+      </c>
+      <c r="F211" t="n">
+        <v>6</v>
+      </c>
+      <c r="G211" t="n">
+        <v>8</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>J05, F26</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>A little more TP outside the Maid line, which keeps Cook, Self-Sacrifice and Generous Heart as its own; measured: Actim without a Maid 7.0 to 6.4 of 20 battles (no real change), with one 15.6 to 16.9</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>R001.3</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Passive 256 Auto-Refresh</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>TP per turn (effect 247)</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>3</v>
+      </c>
+      <c r="F212" t="n">
+        <v>9</v>
+      </c>
+      <c r="G212" t="n">
+        <v>12</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>J05, F26</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>A little more TP outside the Maid line, which keeps Cook, Self-Sacrifice and Generous Heart as its own; measured: Actim without a Maid 7.0 to 6.4 of 20 battles (no real change), with one 15.6 to 16.9</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>R001.4</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Passive 256 Auto-Refresh</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>TP per turn (effect 247)</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>4</v>
+      </c>
+      <c r="F213" t="n">
+        <v>12</v>
+      </c>
+      <c r="G213" t="n">
+        <v>16</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>J05, F26</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>A little more TP outside the Maid line, which keeps Cook, Self-Sacrifice and Generous Heart as its own; measured: Actim without a Maid 7.0 to 6.4 of 20 battles (no real change), with one 15.6 to 16.9</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>R001.5</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Passive 256 Auto-Refresh</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>TP per turn (effect 247)</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>5</v>
+      </c>
+      <c r="F214" t="n">
+        <v>16</v>
+      </c>
+      <c r="G214" t="n">
+        <v>20</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>J05, F26</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>A little more TP outside the Maid line, which keeps Cook, Self-Sacrifice and Generous Heart as its own; measured: Actim without a Maid 7.0 to 6.4 of 20 battles (no real change), with one 15.6 to 16.9</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>R002.1</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Passive 257 Mini Auto-Refresh</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>TP per turn (effect 247)</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>1</v>
+      </c>
+      <c r="F215" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" t="n">
+        <v>2</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>J05, F26</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>A little more TP outside the Maid line, which keeps Cook, Self-Sacrifice and Generous Heart as its own; measured: Actim without a Maid 7.0 to 6.4 of 20 battles (no real change), with one 15.6 to 16.9</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>R002.2</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Passive 257 Mini Auto-Refresh</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>TP per turn (effect 247)</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>2</v>
+      </c>
+      <c r="F216" t="n">
+        <v>3</v>
+      </c>
+      <c r="G216" t="n">
+        <v>4</v>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>J05, F26</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>A little more TP outside the Maid line, which keeps Cook, Self-Sacrifice and Generous Heart as its own; measured: Actim without a Maid 7.0 to 6.4 of 20 battles (no real change), with one 15.6 to 16.9</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>R002.3</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Passive 257 Mini Auto-Refresh</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>TP per turn (effect 247)</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>3</v>
+      </c>
+      <c r="F217" t="n">
+        <v>5</v>
+      </c>
+      <c r="G217" t="n">
+        <v>6</v>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>J05, F26</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>A little more TP outside the Maid line, which keeps Cook, Self-Sacrifice and Generous Heart as its own; measured: Actim without a Maid 7.0 to 6.4 of 20 battles (no real change), with one 15.6 to 16.9</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>R002.4</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Passive 257 Mini Auto-Refresh</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>TP per turn (effect 247)</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>4</v>
+      </c>
+      <c r="F218" t="n">
+        <v>7</v>
+      </c>
+      <c r="G218" t="n">
+        <v>8</v>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>J05, F26</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>A little more TP outside the Maid line, which keeps Cook, Self-Sacrifice and Generous Heart as its own; measured: Actim without a Maid 7.0 to 6.4 of 20 battles (no real change), with one 15.6 to 16.9</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>R002.5</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Passive 257 Mini Auto-Refresh</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>TP per turn (effect 247)</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>5</v>
+      </c>
+      <c r="F219" t="n">
+        <v>9</v>
+      </c>
+      <c r="G219" t="n">
+        <v>11</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>J05, F26</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>A little more TP outside the Maid line, which keeps Cook, Self-Sacrifice and Generous Heart as its own; measured: Actim without a Maid 7.0 to 6.4 of 20 battles (no real change), with one 15.6 to 16.9</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L462"/>
+  <dimension ref="A1:L473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26341,6 +26341,622 @@
         </is>
       </c>
     </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>L001</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Technique 114 Roulette Circus Effect</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>effect 128 (HP recovery of a random enemy)</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>1</v>
+      </c>
+      <c r="F463" t="n">
+        <v>1</v>
+      </c>
+      <c r="G463" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>J30, F22</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>Less luck: a bad draw no longer sinks the fight: it healed an enemy fully. The chances of the outcomes (executable, L37) are not touched; the empty outcome, the 666 damage and the money ones stay</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>L002</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Technique 115 Roulette Circus Effect</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>effect 435 (damage = level x value)</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>1</v>
+      </c>
+      <c r="F464" t="n">
+        <v>10</v>
+      </c>
+      <c r="G464" t="n">
+        <v>15</v>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>J30, F22</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>A good draw pays for the TP of the skill. The chances of the outcomes (executable, L37) are not touched; the empty outcome, the 666 damage and the money ones stay</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>L003</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Technique 126 Magic Box Effect</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>effect 119 (instant death of the user)</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>1</v>
+      </c>
+      <c r="F465" t="n">
+        <v>10</v>
+      </c>
+      <c r="G465" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>J30, F22</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>Less luck: a bad draw no longer sinks the fight: it was certain. The chances of the outcomes (executable, L37) are not touched; the empty outcome, the 666 damage and the money ones stay</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>L004</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Technique 122 Magic Box Effect</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>effect 26 (power of the hit on the user)</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>1</v>
+      </c>
+      <c r="F466" t="n">
+        <v>1</v>
+      </c>
+      <c r="G466" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>J30, F22</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>Less luck: a bad draw no longer sinks the fight: a fright instead of a double hit. The chances of the outcomes (executable, L37) are not touched; the empty outcome, the 666 damage and the money ones stay</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>L005</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Technique 118 Magic Box Effect</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>effect 26 (power on all enemies)</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>1</v>
+      </c>
+      <c r="F467" t="n">
+        <v>1</v>
+      </c>
+      <c r="G467" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>J30, F22</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>A good draw pays for the TP of the skill. The chances of the outcomes (executable, L37) are not touched; the empty outcome, the 666 damage and the money ones stay</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>L006</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Technique 131 Showtime Effect</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>effect 118 (stun of the whole party)</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>1</v>
+      </c>
+      <c r="F468" t="n">
+        <v>10</v>
+      </c>
+      <c r="G468" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>J30, F22</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>Less luck: a bad draw no longer sinks the fight: it was certain. The chances of the outcomes (executable, L37) are not touched; the empty outcome, the 666 damage and the money ones stay</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>L007</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Technique 139 Showtime Effect</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>effect 26 (power of the seven hits)</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>1</v>
+      </c>
+      <c r="F469" t="n">
+        <v>1</v>
+      </c>
+      <c r="G469" t="n">
+        <v>2</v>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>J30, F22</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>A good draw pays for the TP of the skill and makes up for the rest of the table (the user, 2026-10-09). The chances of the outcomes (executable, L37) are not touched; the empty outcome, the 666 damage and the money ones stay</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>L008</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Technique 141 Heaven or Hell Effect</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>effect 138 (damage, share of the target max HP)</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>1</v>
+      </c>
+      <c r="F470" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G470" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>J30, F22</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>Heaven or Hell was never worth it (the user, 2026-10-09). The chances of the outcomes (executable, L37) are not touched; the empty outcome, the 666 damage and the money ones stay</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>L009</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Technique 141 Heaven or Hell Effect</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>effect 296 (damage cap)</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>1</v>
+      </c>
+      <c r="F471" t="n">
+        <v>222</v>
+      </c>
+      <c r="G471" t="n">
+        <v>2220</v>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>J30, F22</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>The cap kept the damage at 222 against bosses of tens of thousands of HP. The chances of the outcomes (executable, L37) are not touched; the empty outcome, the 666 damage and the money ones stay</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>L010</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Technique 142 Heaven or Hell Effect</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>effect 132 (heal of the target, share of its max HP)</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>1</v>
+      </c>
+      <c r="F472" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G472" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>J30, F22</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>Less luck: a bad draw no longer sinks the fight. The chances of the outcomes (executable, L37) are not touched; the empty outcome, the 666 damage and the money ones stay</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>L011</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Technique 142 Heaven or Hell Effect</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>effect 295 (heal cap)</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>1</v>
+      </c>
+      <c r="F473" t="n">
+        <v>555</v>
+      </c>
+      <c r="G473" t="n">
+        <v>222</v>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>J30, F22</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>Less luck: a bad draw no longer sinks the fight. The chances of the outcomes (executable, L37) are not touched; the empty outcome, the 666 damage and the money ones stay</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L473"/>
+  <dimension ref="A1:L494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26957,6 +26957,1182 @@
         </is>
       </c>
     </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>S001</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Technique 89 Graceful Rose</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>1</v>
+      </c>
+      <c r="F474" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G474" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>F75</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>The single-target fan strike of the Papillon (her only tool against a lone boss was the area attack Rose Queen). The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>S002</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Technique 89 Graceful Rose</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>1</v>
+      </c>
+      <c r="F475" t="n">
+        <v>5</v>
+      </c>
+      <c r="G475" t="n">
+        <v>12</v>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>F75</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>The single-target fan strike of the Papillon (her only tool against a lone boss was the area attack Rose Queen). The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Technique 82 Checkmate</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>1</v>
+      </c>
+      <c r="F476" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G476" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>U02 (the Spieler line)</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>S004</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Technique 82 Checkmate</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>2</v>
+      </c>
+      <c r="F477" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G477" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>U02 (the Spieler line)</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>S005</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Technique 82 Checkmate</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>3</v>
+      </c>
+      <c r="F478" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G478" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>U02 (the Spieler line)</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>S006</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Technique 82 Checkmate</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>4</v>
+      </c>
+      <c r="F479" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G479" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>U02 (the Spieler line)</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>S007</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Technique 82 Checkmate</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E480" t="n">
+        <v>5</v>
+      </c>
+      <c r="F480" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G480" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>U02 (the Spieler line)</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>S008</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Technique 82 Checkmate</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E481" t="n">
+        <v>6</v>
+      </c>
+      <c r="F481" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G481" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>U02 (the Spieler line)</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>S009</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Technique 82 Checkmate</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>7</v>
+      </c>
+      <c r="F482" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G482" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>U02 (the Spieler line)</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>S010</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Technique 82 Checkmate</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>8</v>
+      </c>
+      <c r="F483" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G483" t="n">
+        <v>1.184</v>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>U02 (the Spieler line)</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>S011</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Technique 82 Checkmate</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E484" t="n">
+        <v>9</v>
+      </c>
+      <c r="F484" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G484" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>U02 (the Spieler line)</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>S012</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Technique 82 Checkmate</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>10</v>
+      </c>
+      <c r="F485" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G485" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>U02 (the Spieler line)</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>S013</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Technique 92 Trump Card</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>effect 48 (ATK gained, DEF x value)</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>1</v>
+      </c>
+      <c r="F486" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G486" t="n">
+        <v>1</v>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>F19</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>Trump Card worth it before its top level; the top is unchanged; the DEF of -10,000 (code) is the Joker's identity. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>S014</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Technique 92 Trump Card</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>effect 48 (ATK gained, DEF x value)</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>2</v>
+      </c>
+      <c r="F487" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G487" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>F19</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>Trump Card worth it before its top level; the top is unchanged; the DEF of -10,000 (code) is the Joker's identity. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>S015</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Technique 92 Trump Card</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>effect 48 (ATK gained, DEF x value)</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>3</v>
+      </c>
+      <c r="F488" t="n">
+        <v>1</v>
+      </c>
+      <c r="G488" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>F19</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>Trump Card worth it before its top level; the top is unchanged; the DEF of -10,000 (code) is the Joker's identity. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Technique 92 Trump Card</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>effect 48 (ATK gained, DEF x value)</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>4</v>
+      </c>
+      <c r="F489" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G489" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>F19</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>Trump Card worth it before its top level; the top is unchanged; the DEF of -10,000 (code) is the Joker's identity. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>S017</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Magic 228 Limit Field</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>1</v>
+      </c>
+      <c r="F490" t="n">
+        <v>28</v>
+      </c>
+      <c r="G490" t="n">
+        <v>16</v>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>F74</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>Limit Field lowers damage on both sides (the value cannot make it one-sided): a cheaper niche tool. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>S018</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Magic 228 Limit Field</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>2</v>
+      </c>
+      <c r="F491" t="n">
+        <v>31</v>
+      </c>
+      <c r="G491" t="n">
+        <v>18</v>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>F74</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>Limit Field lowers damage on both sides (the value cannot make it one-sided): a cheaper niche tool. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>S019</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Magic 228 Limit Field</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E492" t="n">
+        <v>3</v>
+      </c>
+      <c r="F492" t="n">
+        <v>34</v>
+      </c>
+      <c r="G492" t="n">
+        <v>19</v>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>F74</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>Limit Field lowers damage on both sides (the value cannot make it one-sided): a cheaper niche tool. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>S020</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Magic 228 Limit Field</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>4</v>
+      </c>
+      <c r="F493" t="n">
+        <v>37</v>
+      </c>
+      <c r="G493" t="n">
+        <v>21</v>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>F74</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>Limit Field lowers damage on both sides (the value cannot make it one-sided): a cheaper niche tool. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>S021</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Magic 228 Limit Field</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>5</v>
+      </c>
+      <c r="F494" t="n">
+        <v>40</v>
+      </c>
+      <c r="G494" t="n">
+        <v>22</v>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>F74</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>Limit Field lowers damage on both sides (the value cannot make it one-sided): a cheaper niche tool. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L494"/>
+  <dimension ref="A1:L533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28133,6 +28133,2179 @@
         </is>
       </c>
     </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>W001</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>27 Claymore</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>ATK (base)</t>
+        </is>
+      </c>
+      <c r="F495" t="n">
+        <v>37</v>
+      </c>
+      <c r="G495" t="n">
+        <v>33</v>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>L14</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>J07, F08</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>A small cut to two-handed pieces (the user, 2026-10-09): base ATK -10%, the upgrade rate kept, so the middle of the game moves (one-handed from 68 - 69% to 71 - 72% of the axe) and the end hardly does, where one hand and a shield already win more boss fights (P24: 82% against 57%)</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>W002</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>131 Heavy Axe</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>ATK (base)</t>
+        </is>
+      </c>
+      <c r="F496" t="n">
+        <v>43</v>
+      </c>
+      <c r="G496" t="n">
+        <v>38</v>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>L14</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>J07, F08</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>A small cut to two-handed pieces (the user, 2026-10-09): base ATK -10%, the upgrade rate kept, so the middle of the game moves (one-handed from 68 - 69% to 71 - 72% of the axe) and the end hardly does, where one hand and a shield already win more boss fights (P24: 82% against 57%)</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>W003</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>183 Heavy Lance</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>ATK (base)</t>
+        </is>
+      </c>
+      <c r="F497" t="n">
+        <v>39</v>
+      </c>
+      <c r="G497" t="n">
+        <v>35</v>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>L14</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>J07, F08</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>A small cut to two-handed pieces (the user, 2026-10-09): base ATK -10%, the upgrade rate kept, so the middle of the game moves (one-handed from 68 - 69% to 71 - 72% of the axe) and the end hardly does, where one hand and a shield already win more boss fights (P24: 82% against 57%)</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>W004</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>382 Tachi</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>ATK (base)</t>
+        </is>
+      </c>
+      <c r="F498" t="n">
+        <v>45</v>
+      </c>
+      <c r="G498" t="n">
+        <v>40</v>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>L14</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>J07, F08</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>A small cut to two-handed pieces (the user, 2026-10-09): base ATK -10%, the upgrade rate kept, so the middle of the game moves (one-handed from 68 - 69% to 71 - 72% of the axe) and the end hardly does, where one hand and a shield already win more boss fights (P24: 82% against 57%)</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>W005</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>434 Whip</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>upgrade rate</t>
+        </is>
+      </c>
+      <c r="F499" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G499" t="n">
+        <v>2</v>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>L14</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>Whips: the Mistress from 40% to 82% of the Dark Lord at C34 and from 10% to 30% at P24, with Whip Mastery x2; more makes her pass the Dark Lord in the middle of the game</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>W006</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Passive 249 Whip Mastery</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>effect 243</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>1</v>
+      </c>
+      <c r="F500" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G500" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>Whip Mastery multiplies the whip, so it weighs most late, where the whip lagged most</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>W007</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Passive 249 Whip Mastery</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>effect 243</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>2</v>
+      </c>
+      <c r="F501" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G501" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>Whip Mastery multiplies the whip, so it weighs most late, where the whip lagged most</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>W008</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Passive 249 Whip Mastery</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>effect 243</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>3</v>
+      </c>
+      <c r="F502" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G502" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>Whip Mastery multiplies the whip, so it weighs most late, where the whip lagged most</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>W009</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Passive 249 Whip Mastery</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>effect 243</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>4</v>
+      </c>
+      <c r="F503" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G503" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>Whip Mastery multiplies the whip, so it weighs most late, where the whip lagged most</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>W010</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Passive 249 Whip Mastery</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>effect 243</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>5</v>
+      </c>
+      <c r="F504" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G504" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>Whip Mastery multiplies the whip, so it weighs most late, where the whip lagged most</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>W011</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Passive 249 Whip Mastery</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>effect 243</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>6</v>
+      </c>
+      <c r="F505" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G505" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>Whip Mastery multiplies the whip, so it weighs most late, where the whip lagged most</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>W012</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Passive 249 Whip Mastery</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>effect 243</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>7</v>
+      </c>
+      <c r="F506" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G506" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>Whip Mastery multiplies the whip, so it weighs most late, where the whip lagged most</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>W013</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Passive 249 Whip Mastery</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>effect 243</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>8</v>
+      </c>
+      <c r="F507" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G507" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>Whip Mastery multiplies the whip, so it weighs most late, where the whip lagged most</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>W014</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Passive 249 Whip Mastery</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>effect 243</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>9</v>
+      </c>
+      <c r="F508" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G508" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>Whip Mastery multiplies the whip, so it weighs most late, where the whip lagged most</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>W015</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Passive 249 Whip Mastery</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>effect 243</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>10</v>
+      </c>
+      <c r="F509" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G509" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>Whip Mastery multiplies the whip, so it weighs most late, where the whip lagged most</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>W016</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Passive 261 Double Attack</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>effect 251</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>1</v>
+      </c>
+      <c r="F510" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G510" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>A little more for the characters who hit many times (+25%)</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>W017</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Passive 261 Double Attack</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>effect 251</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>2</v>
+      </c>
+      <c r="F511" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G511" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>A little more for the characters who hit many times (+25%)</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>W018</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Passive 261 Double Attack</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>effect 251</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>3</v>
+      </c>
+      <c r="F512" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G512" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>A little more for the characters who hit many times (+25%)</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>W019</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Passive 261 Double Attack</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>effect 251</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>4</v>
+      </c>
+      <c r="F513" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G513" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>A little more for the characters who hit many times (+25%)</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>W020</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Passive 261 Double Attack</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>effect 251</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>5</v>
+      </c>
+      <c r="F514" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G514" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>A little more for the characters who hit many times (+25%)</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>W021</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Passive 262 Triple Attack</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>effect 252</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>1</v>
+      </c>
+      <c r="F515" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G515" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>A little more for the characters who hit many times (+25%)</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>W022</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Passive 262 Triple Attack</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>effect 252</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>2</v>
+      </c>
+      <c r="F516" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G516" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>A little more for the characters who hit many times (+25%)</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>W023</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Passive 262 Triple Attack</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>effect 252</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>3</v>
+      </c>
+      <c r="F517" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G517" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>A little more for the characters who hit many times (+25%)</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>W024</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Passive 262 Triple Attack</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>effect 252</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>4</v>
+      </c>
+      <c r="F518" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G518" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>A little more for the characters who hit many times (+25%)</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>W025</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Passive 262 Triple Attack</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>effect 252</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>5</v>
+      </c>
+      <c r="F519" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G519" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>A little more for the characters who hit many times (+25%)</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>W026</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Passive 302 Barrage</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>effect 251</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>1</v>
+      </c>
+      <c r="F520" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G520" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>A little more for the characters who hit many times (+25%)</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>W027</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Passive 302 Barrage</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>effect 251</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>2</v>
+      </c>
+      <c r="F521" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G521" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>A little more for the characters who hit many times (+25%)</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>W028</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Passive 302 Barrage</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>effect 251</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>3</v>
+      </c>
+      <c r="F522" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G522" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>A little more for the characters who hit many times (+25%)</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>W029</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Passive 302 Barrage</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>effect 251</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>4</v>
+      </c>
+      <c r="F523" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G523" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>A little more for the characters who hit many times (+25%)</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>W030</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Passive 302 Barrage</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>effect 251</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>5</v>
+      </c>
+      <c r="F524" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G524" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>A little more for the characters who hit many times (+25%)</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>W031</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Passive 302 Barrage</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>effect 251</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>6</v>
+      </c>
+      <c r="F525" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G525" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>A little more for the characters who hit many times (+25%)</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>W032</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Passive 302 Barrage</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>effect 251</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>7</v>
+      </c>
+      <c r="F526" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G526" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>A little more for the characters who hit many times (+25%)</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>W033</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Passive 302 Barrage</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>effect 251</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>8</v>
+      </c>
+      <c r="F527" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G527" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>A little more for the characters who hit many times (+25%)</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>W034</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Passive 302 Barrage</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>effect 251</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>9</v>
+      </c>
+      <c r="F528" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G528" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>A little more for the characters who hit many times (+25%)</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>W035</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Passive 302 Barrage</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>effect 251</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>10</v>
+      </c>
+      <c r="F529" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G529" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>A little more for the characters who hit many times (+25%)</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>W036</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Technique 43 Spiral Arrow</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>weapon codes</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>8, 15</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>J06, F10</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>Guns may use four more bow skills (structural: a weapon mask the game already uses for Chain Spike, Guided Shot and Poison Shot)</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>W037</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Technique 50 Divine Cannon</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>weapon codes</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>8, 15</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>J06, F10</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>Guns may use four more bow skills (structural: a weapon mask the game already uses for Chain Spike, Guided Shot and Poison Shot)</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>W038</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Passive 270 Warning Shot</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>weapon codes</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>8, 15</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>J06, F10</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>Guns may use four more bow skills (structural: a weapon mask the game already uses for Chain Spike, Guided Shot and Poison Shot)</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>W039</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Passive 271 Support Shot</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>weapon codes</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>8, 15</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>J06, F10</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>Guns may use four more bow skills (structural: a weapon mask the game already uses for Chain Spike, Guided Shot and Poison Shot)</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L533"/>
+  <dimension ref="A1:L618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30306,6 +30306,4766 @@
         </is>
       </c>
     </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Magic 146 Crimson Flare</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>1</v>
+      </c>
+      <c r="F534" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G534" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>M002</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Magic 146 Crimson Flare</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>2</v>
+      </c>
+      <c r="F535" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G535" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>M003</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Magic 146 Crimson Flare</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>3</v>
+      </c>
+      <c r="F536" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G536" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>M004</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Magic 146 Crimson Flare</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>4</v>
+      </c>
+      <c r="F537" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G537" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>M005</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Magic 146 Crimson Flare</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>5</v>
+      </c>
+      <c r="F538" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G538" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>M006</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Magic 150 Cocytus</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>1</v>
+      </c>
+      <c r="F539" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G539" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>M007</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Magic 150 Cocytus</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>2</v>
+      </c>
+      <c r="F540" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G540" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>M008</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Magic 150 Cocytus</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>3</v>
+      </c>
+      <c r="F541" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G541" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>M009</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Magic 150 Cocytus</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>4</v>
+      </c>
+      <c r="F542" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G542" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>M010</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Magic 150 Cocytus</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>5</v>
+      </c>
+      <c r="F543" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G543" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>M011</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Magic 154 Muon Plasma</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>1</v>
+      </c>
+      <c r="F544" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G544" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>M012</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Magic 154 Muon Plasma</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>2</v>
+      </c>
+      <c r="F545" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G545" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>M013</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Magic 154 Muon Plasma</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>3</v>
+      </c>
+      <c r="F546" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G546" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>M014</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Magic 154 Muon Plasma</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E547" t="n">
+        <v>4</v>
+      </c>
+      <c r="F547" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G547" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>M015</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Magic 154 Muon Plasma</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E548" t="n">
+        <v>5</v>
+      </c>
+      <c r="F548" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G548" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>M016</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Magic 158 Tempest</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E549" t="n">
+        <v>1</v>
+      </c>
+      <c r="F549" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G549" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>M017</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Magic 158 Tempest</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E550" t="n">
+        <v>2</v>
+      </c>
+      <c r="F550" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G550" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>M018</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Magic 158 Tempest</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>3</v>
+      </c>
+      <c r="F551" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G551" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>M019</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Magic 158 Tempest</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E552" t="n">
+        <v>4</v>
+      </c>
+      <c r="F552" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G552" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>M020</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Magic 158 Tempest</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E553" t="n">
+        <v>5</v>
+      </c>
+      <c r="F553" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G553" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>M021</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Magic 162 Gaia Crush</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>1</v>
+      </c>
+      <c r="F554" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G554" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>M022</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Magic 162 Gaia Crush</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>2</v>
+      </c>
+      <c r="F555" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G555" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>M023</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Magic 162 Gaia Crush</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>3</v>
+      </c>
+      <c r="F556" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G556" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>M024</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Magic 162 Gaia Crush</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E557" t="n">
+        <v>4</v>
+      </c>
+      <c r="F557" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G557" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>M025</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Magic 162 Gaia Crush</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E558" t="n">
+        <v>5</v>
+      </c>
+      <c r="F558" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G558" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>J33, J14</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>The top single spell chants faster (0.85 at every level, it was 0.75 - 0.70): less time exposed to interruption, its power per time closer to its power per TP</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>M026</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Magic 145 Inferno</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E559" t="n">
+        <v>2</v>
+      </c>
+      <c r="F559" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G559" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>M027</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Magic 145 Inferno</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E560" t="n">
+        <v>3</v>
+      </c>
+      <c r="F560" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G560" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>M028</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Magic 145 Inferno</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E561" t="n">
+        <v>4</v>
+      </c>
+      <c r="F561" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G561" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>M029</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Magic 145 Inferno</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E562" t="n">
+        <v>5</v>
+      </c>
+      <c r="F562" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G562" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>M030</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Magic 145 Inferno</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E563" t="n">
+        <v>6</v>
+      </c>
+      <c r="F563" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G563" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>M031</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Magic 145 Inferno</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E564" t="n">
+        <v>7</v>
+      </c>
+      <c r="F564" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G564" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>M032</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Magic 145 Inferno</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E565" t="n">
+        <v>8</v>
+      </c>
+      <c r="F565" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G565" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>M033</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Magic 145 Inferno</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E566" t="n">
+        <v>9</v>
+      </c>
+      <c r="F566" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G566" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>M034</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Magic 145 Inferno</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E567" t="n">
+        <v>10</v>
+      </c>
+      <c r="F567" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G567" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>M035</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Magic 149 Diamond Dust</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E568" t="n">
+        <v>2</v>
+      </c>
+      <c r="F568" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G568" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>M036</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Magic 149 Diamond Dust</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E569" t="n">
+        <v>3</v>
+      </c>
+      <c r="F569" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G569" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>M037</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Magic 149 Diamond Dust</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E570" t="n">
+        <v>4</v>
+      </c>
+      <c r="F570" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G570" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>M038</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Magic 149 Diamond Dust</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E571" t="n">
+        <v>5</v>
+      </c>
+      <c r="F571" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G571" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>M039</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Magic 149 Diamond Dust</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E572" t="n">
+        <v>6</v>
+      </c>
+      <c r="F572" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G572" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>M040</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Magic 149 Diamond Dust</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E573" t="n">
+        <v>7</v>
+      </c>
+      <c r="F573" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G573" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>M041</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Magic 149 Diamond Dust</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E574" t="n">
+        <v>8</v>
+      </c>
+      <c r="F574" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G574" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>M042</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Magic 149 Diamond Dust</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E575" t="n">
+        <v>9</v>
+      </c>
+      <c r="F575" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G575" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>M043</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Magic 149 Diamond Dust</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E576" t="n">
+        <v>10</v>
+      </c>
+      <c r="F576" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G576" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>M044</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Magic 153 Lightning</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E577" t="n">
+        <v>2</v>
+      </c>
+      <c r="F577" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G577" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>M045</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Magic 153 Lightning</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E578" t="n">
+        <v>3</v>
+      </c>
+      <c r="F578" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G578" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>M046</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Magic 153 Lightning</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E579" t="n">
+        <v>4</v>
+      </c>
+      <c r="F579" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G579" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>M047</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Magic 153 Lightning</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E580" t="n">
+        <v>5</v>
+      </c>
+      <c r="F580" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G580" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>M048</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Magic 153 Lightning</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E581" t="n">
+        <v>6</v>
+      </c>
+      <c r="F581" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G581" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>M049</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Magic 153 Lightning</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E582" t="n">
+        <v>7</v>
+      </c>
+      <c r="F582" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G582" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>M050</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Magic 153 Lightning</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E583" t="n">
+        <v>8</v>
+      </c>
+      <c r="F583" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G583" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>M051</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Magic 153 Lightning</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E584" t="n">
+        <v>9</v>
+      </c>
+      <c r="F584" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G584" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>M052</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Magic 153 Lightning</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E585" t="n">
+        <v>10</v>
+      </c>
+      <c r="F585" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G585" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>M053</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Magic 157 Tornado</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E586" t="n">
+        <v>2</v>
+      </c>
+      <c r="F586" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G586" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>M054</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Magic 157 Tornado</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E587" t="n">
+        <v>3</v>
+      </c>
+      <c r="F587" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G587" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>M055</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Magic 157 Tornado</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E588" t="n">
+        <v>4</v>
+      </c>
+      <c r="F588" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G588" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>M056</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Magic 157 Tornado</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E589" t="n">
+        <v>5</v>
+      </c>
+      <c r="F589" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G589" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>M057</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Magic 157 Tornado</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E590" t="n">
+        <v>6</v>
+      </c>
+      <c r="F590" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G590" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>M058</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Magic 157 Tornado</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E591" t="n">
+        <v>7</v>
+      </c>
+      <c r="F591" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G591" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>M059</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Magic 157 Tornado</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E592" t="n">
+        <v>8</v>
+      </c>
+      <c r="F592" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G592" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>M060</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Magic 157 Tornado</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E593" t="n">
+        <v>9</v>
+      </c>
+      <c r="F593" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G593" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>M061</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Magic 157 Tornado</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E594" t="n">
+        <v>10</v>
+      </c>
+      <c r="F594" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G594" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>M062</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Magic 161 Meteor</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E595" t="n">
+        <v>2</v>
+      </c>
+      <c r="F595" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G595" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>M063</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Magic 161 Meteor</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E596" t="n">
+        <v>3</v>
+      </c>
+      <c r="F596" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G596" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>M064</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Magic 161 Meteor</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E597" t="n">
+        <v>4</v>
+      </c>
+      <c r="F597" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G597" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>M065</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Magic 161 Meteor</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E598" t="n">
+        <v>5</v>
+      </c>
+      <c r="F598" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G598" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>M066</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Magic 161 Meteor</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E599" t="n">
+        <v>6</v>
+      </c>
+      <c r="F599" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G599" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>M067</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Magic 161 Meteor</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E600" t="n">
+        <v>7</v>
+      </c>
+      <c r="F600" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G600" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>M068</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Magic 161 Meteor</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E601" t="n">
+        <v>8</v>
+      </c>
+      <c r="F601" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G601" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>M069</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Magic 161 Meteor</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E602" t="n">
+        <v>9</v>
+      </c>
+      <c r="F602" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G602" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>M070</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Magic 161 Meteor</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E603" t="n">
+        <v>10</v>
+      </c>
+      <c r="F603" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G603" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>J33</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>The area spell no longer chants slower as it rises (0.70 at every level, it fell to 0.60)</t>
+        </is>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>M071</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Magic 195 Sun Veil</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>effect 163 (magic defence modifier)</t>
+        </is>
+      </c>
+      <c r="E604" t="n">
+        <v>1</v>
+      </c>
+      <c r="F604" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G604" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>Magic defence buffs and debuffs x1.5: +27% at the top of Sun Veil cuts a spell by 12% (it was 8%; INT 300, power 900, RES 300)</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>M072</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Magic 195 Sun Veil</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>effect 163 (magic defence modifier)</t>
+        </is>
+      </c>
+      <c r="E605" t="n">
+        <v>2</v>
+      </c>
+      <c r="F605" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G605" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>Magic defence buffs and debuffs x1.5: +27% at the top of Sun Veil cuts a spell by 12% (it was 8%; INT 300, power 900, RES 300)</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>M073</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Magic 195 Sun Veil</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>effect 163 (magic defence modifier)</t>
+        </is>
+      </c>
+      <c r="E606" t="n">
+        <v>3</v>
+      </c>
+      <c r="F606" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G606" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>Magic defence buffs and debuffs x1.5: +27% at the top of Sun Veil cuts a spell by 12% (it was 8%; INT 300, power 900, RES 300)</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>M074</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Magic 195 Sun Veil</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>effect 163 (magic defence modifier)</t>
+        </is>
+      </c>
+      <c r="E607" t="n">
+        <v>4</v>
+      </c>
+      <c r="F607" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G607" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>Magic defence buffs and debuffs x1.5: +27% at the top of Sun Veil cuts a spell by 12% (it was 8%; INT 300, power 900, RES 300)</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>M075</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Magic 195 Sun Veil</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>effect 163 (magic defence modifier)</t>
+        </is>
+      </c>
+      <c r="E608" t="n">
+        <v>5</v>
+      </c>
+      <c r="F608" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G608" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>Magic defence buffs and debuffs x1.5: +27% at the top of Sun Veil cuts a spell by 12% (it was 8%; INT 300, power 900, RES 300)</t>
+        </is>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>M076</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Magic 220 Water Scroll</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>effect 163 (magic defence modifier)</t>
+        </is>
+      </c>
+      <c r="E609" t="n">
+        <v>1</v>
+      </c>
+      <c r="F609" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G609" t="n">
+        <v>-0.105</v>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>Magic defence buffs and debuffs x1.5: +27% at the top of Sun Veil cuts a spell by 12% (it was 8%; INT 300, power 900, RES 300)</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>M077</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Magic 220 Water Scroll</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>effect 163 (magic defence modifier)</t>
+        </is>
+      </c>
+      <c r="E610" t="n">
+        <v>2</v>
+      </c>
+      <c r="F610" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="G610" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>Magic defence buffs and debuffs x1.5: +27% at the top of Sun Veil cuts a spell by 12% (it was 8%; INT 300, power 900, RES 300)</t>
+        </is>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>M078</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Magic 220 Water Scroll</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>effect 163 (magic defence modifier)</t>
+        </is>
+      </c>
+      <c r="E611" t="n">
+        <v>3</v>
+      </c>
+      <c r="F611" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="G611" t="n">
+        <v>-0.195</v>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>Magic defence buffs and debuffs x1.5: +27% at the top of Sun Veil cuts a spell by 12% (it was 8%; INT 300, power 900, RES 300)</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>M079</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Magic 220 Water Scroll</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>effect 163 (magic defence modifier)</t>
+        </is>
+      </c>
+      <c r="E612" t="n">
+        <v>4</v>
+      </c>
+      <c r="F612" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="G612" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>Magic defence buffs and debuffs x1.5: +27% at the top of Sun Veil cuts a spell by 12% (it was 8%; INT 300, power 900, RES 300)</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>M080</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Magic 220 Water Scroll</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>effect 163 (magic defence modifier)</t>
+        </is>
+      </c>
+      <c r="E613" t="n">
+        <v>5</v>
+      </c>
+      <c r="F613" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="G613" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>Magic defence buffs and debuffs x1.5: +27% at the top of Sun Veil cuts a spell by 12% (it was 8%; INT 300, power 900, RES 300)</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>M081</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Magic 231 Carrot and Stick</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>effect 163 (magic defence modifier)</t>
+        </is>
+      </c>
+      <c r="E614" t="n">
+        <v>1</v>
+      </c>
+      <c r="F614" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="G614" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>Magic defence buffs and debuffs x1.5: +27% at the top of Sun Veil cuts a spell by 12% (it was 8%; INT 300, power 900, RES 300)</t>
+        </is>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>M082</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Magic 231 Carrot and Stick</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>effect 163 (magic defence modifier)</t>
+        </is>
+      </c>
+      <c r="E615" t="n">
+        <v>2</v>
+      </c>
+      <c r="F615" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="G615" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>Magic defence buffs and debuffs x1.5: +27% at the top of Sun Veil cuts a spell by 12% (it was 8%; INT 300, power 900, RES 300)</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>M083</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Magic 231 Carrot and Stick</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>effect 163 (magic defence modifier)</t>
+        </is>
+      </c>
+      <c r="E616" t="n">
+        <v>3</v>
+      </c>
+      <c r="F616" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="G616" t="n">
+        <v>-0.195</v>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>Magic defence buffs and debuffs x1.5: +27% at the top of Sun Veil cuts a spell by 12% (it was 8%; INT 300, power 900, RES 300)</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>M084</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Magic 231 Carrot and Stick</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>effect 163 (magic defence modifier)</t>
+        </is>
+      </c>
+      <c r="E617" t="n">
+        <v>4</v>
+      </c>
+      <c r="F617" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="G617" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>Magic defence buffs and debuffs x1.5: +27% at the top of Sun Veil cuts a spell by 12% (it was 8%; INT 300, power 900, RES 300)</t>
+        </is>
+      </c>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>M085</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Magic 231 Carrot and Stick</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>effect 163 (magic defence modifier)</t>
+        </is>
+      </c>
+      <c r="E618" t="n">
+        <v>5</v>
+      </c>
+      <c r="F618" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="G618" t="n">
+        <v>-0.225</v>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>Magic defence buffs and debuffs x1.5: +27% at the top of Sun Veil cuts a spell by 12% (it was 8%; INT 300, power 900, RES 300)</t>
+        </is>
+      </c>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L856"/>
+  <dimension ref="A1:L1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48467,6 +48467,7850 @@
         </is>
       </c>
     </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>17 Odin</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F857" t="n">
+        <v>90</v>
+      </c>
+      <c r="G857" t="n">
+        <v>80</v>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J857" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L857" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>17 Odin</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F858" t="n">
+        <v>100</v>
+      </c>
+      <c r="G858" t="n">
+        <v>90</v>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L858" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>E003</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>17 Odin</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F859" t="n">
+        <v>90</v>
+      </c>
+      <c r="G859" t="n">
+        <v>80</v>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J859" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L859" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>E004</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>40 Myrddin</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F860" t="n">
+        <v>75</v>
+      </c>
+      <c r="G860" t="n">
+        <v>65</v>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J860" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L860" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>E005</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>40 Myrddin</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F861" t="n">
+        <v>75</v>
+      </c>
+      <c r="G861" t="n">
+        <v>65</v>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J861" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L861" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>E006</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>40 Myrddin</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F862" t="n">
+        <v>75</v>
+      </c>
+      <c r="G862" t="n">
+        <v>65</v>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J862" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L862" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>E007</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>56 Himiko</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F863" t="n">
+        <v>50</v>
+      </c>
+      <c r="G863" t="n">
+        <v>40</v>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J863" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L863" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>E008</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>56 Himiko</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F864" t="n">
+        <v>70</v>
+      </c>
+      <c r="G864" t="n">
+        <v>60</v>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J864" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L864" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>E009</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>66 Roland</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F865" t="n">
+        <v>50</v>
+      </c>
+      <c r="G865" t="n">
+        <v>40</v>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J865" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L865" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>E010</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>66 Roland</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F866" t="n">
+        <v>100</v>
+      </c>
+      <c r="G866" t="n">
+        <v>90</v>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J866" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L866" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>E011</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>66 Roland</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F867" t="n">
+        <v>50</v>
+      </c>
+      <c r="G867" t="n">
+        <v>40</v>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J867" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L867" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>E012</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>67 Death 13</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F868" t="n">
+        <v>40</v>
+      </c>
+      <c r="G868" t="n">
+        <v>30</v>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J868" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L868" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>E013</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>67 Death 13</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F869" t="n">
+        <v>100</v>
+      </c>
+      <c r="G869" t="n">
+        <v>90</v>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J869" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L869" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>E014</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>67 Death 13</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F870" t="n">
+        <v>40</v>
+      </c>
+      <c r="G870" t="n">
+        <v>30</v>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J870" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L870" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>E015</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>79 Neamhain</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F871" t="n">
+        <v>50</v>
+      </c>
+      <c r="G871" t="n">
+        <v>40</v>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L871" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>E016</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>79 Neamhain</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F872" t="n">
+        <v>100</v>
+      </c>
+      <c r="G872" t="n">
+        <v>90</v>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L872" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>E017</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>79 Neamhain</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F873" t="n">
+        <v>50</v>
+      </c>
+      <c r="G873" t="n">
+        <v>40</v>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J873" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L873" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>E018</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>80 Morrighan</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F874" t="n">
+        <v>80</v>
+      </c>
+      <c r="G874" t="n">
+        <v>70</v>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L874" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>E019</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>80 Morrighan</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F875" t="n">
+        <v>80</v>
+      </c>
+      <c r="G875" t="n">
+        <v>70</v>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J875" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L875" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>E020</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>80 Morrighan</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F876" t="n">
+        <v>50</v>
+      </c>
+      <c r="G876" t="n">
+        <v>40</v>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J876" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L876" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>E021</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>81 Seraph</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F877" t="n">
+        <v>100</v>
+      </c>
+      <c r="G877" t="n">
+        <v>90</v>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J877" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L877" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>E022</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>81 Seraph</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F878" t="n">
+        <v>100</v>
+      </c>
+      <c r="G878" t="n">
+        <v>90</v>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J878" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L878" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>E023</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>81 Seraph</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F879" t="n">
+        <v>90</v>
+      </c>
+      <c r="G879" t="n">
+        <v>80</v>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J879" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L879" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>E024</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>104 Kurarin</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F880" t="n">
+        <v>60</v>
+      </c>
+      <c r="G880" t="n">
+        <v>50</v>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J880" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L880" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>E025</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>104 Kurarin</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F881" t="n">
+        <v>90</v>
+      </c>
+      <c r="G881" t="n">
+        <v>80</v>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J881" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L881" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>E026</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>104 Kurarin</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F882" t="n">
+        <v>70</v>
+      </c>
+      <c r="G882" t="n">
+        <v>60</v>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J882" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L882" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>E027</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>121 Euryale</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F883" t="n">
+        <v>70</v>
+      </c>
+      <c r="G883" t="n">
+        <v>60</v>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J883" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L883" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>E028</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>121 Euryale</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F884" t="n">
+        <v>70</v>
+      </c>
+      <c r="G884" t="n">
+        <v>60</v>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J884" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L884" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>E029</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>121 Euryale</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F885" t="n">
+        <v>70</v>
+      </c>
+      <c r="G885" t="n">
+        <v>60</v>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J885" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L885" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>E030</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>122 Medusa</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F886" t="n">
+        <v>80</v>
+      </c>
+      <c r="G886" t="n">
+        <v>70</v>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J886" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L886" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>E031</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>122 Medusa</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F887" t="n">
+        <v>80</v>
+      </c>
+      <c r="G887" t="n">
+        <v>70</v>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J887" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L887" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>E032</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>122 Medusa</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F888" t="n">
+        <v>80</v>
+      </c>
+      <c r="G888" t="n">
+        <v>70</v>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J888" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L888" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>E033</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>127 Prometheus</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F889" t="n">
+        <v>40</v>
+      </c>
+      <c r="G889" t="n">
+        <v>30</v>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J889" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L889" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>E034</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>127 Prometheus</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F890" t="n">
+        <v>50</v>
+      </c>
+      <c r="G890" t="n">
+        <v>40</v>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J890" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L890" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>E035</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>127 Prometheus</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F891" t="n">
+        <v>90</v>
+      </c>
+      <c r="G891" t="n">
+        <v>80</v>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J891" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L891" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>E036</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>144 Asmodeus</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F892" t="n">
+        <v>70</v>
+      </c>
+      <c r="G892" t="n">
+        <v>60</v>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J892" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L892" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>E037</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>144 Asmodeus</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F893" t="n">
+        <v>80</v>
+      </c>
+      <c r="G893" t="n">
+        <v>70</v>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J893" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L893" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>E038</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>144 Asmodeus</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F894" t="n">
+        <v>100</v>
+      </c>
+      <c r="G894" t="n">
+        <v>90</v>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J894" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L894" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>E039</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>163 Dairokuten Maou</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F895" t="n">
+        <v>45</v>
+      </c>
+      <c r="G895" t="n">
+        <v>35</v>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I895" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J895" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L895" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>E040</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>163 Dairokuten Maou</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F896" t="n">
+        <v>90</v>
+      </c>
+      <c r="G896" t="n">
+        <v>80</v>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J896" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L896" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>E041</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>163 Dairokuten Maou</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F897" t="n">
+        <v>30</v>
+      </c>
+      <c r="G897" t="n">
+        <v>20</v>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I897" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J897" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L897" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>E042</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>184 Fudo Myouou</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F898" t="n">
+        <v>100</v>
+      </c>
+      <c r="G898" t="n">
+        <v>90</v>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I898" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J898" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L898" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>E043</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>184 Fudo Myouou</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F899" t="n">
+        <v>75</v>
+      </c>
+      <c r="G899" t="n">
+        <v>65</v>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J899" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L899" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>E044</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>184 Fudo Myouou</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F900" t="n">
+        <v>75</v>
+      </c>
+      <c r="G900" t="n">
+        <v>65</v>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J900" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L900" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>E045</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>190 Rathty</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F901" t="n">
+        <v>70</v>
+      </c>
+      <c r="G901" t="n">
+        <v>60</v>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J901" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L901" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>E046</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>190 Rathty</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F902" t="n">
+        <v>80</v>
+      </c>
+      <c r="G902" t="n">
+        <v>70</v>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J902" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L902" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>E047</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>190 Rathty</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F903" t="n">
+        <v>95</v>
+      </c>
+      <c r="G903" t="n">
+        <v>85</v>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J903" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L903" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>E048</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>207 Little Mermaid</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F904" t="n">
+        <v>90</v>
+      </c>
+      <c r="G904" t="n">
+        <v>80</v>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J904" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L904" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>E049</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>207 Little Mermaid</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F905" t="n">
+        <v>40</v>
+      </c>
+      <c r="G905" t="n">
+        <v>30</v>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J905" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L905" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>E050</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>207 Little Mermaid</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F906" t="n">
+        <v>90</v>
+      </c>
+      <c r="G906" t="n">
+        <v>80</v>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J906" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L906" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>E051</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>236 Thor</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F907" t="n">
+        <v>80</v>
+      </c>
+      <c r="G907" t="n">
+        <v>70</v>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J907" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L907" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>E052</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>236 Thor</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F908" t="n">
+        <v>90</v>
+      </c>
+      <c r="G908" t="n">
+        <v>80</v>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J908" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L908" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>E053</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>236 Thor</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F909" t="n">
+        <v>100</v>
+      </c>
+      <c r="G909" t="n">
+        <v>90</v>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I909" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J909" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L909" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>E054</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>264 Cerberus</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F910" t="n">
+        <v>75</v>
+      </c>
+      <c r="G910" t="n">
+        <v>65</v>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J910" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L910" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>E055</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>264 Cerberus</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F911" t="n">
+        <v>50</v>
+      </c>
+      <c r="G911" t="n">
+        <v>40</v>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J911" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L911" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>E056</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>264 Cerberus</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F912" t="n">
+        <v>75</v>
+      </c>
+      <c r="G912" t="n">
+        <v>65</v>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J912" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K912" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L912" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>E057</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>297 Ganesha</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F913" t="n">
+        <v>70</v>
+      </c>
+      <c r="G913" t="n">
+        <v>60</v>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J913" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L913" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>E058</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>297 Ganesha</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F914" t="n">
+        <v>70</v>
+      </c>
+      <c r="G914" t="n">
+        <v>60</v>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J914" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L914" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>E059</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>297 Ganesha</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F915" t="n">
+        <v>100</v>
+      </c>
+      <c r="G915" t="n">
+        <v>90</v>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J915" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L915" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>E060</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>339 Doom Bringer</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F916" t="n">
+        <v>90</v>
+      </c>
+      <c r="G916" t="n">
+        <v>80</v>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J916" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L916" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>E061</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>339 Doom Bringer</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F917" t="n">
+        <v>90</v>
+      </c>
+      <c r="G917" t="n">
+        <v>80</v>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J917" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L917" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>E062</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>339 Doom Bringer</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F918" t="n">
+        <v>90</v>
+      </c>
+      <c r="G918" t="n">
+        <v>80</v>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J918" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K918" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L918" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>E063</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>345 Enkky</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F919" t="n">
+        <v>60</v>
+      </c>
+      <c r="G919" t="n">
+        <v>50</v>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J919" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K919" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L919" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>E064</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>345 Enkky</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F920" t="n">
+        <v>20</v>
+      </c>
+      <c r="G920" t="n">
+        <v>10</v>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J920" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L920" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>E065</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>345 Enkky</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F921" t="n">
+        <v>80</v>
+      </c>
+      <c r="G921" t="n">
+        <v>70</v>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J921" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L921" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>E066</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>370 Otohime</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F922" t="n">
+        <v>40</v>
+      </c>
+      <c r="G922" t="n">
+        <v>30</v>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J922" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L922" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>E067</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>370 Otohime</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F923" t="n">
+        <v>80</v>
+      </c>
+      <c r="G923" t="n">
+        <v>70</v>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J923" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K923" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L923" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>E068</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>370 Otohime</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F924" t="n">
+        <v>20</v>
+      </c>
+      <c r="G924" t="n">
+        <v>10</v>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J924" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L924" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>E069</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>376 Leviathan</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F925" t="n">
+        <v>40</v>
+      </c>
+      <c r="G925" t="n">
+        <v>30</v>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J925" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L925" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>E070</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>376 Leviathan</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F926" t="n">
+        <v>60</v>
+      </c>
+      <c r="G926" t="n">
+        <v>50</v>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J926" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K926" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L926" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>E071</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>376 Leviathan</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F927" t="n">
+        <v>80</v>
+      </c>
+      <c r="G927" t="n">
+        <v>70</v>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J927" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L927" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>E072</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>381 Dragon Lord</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F928" t="n">
+        <v>70</v>
+      </c>
+      <c r="G928" t="n">
+        <v>60</v>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J928" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L928" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>E073</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>381 Dragon Lord</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F929" t="n">
+        <v>70</v>
+      </c>
+      <c r="G929" t="n">
+        <v>60</v>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J929" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K929" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L929" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>E074</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>381 Dragon Lord</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F930" t="n">
+        <v>80</v>
+      </c>
+      <c r="G930" t="n">
+        <v>70</v>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J930" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K930" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L930" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>E075</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>382 Astaroth</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F931" t="n">
+        <v>80</v>
+      </c>
+      <c r="G931" t="n">
+        <v>70</v>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J931" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L931" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>E076</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>382 Astaroth</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F932" t="n">
+        <v>80</v>
+      </c>
+      <c r="G932" t="n">
+        <v>70</v>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J932" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K932" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L932" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>E077</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>382 Astaroth</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F933" t="n">
+        <v>90</v>
+      </c>
+      <c r="G933" t="n">
+        <v>80</v>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J933" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L933" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>E078</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>388 Thunder Dragon</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F934" t="n">
+        <v>50</v>
+      </c>
+      <c r="G934" t="n">
+        <v>40</v>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J934" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K934" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L934" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>E079</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>388 Thunder Dragon</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F935" t="n">
+        <v>70</v>
+      </c>
+      <c r="G935" t="n">
+        <v>60</v>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J935" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L935" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>E080</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>388 Thunder Dragon</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F936" t="n">
+        <v>50</v>
+      </c>
+      <c r="G936" t="n">
+        <v>40</v>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J936" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K936" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L936" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>E081</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>390 Zahhak</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F937" t="n">
+        <v>80</v>
+      </c>
+      <c r="G937" t="n">
+        <v>70</v>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J937" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L937" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>E082</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>390 Zahhak</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F938" t="n">
+        <v>80</v>
+      </c>
+      <c r="G938" t="n">
+        <v>70</v>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J938" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L938" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>E083</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>390 Zahhak</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F939" t="n">
+        <v>100</v>
+      </c>
+      <c r="G939" t="n">
+        <v>90</v>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J939" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L939" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>E084</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>395 Vasuki</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F940" t="n">
+        <v>60</v>
+      </c>
+      <c r="G940" t="n">
+        <v>50</v>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J940" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K940" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L940" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>E085</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>395 Vasuki</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F941" t="n">
+        <v>50</v>
+      </c>
+      <c r="G941" t="n">
+        <v>40</v>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J941" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K941" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L941" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>E086</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>395 Vasuki</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F942" t="n">
+        <v>50</v>
+      </c>
+      <c r="G942" t="n">
+        <v>40</v>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J942" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K942" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L942" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>E087</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>404 Rahab</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F943" t="n">
+        <v>60</v>
+      </c>
+      <c r="G943" t="n">
+        <v>50</v>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J943" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L943" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>E088</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>404 Rahab</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F944" t="n">
+        <v>60</v>
+      </c>
+      <c r="G944" t="n">
+        <v>50</v>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J944" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K944" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L944" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>E089</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>404 Rahab</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F945" t="n">
+        <v>60</v>
+      </c>
+      <c r="G945" t="n">
+        <v>50</v>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J945" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K945" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L945" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>E090</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>405 Tiamat</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F946" t="n">
+        <v>75</v>
+      </c>
+      <c r="G946" t="n">
+        <v>65</v>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J946" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L946" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>E091</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>405 Tiamat</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F947" t="n">
+        <v>75</v>
+      </c>
+      <c r="G947" t="n">
+        <v>65</v>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J947" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L947" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>E092</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>405 Tiamat</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F948" t="n">
+        <v>75</v>
+      </c>
+      <c r="G948" t="n">
+        <v>65</v>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J948" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L948" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>E093</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>444 Carmilla</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F949" t="n">
+        <v>90</v>
+      </c>
+      <c r="G949" t="n">
+        <v>80</v>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J949" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L949" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>E094</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>444 Carmilla</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F950" t="n">
+        <v>80</v>
+      </c>
+      <c r="G950" t="n">
+        <v>70</v>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J950" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L950" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>E095</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>444 Carmilla</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F951" t="n">
+        <v>80</v>
+      </c>
+      <c r="G951" t="n">
+        <v>70</v>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J951" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K951" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L951" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>E096</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>454 Charon</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F952" t="n">
+        <v>90</v>
+      </c>
+      <c r="G952" t="n">
+        <v>80</v>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J952" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K952" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L952" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>E097</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>454 Charon</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F953" t="n">
+        <v>55</v>
+      </c>
+      <c r="G953" t="n">
+        <v>45</v>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J953" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K953" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L953" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>E098</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>454 Charon</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F954" t="n">
+        <v>75</v>
+      </c>
+      <c r="G954" t="n">
+        <v>65</v>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J954" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K954" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L954" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>E099</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>459 Hel</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F955" t="n">
+        <v>80</v>
+      </c>
+      <c r="G955" t="n">
+        <v>70</v>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J955" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K955" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L955" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>E100</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>459 Hel</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F956" t="n">
+        <v>80</v>
+      </c>
+      <c r="G956" t="n">
+        <v>70</v>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J956" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K956" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L956" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>E101</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>459 Hel</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F957" t="n">
+        <v>100</v>
+      </c>
+      <c r="G957" t="n">
+        <v>90</v>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J957" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K957" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L957" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>E102</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>464 Enma</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F958" t="n">
+        <v>45</v>
+      </c>
+      <c r="G958" t="n">
+        <v>35</v>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J958" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K958" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L958" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>E103</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>464 Enma</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F959" t="n">
+        <v>70</v>
+      </c>
+      <c r="G959" t="n">
+        <v>60</v>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J959" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K959" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L959" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>E104</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>464 Enma</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F960" t="n">
+        <v>45</v>
+      </c>
+      <c r="G960" t="n">
+        <v>35</v>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J960" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K960" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L960" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>E105</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>474 Scathach</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F961" t="n">
+        <v>60</v>
+      </c>
+      <c r="G961" t="n">
+        <v>50</v>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J961" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K961" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L961" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>E106</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>474 Scathach</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F962" t="n">
+        <v>75</v>
+      </c>
+      <c r="G962" t="n">
+        <v>65</v>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J962" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K962" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L962" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>E107</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>474 Scathach</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F963" t="n">
+        <v>50</v>
+      </c>
+      <c r="G963" t="n">
+        <v>40</v>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J963" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K963" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L963" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>E108</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>510 Meta-Kindra ♀</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F964" t="n">
+        <v>50</v>
+      </c>
+      <c r="G964" t="n">
+        <v>40</v>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J964" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K964" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L964" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>E109</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>732 Knuckle Saint</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F965" t="n">
+        <v>75</v>
+      </c>
+      <c r="G965" t="n">
+        <v>65</v>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J965" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K965" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L965" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>E110</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>732 Knuckle Saint</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F966" t="n">
+        <v>75</v>
+      </c>
+      <c r="G966" t="n">
+        <v>65</v>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J966" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K966" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L966" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>E111</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>732 Knuckle Saint</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F967" t="n">
+        <v>75</v>
+      </c>
+      <c r="G967" t="n">
+        <v>65</v>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J967" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K967" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L967" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>E112</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>750 Mephistopheles</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F968" t="n">
+        <v>65</v>
+      </c>
+      <c r="G968" t="n">
+        <v>55</v>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J968" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K968" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L968" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>E113</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>750 Mephistopheles</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F969" t="n">
+        <v>85</v>
+      </c>
+      <c r="G969" t="n">
+        <v>75</v>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J969" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K969" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L969" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>E114</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>750 Mephistopheles</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F970" t="n">
+        <v>75</v>
+      </c>
+      <c r="G970" t="n">
+        <v>65</v>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J970" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K970" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L970" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>E115</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>802 Akupara</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F971" t="n">
+        <v>80</v>
+      </c>
+      <c r="G971" t="n">
+        <v>70</v>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J971" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K971" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L971" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>E116</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>802 Akupara</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F972" t="n">
+        <v>80</v>
+      </c>
+      <c r="G972" t="n">
+        <v>70</v>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J972" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K972" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L972" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>E117</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>802 Akupara</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F973" t="n">
+        <v>100</v>
+      </c>
+      <c r="G973" t="n">
+        <v>90</v>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J973" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K973" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L973" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>E118</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>842 Aspidochelone</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F974" t="n">
+        <v>100</v>
+      </c>
+      <c r="G974" t="n">
+        <v>90</v>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J974" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K974" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L974" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>E119</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>842 Aspidochelone</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F975" t="n">
+        <v>70</v>
+      </c>
+      <c r="G975" t="n">
+        <v>60</v>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J975" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K975" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L975" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>E120</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>842 Aspidochelone</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F976" t="n">
+        <v>100</v>
+      </c>
+      <c r="G976" t="n">
+        <v>90</v>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J976" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K976" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L976" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>E121</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>868 Kuroganehime</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F977" t="n">
+        <v>80</v>
+      </c>
+      <c r="G977" t="n">
+        <v>70</v>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J977" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K977" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L977" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>E122</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>868 Kuroganehime</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F978" t="n">
+        <v>100</v>
+      </c>
+      <c r="G978" t="n">
+        <v>90</v>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J978" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K978" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L978" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>E123</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>868 Kuroganehime</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F979" t="n">
+        <v>100</v>
+      </c>
+      <c r="G979" t="n">
+        <v>90</v>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J979" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K979" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L979" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>E124</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>892 Jormungandr</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>resistance slash</t>
+        </is>
+      </c>
+      <c r="F980" t="n">
+        <v>80</v>
+      </c>
+      <c r="G980" t="n">
+        <v>70</v>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I980" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J980" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K980" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L980" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>E125</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>892 Jormungandr</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>resistance stab</t>
+        </is>
+      </c>
+      <c r="F981" t="n">
+        <v>70</v>
+      </c>
+      <c r="G981" t="n">
+        <v>60</v>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I981" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J981" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K981" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L981" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>E126</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>892 Jormungandr</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>resistance bash</t>
+        </is>
+      </c>
+      <c r="F982" t="n">
+        <v>100</v>
+      </c>
+      <c r="G982" t="n">
+        <v>90</v>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="J982" t="inlineStr">
+        <is>
+          <t>Common enemies of level 80 and above: physical resistances 10 points lower</t>
+        </is>
+      </c>
+      <c r="K982" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L982" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>E127</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>attacks</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>1515 Avenger</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>effect 249</t>
+        </is>
+      </c>
+      <c r="F983" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G983" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>L08</t>
+        </is>
+      </c>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="J983" t="inlineStr">
+        <is>
+          <t>An enemy passive at most the top value the party can have of the same passive</t>
+        </is>
+      </c>
+      <c r="K983" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L983" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>E128</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>attacks</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>1516 Avenger</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>effect 249</t>
+        </is>
+      </c>
+      <c r="F984" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G984" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>L08</t>
+        </is>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="J984" t="inlineStr">
+        <is>
+          <t>An enemy passive at most the top value the party can have of the same passive</t>
+        </is>
+      </c>
+      <c r="K984" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L984" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>E129</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>attacks</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>1517 Avenger</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>effect 249</t>
+        </is>
+      </c>
+      <c r="F985" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G985" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>L08</t>
+        </is>
+      </c>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="J985" t="inlineStr">
+        <is>
+          <t>An enemy passive at most the top value the party can have of the same passive</t>
+        </is>
+      </c>
+      <c r="K985" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L985" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>E130</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>attacks</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>1519 Mind's Eye</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>effect 250</t>
+        </is>
+      </c>
+      <c r="F986" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G986" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>L08</t>
+        </is>
+      </c>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="J986" t="inlineStr">
+        <is>
+          <t>An enemy passive at most the top value the party can have of the same passive</t>
+        </is>
+      </c>
+      <c r="K986" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L986" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>E131</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>attacks</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>1520 Mind's Eye</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>effect 250</t>
+        </is>
+      </c>
+      <c r="F987" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G987" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>L08</t>
+        </is>
+      </c>
+      <c r="I987" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="J987" t="inlineStr">
+        <is>
+          <t>An enemy passive at most the top value the party can have of the same passive</t>
+        </is>
+      </c>
+      <c r="K987" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L987" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>E132</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>attacks</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>1534 Auto-Guard</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>effect 255</t>
+        </is>
+      </c>
+      <c r="F988" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G988" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>L08</t>
+        </is>
+      </c>
+      <c r="I988" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="J988" t="inlineStr">
+        <is>
+          <t>An enemy passive at most the top value the party can have of the same passive</t>
+        </is>
+      </c>
+      <c r="K988" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L988" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>E133</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>attacks</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>1535 Auto-Guard</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>effect 255</t>
+        </is>
+      </c>
+      <c r="F989" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G989" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>L08</t>
+        </is>
+      </c>
+      <c r="I989" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="J989" t="inlineStr">
+        <is>
+          <t>An enemy passive at most the top value the party can have of the same passive</t>
+        </is>
+      </c>
+      <c r="K989" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L989" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>E134</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>attacks</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>1536 Auto-Guard</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>effect 255</t>
+        </is>
+      </c>
+      <c r="F990" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G990" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>L08</t>
+        </is>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="J990" t="inlineStr">
+        <is>
+          <t>An enemy passive at most the top value the party can have of the same passive</t>
+        </is>
+      </c>
+      <c r="K990" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L990" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>E135</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>attacks</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>1552 Ecstasy</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>effect 312</t>
+        </is>
+      </c>
+      <c r="F991" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G991" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>L08</t>
+        </is>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="J991" t="inlineStr">
+        <is>
+          <t>An enemy passive at most the top value the party can have of the same passive</t>
+        </is>
+      </c>
+      <c r="K991" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L991" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>E136</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>attacks</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>1553 Ecstasy</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>effect 312</t>
+        </is>
+      </c>
+      <c r="F992" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G992" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>L08</t>
+        </is>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="J992" t="inlineStr">
+        <is>
+          <t>An enemy passive at most the top value the party can have of the same passive</t>
+        </is>
+      </c>
+      <c r="K992" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L992" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>E201</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>17 Odin</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>passive skill id (0xF4 list)</t>
+        </is>
+      </c>
+      <c r="F993" t="n">
+        <v>1544</v>
+      </c>
+      <c r="G993" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>L35</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="J993" t="inlineStr">
+        <is>
+          <t>Dark Aura of a common enemy lowers four stats per hit instead of six: its passive record 1544 (value 6) swapped for 1543 (value 4), an existing record; same slot, same shape (structural, justified: the value cannot be changed without touching the bosses that share the record)</t>
+        </is>
+      </c>
+      <c r="K993" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L993" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>E202</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>81 Seraph</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>passive skill id (0xF4 list)</t>
+        </is>
+      </c>
+      <c r="F994" t="n">
+        <v>1544</v>
+      </c>
+      <c r="G994" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>L35</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="J994" t="inlineStr">
+        <is>
+          <t>Dark Aura of a common enemy lowers four stats per hit instead of six: its passive record 1544 (value 6) swapped for 1543 (value 4), an existing record; same slot, same shape (structural, justified: the value cannot be changed without touching the bosses that share the record)</t>
+        </is>
+      </c>
+      <c r="K994" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L994" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>E203</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>264 Cerberus</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>passive skill id (0xF4 list)</t>
+        </is>
+      </c>
+      <c r="F995" t="n">
+        <v>1544</v>
+      </c>
+      <c r="G995" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>L35</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="J995" t="inlineStr">
+        <is>
+          <t>Dark Aura of a common enemy lowers four stats per hit instead of six: its passive record 1544 (value 6) swapped for 1543 (value 4), an existing record; same slot, same shape (structural, justified: the value cannot be changed without touching the bosses that share the record)</t>
+        </is>
+      </c>
+      <c r="K995" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L995" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>E204</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>390 Zahhak</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>passive skill id (0xF4 list)</t>
+        </is>
+      </c>
+      <c r="F996" t="n">
+        <v>1544</v>
+      </c>
+      <c r="G996" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>L35</t>
+        </is>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="J996" t="inlineStr">
+        <is>
+          <t>Dark Aura of a common enemy lowers four stats per hit instead of six: its passive record 1544 (value 6) swapped for 1543 (value 4), an existing record; same slot, same shape (structural, justified: the value cannot be changed without touching the bosses that share the record)</t>
+        </is>
+      </c>
+      <c r="K996" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L996" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>E205</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>405 Tiamat</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>passive skill id (0xF4 list)</t>
+        </is>
+      </c>
+      <c r="F997" t="n">
+        <v>1544</v>
+      </c>
+      <c r="G997" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>L35</t>
+        </is>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="J997" t="inlineStr">
+        <is>
+          <t>Dark Aura of a common enemy lowers four stats per hit instead of six: its passive record 1544 (value 6) swapped for 1543 (value 4), an existing record; same slot, same shape (structural, justified: the value cannot be changed without touching the bosses that share the record)</t>
+        </is>
+      </c>
+      <c r="K997" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L997" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>E206</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>444 Carmilla</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>passive skill id (0xF4 list)</t>
+        </is>
+      </c>
+      <c r="F998" t="n">
+        <v>1544</v>
+      </c>
+      <c r="G998" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>L35</t>
+        </is>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="J998" t="inlineStr">
+        <is>
+          <t>Dark Aura of a common enemy lowers four stats per hit instead of six: its passive record 1544 (value 6) swapped for 1543 (value 4), an existing record; same slot, same shape (structural, justified: the value cannot be changed without touching the bosses that share the record)</t>
+        </is>
+      </c>
+      <c r="K998" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L998" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>E207</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>454 Charon</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>passive skill id (0xF4 list)</t>
+        </is>
+      </c>
+      <c r="F999" t="n">
+        <v>1544</v>
+      </c>
+      <c r="G999" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>L35</t>
+        </is>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="J999" t="inlineStr">
+        <is>
+          <t>Dark Aura of a common enemy lowers four stats per hit instead of six: its passive record 1544 (value 6) swapped for 1543 (value 4), an existing record; same slot, same shape (structural, justified: the value cannot be changed without touching the bosses that share the record)</t>
+        </is>
+      </c>
+      <c r="K999" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L999" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>E208</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>459 Hel</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>passive skill id (0xF4 list)</t>
+        </is>
+      </c>
+      <c r="F1000" t="n">
+        <v>1544</v>
+      </c>
+      <c r="G1000" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>L35</t>
+        </is>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="J1000" t="inlineStr">
+        <is>
+          <t>Dark Aura of a common enemy lowers four stats per hit instead of six: its passive record 1544 (value 6) swapped for 1543 (value 4), an existing record; same slot, same shape (structural, justified: the value cannot be changed without touching the bosses that share the record)</t>
+        </is>
+      </c>
+      <c r="K1000" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1000" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>E209</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>469 Tsukuyomi</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>passive skill id (0xF4 list)</t>
+        </is>
+      </c>
+      <c r="F1001" t="n">
+        <v>1544</v>
+      </c>
+      <c r="G1001" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>L35</t>
+        </is>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="J1001" t="inlineStr">
+        <is>
+          <t>Dark Aura of a common enemy lowers four stats per hit instead of six: its passive record 1544 (value 6) swapped for 1543 (value 4), an existing record; same slot, same shape (structural, justified: the value cannot be changed without touching the bosses that share the record)</t>
+        </is>
+      </c>
+      <c r="K1001" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1001" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>E210</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>780 Default</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>passive skill id (0xF4 list)</t>
+        </is>
+      </c>
+      <c r="F1002" t="n">
+        <v>1544</v>
+      </c>
+      <c r="G1002" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>L35</t>
+        </is>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="J1002" t="inlineStr">
+        <is>
+          <t>Dark Aura of a common enemy lowers four stats per hit instead of six: its passive record 1544 (value 6) swapped for 1543 (value 4), an existing record; same slot, same shape (structural, justified: the value cannot be changed without touching the bosses that share the record)</t>
+        </is>
+      </c>
+      <c r="K1002" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1002" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>E211</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>909 Dullahan</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>passive skill id (0xF4 list)</t>
+        </is>
+      </c>
+      <c r="F1003" t="n">
+        <v>1544</v>
+      </c>
+      <c r="G1003" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>L35</t>
+        </is>
+      </c>
+      <c r="I1003" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="J1003" t="inlineStr">
+        <is>
+          <t>Dark Aura of a common enemy lowers four stats per hit instead of six: its passive record 1544 (value 6) swapped for 1543 (value 4), an existing record; same slot, same shape (structural, justified: the value cannot be changed without touching the bosses that share the record)</t>
+        </is>
+      </c>
+      <c r="K1003" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1003" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>E212</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>910 Overlord</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>passive skill id (0xF4 list)</t>
+        </is>
+      </c>
+      <c r="F1004" t="n">
+        <v>1544</v>
+      </c>
+      <c r="G1004" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>L35</t>
+        </is>
+      </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="J1004" t="inlineStr">
+        <is>
+          <t>Dark Aura of a common enemy lowers four stats per hit instead of six: its passive record 1544 (value 6) swapped for 1543 (value 4), an existing record; same slot, same shape (structural, justified: the value cannot be changed without touching the bosses that share the record)</t>
+        </is>
+      </c>
+      <c r="K1004" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1004" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -26985,7 +26985,7 @@
         <v>0.2</v>
       </c>
       <c r="G474" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="H474" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>The single-target fan strike of the Papillon (her only tool against a lone boss was the area attack Rose Queen). The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+          <t>The single-target fan strike of the Papillon (her only tool against a lone boss was the area attack Rose Queen). Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
         </is>
       </c>
       <c r="K474" t="inlineStr">
@@ -27055,7 +27055,7 @@
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>The single-target fan strike of the Papillon (her only tool against a lone boss was the area attack Rose Queen). The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+          <t>The single-target fan strike of the Papillon (her only tool against a lone boss was the area attack Rose Queen). Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
         </is>
       </c>
       <c r="K475" t="inlineStr">
@@ -27097,7 +27097,7 @@
         <v>0.2</v>
       </c>
       <c r="G476" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="H476" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
         </is>
       </c>
       <c r="K476" t="inlineStr">
@@ -27153,7 +27153,7 @@
         <v>0.26</v>
       </c>
       <c r="G477" t="n">
-        <v>0.638</v>
+        <v>0.449</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
         </is>
       </c>
       <c r="K477" t="inlineStr">
@@ -27209,7 +27209,7 @@
         <v>0.32</v>
       </c>
       <c r="G478" t="n">
-        <v>0.716</v>
+        <v>0.518</v>
       </c>
       <c r="H478" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
         </is>
       </c>
       <c r="K478" t="inlineStr">
@@ -27265,7 +27265,7 @@
         <v>0.38</v>
       </c>
       <c r="G479" t="n">
-        <v>0.794</v>
+        <v>0.587</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
         </is>
       </c>
       <c r="K479" t="inlineStr">
@@ -27321,7 +27321,7 @@
         <v>0.42</v>
       </c>
       <c r="G480" t="n">
-        <v>0.846</v>
+        <v>0.633</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
         </is>
       </c>
       <c r="K480" t="inlineStr">
@@ -27377,7 +27377,7 @@
         <v>0.5</v>
       </c>
       <c r="G481" t="n">
-        <v>0.95</v>
+        <v>0.725</v>
       </c>
       <c r="H481" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
         </is>
       </c>
       <c r="K481" t="inlineStr">
@@ -27433,7 +27433,7 @@
         <v>0.58</v>
       </c>
       <c r="G482" t="n">
-        <v>1.054</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
         </is>
       </c>
       <c r="K482" t="inlineStr">
@@ -27489,7 +27489,7 @@
         <v>0.68</v>
       </c>
       <c r="G483" t="n">
-        <v>1.184</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
         </is>
       </c>
       <c r="K483" t="inlineStr">
@@ -27545,7 +27545,7 @@
         <v>0.78</v>
       </c>
       <c r="G484" t="n">
-        <v>1.314</v>
+        <v>1.047</v>
       </c>
       <c r="H484" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
         </is>
       </c>
       <c r="K484" t="inlineStr">
@@ -27601,7 +27601,7 @@
         <v>0.9</v>
       </c>
       <c r="G485" t="n">
-        <v>1.47</v>
+        <v>1.185</v>
       </c>
       <c r="H485" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. The first Papillon slot goes from 70% to 94% of the Fighter/Scout band (C13 74%, C18 111%, C25 113%, C34 70%, C38 101%; sim/measures.py slot_share, 20 battles)</t>
+          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
         </is>
       </c>
       <c r="K485" t="inlineStr">

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1004"/>
+  <dimension ref="A1:L1029"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56311,6 +56311,1406 @@
         </is>
       </c>
     </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>K001</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>Magic 216 Shadow Clone</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1005" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1005" t="n">
+        <v>23</v>
+      </c>
+      <c r="G1005" t="n">
+        <v>17</v>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1005" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1005" t="inlineStr">
+        <is>
+          <t>The Kunoichi wins as often as the Papillon in her slot but takes much longer (C40 40 s against 29, P24 21 s against 13): Shadow Clone and Ninja Piledriver drain her TP and she ends on plain hits. A quarter off both (the cap of the user on TP cuts); the JP guide notes Shadow Clone cost more than in the prequel (atwiki dt2-2 page 142)</t>
+        </is>
+      </c>
+      <c r="K1005" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1005" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>K002</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>Magic 216 Shadow Clone</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1006" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1006" t="n">
+        <v>27</v>
+      </c>
+      <c r="G1006" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1006" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1006" t="inlineStr">
+        <is>
+          <t>The Kunoichi wins as often as the Papillon in her slot but takes much longer (C40 40 s against 29, P24 21 s against 13): Shadow Clone and Ninja Piledriver drain her TP and she ends on plain hits. A quarter off both (the cap of the user on TP cuts); the JP guide notes Shadow Clone cost more than in the prequel (atwiki dt2-2 page 142)</t>
+        </is>
+      </c>
+      <c r="K1006" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1006" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>K003</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>Magic 216 Shadow Clone</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1007" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1007" t="n">
+        <v>24</v>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1007" t="inlineStr">
+        <is>
+          <t>The Kunoichi wins as often as the Papillon in her slot but takes much longer (C40 40 s against 29, P24 21 s against 13): Shadow Clone and Ninja Piledriver drain her TP and she ends on plain hits. A quarter off both (the cap of the user on TP cuts); the JP guide notes Shadow Clone cost more than in the prequel (atwiki dt2-2 page 142)</t>
+        </is>
+      </c>
+      <c r="K1007" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1007" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>K004</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>Magic 216 Shadow Clone</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1008" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1008" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1008" t="n">
+        <v>28</v>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1008" t="inlineStr">
+        <is>
+          <t>The Kunoichi wins as often as the Papillon in her slot but takes much longer (C40 40 s against 29, P24 21 s against 13): Shadow Clone and Ninja Piledriver drain her TP and she ends on plain hits. A quarter off both (the cap of the user on TP cuts); the JP guide notes Shadow Clone cost more than in the prequel (atwiki dt2-2 page 142)</t>
+        </is>
+      </c>
+      <c r="K1008" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1008" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>K005</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>Magic 216 Shadow Clone</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1009" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1009" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1009" t="n">
+        <v>33</v>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1009" t="inlineStr">
+        <is>
+          <t>The Kunoichi wins as often as the Papillon in her slot but takes much longer (C40 40 s against 29, P24 21 s against 13): Shadow Clone and Ninja Piledriver drain her TP and she ends on plain hits. A quarter off both (the cap of the user on TP cuts); the JP guide notes Shadow Clone cost more than in the prequel (atwiki dt2-2 page 142)</t>
+        </is>
+      </c>
+      <c r="K1009" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1009" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>K006</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Technique 52 Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1010" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1010" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1010" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1010" t="inlineStr">
+        <is>
+          <t>The Kunoichi wins as often as the Papillon in her slot but takes much longer (C40 40 s against 29, P24 21 s against 13): Shadow Clone and Ninja Piledriver drain her TP and she ends on plain hits. A quarter off both (the cap of the user on TP cuts); the JP guide notes Shadow Clone cost more than in the prequel (atwiki dt2-2 page 142)</t>
+        </is>
+      </c>
+      <c r="K1010" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1010" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>K007</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>Technique 52 Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1011" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1011" t="n">
+        <v>15</v>
+      </c>
+      <c r="G1011" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1011" t="inlineStr">
+        <is>
+          <t>The Kunoichi wins as often as the Papillon in her slot but takes much longer (C40 40 s against 29, P24 21 s against 13): Shadow Clone and Ninja Piledriver drain her TP and she ends on plain hits. A quarter off both (the cap of the user on TP cuts); the JP guide notes Shadow Clone cost more than in the prequel (atwiki dt2-2 page 142)</t>
+        </is>
+      </c>
+      <c r="K1011" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1011" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>K008</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>Technique 52 Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1012" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1012" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1012" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1012" t="inlineStr">
+        <is>
+          <t>The Kunoichi wins as often as the Papillon in her slot but takes much longer (C40 40 s against 29, P24 21 s against 13): Shadow Clone and Ninja Piledriver drain her TP and she ends on plain hits. A quarter off both (the cap of the user on TP cuts); the JP guide notes Shadow Clone cost more than in the prequel (atwiki dt2-2 page 142)</t>
+        </is>
+      </c>
+      <c r="K1012" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1012" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>K009</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>Technique 52 Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1013" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1013" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1013" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1013" t="inlineStr">
+        <is>
+          <t>The Kunoichi wins as often as the Papillon in her slot but takes much longer (C40 40 s against 29, P24 21 s against 13): Shadow Clone and Ninja Piledriver drain her TP and she ends on plain hits. A quarter off both (the cap of the user on TP cuts); the JP guide notes Shadow Clone cost more than in the prequel (atwiki dt2-2 page 142)</t>
+        </is>
+      </c>
+      <c r="K1013" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1013" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>K010</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>Technique 52 Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1014" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1014" t="n">
+        <v>24</v>
+      </c>
+      <c r="G1014" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1014" t="inlineStr">
+        <is>
+          <t>The Kunoichi wins as often as the Papillon in her slot but takes much longer (C40 40 s against 29, P24 21 s against 13): Shadow Clone and Ninja Piledriver drain her TP and she ends on plain hits. A quarter off both (the cap of the user on TP cuts); the JP guide notes Shadow Clone cost more than in the prequel (atwiki dt2-2 page 142)</t>
+        </is>
+      </c>
+      <c r="K1014" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1014" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>K011</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>Technique 52 Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1015" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1015" t="n">
+        <v>27</v>
+      </c>
+      <c r="G1015" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1015" t="inlineStr">
+        <is>
+          <t>The Kunoichi wins as often as the Papillon in her slot but takes much longer (C40 40 s against 29, P24 21 s against 13): Shadow Clone and Ninja Piledriver drain her TP and she ends on plain hits. A quarter off both (the cap of the user on TP cuts); the JP guide notes Shadow Clone cost more than in the prequel (atwiki dt2-2 page 142)</t>
+        </is>
+      </c>
+      <c r="K1015" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1015" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>K012</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Technique 52 Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1016" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1016" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1016" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1016" t="inlineStr">
+        <is>
+          <t>The Kunoichi wins as often as the Papillon in her slot but takes much longer (C40 40 s against 29, P24 21 s against 13): Shadow Clone and Ninja Piledriver drain her TP and she ends on plain hits. A quarter off both (the cap of the user on TP cuts); the JP guide notes Shadow Clone cost more than in the prequel (atwiki dt2-2 page 142)</t>
+        </is>
+      </c>
+      <c r="K1016" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1016" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>K013</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>Technique 52 Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1017" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1017" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1017" t="n">
+        <v>24</v>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1017" t="inlineStr">
+        <is>
+          <t>The Kunoichi wins as often as the Papillon in her slot but takes much longer (C40 40 s against 29, P24 21 s against 13): Shadow Clone and Ninja Piledriver drain her TP and she ends on plain hits. A quarter off both (the cap of the user on TP cuts); the JP guide notes Shadow Clone cost more than in the prequel (atwiki dt2-2 page 142)</t>
+        </is>
+      </c>
+      <c r="K1017" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1017" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>K014</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>Technique 52 Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1018" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1018" t="n">
+        <v>34</v>
+      </c>
+      <c r="G1018" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1018" t="inlineStr">
+        <is>
+          <t>The Kunoichi wins as often as the Papillon in her slot but takes much longer (C40 40 s against 29, P24 21 s against 13): Shadow Clone and Ninja Piledriver drain her TP and she ends on plain hits. A quarter off both (the cap of the user on TP cuts); the JP guide notes Shadow Clone cost more than in the prequel (atwiki dt2-2 page 142)</t>
+        </is>
+      </c>
+      <c r="K1018" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1018" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>K015</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>Technique 52 Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1019" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1019" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1019" t="n">
+        <v>27</v>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1019" t="inlineStr">
+        <is>
+          <t>The Kunoichi wins as often as the Papillon in her slot but takes much longer (C40 40 s against 29, P24 21 s against 13): Shadow Clone and Ninja Piledriver drain her TP and she ends on plain hits. A quarter off both (the cap of the user on TP cuts); the JP guide notes Shadow Clone cost more than in the prequel (atwiki dt2-2 page 142)</t>
+        </is>
+      </c>
+      <c r="K1019" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1019" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>K016</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>Technique 52 Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1020" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1020" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G1020" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1020" t="inlineStr">
+        <is>
+          <t>Her own strike, Ninja Piledriver, x2.5 power at every level: with the TP cut she matches the Papillon in time at C34 and C40 (31 / 28 s against 31 / 29) and is 23% slower at P24 while winning more (100% against 80%); her share of damage (20 - 39%) stays below the Papillon (29 - 44%), so she does not become mandatory. Measured: measures.slot_share, 15 battles, on the variant</t>
+        </is>
+      </c>
+      <c r="K1020" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1020" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>K017</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>Technique 52 Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1021" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1021" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G1021" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1021" t="inlineStr">
+        <is>
+          <t>Her own strike, Ninja Piledriver, x2.5 power at every level: with the TP cut she matches the Papillon in time at C34 and C40 (31 / 28 s against 31 / 29) and is 23% slower at P24 while winning more (100% against 80%); her share of damage (20 - 39%) stays below the Papillon (29 - 44%), so she does not become mandatory. Measured: measures.slot_share, 15 battles, on the variant</t>
+        </is>
+      </c>
+      <c r="K1021" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1021" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>K018</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>Technique 52 Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1022" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1022" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G1022" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1022" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1022" t="inlineStr">
+        <is>
+          <t>Her own strike, Ninja Piledriver, x2.5 power at every level: with the TP cut she matches the Papillon in time at C34 and C40 (31 / 28 s against 31 / 29) and is 23% slower at P24 while winning more (100% against 80%); her share of damage (20 - 39%) stays below the Papillon (29 - 44%), so she does not become mandatory. Measured: measures.slot_share, 15 battles, on the variant</t>
+        </is>
+      </c>
+      <c r="K1022" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1022" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>K019</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Technique 52 Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1023" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1023" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G1023" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1023" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1023" t="inlineStr">
+        <is>
+          <t>Her own strike, Ninja Piledriver, x2.5 power at every level: with the TP cut she matches the Papillon in time at C34 and C40 (31 / 28 s against 31 / 29) and is 23% slower at P24 while winning more (100% against 80%); her share of damage (20 - 39%) stays below the Papillon (29 - 44%), so she does not become mandatory. Measured: measures.slot_share, 15 battles, on the variant</t>
+        </is>
+      </c>
+      <c r="K1023" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1023" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>K020</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>Technique 52 Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1024" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1024" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G1024" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1024" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1024" t="inlineStr">
+        <is>
+          <t>Her own strike, Ninja Piledriver, x2.5 power at every level: with the TP cut she matches the Papillon in time at C34 and C40 (31 / 28 s against 31 / 29) and is 23% slower at P24 while winning more (100% against 80%); her share of damage (20 - 39%) stays below the Papillon (29 - 44%), so she does not become mandatory. Measured: measures.slot_share, 15 battles, on the variant</t>
+        </is>
+      </c>
+      <c r="K1024" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1024" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>K021</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>Technique 52 Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1025" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1025" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G1025" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1025" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1025" t="inlineStr">
+        <is>
+          <t>Her own strike, Ninja Piledriver, x2.5 power at every level: with the TP cut she matches the Papillon in time at C34 and C40 (31 / 28 s against 31 / 29) and is 23% slower at P24 while winning more (100% against 80%); her share of damage (20 - 39%) stays below the Papillon (29 - 44%), so she does not become mandatory. Measured: measures.slot_share, 15 battles, on the variant</t>
+        </is>
+      </c>
+      <c r="K1025" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1025" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>K022</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>Technique 52 Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1026" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1026" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G1026" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1026" t="inlineStr">
+        <is>
+          <t>Her own strike, Ninja Piledriver, x2.5 power at every level: with the TP cut she matches the Papillon in time at C34 and C40 (31 / 28 s against 31 / 29) and is 23% slower at P24 while winning more (100% against 80%); her share of damage (20 - 39%) stays below the Papillon (29 - 44%), so she does not become mandatory. Measured: measures.slot_share, 15 battles, on the variant</t>
+        </is>
+      </c>
+      <c r="K1026" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1026" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>K023</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>Technique 52 Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1027" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1027" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1027" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1027" t="inlineStr">
+        <is>
+          <t>Her own strike, Ninja Piledriver, x2.5 power at every level: with the TP cut she matches the Papillon in time at C34 and C40 (31 / 28 s against 31 / 29) and is 23% slower at P24 while winning more (100% against 80%); her share of damage (20 - 39%) stays below the Papillon (29 - 44%), so she does not become mandatory. Measured: measures.slot_share, 15 battles, on the variant</t>
+        </is>
+      </c>
+      <c r="K1027" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1027" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>K024</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>Technique 52 Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1028" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1028" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1028" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1028" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1028" t="inlineStr">
+        <is>
+          <t>Her own strike, Ninja Piledriver, x2.5 power at every level: with the TP cut she matches the Papillon in time at C34 and C40 (31 / 28 s against 31 / 29) and is 23% slower at P24 while winning more (100% against 80%); her share of damage (20 - 39%) stays below the Papillon (29 - 44%), so she does not become mandatory. Measured: measures.slot_share, 15 battles, on the variant</t>
+        </is>
+      </c>
+      <c r="K1028" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1028" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>K025</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>Technique 52 Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1029" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1029" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1029" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1029" t="inlineStr">
+        <is>
+          <t>F04, J27, F88</t>
+        </is>
+      </c>
+      <c r="J1029" t="inlineStr">
+        <is>
+          <t>Her own strike, Ninja Piledriver, x2.5 power at every level: with the TP cut she matches the Papillon in time at C34 and C40 (31 / 28 s against 31 / 29) and is 23% slower at P24 while winning more (100% against 80%); her share of damage (20 - 39%) stays below the Papillon (29 - 44%), so she does not become mandatory. Measured: measures.slot_share, 15 battles, on the variant</t>
+        </is>
+      </c>
+      <c r="K1029" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1029" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1029"/>
+  <dimension ref="A1:L1044"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57711,6 +57711,846 @@
         </is>
       </c>
     </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>Q001</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>Technique 59 Magical Change</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1030" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1030" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1030" t="n">
+        <v>39</v>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>F05, J25</t>
+        </is>
+      </c>
+      <c r="J1030" t="inlineStr">
+        <is>
+          <t>The Magical Princess wins as often as the Papillon in her slot but her fights last 10 - 34% longer: Magical Change (92 TP at the top level, renewed every few turns) drains her TP. A quarter off (the cap of the user on TP cuts)</t>
+        </is>
+      </c>
+      <c r="K1030" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1030" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>Q002</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>Technique 59 Magical Change</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1031" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1031" t="n">
+        <v>60</v>
+      </c>
+      <c r="G1031" t="n">
+        <v>45</v>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>F05, J25</t>
+        </is>
+      </c>
+      <c r="J1031" t="inlineStr">
+        <is>
+          <t>The Magical Princess wins as often as the Papillon in her slot but her fights last 10 - 34% longer: Magical Change (92 TP at the top level, renewed every few turns) drains her TP. A quarter off (the cap of the user on TP cuts)</t>
+        </is>
+      </c>
+      <c r="K1031" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1031" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>Q003</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Technique 59 Magical Change</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1032" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1032" t="n">
+        <v>70</v>
+      </c>
+      <c r="G1032" t="n">
+        <v>52</v>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>F05, J25</t>
+        </is>
+      </c>
+      <c r="J1032" t="inlineStr">
+        <is>
+          <t>The Magical Princess wins as often as the Papillon in her slot but her fights last 10 - 34% longer: Magical Change (92 TP at the top level, renewed every few turns) drains her TP. A quarter off (the cap of the user on TP cuts)</t>
+        </is>
+      </c>
+      <c r="K1032" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1032" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>Q004</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>Technique 59 Magical Change</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1033" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1033" t="n">
+        <v>80</v>
+      </c>
+      <c r="G1033" t="n">
+        <v>60</v>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>F05, J25</t>
+        </is>
+      </c>
+      <c r="J1033" t="inlineStr">
+        <is>
+          <t>The Magical Princess wins as often as the Papillon in her slot but her fights last 10 - 34% longer: Magical Change (92 TP at the top level, renewed every few turns) drains her TP. A quarter off (the cap of the user on TP cuts)</t>
+        </is>
+      </c>
+      <c r="K1033" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1033" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>Q005</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Technique 59 Magical Change</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1034" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1034" t="n">
+        <v>92</v>
+      </c>
+      <c r="G1034" t="n">
+        <v>69</v>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>F05, J25</t>
+        </is>
+      </c>
+      <c r="J1034" t="inlineStr">
+        <is>
+          <t>The Magical Princess wins as often as the Papillon in her slot but her fights last 10 - 34% longer: Magical Change (92 TP at the top level, renewed every few turns) drains her TP. A quarter off (the cap of the user on TP cuts)</t>
+        </is>
+      </c>
+      <c r="K1034" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1034" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>Q006</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>Technique 60 Magical Spark</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1035" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1035" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G1035" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1035" t="inlineStr">
+        <is>
+          <t>F05, J25</t>
+        </is>
+      </c>
+      <c r="J1035" t="inlineStr">
+        <is>
+          <t>Magical Spark, her main strike, x1.7 power at every level: with the TP cut she is within 6 - 15% of the time of the Papillon (C34, C40, P24) with the same share of damage (27 / 44 / 38% against 29 / 44 / 42%), so she does not become mandatory. Magical Change stays her transformation (atwiki dt2-2 page 137). Measured: measures.slot_share, 15 battles, on the variant</t>
+        </is>
+      </c>
+      <c r="K1035" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1035" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>Q007</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Technique 60 Magical Spark</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1036" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1036" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G1036" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1036" t="inlineStr">
+        <is>
+          <t>F05, J25</t>
+        </is>
+      </c>
+      <c r="J1036" t="inlineStr">
+        <is>
+          <t>Magical Spark, her main strike, x1.7 power at every level: with the TP cut she is within 6 - 15% of the time of the Papillon (C34, C40, P24) with the same share of damage (27 / 44 / 38% against 29 / 44 / 42%), so she does not become mandatory. Magical Change stays her transformation (atwiki dt2-2 page 137). Measured: measures.slot_share, 15 battles, on the variant</t>
+        </is>
+      </c>
+      <c r="K1036" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1036" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>Q008</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Technique 60 Magical Spark</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1037" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1037" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G1037" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>F05, J25</t>
+        </is>
+      </c>
+      <c r="J1037" t="inlineStr">
+        <is>
+          <t>Magical Spark, her main strike, x1.7 power at every level: with the TP cut she is within 6 - 15% of the time of the Papillon (C34, C40, P24) with the same share of damage (27 / 44 / 38% against 29 / 44 / 42%), so she does not become mandatory. Magical Change stays her transformation (atwiki dt2-2 page 137). Measured: measures.slot_share, 15 battles, on the variant</t>
+        </is>
+      </c>
+      <c r="K1037" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1037" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>Q009</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Technique 60 Magical Spark</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1038" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1038" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G1038" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>F05, J25</t>
+        </is>
+      </c>
+      <c r="J1038" t="inlineStr">
+        <is>
+          <t>Magical Spark, her main strike, x1.7 power at every level: with the TP cut she is within 6 - 15% of the time of the Papillon (C34, C40, P24) with the same share of damage (27 / 44 / 38% against 29 / 44 / 42%), so she does not become mandatory. Magical Change stays her transformation (atwiki dt2-2 page 137). Measured: measures.slot_share, 15 battles, on the variant</t>
+        </is>
+      </c>
+      <c r="K1038" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1038" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>Q010</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Technique 60 Magical Spark</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1039" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1039" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G1039" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>F05, J25</t>
+        </is>
+      </c>
+      <c r="J1039" t="inlineStr">
+        <is>
+          <t>Magical Spark, her main strike, x1.7 power at every level: with the TP cut she is within 6 - 15% of the time of the Papillon (C34, C40, P24) with the same share of damage (27 / 44 / 38% against 29 / 44 / 42%), so she does not become mandatory. Magical Change stays her transformation (atwiki dt2-2 page 137). Measured: measures.slot_share, 15 battles, on the variant</t>
+        </is>
+      </c>
+      <c r="K1039" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1039" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>Q011</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Technique 60 Magical Spark</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1040" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1040" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1040" t="n">
+        <v>1.224</v>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1040" t="inlineStr">
+        <is>
+          <t>F05, J25</t>
+        </is>
+      </c>
+      <c r="J1040" t="inlineStr">
+        <is>
+          <t>Magical Spark, her main strike, x1.7 power at every level: with the TP cut she is within 6 - 15% of the time of the Papillon (C34, C40, P24) with the same share of damage (27 / 44 / 38% against 29 / 44 / 42%), so she does not become mandatory. Magical Change stays her transformation (atwiki dt2-2 page 137). Measured: measures.slot_share, 15 battles, on the variant</t>
+        </is>
+      </c>
+      <c r="K1040" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1040" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>Q012</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Technique 60 Magical Spark</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1041" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1041" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1041" t="n">
+        <v>1.394</v>
+      </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1041" t="inlineStr">
+        <is>
+          <t>F05, J25</t>
+        </is>
+      </c>
+      <c r="J1041" t="inlineStr">
+        <is>
+          <t>Magical Spark, her main strike, x1.7 power at every level: with the TP cut she is within 6 - 15% of the time of the Papillon (C34, C40, P24) with the same share of damage (27 / 44 / 38% against 29 / 44 / 42%), so she does not become mandatory. Magical Change stays her transformation (atwiki dt2-2 page 137). Measured: measures.slot_share, 15 battles, on the variant</t>
+        </is>
+      </c>
+      <c r="K1041" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1041" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>Q013</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>Technique 60 Magical Spark</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1042" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1042" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G1042" t="n">
+        <v>1.581</v>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>F05, J25</t>
+        </is>
+      </c>
+      <c r="J1042" t="inlineStr">
+        <is>
+          <t>Magical Spark, her main strike, x1.7 power at every level: with the TP cut she is within 6 - 15% of the time of the Papillon (C34, C40, P24) with the same share of damage (27 / 44 / 38% against 29 / 44 / 42%), so she does not become mandatory. Magical Change stays her transformation (atwiki dt2-2 page 137). Measured: measures.slot_share, 15 battles, on the variant</t>
+        </is>
+      </c>
+      <c r="K1042" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1042" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>Q014</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Technique 60 Magical Spark</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1043" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1043" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G1043" t="n">
+        <v>1.768</v>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>F05, J25</t>
+        </is>
+      </c>
+      <c r="J1043" t="inlineStr">
+        <is>
+          <t>Magical Spark, her main strike, x1.7 power at every level: with the TP cut she is within 6 - 15% of the time of the Papillon (C34, C40, P24) with the same share of damage (27 / 44 / 38% against 29 / 44 / 42%), so she does not become mandatory. Magical Change stays her transformation (atwiki dt2-2 page 137). Measured: measures.slot_share, 15 battles, on the variant</t>
+        </is>
+      </c>
+      <c r="K1043" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1043" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>Q015</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Technique 60 Magical Spark</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1044" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1044" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G1044" t="n">
+        <v>1.972</v>
+      </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>F05, J25</t>
+        </is>
+      </c>
+      <c r="J1044" t="inlineStr">
+        <is>
+          <t>Magical Spark, her main strike, x1.7 power at every level: with the TP cut she is within 6 - 15% of the time of the Papillon (C34, C40, P24) with the same share of damage (27 / 44 / 38% against 29 / 44 / 42%), so she does not become mandatory. Magical Change stays her transformation (atwiki dt2-2 page 137). Measured: measures.slot_share, 15 battles, on the variant</t>
+        </is>
+      </c>
+      <c r="K1044" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1044" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1044"/>
+  <dimension ref="A1:L1119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58551,6 +58551,4206 @@
         </is>
       </c>
     </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>T001</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>Technique 38 Sleep Sting</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1045" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1045" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G1045" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1045" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1045" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1045" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1045" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>T002</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>Technique 38 Sleep Sting</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1046" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1046" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G1046" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1046" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1046" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1046" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>T003</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>Technique 38 Sleep Sting</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1047" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1047" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G1047" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1047" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1047" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1047" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1047" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>T004</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Technique 38 Sleep Sting</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1048" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1048" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G1048" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1048" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1048" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1048" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1048" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>T005</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Technique 38 Sleep Sting</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1049" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1049" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G1049" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1049" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1049" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1049" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1049" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>T006</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>Technique 38 Sleep Sting</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1050" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1050" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G1050" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1050" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1050" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1050" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1050" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>T007</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>Technique 38 Sleep Sting</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1051" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1051" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G1051" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1051" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1051" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1051" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1051" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>T008</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Technique 38 Sleep Sting</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1052" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1052" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G1052" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1052" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1052" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1052" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1052" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>T009</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>Technique 38 Sleep Sting</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1053" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1053" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G1053" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1053" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1053" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1053" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1053" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>T010</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Technique 38 Sleep Sting</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1054" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1054" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G1054" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1054" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1054" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1054" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1054" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>T011</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>Technique 40 Stun Sting</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1055" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1055" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G1055" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1055" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1055" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1055" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1055" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>T012</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>Technique 40 Stun Sting</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1056" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1056" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G1056" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1056" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1056" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1056" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1056" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>T013</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Technique 40 Stun Sting</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1057" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1057" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G1057" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1057" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1057" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1057" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1057" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>T014</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>Technique 40 Stun Sting</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1058" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1058" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G1058" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1058" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1058" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1058" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1058" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>T015</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>Technique 40 Stun Sting</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1059" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1059" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G1059" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1059" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1059" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1059" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1059" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>T016</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>Technique 40 Stun Sting</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1060" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1060" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G1060" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1060" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1060" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1060" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1060" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>T017</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>Technique 40 Stun Sting</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1061" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1061" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G1061" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1061" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1061" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1061" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1061" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>T018</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>Technique 40 Stun Sting</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1062" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1062" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G1062" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1062" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1062" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1062" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1062" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>T019</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Technique 40 Stun Sting</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1063" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1063" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G1063" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1063" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1063" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1063" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1063" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>T020</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Technique 40 Stun Sting</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1064" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1064" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G1064" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1064" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1064" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1064" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1064" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>T021</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>Technique 39 Silence Sting</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1065" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1065" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G1065" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1065" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1065" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1065" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1065" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>T022</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Technique 39 Silence Sting</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1066" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1066" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G1066" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1066" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1066" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1066" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1066" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>T023</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>Technique 39 Silence Sting</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1067" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G1067" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1067" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1067" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1067" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1067" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>T024</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>Technique 39 Silence Sting</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1068" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G1068" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1068" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1068" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1068" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1068" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>T025</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>Technique 39 Silence Sting</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1069" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1069" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G1069" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1069" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1069" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1069" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1069" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>T026</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Technique 39 Silence Sting</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1070" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G1070" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1070" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1070" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1070" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1070" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>T027</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Technique 39 Silence Sting</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1071" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1071" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G1071" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1071" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1071" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1071" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1071" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>T028</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>Technique 39 Silence Sting</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1072" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1072" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G1072" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1072" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1072" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1072" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1072" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>T029</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>Technique 39 Silence Sting</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1073" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1073" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G1073" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1073" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1073" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1073" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1073" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>T030</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Technique 39 Silence Sting</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1074" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1074" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G1074" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1074" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1074" t="inlineStr">
+        <is>
+          <t>The stings, the own strikes of the Assassin, x2.5 power at every level: their power (0.12 - 0.56) was about half of the strikes of the other intermediate classes (Frost Slash 0.30 - 1.28, Gust Thrust 0.35 - 1.45). Measured at C10, C13, C18 (tools/class_stages.py, the Kunoichi build): fights 26% longer than the median attacker, 12% after; still below the other strikes at the top levels, the ailment chance kept</t>
+        </is>
+      </c>
+      <c r="K1074" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1074" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>T031</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>Technique 82 Checkmate</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1075" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1075" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G1075" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1075" t="inlineStr">
+        <is>
+          <t>F17</t>
+        </is>
+      </c>
+      <c r="J1075" t="inlineStr">
+        <is>
+          <t>Trickster (intermediate). Checkmate, the single strike of the Trickster, x1.6 power at every level (on top of S): the Trickster fought 16 - 20% longer than the median attacker at C10, C13, C18 (12 - 15% after); the Papillon and the Joker who keep it stay within the band later (0.88 - 0.97 of the median). High Risk High Return x1.6 was measured too and changes nothing</t>
+        </is>
+      </c>
+      <c r="K1075" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1075" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>T032</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>Technique 82 Checkmate</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1076" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1076" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="G1076" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1076" t="inlineStr">
+        <is>
+          <t>F17</t>
+        </is>
+      </c>
+      <c r="J1076" t="inlineStr">
+        <is>
+          <t>Trickster (intermediate). Checkmate, the single strike of the Trickster, x1.6 power at every level (on top of S): the Trickster fought 16 - 20% longer than the median attacker at C10, C13, C18 (12 - 15% after); the Papillon and the Joker who keep it stay within the band later (0.88 - 0.97 of the median). High Risk High Return x1.6 was measured too and changes nothing</t>
+        </is>
+      </c>
+      <c r="K1076" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1076" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>T033</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>Technique 82 Checkmate</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1077" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1077" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="G1077" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1077" t="inlineStr">
+        <is>
+          <t>F17</t>
+        </is>
+      </c>
+      <c r="J1077" t="inlineStr">
+        <is>
+          <t>Trickster (intermediate). Checkmate, the single strike of the Trickster, x1.6 power at every level (on top of S): the Trickster fought 16 - 20% longer than the median attacker at C10, C13, C18 (12 - 15% after); the Papillon and the Joker who keep it stay within the band later (0.88 - 0.97 of the median). High Risk High Return x1.6 was measured too and changes nothing</t>
+        </is>
+      </c>
+      <c r="K1077" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1077" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>T034</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Technique 82 Checkmate</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1078" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1078" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="G1078" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1078" t="inlineStr">
+        <is>
+          <t>F17</t>
+        </is>
+      </c>
+      <c r="J1078" t="inlineStr">
+        <is>
+          <t>Trickster (intermediate). Checkmate, the single strike of the Trickster, x1.6 power at every level (on top of S): the Trickster fought 16 - 20% longer than the median attacker at C10, C13, C18 (12 - 15% after); the Papillon and the Joker who keep it stay within the band later (0.88 - 0.97 of the median). High Risk High Return x1.6 was measured too and changes nothing</t>
+        </is>
+      </c>
+      <c r="K1078" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1078" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>T035</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>Technique 82 Checkmate</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1079" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1079" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="G1079" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="H1079" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1079" t="inlineStr">
+        <is>
+          <t>F17</t>
+        </is>
+      </c>
+      <c r="J1079" t="inlineStr">
+        <is>
+          <t>Trickster (intermediate). Checkmate, the single strike of the Trickster, x1.6 power at every level (on top of S): the Trickster fought 16 - 20% longer than the median attacker at C10, C13, C18 (12 - 15% after); the Papillon and the Joker who keep it stay within the band later (0.88 - 0.97 of the median). High Risk High Return x1.6 was measured too and changes nothing</t>
+        </is>
+      </c>
+      <c r="K1079" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1079" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>T036</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>Technique 82 Checkmate</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1080" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1080" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="G1080" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1080" t="inlineStr">
+        <is>
+          <t>F17</t>
+        </is>
+      </c>
+      <c r="J1080" t="inlineStr">
+        <is>
+          <t>Trickster (intermediate). Checkmate, the single strike of the Trickster, x1.6 power at every level (on top of S): the Trickster fought 16 - 20% longer than the median attacker at C10, C13, C18 (12 - 15% after); the Papillon and the Joker who keep it stay within the band later (0.88 - 0.97 of the median). High Risk High Return x1.6 was measured too and changes nothing</t>
+        </is>
+      </c>
+      <c r="K1080" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1080" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>T037</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>Technique 82 Checkmate</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1081" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1081" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="G1081" t="n">
+        <v>1.307</v>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1081" t="inlineStr">
+        <is>
+          <t>F17</t>
+        </is>
+      </c>
+      <c r="J1081" t="inlineStr">
+        <is>
+          <t>Trickster (intermediate). Checkmate, the single strike of the Trickster, x1.6 power at every level (on top of S): the Trickster fought 16 - 20% longer than the median attacker at C10, C13, C18 (12 - 15% after); the Papillon and the Joker who keep it stay within the band later (0.88 - 0.97 of the median). High Risk High Return x1.6 was measured too and changes nothing</t>
+        </is>
+      </c>
+      <c r="K1081" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1081" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>T038</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>Technique 82 Checkmate</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1082" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="G1082" t="n">
+        <v>1.491</v>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1082" t="inlineStr">
+        <is>
+          <t>F17</t>
+        </is>
+      </c>
+      <c r="J1082" t="inlineStr">
+        <is>
+          <t>Trickster (intermediate). Checkmate, the single strike of the Trickster, x1.6 power at every level (on top of S): the Trickster fought 16 - 20% longer than the median attacker at C10, C13, C18 (12 - 15% after); the Papillon and the Joker who keep it stay within the band later (0.88 - 0.97 of the median). High Risk High Return x1.6 was measured too and changes nothing</t>
+        </is>
+      </c>
+      <c r="K1082" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1082" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>T039</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>Technique 82 Checkmate</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1083" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="G1083" t="n">
+        <v>1.675</v>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1083" t="inlineStr">
+        <is>
+          <t>F17</t>
+        </is>
+      </c>
+      <c r="J1083" t="inlineStr">
+        <is>
+          <t>Trickster (intermediate). Checkmate, the single strike of the Trickster, x1.6 power at every level (on top of S): the Trickster fought 16 - 20% longer than the median attacker at C10, C13, C18 (12 - 15% after); the Papillon and the Joker who keep it stay within the band later (0.88 - 0.97 of the median). High Risk High Return x1.6 was measured too and changes nothing</t>
+        </is>
+      </c>
+      <c r="K1083" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1083" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>T040</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>Technique 82 Checkmate</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1084" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>1.185</v>
+      </c>
+      <c r="G1084" t="n">
+        <v>1.896</v>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1084" t="inlineStr">
+        <is>
+          <t>F17</t>
+        </is>
+      </c>
+      <c r="J1084" t="inlineStr">
+        <is>
+          <t>Trickster (intermediate). Checkmate, the single strike of the Trickster, x1.6 power at every level (on top of S): the Trickster fought 16 - 20% longer than the median attacker at C10, C13, C18 (12 - 15% after); the Papillon and the Joker who keep it stay within the band later (0.88 - 0.97 of the median). High Risk High Return x1.6 was measured too and changes nothing</t>
+        </is>
+      </c>
+      <c r="K1084" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1084" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>T041</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>Technique 32 Pursuit Stab</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1085" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>24</v>
+      </c>
+      <c r="G1085" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1085" t="inlineStr">
+        <is>
+          <t>J26</t>
+        </is>
+      </c>
+      <c r="J1085" t="inlineStr">
+        <is>
+          <t>Treasure Hunter (advanced): Pursuit Stab, her one strike with a dagger, -25% TP and x2 power. Her basic hit with a dagger does not pass a boss defence (3 damage), so with 187 TP and 38 a strike she ran dry in five turns: fights 31% longer than the median attacker at C22, C29, C34, C40; 1.01 after, and 0.89 at the late checkpoints (the Dark Lord 0.88). x1.5 leaves 1.21</t>
+        </is>
+      </c>
+      <c r="K1085" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1085" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>T042</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>Technique 32 Pursuit Stab</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1086" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>28</v>
+      </c>
+      <c r="G1086" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1086" t="inlineStr">
+        <is>
+          <t>J26</t>
+        </is>
+      </c>
+      <c r="J1086" t="inlineStr">
+        <is>
+          <t>Treasure Hunter (advanced): Pursuit Stab, her one strike with a dagger, -25% TP and x2 power. Her basic hit with a dagger does not pass a boss defence (3 damage), so with 187 TP and 38 a strike she ran dry in five turns: fights 31% longer than the median attacker at C22, C29, C34, C40; 1.01 after, and 0.89 at the late checkpoints (the Dark Lord 0.88). x1.5 leaves 1.21</t>
+        </is>
+      </c>
+      <c r="K1086" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1086" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>T043</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Technique 32 Pursuit Stab</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1087" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1087" t="n">
+        <v>24</v>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1087" t="inlineStr">
+        <is>
+          <t>J26</t>
+        </is>
+      </c>
+      <c r="J1087" t="inlineStr">
+        <is>
+          <t>Treasure Hunter (advanced): Pursuit Stab, her one strike with a dagger, -25% TP and x2 power. Her basic hit with a dagger does not pass a boss defence (3 damage), so with 187 TP and 38 a strike she ran dry in five turns: fights 31% longer than the median attacker at C22, C29, C34, C40; 1.01 after, and 0.89 at the late checkpoints (the Dark Lord 0.88). x1.5 leaves 1.21</t>
+        </is>
+      </c>
+      <c r="K1087" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1087" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>T044</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Technique 32 Pursuit Stab</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1088" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>35</v>
+      </c>
+      <c r="G1088" t="n">
+        <v>26</v>
+      </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1088" t="inlineStr">
+        <is>
+          <t>J26</t>
+        </is>
+      </c>
+      <c r="J1088" t="inlineStr">
+        <is>
+          <t>Treasure Hunter (advanced): Pursuit Stab, her one strike with a dagger, -25% TP and x2 power. Her basic hit with a dagger does not pass a boss defence (3 damage), so with 187 TP and 38 a strike she ran dry in five turns: fights 31% longer than the median attacker at C22, C29, C34, C40; 1.01 after, and 0.89 at the late checkpoints (the Dark Lord 0.88). x1.5 leaves 1.21</t>
+        </is>
+      </c>
+      <c r="K1088" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1088" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>T045</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>Technique 32 Pursuit Stab</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1089" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1089" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1089" t="n">
+        <v>28</v>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1089" t="inlineStr">
+        <is>
+          <t>J26</t>
+        </is>
+      </c>
+      <c r="J1089" t="inlineStr">
+        <is>
+          <t>Treasure Hunter (advanced): Pursuit Stab, her one strike with a dagger, -25% TP and x2 power. Her basic hit with a dagger does not pass a boss defence (3 damage), so with 187 TP and 38 a strike she ran dry in five turns: fights 31% longer than the median attacker at C22, C29, C34, C40; 1.01 after, and 0.89 at the late checkpoints (the Dark Lord 0.88). x1.5 leaves 1.21</t>
+        </is>
+      </c>
+      <c r="K1089" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1089" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>T046</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>Technique 32 Pursuit Stab</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1090" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1090" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1090" t="inlineStr">
+        <is>
+          <t>J26</t>
+        </is>
+      </c>
+      <c r="J1090" t="inlineStr">
+        <is>
+          <t>Treasure Hunter (advanced): Pursuit Stab, her one strike with a dagger, -25% TP and x2 power. Her basic hit with a dagger does not pass a boss defence (3 damage), so with 187 TP and 38 a strike she ran dry in five turns: fights 31% longer than the median attacker at C22, C29, C34, C40; 1.01 after, and 0.89 at the late checkpoints (the Dark Lord 0.88). x1.5 leaves 1.21</t>
+        </is>
+      </c>
+      <c r="K1090" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1090" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>T047</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>Technique 32 Pursuit Stab</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1091" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1091" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1091" t="inlineStr">
+        <is>
+          <t>J26</t>
+        </is>
+      </c>
+      <c r="J1091" t="inlineStr">
+        <is>
+          <t>Treasure Hunter (advanced): Pursuit Stab, her one strike with a dagger, -25% TP and x2 power. Her basic hit with a dagger does not pass a boss defence (3 damage), so with 187 TP and 38 a strike she ran dry in five turns: fights 31% longer than the median attacker at C22, C29, C34, C40; 1.01 after, and 0.89 at the late checkpoints (the Dark Lord 0.88). x1.5 leaves 1.21</t>
+        </is>
+      </c>
+      <c r="K1091" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1091" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>T048</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>Technique 32 Pursuit Stab</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1092" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1092" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1092" t="inlineStr">
+        <is>
+          <t>J26</t>
+        </is>
+      </c>
+      <c r="J1092" t="inlineStr">
+        <is>
+          <t>Treasure Hunter (advanced): Pursuit Stab, her one strike with a dagger, -25% TP and x2 power. Her basic hit with a dagger does not pass a boss defence (3 damage), so with 187 TP and 38 a strike she ran dry in five turns: fights 31% longer than the median attacker at C22, C29, C34, C40; 1.01 after, and 0.89 at the late checkpoints (the Dark Lord 0.88). x1.5 leaves 1.21</t>
+        </is>
+      </c>
+      <c r="K1092" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1092" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>T049</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>Technique 32 Pursuit Stab</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1093" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G1093" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1093" t="inlineStr">
+        <is>
+          <t>J26</t>
+        </is>
+      </c>
+      <c r="J1093" t="inlineStr">
+        <is>
+          <t>Treasure Hunter (advanced): Pursuit Stab, her one strike with a dagger, -25% TP and x2 power. Her basic hit with a dagger does not pass a boss defence (3 damage), so with 187 TP and 38 a strike she ran dry in five turns: fights 31% longer than the median attacker at C22, C29, C34, C40; 1.01 after, and 0.89 at the late checkpoints (the Dark Lord 0.88). x1.5 leaves 1.21</t>
+        </is>
+      </c>
+      <c r="K1093" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1093" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>T050</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>Technique 32 Pursuit Stab</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1094" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G1094" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1094" t="inlineStr">
+        <is>
+          <t>J26</t>
+        </is>
+      </c>
+      <c r="J1094" t="inlineStr">
+        <is>
+          <t>Treasure Hunter (advanced): Pursuit Stab, her one strike with a dagger, -25% TP and x2 power. Her basic hit with a dagger does not pass a boss defence (3 damage), so with 187 TP and 38 a strike she ran dry in five turns: fights 31% longer than the median attacker at C22, C29, C34, C40; 1.01 after, and 0.89 at the late checkpoints (the Dark Lord 0.88). x1.5 leaves 1.21</t>
+        </is>
+      </c>
+      <c r="K1094" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1094" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>T051</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>Technique 77 Enticing Love</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1095" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1095" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>F03, J29, F88</t>
+        </is>
+      </c>
+      <c r="J1095" t="inlineStr">
+        <is>
+          <t>Mistress (advanced): fights 16 - 18% longer than the median attacker at C22, C29, C34, C40 (her TP spent on Enticing Love). Enticing Love -25% TP and Hard Whipping, her single whip strike, x1.6 power: 1.07 after. Hard Whipping alone leaves 1.16. At the late checkpoints she is already within the band (1.01)</t>
+        </is>
+      </c>
+      <c r="K1095" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1095" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>T052</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>Technique 77 Enticing Love</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1096" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>34</v>
+      </c>
+      <c r="G1096" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1096" t="inlineStr">
+        <is>
+          <t>F03, J29, F88</t>
+        </is>
+      </c>
+      <c r="J1096" t="inlineStr">
+        <is>
+          <t>Mistress (advanced): fights 16 - 18% longer than the median attacker at C22, C29, C34, C40 (her TP spent on Enticing Love). Enticing Love -25% TP and Hard Whipping, her single whip strike, x1.6 power: 1.07 after. Hard Whipping alone leaves 1.16. At the late checkpoints she is already within the band (1.01)</t>
+        </is>
+      </c>
+      <c r="K1096" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1096" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>T053</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>Technique 77 Enticing Love</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1097" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1097" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1097" t="n">
+        <v>28</v>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1097" t="inlineStr">
+        <is>
+          <t>F03, J29, F88</t>
+        </is>
+      </c>
+      <c r="J1097" t="inlineStr">
+        <is>
+          <t>Mistress (advanced): fights 16 - 18% longer than the median attacker at C22, C29, C34, C40 (her TP spent on Enticing Love). Enticing Love -25% TP and Hard Whipping, her single whip strike, x1.6 power: 1.07 after. Hard Whipping alone leaves 1.16. At the late checkpoints she is already within the band (1.01)</t>
+        </is>
+      </c>
+      <c r="K1097" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1097" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>T054</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>Technique 77 Enticing Love</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1098" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1098" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1098" t="n">
+        <v>31</v>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1098" t="inlineStr">
+        <is>
+          <t>F03, J29, F88</t>
+        </is>
+      </c>
+      <c r="J1098" t="inlineStr">
+        <is>
+          <t>Mistress (advanced): fights 16 - 18% longer than the median attacker at C22, C29, C34, C40 (her TP spent on Enticing Love). Enticing Love -25% TP and Hard Whipping, her single whip strike, x1.6 power: 1.07 after. Hard Whipping alone leaves 1.16. At the late checkpoints she is already within the band (1.01)</t>
+        </is>
+      </c>
+      <c r="K1098" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1098" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>T055</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>Technique 77 Enticing Love</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1099" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1099" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1099" t="n">
+        <v>34</v>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1099" t="inlineStr">
+        <is>
+          <t>F03, J29, F88</t>
+        </is>
+      </c>
+      <c r="J1099" t="inlineStr">
+        <is>
+          <t>Mistress (advanced): fights 16 - 18% longer than the median attacker at C22, C29, C34, C40 (her TP spent on Enticing Love). Enticing Love -25% TP and Hard Whipping, her single whip strike, x1.6 power: 1.07 after. Hard Whipping alone leaves 1.16. At the late checkpoints she is already within the band (1.01)</t>
+        </is>
+      </c>
+      <c r="K1099" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1099" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>T056</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>Technique 76 Hard Whipping</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1100" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1100" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G1100" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1100" t="inlineStr">
+        <is>
+          <t>F03, J29, F88</t>
+        </is>
+      </c>
+      <c r="J1100" t="inlineStr">
+        <is>
+          <t>Mistress (advanced): fights 16 - 18% longer than the median attacker at C22, C29, C34, C40 (her TP spent on Enticing Love). Enticing Love -25% TP and Hard Whipping, her single whip strike, x1.6 power: 1.07 after. Hard Whipping alone leaves 1.16. At the late checkpoints she is already within the band (1.01)</t>
+        </is>
+      </c>
+      <c r="K1100" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1100" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>T057</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>Technique 76 Hard Whipping</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1101" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1101" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G1101" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1101" t="inlineStr">
+        <is>
+          <t>F03, J29, F88</t>
+        </is>
+      </c>
+      <c r="J1101" t="inlineStr">
+        <is>
+          <t>Mistress (advanced): fights 16 - 18% longer than the median attacker at C22, C29, C34, C40 (her TP spent on Enticing Love). Enticing Love -25% TP and Hard Whipping, her single whip strike, x1.6 power: 1.07 after. Hard Whipping alone leaves 1.16. At the late checkpoints she is already within the band (1.01)</t>
+        </is>
+      </c>
+      <c r="K1101" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1101" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>T058</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>Technique 76 Hard Whipping</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1102" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1102" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G1102" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1102" t="inlineStr">
+        <is>
+          <t>F03, J29, F88</t>
+        </is>
+      </c>
+      <c r="J1102" t="inlineStr">
+        <is>
+          <t>Mistress (advanced): fights 16 - 18% longer than the median attacker at C22, C29, C34, C40 (her TP spent on Enticing Love). Enticing Love -25% TP and Hard Whipping, her single whip strike, x1.6 power: 1.07 after. Hard Whipping alone leaves 1.16. At the late checkpoints she is already within the band (1.01)</t>
+        </is>
+      </c>
+      <c r="K1102" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1102" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>T059</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>Technique 76 Hard Whipping</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1103" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G1103" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1103" t="inlineStr">
+        <is>
+          <t>F03, J29, F88</t>
+        </is>
+      </c>
+      <c r="J1103" t="inlineStr">
+        <is>
+          <t>Mistress (advanced): fights 16 - 18% longer than the median attacker at C22, C29, C34, C40 (her TP spent on Enticing Love). Enticing Love -25% TP and Hard Whipping, her single whip strike, x1.6 power: 1.07 after. Hard Whipping alone leaves 1.16. At the late checkpoints she is already within the band (1.01)</t>
+        </is>
+      </c>
+      <c r="K1103" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1103" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>T060</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>Technique 76 Hard Whipping</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1104" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G1104" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1104" t="inlineStr">
+        <is>
+          <t>F03, J29, F88</t>
+        </is>
+      </c>
+      <c r="J1104" t="inlineStr">
+        <is>
+          <t>Mistress (advanced): fights 16 - 18% longer than the median attacker at C22, C29, C34, C40 (her TP spent on Enticing Love). Enticing Love -25% TP and Hard Whipping, her single whip strike, x1.6 power: 1.07 after. Hard Whipping alone leaves 1.16. At the late checkpoints she is already within the band (1.01)</t>
+        </is>
+      </c>
+      <c r="K1104" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1104" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>T061</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>Technique 76 Hard Whipping</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1105" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1105" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G1105" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1105" t="inlineStr">
+        <is>
+          <t>F03, J29, F88</t>
+        </is>
+      </c>
+      <c r="J1105" t="inlineStr">
+        <is>
+          <t>Mistress (advanced): fights 16 - 18% longer than the median attacker at C22, C29, C34, C40 (her TP spent on Enticing Love). Enticing Love -25% TP and Hard Whipping, her single whip strike, x1.6 power: 1.07 after. Hard Whipping alone leaves 1.16. At the late checkpoints she is already within the band (1.01)</t>
+        </is>
+      </c>
+      <c r="K1105" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1105" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>T062</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>Technique 76 Hard Whipping</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1106" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G1106" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1106" t="inlineStr">
+        <is>
+          <t>F03, J29, F88</t>
+        </is>
+      </c>
+      <c r="J1106" t="inlineStr">
+        <is>
+          <t>Mistress (advanced): fights 16 - 18% longer than the median attacker at C22, C29, C34, C40 (her TP spent on Enticing Love). Enticing Love -25% TP and Hard Whipping, her single whip strike, x1.6 power: 1.07 after. Hard Whipping alone leaves 1.16. At the late checkpoints she is already within the band (1.01)</t>
+        </is>
+      </c>
+      <c r="K1106" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1106" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>T063</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>Technique 76 Hard Whipping</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1107" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G1107" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1107" t="inlineStr">
+        <is>
+          <t>F03, J29, F88</t>
+        </is>
+      </c>
+      <c r="J1107" t="inlineStr">
+        <is>
+          <t>Mistress (advanced): fights 16 - 18% longer than the median attacker at C22, C29, C34, C40 (her TP spent on Enticing Love). Enticing Love -25% TP and Hard Whipping, her single whip strike, x1.6 power: 1.07 after. Hard Whipping alone leaves 1.16. At the late checkpoints she is already within the band (1.01)</t>
+        </is>
+      </c>
+      <c r="K1107" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1107" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>T064</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>Technique 76 Hard Whipping</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1108" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1108" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G1108" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1108" t="inlineStr">
+        <is>
+          <t>F03, J29, F88</t>
+        </is>
+      </c>
+      <c r="J1108" t="inlineStr">
+        <is>
+          <t>Mistress (advanced): fights 16 - 18% longer than the median attacker at C22, C29, C34, C40 (her TP spent on Enticing Love). Enticing Love -25% TP and Hard Whipping, her single whip strike, x1.6 power: 1.07 after. Hard Whipping alone leaves 1.16. At the late checkpoints she is already within the band (1.01)</t>
+        </is>
+      </c>
+      <c r="K1108" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1108" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>T065</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>Technique 76 Hard Whipping</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1109" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1109" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G1109" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1109" t="inlineStr">
+        <is>
+          <t>F03, J29, F88</t>
+        </is>
+      </c>
+      <c r="J1109" t="inlineStr">
+        <is>
+          <t>Mistress (advanced): fights 16 - 18% longer than the median attacker at C22, C29, C34, C40 (her TP spent on Enticing Love). Enticing Love -25% TP and Hard Whipping, her single whip strike, x1.6 power: 1.07 after. Hard Whipping alone leaves 1.16. At the late checkpoints she is already within the band (1.01)</t>
+        </is>
+      </c>
+      <c r="K1109" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1109" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>T066</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>Magic 226 Circle Brave</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>effect 161 (party ATK)</t>
+        </is>
+      </c>
+      <c r="E1110" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1110" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G1110" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1110" t="inlineStr">
+        <is>
+          <t>J23</t>
+        </is>
+      </c>
+      <c r="J1110" t="inlineStr">
+        <is>
+          <t>Sage (advanced): the weakest support in the same place of the party (wins in the contested fights C29, C40: 30 / 62% against 55 - 92% for the Bishop and the Etoile). Her party buffs Circle Brave and Circle Protect x1.6 (0.08 - 0.16 to 0.13 - 0.26, the range of the single-target Brave and Protect of the Valkyrie line): C40 62 to 85%, fights 1.39 to 1.27 of the median. Prism Dawn x1.6 changes nothing (she seldom attacks). C29 is the heal wall of Calliope, which needs damage, not buffs</t>
+        </is>
+      </c>
+      <c r="K1110" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1110" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>T067</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>Magic 226 Circle Brave</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>effect 161 (party ATK)</t>
+        </is>
+      </c>
+      <c r="E1111" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1111" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1111" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1111" t="inlineStr">
+        <is>
+          <t>J23</t>
+        </is>
+      </c>
+      <c r="J1111" t="inlineStr">
+        <is>
+          <t>Sage (advanced): the weakest support in the same place of the party (wins in the contested fights C29, C40: 30 / 62% against 55 - 92% for the Bishop and the Etoile). Her party buffs Circle Brave and Circle Protect x1.6 (0.08 - 0.16 to 0.13 - 0.26, the range of the single-target Brave and Protect of the Valkyrie line): C40 62 to 85%, fights 1.39 to 1.27 of the median. Prism Dawn x1.6 changes nothing (she seldom attacks). C29 is the heal wall of Calliope, which needs damage, not buffs</t>
+        </is>
+      </c>
+      <c r="K1111" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1111" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>T068</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>Magic 226 Circle Brave</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>effect 161 (party ATK)</t>
+        </is>
+      </c>
+      <c r="E1112" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1112" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G1112" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1112" t="inlineStr">
+        <is>
+          <t>J23</t>
+        </is>
+      </c>
+      <c r="J1112" t="inlineStr">
+        <is>
+          <t>Sage (advanced): the weakest support in the same place of the party (wins in the contested fights C29, C40: 30 / 62% against 55 - 92% for the Bishop and the Etoile). Her party buffs Circle Brave and Circle Protect x1.6 (0.08 - 0.16 to 0.13 - 0.26, the range of the single-target Brave and Protect of the Valkyrie line): C40 62 to 85%, fights 1.39 to 1.27 of the median. Prism Dawn x1.6 changes nothing (she seldom attacks). C29 is the heal wall of Calliope, which needs damage, not buffs</t>
+        </is>
+      </c>
+      <c r="K1112" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1112" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>T069</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>Magic 226 Circle Brave</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>effect 161 (party ATK)</t>
+        </is>
+      </c>
+      <c r="E1113" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1113" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G1113" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1113" t="inlineStr">
+        <is>
+          <t>J23</t>
+        </is>
+      </c>
+      <c r="J1113" t="inlineStr">
+        <is>
+          <t>Sage (advanced): the weakest support in the same place of the party (wins in the contested fights C29, C40: 30 / 62% against 55 - 92% for the Bishop and the Etoile). Her party buffs Circle Brave and Circle Protect x1.6 (0.08 - 0.16 to 0.13 - 0.26, the range of the single-target Brave and Protect of the Valkyrie line): C40 62 to 85%, fights 1.39 to 1.27 of the median. Prism Dawn x1.6 changes nothing (she seldom attacks). C29 is the heal wall of Calliope, which needs damage, not buffs</t>
+        </is>
+      </c>
+      <c r="K1113" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1113" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>T070</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>Magic 226 Circle Brave</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>effect 161 (party ATK)</t>
+        </is>
+      </c>
+      <c r="E1114" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1114" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G1114" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1114" t="inlineStr">
+        <is>
+          <t>J23</t>
+        </is>
+      </c>
+      <c r="J1114" t="inlineStr">
+        <is>
+          <t>Sage (advanced): the weakest support in the same place of the party (wins in the contested fights C29, C40: 30 / 62% against 55 - 92% for the Bishop and the Etoile). Her party buffs Circle Brave and Circle Protect x1.6 (0.08 - 0.16 to 0.13 - 0.26, the range of the single-target Brave and Protect of the Valkyrie line): C40 62 to 85%, fights 1.39 to 1.27 of the median. Prism Dawn x1.6 changes nothing (she seldom attacks). C29 is the heal wall of Calliope, which needs damage, not buffs</t>
+        </is>
+      </c>
+      <c r="K1114" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1114" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>T071</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>Magic 227 Circle Protect</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>effect 162 (party DEF)</t>
+        </is>
+      </c>
+      <c r="E1115" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1115" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G1115" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1115" t="inlineStr">
+        <is>
+          <t>J23</t>
+        </is>
+      </c>
+      <c r="J1115" t="inlineStr">
+        <is>
+          <t>Sage (advanced): the weakest support in the same place of the party (wins in the contested fights C29, C40: 30 / 62% against 55 - 92% for the Bishop and the Etoile). Her party buffs Circle Brave and Circle Protect x1.6 (0.08 - 0.16 to 0.13 - 0.26, the range of the single-target Brave and Protect of the Valkyrie line): C40 62 to 85%, fights 1.39 to 1.27 of the median. Prism Dawn x1.6 changes nothing (she seldom attacks). C29 is the heal wall of Calliope, which needs damage, not buffs</t>
+        </is>
+      </c>
+      <c r="K1115" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1115" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>T072</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>Magic 227 Circle Protect</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>effect 162 (party DEF)</t>
+        </is>
+      </c>
+      <c r="E1116" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1116" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1116" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1116" t="inlineStr">
+        <is>
+          <t>J23</t>
+        </is>
+      </c>
+      <c r="J1116" t="inlineStr">
+        <is>
+          <t>Sage (advanced): the weakest support in the same place of the party (wins in the contested fights C29, C40: 30 / 62% against 55 - 92% for the Bishop and the Etoile). Her party buffs Circle Brave and Circle Protect x1.6 (0.08 - 0.16 to 0.13 - 0.26, the range of the single-target Brave and Protect of the Valkyrie line): C40 62 to 85%, fights 1.39 to 1.27 of the median. Prism Dawn x1.6 changes nothing (she seldom attacks). C29 is the heal wall of Calliope, which needs damage, not buffs</t>
+        </is>
+      </c>
+      <c r="K1116" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1116" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>T073</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>Magic 227 Circle Protect</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>effect 162 (party DEF)</t>
+        </is>
+      </c>
+      <c r="E1117" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1117" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G1117" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1117" t="inlineStr">
+        <is>
+          <t>J23</t>
+        </is>
+      </c>
+      <c r="J1117" t="inlineStr">
+        <is>
+          <t>Sage (advanced): the weakest support in the same place of the party (wins in the contested fights C29, C40: 30 / 62% against 55 - 92% for the Bishop and the Etoile). Her party buffs Circle Brave and Circle Protect x1.6 (0.08 - 0.16 to 0.13 - 0.26, the range of the single-target Brave and Protect of the Valkyrie line): C40 62 to 85%, fights 1.39 to 1.27 of the median. Prism Dawn x1.6 changes nothing (she seldom attacks). C29 is the heal wall of Calliope, which needs damage, not buffs</t>
+        </is>
+      </c>
+      <c r="K1117" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1117" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>T074</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>Magic 227 Circle Protect</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>effect 162 (party DEF)</t>
+        </is>
+      </c>
+      <c r="E1118" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1118" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G1118" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1118" t="inlineStr">
+        <is>
+          <t>J23</t>
+        </is>
+      </c>
+      <c r="J1118" t="inlineStr">
+        <is>
+          <t>Sage (advanced): the weakest support in the same place of the party (wins in the contested fights C29, C40: 30 / 62% against 55 - 92% for the Bishop and the Etoile). Her party buffs Circle Brave and Circle Protect x1.6 (0.08 - 0.16 to 0.13 - 0.26, the range of the single-target Brave and Protect of the Valkyrie line): C40 62 to 85%, fights 1.39 to 1.27 of the median. Prism Dawn x1.6 changes nothing (she seldom attacks). C29 is the heal wall of Calliope, which needs damage, not buffs</t>
+        </is>
+      </c>
+      <c r="K1118" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1118" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>T075</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>Magic 227 Circle Protect</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>effect 162 (party DEF)</t>
+        </is>
+      </c>
+      <c r="E1119" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1119" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G1119" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1119" t="inlineStr">
+        <is>
+          <t>J23</t>
+        </is>
+      </c>
+      <c r="J1119" t="inlineStr">
+        <is>
+          <t>Sage (advanced): the weakest support in the same place of the party (wins in the contested fights C29, C40: 30 / 62% against 55 - 92% for the Bishop and the Etoile). Her party buffs Circle Brave and Circle Protect x1.6 (0.08 - 0.16 to 0.13 - 0.26, the range of the single-target Brave and Protect of the Valkyrie line): C40 62 to 85%, fights 1.39 to 1.27 of the median. Prism Dawn x1.6 changes nothing (she seldom attacks). C29 is the heal wall of Calliope, which needs damage, not buffs</t>
+        </is>
+      </c>
+      <c r="K1119" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1119" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -60283,7 +60283,7 @@
       </c>
       <c r="L1075" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -60339,7 +60339,7 @@
       </c>
       <c r="L1076" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -60395,7 +60395,7 @@
       </c>
       <c r="L1077" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -60451,7 +60451,7 @@
       </c>
       <c r="L1078" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -60507,7 +60507,7 @@
       </c>
       <c r="L1079" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -60563,7 +60563,7 @@
       </c>
       <c r="L1080" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -60619,7 +60619,7 @@
       </c>
       <c r="L1081" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -60675,7 +60675,7 @@
       </c>
       <c r="L1082" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -60731,7 +60731,7 @@
       </c>
       <c r="L1083" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -60787,7 +60787,7 @@
       </c>
       <c r="L1084" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -60843,7 +60843,7 @@
       </c>
       <c r="L1085" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -60899,7 +60899,7 @@
       </c>
       <c r="L1086" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -60955,7 +60955,7 @@
       </c>
       <c r="L1087" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -61011,7 +61011,7 @@
       </c>
       <c r="L1088" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -61067,7 +61067,7 @@
       </c>
       <c r="L1089" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -61123,7 +61123,7 @@
       </c>
       <c r="L1090" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -61179,7 +61179,7 @@
       </c>
       <c r="L1091" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -61235,7 +61235,7 @@
       </c>
       <c r="L1092" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -61291,7 +61291,7 @@
       </c>
       <c r="L1093" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -61347,7 +61347,7 @@
       </c>
       <c r="L1094" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -61403,7 +61403,7 @@
       </c>
       <c r="L1095" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -61459,7 +61459,7 @@
       </c>
       <c r="L1096" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -61515,7 +61515,7 @@
       </c>
       <c r="L1097" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -61571,7 +61571,7 @@
       </c>
       <c r="L1098" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -61627,7 +61627,7 @@
       </c>
       <c r="L1099" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -61683,7 +61683,7 @@
       </c>
       <c r="L1100" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -61739,7 +61739,7 @@
       </c>
       <c r="L1101" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -61795,7 +61795,7 @@
       </c>
       <c r="L1102" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -61851,7 +61851,7 @@
       </c>
       <c r="L1103" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -61907,7 +61907,7 @@
       </c>
       <c r="L1104" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -61963,7 +61963,7 @@
       </c>
       <c r="L1105" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -62019,7 +62019,7 @@
       </c>
       <c r="L1106" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -62075,7 +62075,7 @@
       </c>
       <c r="L1107" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -62131,7 +62131,7 @@
       </c>
       <c r="L1108" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -62187,7 +62187,7 @@
       </c>
       <c r="L1109" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -62243,7 +62243,7 @@
       </c>
       <c r="L1110" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -62299,7 +62299,7 @@
       </c>
       <c r="L1111" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -62355,7 +62355,7 @@
       </c>
       <c r="L1112" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -62411,7 +62411,7 @@
       </c>
       <c r="L1113" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -62467,7 +62467,7 @@
       </c>
       <c r="L1114" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -62523,7 +62523,7 @@
       </c>
       <c r="L1115" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -62579,7 +62579,7 @@
       </c>
       <c r="L1116" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -62635,7 +62635,7 @@
       </c>
       <c r="L1117" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -62691,7 +62691,7 @@
       </c>
       <c r="L1118" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -62747,7 +62747,7 @@
       </c>
       <c r="L1119" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1119"/>
+  <dimension ref="A1:L1207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62751,6 +62751,4934 @@
         </is>
       </c>
     </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>X001</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>Magic 219 Fire Scroll</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1120" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1120" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G1120" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1120" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1120" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1120" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1120" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>X002</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>Magic 219 Fire Scroll</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1121" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1121" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G1121" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1121" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1121" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1121" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1121" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>X003</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>Magic 219 Fire Scroll</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1122" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1122" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G1122" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1122" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1122" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1122" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1122" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>X004</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>Magic 219 Fire Scroll</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1123" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1123" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G1123" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="H1123" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1123" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1123" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1123" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1123" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>X005</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>Magic 219 Fire Scroll</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1124" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1124" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G1124" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H1124" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1124" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1124" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1124" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1124" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>X006</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>Magic 220 Water Scroll</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1125" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1125" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G1125" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H1125" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1125" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1125" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1125" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1125" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>X007</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>Magic 220 Water Scroll</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1126" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1126" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G1126" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H1126" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1126" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1126" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1126" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1126" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>X008</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>Magic 220 Water Scroll</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1127" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1127" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G1127" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H1127" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1127" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1127" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1127" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1127" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>X009</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>Magic 220 Water Scroll</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1128" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1128" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G1128" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="H1128" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1128" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1128" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1128" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1128" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>X010</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>Magic 220 Water Scroll</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1129" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1129" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G1129" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H1129" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1129" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1129" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1129" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1129" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>X011</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>Magic 222 Wind Scroll</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1130" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1130" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G1130" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H1130" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1130" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1130" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1130" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1130" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>X012</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>Magic 222 Wind Scroll</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1131" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1131" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G1131" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H1131" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1131" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1131" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1131" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1131" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>X013</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>Magic 222 Wind Scroll</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1132" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1132" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G1132" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H1132" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1132" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1132" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1132" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1132" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>X014</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>Magic 222 Wind Scroll</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1133" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1133" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G1133" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="H1133" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1133" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1133" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1133" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1133" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>X015</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>Magic 222 Wind Scroll</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1134" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1134" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G1134" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H1134" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1134" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1134" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1134" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1134" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>X016</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>Magic 223 Earth Scroll</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1135" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1135" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G1135" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H1135" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1135" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1135" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1135" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1135" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>X017</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>Magic 223 Earth Scroll</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1136" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1136" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G1136" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H1136" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1136" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1136" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1136" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1136" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>X018</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>Magic 223 Earth Scroll</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1137" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1137" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G1137" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1137" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1137" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1137" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1137" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>X019</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>Magic 223 Earth Scroll</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1138" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1138" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G1138" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="H1138" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1138" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1138" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1138" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1138" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>X020</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>Magic 223 Earth Scroll</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1139" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1139" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G1139" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H1139" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1139" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1139" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1139" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1139" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>X021</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Magic 221 Lightning Scroll</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1140" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1140" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G1140" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H1140" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1140" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1140" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1140" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1140" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>X022</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>Magic 221 Lightning Scroll</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1141" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1141" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G1141" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H1141" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1141" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1141" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1141" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1141" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>X023</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>Magic 221 Lightning Scroll</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1142" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1142" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G1142" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H1142" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1142" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1142" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1142" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1142" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>X024</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>Magic 221 Lightning Scroll</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1143" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1143" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G1143" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="H1143" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1143" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1143" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1143" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1143" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>X025</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>Magic 221 Lightning Scroll</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>effect 138</t>
+        </is>
+      </c>
+      <c r="E1144" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1144" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G1144" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H1144" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1144" t="inlineStr">
+        <is>
+          <t>F62, J27</t>
+        </is>
+      </c>
+      <c r="J1144" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): the scrolls dealt 44 - 51% of Ninja Piledriver; their share of the target max HP x1.5 brings them to 66 - 77% (x2 made Fire Scroll pass Ninja Piledriver; the cap x2 changed nothing). Their debuff, the reason to cast them, is kept</t>
+        </is>
+      </c>
+      <c r="K1144" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1144" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>X026</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>Magic 164 Soul Absorb</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>effect 1</t>
+        </is>
+      </c>
+      <c r="E1145" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1145" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1145" t="n">
+        <v>55</v>
+      </c>
+      <c r="H1145" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1145" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="J1145" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 41% of Blood Absorb, the other drain of the Witch; magic power x2.5 brings it to 68%, the TP drain kept</t>
+        </is>
+      </c>
+      <c r="K1145" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1145" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>X027</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>Magic 164 Soul Absorb</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>effect 1</t>
+        </is>
+      </c>
+      <c r="E1146" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1146" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1146" t="n">
+        <v>75</v>
+      </c>
+      <c r="H1146" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1146" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="J1146" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 41% of Blood Absorb, the other drain of the Witch; magic power x2.5 brings it to 68%, the TP drain kept</t>
+        </is>
+      </c>
+      <c r="K1146" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1146" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>X028</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>Magic 164 Soul Absorb</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>effect 1</t>
+        </is>
+      </c>
+      <c r="E1147" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1147" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1147" t="n">
+        <v>95</v>
+      </c>
+      <c r="H1147" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1147" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="J1147" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 41% of Blood Absorb, the other drain of the Witch; magic power x2.5 brings it to 68%, the TP drain kept</t>
+        </is>
+      </c>
+      <c r="K1147" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1147" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>X029</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>Magic 164 Soul Absorb</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>effect 1</t>
+        </is>
+      </c>
+      <c r="E1148" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1148" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1148" t="n">
+        <v>115</v>
+      </c>
+      <c r="H1148" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1148" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="J1148" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 41% of Blood Absorb, the other drain of the Witch; magic power x2.5 brings it to 68%, the TP drain kept</t>
+        </is>
+      </c>
+      <c r="K1148" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1148" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>X030</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>Magic 164 Soul Absorb</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>effect 1</t>
+        </is>
+      </c>
+      <c r="E1149" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1149" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1149" t="n">
+        <v>135</v>
+      </c>
+      <c r="H1149" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1149" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="J1149" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 41% of Blood Absorb, the other drain of the Witch; magic power x2.5 brings it to 68%, the TP drain kept</t>
+        </is>
+      </c>
+      <c r="K1149" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1149" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>X031</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>Magic 164 Soul Absorb</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>effect 1</t>
+        </is>
+      </c>
+      <c r="E1150" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1150" t="n">
+        <v>60</v>
+      </c>
+      <c r="G1150" t="n">
+        <v>150</v>
+      </c>
+      <c r="H1150" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1150" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="J1150" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 41% of Blood Absorb, the other drain of the Witch; magic power x2.5 brings it to 68%, the TP drain kept</t>
+        </is>
+      </c>
+      <c r="K1150" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1150" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>X032</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>Magic 164 Soul Absorb</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>effect 1</t>
+        </is>
+      </c>
+      <c r="E1151" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1151" t="n">
+        <v>66</v>
+      </c>
+      <c r="G1151" t="n">
+        <v>165</v>
+      </c>
+      <c r="H1151" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1151" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="J1151" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 41% of Blood Absorb, the other drain of the Witch; magic power x2.5 brings it to 68%, the TP drain kept</t>
+        </is>
+      </c>
+      <c r="K1151" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1151" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>X033</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>Magic 164 Soul Absorb</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>effect 1</t>
+        </is>
+      </c>
+      <c r="E1152" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1152" t="n">
+        <v>72</v>
+      </c>
+      <c r="G1152" t="n">
+        <v>180</v>
+      </c>
+      <c r="H1152" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1152" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="J1152" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 41% of Blood Absorb, the other drain of the Witch; magic power x2.5 brings it to 68%, the TP drain kept</t>
+        </is>
+      </c>
+      <c r="K1152" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1152" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>X034</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>Magic 164 Soul Absorb</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>effect 1</t>
+        </is>
+      </c>
+      <c r="E1153" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1153" t="n">
+        <v>78</v>
+      </c>
+      <c r="G1153" t="n">
+        <v>195</v>
+      </c>
+      <c r="H1153" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1153" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="J1153" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 41% of Blood Absorb, the other drain of the Witch; magic power x2.5 brings it to 68%, the TP drain kept</t>
+        </is>
+      </c>
+      <c r="K1153" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1153" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>X035</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>Magic 164 Soul Absorb</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>effect 1</t>
+        </is>
+      </c>
+      <c r="E1154" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1154" t="n">
+        <v>82</v>
+      </c>
+      <c r="G1154" t="n">
+        <v>205</v>
+      </c>
+      <c r="H1154" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1154" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="J1154" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 41% of Blood Absorb, the other drain of the Witch; magic power x2.5 brings it to 68%, the TP drain kept</t>
+        </is>
+      </c>
+      <c r="K1154" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1154" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>X036</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>Technique 14 Blood Drain</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1155" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1155" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="G1155" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1155" t="inlineStr">
+        <is>
+          <t>F31</t>
+        </is>
+      </c>
+      <c r="J1155" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 56% of the best strike of the Dark Lord; +0.6 power at every level (it was -0.26 to +0.10) brings it to 69%, the HP drain kept</t>
+        </is>
+      </c>
+      <c r="K1155" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1155" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>X037</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>Technique 14 Blood Drain</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1156" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1156" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="G1156" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H1156" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1156" t="inlineStr">
+        <is>
+          <t>F31</t>
+        </is>
+      </c>
+      <c r="J1156" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 56% of the best strike of the Dark Lord; +0.6 power at every level (it was -0.26 to +0.10) brings it to 69%, the HP drain kept</t>
+        </is>
+      </c>
+      <c r="K1156" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1156" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>X038</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>Technique 14 Blood Drain</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1157" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1157" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="G1157" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H1157" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1157" t="inlineStr">
+        <is>
+          <t>F31</t>
+        </is>
+      </c>
+      <c r="J1157" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 56% of the best strike of the Dark Lord; +0.6 power at every level (it was -0.26 to +0.10) brings it to 69%, the HP drain kept</t>
+        </is>
+      </c>
+      <c r="K1157" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1157" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>X039</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Technique 14 Blood Drain</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1158" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1158" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="G1158" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H1158" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1158" t="inlineStr">
+        <is>
+          <t>F31</t>
+        </is>
+      </c>
+      <c r="J1158" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 56% of the best strike of the Dark Lord; +0.6 power at every level (it was -0.26 to +0.10) brings it to 69%, the HP drain kept</t>
+        </is>
+      </c>
+      <c r="K1158" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1158" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>X040</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>Technique 14 Blood Drain</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1159" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1159" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="G1159" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1159" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1159" t="inlineStr">
+        <is>
+          <t>F31</t>
+        </is>
+      </c>
+      <c r="J1159" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 56% of the best strike of the Dark Lord; +0.6 power at every level (it was -0.26 to +0.10) brings it to 69%, the HP drain kept</t>
+        </is>
+      </c>
+      <c r="K1159" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1159" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>X041</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>Technique 14 Blood Drain</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1160" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1160" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G1160" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H1160" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1160" t="inlineStr">
+        <is>
+          <t>F31</t>
+        </is>
+      </c>
+      <c r="J1160" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 56% of the best strike of the Dark Lord; +0.6 power at every level (it was -0.26 to +0.10) brings it to 69%, the HP drain kept</t>
+        </is>
+      </c>
+      <c r="K1160" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1160" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>X042</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>Technique 14 Blood Drain</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1161" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1161" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G1161" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H1161" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1161" t="inlineStr">
+        <is>
+          <t>F31</t>
+        </is>
+      </c>
+      <c r="J1161" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 56% of the best strike of the Dark Lord; +0.6 power at every level (it was -0.26 to +0.10) brings it to 69%, the HP drain kept</t>
+        </is>
+      </c>
+      <c r="K1161" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1161" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>X043</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>Technique 14 Blood Drain</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1162" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1162" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G1162" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1162" t="inlineStr">
+        <is>
+          <t>F31</t>
+        </is>
+      </c>
+      <c r="J1162" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 56% of the best strike of the Dark Lord; +0.6 power at every level (it was -0.26 to +0.10) brings it to 69%, the HP drain kept</t>
+        </is>
+      </c>
+      <c r="K1162" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1162" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>X044</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>Technique 14 Blood Drain</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1163" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1163" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G1163" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1163" t="inlineStr">
+        <is>
+          <t>F31</t>
+        </is>
+      </c>
+      <c r="J1163" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 56% of the best strike of the Dark Lord; +0.6 power at every level (it was -0.26 to +0.10) brings it to 69%, the HP drain kept</t>
+        </is>
+      </c>
+      <c r="K1163" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1163" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>X045</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>Technique 14 Blood Drain</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1164" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1164" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1164" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1164" t="inlineStr">
+        <is>
+          <t>F31</t>
+        </is>
+      </c>
+      <c r="J1164" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 56% of the best strike of the Dark Lord; +0.6 power at every level (it was -0.26 to +0.10) brings it to 69%, the HP drain kept</t>
+        </is>
+      </c>
+      <c r="K1164" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1164" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>X046</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>Technique 15 Soul Drain</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1165" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1165" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="G1165" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1165" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="J1165" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 56%; +0.6 power at every level (it was -0.35 to 0) brings it to 65%, the TP drain kept</t>
+        </is>
+      </c>
+      <c r="K1165" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1165" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>X047</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Technique 15 Soul Drain</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1166" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1166" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="G1166" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H1166" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1166" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="J1166" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 56%; +0.6 power at every level (it was -0.35 to 0) brings it to 65%, the TP drain kept</t>
+        </is>
+      </c>
+      <c r="K1166" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1166" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>X048</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>Technique 15 Soul Drain</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1167" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1167" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="G1167" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H1167" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1167" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="J1167" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 56%; +0.6 power at every level (it was -0.35 to 0) brings it to 65%, the TP drain kept</t>
+        </is>
+      </c>
+      <c r="K1167" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1167" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>X049</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Technique 15 Soul Drain</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1168" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1168" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="G1168" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H1168" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1168" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="J1168" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 56%; +0.6 power at every level (it was -0.35 to 0) brings it to 65%, the TP drain kept</t>
+        </is>
+      </c>
+      <c r="K1168" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1168" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>X050</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>Technique 15 Soul Drain</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1169" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1169" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="G1169" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H1169" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1169" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="J1169" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 56%; +0.6 power at every level (it was -0.35 to 0) brings it to 65%, the TP drain kept</t>
+        </is>
+      </c>
+      <c r="K1169" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1169" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>X051</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>Technique 15 Soul Drain</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1170" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1170" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="G1170" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H1170" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1170" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="J1170" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 56%; +0.6 power at every level (it was -0.35 to 0) brings it to 65%, the TP drain kept</t>
+        </is>
+      </c>
+      <c r="K1170" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1170" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>X052</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>Technique 15 Soul Drain</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1171" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1171" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="G1171" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H1171" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1171" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="J1171" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 56%; +0.6 power at every level (it was -0.35 to 0) brings it to 65%, the TP drain kept</t>
+        </is>
+      </c>
+      <c r="K1171" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1171" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>X053</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>Technique 15 Soul Drain</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1172" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1172" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G1172" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H1172" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1172" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="J1172" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 56%; +0.6 power at every level (it was -0.35 to 0) brings it to 65%, the TP drain kept</t>
+        </is>
+      </c>
+      <c r="K1172" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1172" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>X054</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>Technique 15 Soul Drain</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1173" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1173" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G1173" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H1173" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1173" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="J1173" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 56%; +0.6 power at every level (it was -0.35 to 0) brings it to 65%, the TP drain kept</t>
+        </is>
+      </c>
+      <c r="K1173" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1173" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>X055</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>Technique 15 Soul Drain</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1174" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1174" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H1174" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1174" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="J1174" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 56%; +0.6 power at every level (it was -0.35 to 0) brings it to 65%, the TP drain kept</t>
+        </is>
+      </c>
+      <c r="K1174" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1174" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>X056</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>Technique 91 Life Bringer</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1175" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1175" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="G1175" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1175" t="inlineStr">
+        <is>
+          <t>F72, F33</t>
+        </is>
+      </c>
+      <c r="J1175" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 41% of the best strike of the Joker; +0.7 power at every level (it was -0.12 to +0.10) brings it to 76%, the max HP cut kept</t>
+        </is>
+      </c>
+      <c r="K1175" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1175" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>X057</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>Technique 91 Life Bringer</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1176" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1176" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G1176" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H1176" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1176" t="inlineStr">
+        <is>
+          <t>F72, F33</t>
+        </is>
+      </c>
+      <c r="J1176" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 41% of the best strike of the Joker; +0.7 power at every level (it was -0.12 to +0.10) brings it to 76%, the max HP cut kept</t>
+        </is>
+      </c>
+      <c r="K1176" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1176" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>X058</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Technique 91 Life Bringer</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1177" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1177" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G1177" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H1177" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1177" t="inlineStr">
+        <is>
+          <t>F72, F33</t>
+        </is>
+      </c>
+      <c r="J1177" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 41% of the best strike of the Joker; +0.7 power at every level (it was -0.12 to +0.10) brings it to 76%, the max HP cut kept</t>
+        </is>
+      </c>
+      <c r="K1177" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1177" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>X059</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>Technique 91 Life Bringer</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1178" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1178" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G1178" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H1178" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1178" t="inlineStr">
+        <is>
+          <t>F72, F33</t>
+        </is>
+      </c>
+      <c r="J1178" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 41% of the best strike of the Joker; +0.7 power at every level (it was -0.12 to +0.10) brings it to 76%, the max HP cut kept</t>
+        </is>
+      </c>
+      <c r="K1178" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1178" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>X060</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Technique 91 Life Bringer</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>effect 26</t>
+        </is>
+      </c>
+      <c r="E1179" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1179" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1179" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H1179" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1179" t="inlineStr">
+        <is>
+          <t>F72, F33</t>
+        </is>
+      </c>
+      <c r="J1179" t="inlineStr">
+        <is>
+          <t>T06, tools/skill_worth.py (each attacking skill against the best option of the same member, top level, boss and random battles of the stages): 41% of the best strike of the Joker; +0.7 power at every level (it was -0.12 to +0.10) brings it to 76%, the max HP cut kept</t>
+        </is>
+      </c>
+      <c r="K1179" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1179" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>X061</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Magic 193 Brave</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>effect 161 (ATK)</t>
+        </is>
+      </c>
+      <c r="E1180" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1180" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1180" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H1180" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1180" t="inlineStr">
+        <is>
+          <t>F35</t>
+        </is>
+      </c>
+      <c r="J1180" t="inlineStr">
+        <is>
+          <t>A single-target buff weaker than the party ones it does not stack with (War Cry 0.18, Circle Brave 0.256 on the whole party): x2 (0.20 - 0.44) makes it the buff of the main attacker, as the guide uses it (Brave on Yae)</t>
+        </is>
+      </c>
+      <c r="K1180" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1180" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>X062</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>Magic 193 Brave</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>effect 161 (ATK)</t>
+        </is>
+      </c>
+      <c r="E1181" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1181" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G1181" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H1181" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1181" t="inlineStr">
+        <is>
+          <t>F35</t>
+        </is>
+      </c>
+      <c r="J1181" t="inlineStr">
+        <is>
+          <t>A single-target buff weaker than the party ones it does not stack with (War Cry 0.18, Circle Brave 0.256 on the whole party): x2 (0.20 - 0.44) makes it the buff of the main attacker, as the guide uses it (Brave on Yae)</t>
+        </is>
+      </c>
+      <c r="K1181" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1181" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>X063</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>Magic 193 Brave</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>effect 161 (ATK)</t>
+        </is>
+      </c>
+      <c r="E1182" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1182" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G1182" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1182" t="inlineStr">
+        <is>
+          <t>F35</t>
+        </is>
+      </c>
+      <c r="J1182" t="inlineStr">
+        <is>
+          <t>A single-target buff weaker than the party ones it does not stack with (War Cry 0.18, Circle Brave 0.256 on the whole party): x2 (0.20 - 0.44) makes it the buff of the main attacker, as the guide uses it (Brave on Yae)</t>
+        </is>
+      </c>
+      <c r="K1182" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1182" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>X064</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>Magic 193 Brave</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>effect 161 (ATK)</t>
+        </is>
+      </c>
+      <c r="E1183" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1183" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="G1183" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H1183" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1183" t="inlineStr">
+        <is>
+          <t>F35</t>
+        </is>
+      </c>
+      <c r="J1183" t="inlineStr">
+        <is>
+          <t>A single-target buff weaker than the party ones it does not stack with (War Cry 0.18, Circle Brave 0.256 on the whole party): x2 (0.20 - 0.44) makes it the buff of the main attacker, as the guide uses it (Brave on Yae)</t>
+        </is>
+      </c>
+      <c r="K1183" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1183" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>X065</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Magic 193 Brave</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>effect 161 (ATK)</t>
+        </is>
+      </c>
+      <c r="E1184" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1184" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G1184" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H1184" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1184" t="inlineStr">
+        <is>
+          <t>F35</t>
+        </is>
+      </c>
+      <c r="J1184" t="inlineStr">
+        <is>
+          <t>A single-target buff weaker than the party ones it does not stack with (War Cry 0.18, Circle Brave 0.256 on the whole party): x2 (0.20 - 0.44) makes it the buff of the main attacker, as the guide uses it (Brave on Yae)</t>
+        </is>
+      </c>
+      <c r="K1184" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1184" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>X066</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>Magic 194 Protect</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>effect 162 (DEF)</t>
+        </is>
+      </c>
+      <c r="E1185" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1185" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1185" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H1185" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1185" t="inlineStr">
+        <is>
+          <t>F35</t>
+        </is>
+      </c>
+      <c r="J1185" t="inlineStr">
+        <is>
+          <t>The same for the single-target Protect beside Circle Protect (0.256 on the party): x2 (0.20 - 0.50), the buff of the tank</t>
+        </is>
+      </c>
+      <c r="K1185" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1185" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>X067</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>Magic 194 Protect</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>effect 162 (DEF)</t>
+        </is>
+      </c>
+      <c r="E1186" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1186" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G1186" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>F35</t>
+        </is>
+      </c>
+      <c r="J1186" t="inlineStr">
+        <is>
+          <t>The same for the single-target Protect beside Circle Protect (0.256 on the party): x2 (0.20 - 0.50), the buff of the tank</t>
+        </is>
+      </c>
+      <c r="K1186" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1186" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>X068</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Magic 194 Protect</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>effect 162 (DEF)</t>
+        </is>
+      </c>
+      <c r="E1187" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1187" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G1187" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H1187" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>F35</t>
+        </is>
+      </c>
+      <c r="J1187" t="inlineStr">
+        <is>
+          <t>The same for the single-target Protect beside Circle Protect (0.256 on the party): x2 (0.20 - 0.50), the buff of the tank</t>
+        </is>
+      </c>
+      <c r="K1187" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1187" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>X069</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>Magic 194 Protect</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>effect 162 (DEF)</t>
+        </is>
+      </c>
+      <c r="E1188" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1188" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G1188" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H1188" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>F35</t>
+        </is>
+      </c>
+      <c r="J1188" t="inlineStr">
+        <is>
+          <t>The same for the single-target Protect beside Circle Protect (0.256 on the party): x2 (0.20 - 0.50), the buff of the tank</t>
+        </is>
+      </c>
+      <c r="K1188" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1188" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>X070</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>Magic 194 Protect</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>effect 162 (DEF)</t>
+        </is>
+      </c>
+      <c r="E1189" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1189" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G1189" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1189" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1189" t="inlineStr">
+        <is>
+          <t>F35</t>
+        </is>
+      </c>
+      <c r="J1189" t="inlineStr">
+        <is>
+          <t>The same for the single-target Protect beside Circle Protect (0.256 on the party): x2 (0.20 - 0.50), the buff of the tank</t>
+        </is>
+      </c>
+      <c r="K1189" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1189" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>X071</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>Magic 200 Illusion</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>effect 102 (hits nullified)</t>
+        </is>
+      </c>
+      <c r="E1190" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1190" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1190" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1190" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1190" t="inlineStr">
+        <is>
+          <t>F44</t>
+        </is>
+      </c>
+      <c r="J1190" t="inlineStr">
+        <is>
+          <t>Two hits nullified for 30 - 46 TP against five for Shadow Clone (17 - 33 TP): 3, 4, 5 by level</t>
+        </is>
+      </c>
+      <c r="K1190" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1190" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>X072</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>Magic 200 Illusion</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>effect 102 (hits nullified)</t>
+        </is>
+      </c>
+      <c r="E1191" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1191" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1191" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1191" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1191" t="inlineStr">
+        <is>
+          <t>F44</t>
+        </is>
+      </c>
+      <c r="J1191" t="inlineStr">
+        <is>
+          <t>Two hits nullified for 30 - 46 TP against five for Shadow Clone (17 - 33 TP): 3, 4, 5 by level</t>
+        </is>
+      </c>
+      <c r="K1191" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1191" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>X073</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>Magic 200 Illusion</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>effect 102 (hits nullified)</t>
+        </is>
+      </c>
+      <c r="E1192" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1192" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1192" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1192" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1192" t="inlineStr">
+        <is>
+          <t>F44</t>
+        </is>
+      </c>
+      <c r="J1192" t="inlineStr">
+        <is>
+          <t>Two hits nullified for 30 - 46 TP against five for Shadow Clone (17 - 33 TP): 3, 4, 5 by level</t>
+        </is>
+      </c>
+      <c r="K1192" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1192" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>X074</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>Magic 216 Shadow Clone</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E1193" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1193" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G1193" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H1193" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1193" t="inlineStr">
+        <is>
+          <t>F60</t>
+        </is>
+      </c>
+      <c r="J1193" t="inlineStr">
+        <is>
+          <t>Its chant got slower with each level (0.75 to 0.53; atwiki dt2-2 page 142 notes it): 0.75 at every level</t>
+        </is>
+      </c>
+      <c r="K1193" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1193" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>X075</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>Magic 216 Shadow Clone</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E1194" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1194" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1194" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H1194" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1194" t="inlineStr">
+        <is>
+          <t>F60</t>
+        </is>
+      </c>
+      <c r="J1194" t="inlineStr">
+        <is>
+          <t>Its chant got slower with each level (0.75 to 0.53; atwiki dt2-2 page 142 notes it): 0.75 at every level</t>
+        </is>
+      </c>
+      <c r="K1194" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1194" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>X076</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>Magic 216 Shadow Clone</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E1195" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1195" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1195" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H1195" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1195" t="inlineStr">
+        <is>
+          <t>F60</t>
+        </is>
+      </c>
+      <c r="J1195" t="inlineStr">
+        <is>
+          <t>Its chant got slower with each level (0.75 to 0.53; atwiki dt2-2 page 142 notes it): 0.75 at every level</t>
+        </is>
+      </c>
+      <c r="K1195" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1195" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>X077</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Magic 216 Shadow Clone</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E1196" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1196" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G1196" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H1196" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1196" t="inlineStr">
+        <is>
+          <t>F60</t>
+        </is>
+      </c>
+      <c r="J1196" t="inlineStr">
+        <is>
+          <t>Its chant got slower with each level (0.75 to 0.53; atwiki dt2-2 page 142 notes it): 0.75 at every level</t>
+        </is>
+      </c>
+      <c r="K1196" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1196" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>X078</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>Magic 216 Shadow Clone</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>chant speed factor</t>
+        </is>
+      </c>
+      <c r="E1197" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1197" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G1197" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H1197" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1197" t="inlineStr">
+        <is>
+          <t>F60</t>
+        </is>
+      </c>
+      <c r="J1197" t="inlineStr">
+        <is>
+          <t>Its chant got slower with each level (0.75 to 0.53; atwiki dt2-2 page 142 notes it): 0.75 at every level</t>
+        </is>
+      </c>
+      <c r="K1197" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1197" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>X079</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>Magic 217 Shadow Sew</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1198" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1198" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1198" t="n">
+        <v>27</v>
+      </c>
+      <c r="H1198" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1198" t="inlineStr">
+        <is>
+          <t>F61</t>
+        </is>
+      </c>
+      <c r="J1198" t="inlineStr">
+        <is>
+          <t>It lands only on lower level targets and lasts three turns: -25% TP (the cap of the user on TP cuts)</t>
+        </is>
+      </c>
+      <c r="K1198" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1198" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>X080</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>Magic 217 Shadow Sew</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1199" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1199" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1199" t="n">
+        <v>29</v>
+      </c>
+      <c r="H1199" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1199" t="inlineStr">
+        <is>
+          <t>F61</t>
+        </is>
+      </c>
+      <c r="J1199" t="inlineStr">
+        <is>
+          <t>It lands only on lower level targets and lasts three turns: -25% TP (the cap of the user on TP cuts)</t>
+        </is>
+      </c>
+      <c r="K1199" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1199" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>X081</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>Magic 217 Shadow Sew</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1200" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1200" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1200" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1200" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1200" t="inlineStr">
+        <is>
+          <t>F61</t>
+        </is>
+      </c>
+      <c r="J1200" t="inlineStr">
+        <is>
+          <t>It lands only on lower level targets and lasts three turns: -25% TP (the cap of the user on TP cuts)</t>
+        </is>
+      </c>
+      <c r="K1200" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1200" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>X082</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>Magic 217 Shadow Sew</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1201" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1201" t="n">
+        <v>35</v>
+      </c>
+      <c r="H1201" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1201" t="inlineStr">
+        <is>
+          <t>F61</t>
+        </is>
+      </c>
+      <c r="J1201" t="inlineStr">
+        <is>
+          <t>It lands only on lower level targets and lasts three turns: -25% TP (the cap of the user on TP cuts)</t>
+        </is>
+      </c>
+      <c r="K1201" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1201" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>X083</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>Magic 217 Shadow Sew</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1202" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1202" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1202" t="n">
+        <v>39</v>
+      </c>
+      <c r="H1202" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1202" t="inlineStr">
+        <is>
+          <t>F61</t>
+        </is>
+      </c>
+      <c r="J1202" t="inlineStr">
+        <is>
+          <t>It lands only on lower level targets and lasts three turns: -25% TP (the cap of the user on TP cuts)</t>
+        </is>
+      </c>
+      <c r="K1202" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1202" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>X084</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>Magic 165 Blood Rage</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1203" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>27</v>
+      </c>
+      <c r="G1203" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1203" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1203" t="inlineStr">
+        <is>
+          <t>F34</t>
+        </is>
+      </c>
+      <c r="J1203" t="inlineStr">
+        <is>
+          <t>Max HP +20 - 50% for 6 - 10 turns, but 43 TP on a Berserker short of TP: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1203" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1203" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>X085</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Magic 165 Blood Rage</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1204" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1204" t="n">
+        <v>23</v>
+      </c>
+      <c r="H1204" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1204" t="inlineStr">
+        <is>
+          <t>F34</t>
+        </is>
+      </c>
+      <c r="J1204" t="inlineStr">
+        <is>
+          <t>Max HP +20 - 50% for 6 - 10 turns, but 43 TP on a Berserker short of TP: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1204" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1204" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>X086</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Magic 165 Blood Rage</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1205" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1205" t="n">
+        <v>35</v>
+      </c>
+      <c r="G1205" t="n">
+        <v>26</v>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1205" t="inlineStr">
+        <is>
+          <t>F34</t>
+        </is>
+      </c>
+      <c r="J1205" t="inlineStr">
+        <is>
+          <t>Max HP +20 - 50% for 6 - 10 turns, but 43 TP on a Berserker short of TP: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1205" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1205" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>X087</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>Magic 165 Blood Rage</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1206" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1206" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1206" t="n">
+        <v>29</v>
+      </c>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1206" t="inlineStr">
+        <is>
+          <t>F34</t>
+        </is>
+      </c>
+      <c r="J1206" t="inlineStr">
+        <is>
+          <t>Max HP +20 - 50% for 6 - 10 turns, but 43 TP on a Berserker short of TP: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1206" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1206" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>X088</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Magic 165 Blood Rage</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1207" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1207" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1207" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1207" t="inlineStr">
+        <is>
+          <t>F34</t>
+        </is>
+      </c>
+      <c r="J1207" t="inlineStr">
+        <is>
+          <t>Max HP +20 - 50% for 6 - 10 turns, but 43 TP on a Berserker short of TP: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1207" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1207" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -66163,7 +66163,7 @@
       </c>
       <c r="L1180" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -66219,7 +66219,7 @@
       </c>
       <c r="L1181" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -66275,7 +66275,7 @@
       </c>
       <c r="L1182" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -66331,7 +66331,7 @@
       </c>
       <c r="L1183" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -66387,7 +66387,7 @@
       </c>
       <c r="L1184" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -66443,7 +66443,7 @@
       </c>
       <c r="L1185" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -66499,7 +66499,7 @@
       </c>
       <c r="L1186" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -66555,7 +66555,7 @@
       </c>
       <c r="L1187" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -66611,7 +66611,7 @@
       </c>
       <c r="L1188" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -66667,7 +66667,7 @@
       </c>
       <c r="L1189" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -66723,7 +66723,7 @@
       </c>
       <c r="L1190" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -66779,7 +66779,7 @@
       </c>
       <c r="L1191" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -66835,7 +66835,7 @@
       </c>
       <c r="L1192" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -66891,7 +66891,7 @@
       </c>
       <c r="L1193" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -66947,7 +66947,7 @@
       </c>
       <c r="L1194" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -67003,7 +67003,7 @@
       </c>
       <c r="L1195" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -67059,7 +67059,7 @@
       </c>
       <c r="L1196" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -67115,7 +67115,7 @@
       </c>
       <c r="L1197" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -67171,7 +67171,7 @@
       </c>
       <c r="L1198" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -67227,7 +67227,7 @@
       </c>
       <c r="L1199" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -67283,7 +67283,7 @@
       </c>
       <c r="L1200" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -67339,7 +67339,7 @@
       </c>
       <c r="L1201" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -67395,7 +67395,7 @@
       </c>
       <c r="L1202" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -67451,7 +67451,7 @@
       </c>
       <c r="L1203" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -67507,7 +67507,7 @@
       </c>
       <c r="L1204" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -67563,7 +67563,7 @@
       </c>
       <c r="L1205" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -67619,7 +67619,7 @@
       </c>
       <c r="L1206" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -67675,7 +67675,7 @@
       </c>
       <c r="L1207" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1207"/>
+  <dimension ref="A1:L1244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67679,6 +67679,2080 @@
         </is>
       </c>
     </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>H001</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>effect 103 (heal power)</t>
+        </is>
+      </c>
+      <c r="E1208" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1208" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1208" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1208" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1208" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): Circle Heal healed 88 to each member at level 1 (C10, C18) where a Sachertorte heals 200 to the party; its low levels raised so it never heals less (210 - 308 at C10 - C22), the top level unchanged (600 cap, 780 at C34)</t>
+        </is>
+      </c>
+      <c r="K1208" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1208" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>H002</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>effect 103 (heal power)</t>
+        </is>
+      </c>
+      <c r="E1209" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1209" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1209" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1209" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1209" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): Circle Heal healed 88 to each member at level 1 (C10, C18) where a Sachertorte heals 200 to the party; its low levels raised so it never heals less (210 - 308 at C10 - C22), the top level unchanged (600 cap, 780 at C34)</t>
+        </is>
+      </c>
+      <c r="K1209" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1209" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>H003</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>effect 103 (heal power)</t>
+        </is>
+      </c>
+      <c r="E1210" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1210" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1210" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1210" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1210" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): Circle Heal healed 88 to each member at level 1 (C10, C18) where a Sachertorte heals 200 to the party; its low levels raised so it never heals less (210 - 308 at C10 - C22), the top level unchanged (600 cap, 780 at C34)</t>
+        </is>
+      </c>
+      <c r="K1210" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1210" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>H004</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>effect 103 (heal power)</t>
+        </is>
+      </c>
+      <c r="E1211" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1211" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1211" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1211" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1211" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): Circle Heal healed 88 to each member at level 1 (C10, C18) where a Sachertorte heals 200 to the party; its low levels raised so it never heals less (210 - 308 at C10 - C22), the top level unchanged (600 cap, 780 at C34)</t>
+        </is>
+      </c>
+      <c r="K1211" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1211" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>H005</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>effect 103 (heal power)</t>
+        </is>
+      </c>
+      <c r="E1212" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1212" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1212" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1212" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1212" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): Circle Heal healed 88 to each member at level 1 (C10, C18) where a Sachertorte heals 200 to the party; its low levels raised so it never heals less (210 - 308 at C10 - C22), the top level unchanged (600 cap, 780 at C34)</t>
+        </is>
+      </c>
+      <c r="K1212" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1212" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>H006</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>effect 103 (heal power)</t>
+        </is>
+      </c>
+      <c r="E1213" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1213" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H1213" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1213" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1213" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): Circle Heal healed 88 to each member at level 1 (C10, C18) where a Sachertorte heals 200 to the party; its low levels raised so it never heals less (210 - 308 at C10 - C22), the top level unchanged (600 cap, 780 at C34)</t>
+        </is>
+      </c>
+      <c r="K1213" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1213" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>H007</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>effect 103 (heal power)</t>
+        </is>
+      </c>
+      <c r="E1214" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1214" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1214" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1214" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1214" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1214" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): Circle Heal healed 88 to each member at level 1 (C10, C18) where a Sachertorte heals 200 to the party; its low levels raised so it never heals less (210 - 308 at C10 - C22), the top level unchanged (600 cap, 780 at C34)</t>
+        </is>
+      </c>
+      <c r="K1214" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1214" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>H008</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>effect 103 (heal power)</t>
+        </is>
+      </c>
+      <c r="E1215" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1215" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1215" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H1215" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1215" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1215" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): Circle Heal healed 88 to each member at level 1 (C10, C18) where a Sachertorte heals 200 to the party; its low levels raised so it never heals less (210 - 308 at C10 - C22), the top level unchanged (600 cap, 780 at C34)</t>
+        </is>
+      </c>
+      <c r="K1215" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1215" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>H009</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>effect 103 (heal power)</t>
+        </is>
+      </c>
+      <c r="E1216" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1216" t="n">
+        <v>13</v>
+      </c>
+      <c r="G1216" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1216" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1216" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1216" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): Circle Heal healed 88 to each member at level 1 (C10, C18) where a Sachertorte heals 200 to the party; its low levels raised so it never heals less (210 - 308 at C10 - C22), the top level unchanged (600 cap, 780 at C34)</t>
+        </is>
+      </c>
+      <c r="K1216" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1216" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>H010</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>effect 295 (heal cap)</t>
+        </is>
+      </c>
+      <c r="E1217" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1217" t="n">
+        <v>80</v>
+      </c>
+      <c r="G1217" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1217" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1217" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): Circle Heal healed 88 to each member at level 1 (C10, C18) where a Sachertorte heals 200 to the party; its low levels raised so it never heals less (210 - 308 at C10 - C22), the top level unchanged (600 cap, 780 at C34)</t>
+        </is>
+      </c>
+      <c r="K1217" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1217" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>H011</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>effect 295 (heal cap)</t>
+        </is>
+      </c>
+      <c r="E1218" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1218" t="n">
+        <v>140</v>
+      </c>
+      <c r="G1218" t="n">
+        <v>240</v>
+      </c>
+      <c r="H1218" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1218" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1218" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): Circle Heal healed 88 to each member at level 1 (C10, C18) where a Sachertorte heals 200 to the party; its low levels raised so it never heals less (210 - 308 at C10 - C22), the top level unchanged (600 cap, 780 at C34)</t>
+        </is>
+      </c>
+      <c r="K1218" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1218" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>H012</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>effect 295 (heal cap)</t>
+        </is>
+      </c>
+      <c r="E1219" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1219" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1219" t="n">
+        <v>280</v>
+      </c>
+      <c r="H1219" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1219" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1219" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): Circle Heal healed 88 to each member at level 1 (C10, C18) where a Sachertorte heals 200 to the party; its low levels raised so it never heals less (210 - 308 at C10 - C22), the top level unchanged (600 cap, 780 at C34)</t>
+        </is>
+      </c>
+      <c r="K1219" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1219" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>H013</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>effect 295 (heal cap)</t>
+        </is>
+      </c>
+      <c r="E1220" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1220" t="n">
+        <v>260</v>
+      </c>
+      <c r="G1220" t="n">
+        <v>320</v>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1220" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1220" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): Circle Heal healed 88 to each member at level 1 (C10, C18) where a Sachertorte heals 200 to the party; its low levels raised so it never heals less (210 - 308 at C10 - C22), the top level unchanged (600 cap, 780 at C34)</t>
+        </is>
+      </c>
+      <c r="K1220" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1220" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>H014</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>effect 295 (heal cap)</t>
+        </is>
+      </c>
+      <c r="E1221" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1221" t="n">
+        <v>320</v>
+      </c>
+      <c r="G1221" t="n">
+        <v>360</v>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1221" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1221" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): Circle Heal healed 88 to each member at level 1 (C10, C18) where a Sachertorte heals 200 to the party; its low levels raised so it never heals less (210 - 308 at C10 - C22), the top level unchanged (600 cap, 780 at C34)</t>
+        </is>
+      </c>
+      <c r="K1221" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1221" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>H015</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>effect 295 (heal cap)</t>
+        </is>
+      </c>
+      <c r="E1222" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1222" t="n">
+        <v>380</v>
+      </c>
+      <c r="G1222" t="n">
+        <v>400</v>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1222" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1222" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): Circle Heal healed 88 to each member at level 1 (C10, C18) where a Sachertorte heals 200 to the party; its low levels raised so it never heals less (210 - 308 at C10 - C22), the top level unchanged (600 cap, 780 at C34)</t>
+        </is>
+      </c>
+      <c r="K1222" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1222" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>H016</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>Magic 187 Heal</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1223" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1223" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1223" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1223" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1223" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): an item costs no TP and anyone can use it; the spells already heal more and sooner (Heal 1,040 at C34 against 500 for a Bagel Sandwich), so their cost comes down: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1223" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1223" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>H017</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>Magic 187 Heal</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1224" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1224" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1224" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1224" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1224" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): an item costs no TP and anyone can use it; the spells already heal more and sooner (Heal 1,040 at C34 against 500 for a Bagel Sandwich), so their cost comes down: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1224" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1224" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>H018</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>Magic 187 Heal</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1225" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1225" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1225" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1225" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1225" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1225" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): an item costs no TP and anyone can use it; the spells already heal more and sooner (Heal 1,040 at C34 against 500 for a Bagel Sandwich), so their cost comes down: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1225" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1225" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>H019</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>Magic 187 Heal</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1226" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1226" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1226" t="n">
+        <v>7</v>
+      </c>
+      <c r="H1226" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1226" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1226" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): an item costs no TP and anyone can use it; the spells already heal more and sooner (Heal 1,040 at C34 against 500 for a Bagel Sandwich), so their cost comes down: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1226" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1226" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>H020</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>Magic 187 Heal</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1227" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1227" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1227" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1227" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1227" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1227" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): an item costs no TP and anyone can use it; the spells already heal more and sooner (Heal 1,040 at C34 against 500 for a Bagel Sandwich), so their cost comes down: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1227" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1227" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>H021</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>Magic 187 Heal</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1228" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1228" t="n">
+        <v>14</v>
+      </c>
+      <c r="G1228" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1228" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1228" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1228" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): an item costs no TP and anyone can use it; the spells already heal more and sooner (Heal 1,040 at C34 against 500 for a Bagel Sandwich), so their cost comes down: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1228" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1228" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>H022</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>Magic 187 Heal</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1229" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1229" t="n">
+        <v>17</v>
+      </c>
+      <c r="G1229" t="n">
+        <v>12</v>
+      </c>
+      <c r="H1229" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1229" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1229" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): an item costs no TP and anyone can use it; the spells already heal more and sooner (Heal 1,040 at C34 against 500 for a Bagel Sandwich), so their cost comes down: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1229" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1229" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>H023</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>Magic 187 Heal</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1230" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1230" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1230" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1230" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1230" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1230" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): an item costs no TP and anyone can use it; the spells already heal more and sooner (Heal 1,040 at C34 against 500 for a Bagel Sandwich), so their cost comes down: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1230" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1230" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>H024</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>Magic 187 Heal</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1231" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1231" t="n">
+        <v>23</v>
+      </c>
+      <c r="G1231" t="n">
+        <v>17</v>
+      </c>
+      <c r="H1231" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1231" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1231" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): an item costs no TP and anyone can use it; the spells already heal more and sooner (Heal 1,040 at C34 against 500 for a Bagel Sandwich), so their cost comes down: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1231" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1231" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>H025</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>Magic 187 Heal</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1232" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1232" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1232" t="n">
+        <v>19</v>
+      </c>
+      <c r="H1232" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1232" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1232" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): an item costs no TP and anyone can use it; the spells already heal more and sooner (Heal 1,040 at C34 against 500 for a Bagel Sandwich), so their cost comes down: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1232" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1232" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>H026</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1233" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1233" t="n">
+        <v>15</v>
+      </c>
+      <c r="G1233" t="n">
+        <v>11</v>
+      </c>
+      <c r="H1233" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1233" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1233" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): an item costs no TP and anyone can use it; the spells already heal more and sooner (Heal 1,040 at C34 against 500 for a Bagel Sandwich), so their cost comes down: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1233" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1233" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>H027</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1234" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1234" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1234" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1234" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1234" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1234" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): an item costs no TP and anyone can use it; the spells already heal more and sooner (Heal 1,040 at C34 against 500 for a Bagel Sandwich), so their cost comes down: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1234" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1234" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>H028</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1235" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1235" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1235" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1235" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1235" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1235" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): an item costs no TP and anyone can use it; the spells already heal more and sooner (Heal 1,040 at C34 against 500 for a Bagel Sandwich), so their cost comes down: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1235" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1235" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>H029</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1236" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1236" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1236" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1236" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1236" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1236" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): an item costs no TP and anyone can use it; the spells already heal more and sooner (Heal 1,040 at C34 against 500 for a Bagel Sandwich), so their cost comes down: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1236" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1236" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>H030</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1237" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1237" t="n">
+        <v>35</v>
+      </c>
+      <c r="G1237" t="n">
+        <v>26</v>
+      </c>
+      <c r="H1237" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1237" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1237" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): an item costs no TP and anyone can use it; the spells already heal more and sooner (Heal 1,040 at C34 against 500 for a Bagel Sandwich), so their cost comes down: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1237" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1237" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>H031</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1238" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1238" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1238" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1238" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1238" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1238" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): an item costs no TP and anyone can use it; the spells already heal more and sooner (Heal 1,040 at C34 against 500 for a Bagel Sandwich), so their cost comes down: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1238" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1238" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>H032</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1239" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1239" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1239" t="n">
+        <v>34</v>
+      </c>
+      <c r="H1239" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1239" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1239" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): an item costs no TP and anyone can use it; the spells already heal more and sooner (Heal 1,040 at C34 against 500 for a Bagel Sandwich), so their cost comes down: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1239" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1239" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>H033</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1240" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1240" t="n">
+        <v>52</v>
+      </c>
+      <c r="G1240" t="n">
+        <v>39</v>
+      </c>
+      <c r="H1240" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1240" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1240" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): an item costs no TP and anyone can use it; the spells already heal more and sooner (Heal 1,040 at C34 against 500 for a Bagel Sandwich), so their cost comes down: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1240" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1240" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>H034</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1241" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1241" t="n">
+        <v>58</v>
+      </c>
+      <c r="G1241" t="n">
+        <v>43</v>
+      </c>
+      <c r="H1241" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1241" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1241" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): an item costs no TP and anyone can use it; the spells already heal more and sooner (Heal 1,040 at C34 against 500 for a Bagel Sandwich), so their cost comes down: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1241" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1241" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>H035</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1242" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1242" t="n">
+        <v>64</v>
+      </c>
+      <c r="G1242" t="n">
+        <v>48</v>
+      </c>
+      <c r="H1242" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1242" t="inlineStr">
+        <is>
+          <t>F21, F41, J24</t>
+        </is>
+      </c>
+      <c r="J1242" t="inlineStr">
+        <is>
+          <t>Healing spells against items (the user, 2026-10-09): an item costs no TP and anyone can use it; the spells already heal more and sooner (Heal 1,040 at C34 against 500 for a Bagel Sandwich), so their cost comes down: -25% TP</t>
+        </is>
+      </c>
+      <c r="K1242" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1242" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>H036</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>Magic 187 Heal</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>added effect 106 (kind 4)</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>empty slot</t>
+        </is>
+      </c>
+      <c r="G1243" t="inlineStr">
+        <is>
+          <t>1, 1, 1, 1, 1, 2, 2, 2, 2, 2</t>
+        </is>
+      </c>
+      <c r="H1243" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I1243" t="inlineStr">
+        <is>
+          <t>F21, F40</t>
+        </is>
+      </c>
+      <c r="J1243" t="inlineStr">
+        <is>
+          <t>Something small that items do not give, which acts only when it serves (the user, 2026-10-09): Heal also cures poison (levels 1 - 5), then poison and paralysis (6 - 10), the first entries of the cure list (FORMULAS, cures). the vanilla game already joins a heal and a cure in one action: the spell Primevil (Magic 230: effects 103, 106, 105) and the actions Military Rations Pill and Fairy Healing (EnemyAttackData 766 - 768, 772: 103 and 106); the record of a skill holds five effect slots and Heal and Circle Heal use two</t>
+        </is>
+      </c>
+      <c r="K1243" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1243" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>H037</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>Magic 188 Circle Heal</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>added effect 106 (kind 4)</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>empty slot</t>
+        </is>
+      </c>
+      <c r="G1244" t="inlineStr">
+        <is>
+          <t>1, 1, 1, 1, 1, 1, 1, 1, 1, 1</t>
+        </is>
+      </c>
+      <c r="H1244" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I1244" t="inlineStr">
+        <is>
+          <t>F21, F40</t>
+        </is>
+      </c>
+      <c r="J1244" t="inlineStr">
+        <is>
+          <t>The same for the party: Circle Heal also cures poison. the vanilla game already joins a heal and a cure in one action: the spell Primevil (Magic 230: effects 103, 106, 105) and the actions Military Rations Pill and Fairy Healing (EnemyAttackData 766 - 768, 772: 103 and 106); the record of a skill holds five effect slots and Heal and Circle Heal use two</t>
+        </is>
+      </c>
+      <c r="K1244" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1244" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -69692,7 +69692,7 @@
       </c>
       <c r="L1243" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -69749,7 +69749,7 @@
       </c>
       <c r="L1244" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1244"/>
+  <dimension ref="A1:L1271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69753,6 +69753,1437 @@
         </is>
       </c>
     </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>G001</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>1006 Agent M (C17)</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1245" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G1245" t="n">
+        <v>3840</v>
+      </c>
+      <c r="H1245" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1245" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1245" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C17 easier (wins / length / lowest HP: vanilla 100% / 47.8 / 52%, variant 100% / 32.5 / 53%); HP x1.20, ATK and INT x1.00 bring it back into the window of vanilla (100% / 39.5 / 52%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1245" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1245" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>G002</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>795 Siesta (C19)</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1246" t="n">
+        <v>3400</v>
+      </c>
+      <c r="G1246" t="n">
+        <v>3740</v>
+      </c>
+      <c r="H1246" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1246" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1246" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C19 easier (wins / length / lowest HP: vanilla 100% / 7.8 / 66%, variant 92% / 5.7 / 64%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (92% / 6.2 / 63%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1246" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1246" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>G003</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>655 Fuzzy Merchandise (C21)</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1247" t="n">
+        <v>852</v>
+      </c>
+      <c r="G1247" t="n">
+        <v>937</v>
+      </c>
+      <c r="H1247" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1247" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1247" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C21 easier (wins / length / lowest HP: vanilla 100% / 14.8 / 60%, variant 100% / 9.8 / 65%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (100% / 11.3 / 63%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1247" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1247" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>G004</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>656 Fluffy Merchandise (C21)</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1248" t="n">
+        <v>824</v>
+      </c>
+      <c r="G1248" t="n">
+        <v>906</v>
+      </c>
+      <c r="H1248" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1248" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1248" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C21 easier (wins / length / lowest HP: vanilla 100% / 14.8 / 60%, variant 100% / 9.8 / 65%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (100% / 11.3 / 63%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1248" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1248" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>G005</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>1008 Trafficker Twinny (C21)</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1249" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G1249" t="n">
+        <v>4180</v>
+      </c>
+      <c r="H1249" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1249" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1249" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C21 easier (wins / length / lowest HP: vanilla 100% / 14.8 / 60%, variant 100% / 9.8 / 65%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (100% / 11.3 / 63%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1249" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1249" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>G006</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>825 Afanc (C24)</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1250" t="n">
+        <v>4582</v>
+      </c>
+      <c r="G1250" t="n">
+        <v>5498</v>
+      </c>
+      <c r="H1250" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1250" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1250" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C24 easier (wins / length / lowest HP: vanilla 100% / 6.1 / 63%, variant 100% / 4.2 / 72%); HP x1.20, ATK and INT x1.00 bring it back into the window of vanilla (100% / 4.8 / 71%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1250" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1250" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>G007</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>1010 Michelle (C26)</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1251" t="n">
+        <v>5025</v>
+      </c>
+      <c r="G1251" t="n">
+        <v>9045</v>
+      </c>
+      <c r="H1251" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1251" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1251" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C26 easier (wins / length / lowest HP: vanilla 85% / 24.9 / 47%, variant 100% / 9.4 / 61%); HP x1.80, ATK and INT x1.16 bring it back into the window of vanilla (95% / 24.0 / 47%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1251" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1251" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>G008</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>1010 Michelle (C26)</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1252" t="n">
+        <v>207</v>
+      </c>
+      <c r="G1252" t="n">
+        <v>240</v>
+      </c>
+      <c r="H1252" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1252" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1252" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C26 easier (wins / length / lowest HP: vanilla 85% / 24.9 / 47%, variant 100% / 9.4 / 61%); HP x1.80, ATK and INT x1.16 bring it back into the window of vanilla (95% / 24.0 / 47%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1252" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1252" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>G009</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>1010 Michelle (C26)</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1253" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1253" t="n">
+        <v>44</v>
+      </c>
+      <c r="H1253" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1253" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1253" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C26 easier (wins / length / lowest HP: vanilla 85% / 24.9 / 47%, variant 100% / 9.4 / 61%); HP x1.80, ATK and INT x1.16 bring it back into the window of vanilla (95% / 24.0 / 47%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1253" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1253" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>G010</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>1011 Beatrice (C26)</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1254" t="n">
+        <v>4625</v>
+      </c>
+      <c r="G1254" t="n">
+        <v>8325</v>
+      </c>
+      <c r="H1254" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1254" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1254" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C26 easier (wins / length / lowest HP: vanilla 85% / 24.9 / 47%, variant 100% / 9.4 / 61%); HP x1.80, ATK and INT x1.16 bring it back into the window of vanilla (95% / 24.0 / 47%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1254" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1254" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>G011</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>1011 Beatrice (C26)</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1255" t="n">
+        <v>163</v>
+      </c>
+      <c r="G1255" t="n">
+        <v>189</v>
+      </c>
+      <c r="H1255" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1255" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1255" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C26 easier (wins / length / lowest HP: vanilla 85% / 24.9 / 47%, variant 100% / 9.4 / 61%); HP x1.80, ATK and INT x1.16 bring it back into the window of vanilla (95% / 24.0 / 47%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1255" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1255" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>G012</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>1011 Beatrice (C26)</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1256" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1256" t="n">
+        <v>56</v>
+      </c>
+      <c r="H1256" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1256" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1256" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C26 easier (wins / length / lowest HP: vanilla 85% / 24.9 / 47%, variant 100% / 9.4 / 61%); HP x1.80, ATK and INT x1.16 bring it back into the window of vanilla (95% / 24.0 / 47%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1256" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1256" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>G013</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>964 Forest Guardian (C27)</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1257" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1257" t="n">
+        <v>2200</v>
+      </c>
+      <c r="H1257" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1257" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1257" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C27 easier (wins / length / lowest HP: vanilla 100% / 5.0 / 83%, variant 100% / 3.6 / 88%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (100% / 3.8 / 89%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1257" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1257" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>G014</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>1012 Spirit of Mag Mell (C28)</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1258" t="n">
+        <v>8200</v>
+      </c>
+      <c r="G1258" t="n">
+        <v>9840</v>
+      </c>
+      <c r="H1258" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1258" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1258" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C28 easier (wins / length / lowest HP: vanilla 95% / 13.2 / 35%, variant 98% / 8.3 / 47%); HP x1.20, ATK and INT x1.00 bring it back into the window of vanilla (95% / 10.2 / 43%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1258" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1258" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>G015</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>785 Calliope (C29)</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1259" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G1259" t="n">
+        <v>9750</v>
+      </c>
+      <c r="H1259" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1259" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1259" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C29 easier (wins / length / lowest HP: vanilla 15% / 39.5 / 13%, variant 40% / 27.2 / 23%); HP x1.30, ATK and INT x1.00 bring it back into the window of vanilla (20% / 33.7 / 11%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1259" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1259" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>G016</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>840 Moby Dick (C32)</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1260" t="n">
+        <v>13280</v>
+      </c>
+      <c r="G1260" t="n">
+        <v>19256</v>
+      </c>
+      <c r="H1260" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1260" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1260" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C32 easier (wins / length / lowest HP: vanilla 92% / 20.6 / 45%, variant 100% / 12.7 / 61%); HP x1.45, ATK and INT x1.00 bring it back into the window of vanilla (100% / 20.7 / 51%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1260" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1260" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>G017</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>1036 Queen of Darkness (C34)</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1261" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G1261" t="n">
+        <v>9600</v>
+      </c>
+      <c r="H1261" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1261" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1261" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C34 easier (wins / length / lowest HP: vanilla 100% / 41.3 / 59%, variant 100% / 22.6 / 64%); HP x1.20, ATK and INT x1.00 bring it back into the window of vanilla (100% / 31.0 / 60%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1261" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1261" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>G018</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>1037 Queen of Darkness (C34)</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1262" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G1262" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H1262" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1262" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1262" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C34 easier (wins / length / lowest HP: vanilla 100% / 41.3 / 59%, variant 100% / 22.6 / 64%); HP x1.20, ATK and INT x1.00 bring it back into the window of vanilla (100% / 31.0 / 60%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1262" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1262" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>G019</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>1015 Demon God Fried (C36)</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1263" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G1263" t="n">
+        <v>19800</v>
+      </c>
+      <c r="H1263" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1263" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1263" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C36 easier (wins / length / lowest HP: vanilla 90% / 17.4 / 0%, variant 95% / 12.6 / 0%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (98% / 14.0 / 1%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1263" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1263" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>G020</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>865 Iron Maiden (C37)</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1264" t="n">
+        <v>16800</v>
+      </c>
+      <c r="G1264" t="n">
+        <v>20160</v>
+      </c>
+      <c r="H1264" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1264" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1264" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C37 easier (wins / length / lowest HP: vanilla 100% / 14.4 / 60%, variant 100% / 9.7 / 62%); HP x1.20, ATK and INT x1.00 bring it back into the window of vanilla (100% / 12.0 / 60%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1264" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1264" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>G021</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>950 Samael (C38)</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1265" t="n">
+        <v>18500</v>
+      </c>
+      <c r="G1265" t="n">
+        <v>26825</v>
+      </c>
+      <c r="H1265" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1265" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1265" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C38 easier (wins / length / lowest HP: vanilla 60% / 18.1 / 27%, variant 92% / 11.8 / 55%); HP x1.45, ATK and INT x1.00 bring it back into the window of vanilla (68% / 18.4 / 36%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1265" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1265" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>G022</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>958 Demiurge (C40)</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1266" t="n">
+        <v>24000</v>
+      </c>
+      <c r="G1266" t="n">
+        <v>34800</v>
+      </c>
+      <c r="H1266" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1266" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1266" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C40 easier (wins / length / lowest HP: vanilla 75% / 37.1 / 26%, variant 95% / 23.5 / 41%); HP x1.45, ATK and INT x1.00 bring it back into the window of vanilla (85% / 41.0 / 31%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1266" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1266" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>G023</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>961 Atialuco (C40)</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1267" t="n">
+        <v>21800</v>
+      </c>
+      <c r="G1267" t="n">
+        <v>31610</v>
+      </c>
+      <c r="H1267" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1267" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1267" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C40 easier (wins / length / lowest HP: vanilla 75% / 37.1 / 26%, variant 95% / 23.5 / 41%); HP x1.45, ATK and INT x1.00 bring it back into the window of vanilla (85% / 41.0 / 31%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1267" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1267" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>G024</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>848 Qitian Dasheng (P08)</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1268" t="n">
+        <v>28000</v>
+      </c>
+      <c r="G1268" t="n">
+        <v>30800</v>
+      </c>
+      <c r="H1268" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1268" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1268" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made P08 easier (wins / length / lowest HP: vanilla 100% / 6.2 / 88%, variant 100% / 4.5 / 90%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (100% / 4.9 / 89%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1268" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1268" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>G025</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>582 Peggy Oversummoner (P24)</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1269" t="n">
+        <v>8501</v>
+      </c>
+      <c r="G1269" t="n">
+        <v>9351</v>
+      </c>
+      <c r="H1269" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1269" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1269" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made P24 easier (wins / length / lowest HP: vanilla 100% / 4.9 / 58%, variant 100% / 3.6 / 62%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (98% / 4.0 / 57%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1269" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1269" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>G026</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>588 Roger Orso (P24)</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1270" t="n">
+        <v>9121</v>
+      </c>
+      <c r="G1270" t="n">
+        <v>10033</v>
+      </c>
+      <c r="H1270" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1270" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1270" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made P24 easier (wins / length / lowest HP: vanilla 100% / 4.9 / 58%, variant 100% / 3.6 / 62%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (98% / 4.0 / 57%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1270" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1270" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>G027</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>1026 Aradia (P24)</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1271" t="n">
+        <v>41500</v>
+      </c>
+      <c r="G1271" t="n">
+        <v>45650</v>
+      </c>
+      <c r="H1271" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1271" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1271" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made P24 easier (wins / length / lowest HP: vanilla 100% / 4.9 / 58%, variant 100% / 3.6 / 62%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (98% / 4.0 / 57%). Only enemies of no random formation</t>
+        </is>
+      </c>
+      <c r="K1271" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1271" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1271"/>
+  <dimension ref="A1:L1337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69802,7 +69802,7 @@
       </c>
       <c r="L1245" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -69855,7 +69855,7 @@
       </c>
       <c r="L1246" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -69908,7 +69908,7 @@
       </c>
       <c r="L1247" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -69961,7 +69961,7 @@
       </c>
       <c r="L1248" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -70014,7 +70014,7 @@
       </c>
       <c r="L1249" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -70067,7 +70067,7 @@
       </c>
       <c r="L1250" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -70120,7 +70120,7 @@
       </c>
       <c r="L1251" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -70173,7 +70173,7 @@
       </c>
       <c r="L1252" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -70226,7 +70226,7 @@
       </c>
       <c r="L1253" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -70279,7 +70279,7 @@
       </c>
       <c r="L1254" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -70332,7 +70332,7 @@
       </c>
       <c r="L1255" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -70385,7 +70385,7 @@
       </c>
       <c r="L1256" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -70438,7 +70438,7 @@
       </c>
       <c r="L1257" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -70491,7 +70491,7 @@
       </c>
       <c r="L1258" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -70544,7 +70544,7 @@
       </c>
       <c r="L1259" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -70597,7 +70597,7 @@
       </c>
       <c r="L1260" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -70650,7 +70650,7 @@
       </c>
       <c r="L1261" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -70703,7 +70703,7 @@
       </c>
       <c r="L1262" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -70756,7 +70756,7 @@
       </c>
       <c r="L1263" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -70809,7 +70809,7 @@
       </c>
       <c r="L1264" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -70862,7 +70862,7 @@
       </c>
       <c r="L1265" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -70915,7 +70915,7 @@
       </c>
       <c r="L1266" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -70968,7 +70968,7 @@
       </c>
       <c r="L1267" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -71021,7 +71021,7 @@
       </c>
       <c r="L1268" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -71074,7 +71074,7 @@
       </c>
       <c r="L1269" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -71127,7 +71127,7 @@
       </c>
       <c r="L1270" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
         </is>
       </c>
     </row>
@@ -71180,7 +71180,3505 @@
       </c>
       <c r="L1271" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>G028</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>1013 Heartless Avenger (C30)</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1272" t="n">
+        <v>8500</v>
+      </c>
+      <c r="G1272" t="n">
+        <v>11050</v>
+      </c>
+      <c r="H1272" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1272" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1272" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py, wider search asked by the user): C30, two fights in a row, was easier on the variant (wins / length / lowest HP: vanilla 90% / 44.4 / 45%, variant 95% / 32.8 / 47%); HP x1.30 with ATK and INT x0.92 bring it back into the window of vanilla (88% / 54.7 / 43%); HP alone made it far harder (42% wins)</t>
+        </is>
+      </c>
+      <c r="K1272" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1272" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>G029</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>1013 Heartless Avenger (C30)</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1273" t="n">
+        <v>236</v>
+      </c>
+      <c r="G1273" t="n">
+        <v>217</v>
+      </c>
+      <c r="H1273" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1273" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1273" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py, wider search asked by the user): C30, two fights in a row, was easier on the variant (wins / length / lowest HP: vanilla 90% / 44.4 / 45%, variant 95% / 32.8 / 47%); HP x1.30 with ATK and INT x0.92 bring it back into the window of vanilla (88% / 54.7 / 43%); HP alone made it far harder (42% wins)</t>
+        </is>
+      </c>
+      <c r="K1273" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1273" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>G030</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>1013 Heartless Avenger (C30)</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1274" t="n">
+        <v>79</v>
+      </c>
+      <c r="G1274" t="n">
+        <v>73</v>
+      </c>
+      <c r="H1274" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1274" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1274" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py, wider search asked by the user): C30, two fights in a row, was easier on the variant (wins / length / lowest HP: vanilla 90% / 44.4 / 45%, variant 95% / 32.8 / 47%); HP x1.30 with ATK and INT x0.92 bring it back into the window of vanilla (88% / 54.7 / 43%); HP alone made it far harder (42% wins)</t>
+        </is>
+      </c>
+      <c r="K1274" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1274" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>G031</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>1035 Heartless Avenger (C30)</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1275" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G1275" t="n">
+        <v>8840</v>
+      </c>
+      <c r="H1275" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1275" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1275" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py, wider search asked by the user): C30, two fights in a row, was easier on the variant (wins / length / lowest HP: vanilla 90% / 44.4 / 45%, variant 95% / 32.8 / 47%); HP x1.30 with ATK and INT x0.92 bring it back into the window of vanilla (88% / 54.7 / 43%); HP alone made it far harder (42% wins)</t>
+        </is>
+      </c>
+      <c r="K1275" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1275" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>G032</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>1035 Heartless Avenger (C30)</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1276" t="n">
+        <v>255</v>
+      </c>
+      <c r="G1276" t="n">
+        <v>235</v>
+      </c>
+      <c r="H1276" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1276" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1276" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py, wider search asked by the user): C30, two fights in a row, was easier on the variant (wins / length / lowest HP: vanilla 90% / 44.4 / 45%, variant 95% / 32.8 / 47%); HP x1.30 with ATK and INT x0.92 bring it back into the window of vanilla (88% / 54.7 / 43%); HP alone made it far harder (42% wins)</t>
+        </is>
+      </c>
+      <c r="K1276" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1276" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>G033</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>1035 Heartless Avenger (C30)</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1277" t="n">
+        <v>79</v>
+      </c>
+      <c r="G1277" t="n">
+        <v>73</v>
+      </c>
+      <c r="H1277" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1277" t="inlineStr">
+        <is>
+          <t>R08, R10, S04</t>
+        </is>
+      </c>
+      <c r="J1277" t="inlineStr">
+        <is>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py, wider search asked by the user): C30, two fights in a row, was easier on the variant (wins / length / lowest HP: vanilla 90% / 44.4 / 45%, variant 95% / 32.8 / 47%); HP x1.30 with ATK and INT x0.92 bring it back into the window of vanilla (88% / 54.7 / 43%); HP alone made it far harder (42% wins)</t>
+        </is>
+      </c>
+      <c r="K1277" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1277" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>G034</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>78 Macha (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1278" t="n">
+        <v>7827</v>
+      </c>
+      <c r="G1278" t="n">
+        <v>15263</v>
+      </c>
+      <c r="H1278" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1278" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1278" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1278" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1278" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>G035</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>78 Macha (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1279" t="n">
+        <v>363</v>
+      </c>
+      <c r="G1279" t="n">
+        <v>613</v>
+      </c>
+      <c r="H1279" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1279" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1279" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1279" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1279" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>G036</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>78 Macha (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1280" t="n">
+        <v>132</v>
+      </c>
+      <c r="G1280" t="n">
+        <v>223</v>
+      </c>
+      <c r="H1280" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1280" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1280" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1280" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1280" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>G037</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>92 Leanan Sidhe (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1281" t="n">
+        <v>1531</v>
+      </c>
+      <c r="G1281" t="n">
+        <v>1990</v>
+      </c>
+      <c r="H1281" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1281" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1281" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1281" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1281" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>G038</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>92 Leanan Sidhe (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1282" t="n">
+        <v>236</v>
+      </c>
+      <c r="G1282" t="n">
+        <v>307</v>
+      </c>
+      <c r="H1282" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1282" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1282" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1282" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1282" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>G039</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>92 Leanan Sidhe (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1283" t="n">
+        <v>68</v>
+      </c>
+      <c r="G1283" t="n">
+        <v>88</v>
+      </c>
+      <c r="H1283" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1283" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1283" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1283" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1283" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>G040</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>108 Shahrazad (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1284" t="n">
+        <v>1544</v>
+      </c>
+      <c r="G1284" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H1284" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1284" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1284" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1284" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1284" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>G041</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>108 Shahrazad (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1285" t="n">
+        <v>242</v>
+      </c>
+      <c r="G1285" t="n">
+        <v>315</v>
+      </c>
+      <c r="H1285" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1285" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1285" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1285" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1285" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>G042</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>108 Shahrazad (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1286" t="n">
+        <v>77</v>
+      </c>
+      <c r="G1286" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1286" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1286" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1286" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1286" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1286" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>G043</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>120 Stheno (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1287" t="n">
+        <v>2397</v>
+      </c>
+      <c r="G1287" t="n">
+        <v>3116</v>
+      </c>
+      <c r="H1287" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1287" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1287" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1287" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1287" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>G044</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>120 Stheno (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1288" t="n">
+        <v>292</v>
+      </c>
+      <c r="G1288" t="n">
+        <v>380</v>
+      </c>
+      <c r="H1288" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1288" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1288" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1288" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1288" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>G045</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>120 Stheno (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1289" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1289" t="n">
+        <v>188</v>
+      </c>
+      <c r="H1289" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1289" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1289" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1289" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1289" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>G046</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>138 Pabilsag (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1290" t="n">
+        <v>1683</v>
+      </c>
+      <c r="G1290" t="n">
+        <v>2188</v>
+      </c>
+      <c r="H1290" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1290" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1290" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1290" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1290" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>G047</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>138 Pabilsag (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1291" t="n">
+        <v>245</v>
+      </c>
+      <c r="G1291" t="n">
+        <v>318</v>
+      </c>
+      <c r="H1291" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1291" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1291" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1291" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1291" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>G048</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>138 Pabilsag (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1292" t="n">
+        <v>67</v>
+      </c>
+      <c r="G1292" t="n">
+        <v>87</v>
+      </c>
+      <c r="H1292" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1292" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1292" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1292" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1292" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>G049</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>189 Leprechaun (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1293" t="n">
+        <v>1745</v>
+      </c>
+      <c r="G1293" t="n">
+        <v>2268</v>
+      </c>
+      <c r="H1293" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1293" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1293" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1293" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1293" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>G050</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>189 Leprechaun (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1294" t="n">
+        <v>291</v>
+      </c>
+      <c r="G1294" t="n">
+        <v>378</v>
+      </c>
+      <c r="H1294" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1294" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1294" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1294" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1294" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>G051</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>189 Leprechaun (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1295" t="n">
+        <v>71</v>
+      </c>
+      <c r="G1295" t="n">
+        <v>92</v>
+      </c>
+      <c r="H1295" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1295" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1295" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1295" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1295" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>G052</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>258 Lorelei (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1296" t="n">
+        <v>1475</v>
+      </c>
+      <c r="G1296" t="n">
+        <v>1918</v>
+      </c>
+      <c r="H1296" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1296" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1296" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1296" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1296" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>G053</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>258 Lorelei (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1297" t="n">
+        <v>217</v>
+      </c>
+      <c r="G1297" t="n">
+        <v>282</v>
+      </c>
+      <c r="H1297" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1297" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1297" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1297" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1297" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>G054</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>258 Lorelei (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1298" t="n">
+        <v>82</v>
+      </c>
+      <c r="G1298" t="n">
+        <v>107</v>
+      </c>
+      <c r="H1298" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1298" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1298" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1298" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1298" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>G055</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>279 Centenary (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1299" t="n">
+        <v>1542</v>
+      </c>
+      <c r="G1299" t="n">
+        <v>2005</v>
+      </c>
+      <c r="H1299" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1299" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1299" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1299" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1299" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>G056</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>279 Centenary (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1300" t="n">
+        <v>231</v>
+      </c>
+      <c r="G1300" t="n">
+        <v>300</v>
+      </c>
+      <c r="H1300" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1300" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1300" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1300" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1300" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>G057</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>279 Centenary (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1301" t="n">
+        <v>109</v>
+      </c>
+      <c r="G1301" t="n">
+        <v>142</v>
+      </c>
+      <c r="H1301" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1301" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1301" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1301" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1301" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>G058</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>296 Purski (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1302" t="n">
+        <v>2673</v>
+      </c>
+      <c r="G1302" t="n">
+        <v>5212</v>
+      </c>
+      <c r="H1302" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1302" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1302" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1302" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1302" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>G059</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>296 Purski (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1303" t="n">
+        <v>313</v>
+      </c>
+      <c r="G1303" t="n">
+        <v>529</v>
+      </c>
+      <c r="H1303" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1303" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1303" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1303" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1303" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>G060</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>296 Purski (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1304" t="n">
+        <v>108</v>
+      </c>
+      <c r="G1304" t="n">
+        <v>183</v>
+      </c>
+      <c r="H1304" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1304" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1304" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1304" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1304" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>G061</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>337 Storm Bringer (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1305" t="n">
+        <v>1631</v>
+      </c>
+      <c r="G1305" t="n">
+        <v>2120</v>
+      </c>
+      <c r="H1305" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1305" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1305" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1305" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1305" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>G062</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>337 Storm Bringer (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1306" t="n">
+        <v>272</v>
+      </c>
+      <c r="G1306" t="n">
+        <v>354</v>
+      </c>
+      <c r="H1306" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1306" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1306" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1306" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1306" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>G063</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>337 Storm Bringer (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1307" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1307" t="n">
+        <v>81</v>
+      </c>
+      <c r="H1307" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1307" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1307" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1307" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1307" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>G064</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>356 Balrog (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1308" t="n">
+        <v>1643</v>
+      </c>
+      <c r="G1308" t="n">
+        <v>2136</v>
+      </c>
+      <c r="H1308" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1308" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1308" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1308" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1308" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>G065</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>356 Balrog (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1309" t="n">
+        <v>275</v>
+      </c>
+      <c r="G1309" t="n">
+        <v>358</v>
+      </c>
+      <c r="H1309" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1309" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1309" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1309" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1309" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>G066</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>356 Balrog (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1310" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1310" t="n">
+        <v>81</v>
+      </c>
+      <c r="H1310" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1310" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1310" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1310" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1310" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>G067</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>368 Melusine (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1311" t="n">
+        <v>1668</v>
+      </c>
+      <c r="G1311" t="n">
+        <v>2168</v>
+      </c>
+      <c r="H1311" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1311" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1311" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1311" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1311" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>G068</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>368 Melusine (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1312" t="n">
+        <v>264</v>
+      </c>
+      <c r="G1312" t="n">
+        <v>343</v>
+      </c>
+      <c r="H1312" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1312" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1312" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1312" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1312" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>G069</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>368 Melusine (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1313" t="n">
+        <v>93</v>
+      </c>
+      <c r="G1313" t="n">
+        <v>121</v>
+      </c>
+      <c r="H1313" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1313" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1313" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1313" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1313" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>G070</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>399 Dzelarhons (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1314" t="n">
+        <v>1729</v>
+      </c>
+      <c r="G1314" t="n">
+        <v>2248</v>
+      </c>
+      <c r="H1314" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1314" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1314" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1314" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1314" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>G071</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>399 Dzelarhons (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1315" t="n">
+        <v>259</v>
+      </c>
+      <c r="G1315" t="n">
+        <v>337</v>
+      </c>
+      <c r="H1315" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1315" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1315" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1315" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1315" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>G072</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>399 Dzelarhons (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1316" t="n">
+        <v>59</v>
+      </c>
+      <c r="G1316" t="n">
+        <v>77</v>
+      </c>
+      <c r="H1316" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1316" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1316" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1316" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1316" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>G073</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>403 Fafnir (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1317" t="n">
+        <v>3042</v>
+      </c>
+      <c r="G1317" t="n">
+        <v>3955</v>
+      </c>
+      <c r="H1317" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1317" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1317" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1317" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1317" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>G074</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>403 Fafnir (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1318" t="n">
+        <v>321</v>
+      </c>
+      <c r="G1318" t="n">
+        <v>417</v>
+      </c>
+      <c r="H1318" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1318" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1318" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1318" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1318" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>G075</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>403 Fafnir (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1319" t="n">
+        <v>91</v>
+      </c>
+      <c r="G1319" t="n">
+        <v>118</v>
+      </c>
+      <c r="H1319" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1319" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1319" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1319" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1319" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>G076</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>423 Isis (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1320" t="n">
+        <v>1559</v>
+      </c>
+      <c r="G1320" t="n">
+        <v>2027</v>
+      </c>
+      <c r="H1320" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1320" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1320" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1320" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1320" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>G077</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>423 Isis (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1321" t="n">
+        <v>237</v>
+      </c>
+      <c r="G1321" t="n">
+        <v>308</v>
+      </c>
+      <c r="H1321" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1321" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1321" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1321" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1321" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>G078</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>423 Isis (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1322" t="n">
+        <v>94</v>
+      </c>
+      <c r="G1322" t="n">
+        <v>122</v>
+      </c>
+      <c r="H1322" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1322" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1322" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1322" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1322" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>G079</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>508 Metal Mandra ♀ (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1323" t="n">
+        <v>1203</v>
+      </c>
+      <c r="G1323" t="n">
+        <v>1564</v>
+      </c>
+      <c r="H1323" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1323" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1323" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1323" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1323" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>G080</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>508 Metal Mandra ♀ (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1324" t="n">
+        <v>218</v>
+      </c>
+      <c r="G1324" t="n">
+        <v>283</v>
+      </c>
+      <c r="H1324" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1324" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1324" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1324" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1324" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>G081</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>508 Metal Mandra ♀ (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1325" t="n">
+        <v>89</v>
+      </c>
+      <c r="G1325" t="n">
+        <v>116</v>
+      </c>
+      <c r="H1325" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1325" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1325" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1325" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1325" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>G082</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>761 Yab-Yum (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1326" t="n">
+        <v>1411</v>
+      </c>
+      <c r="G1326" t="n">
+        <v>1834</v>
+      </c>
+      <c r="H1326" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1326" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1326" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1326" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1326" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>G083</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>761 Yab-Yum (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1327" t="n">
+        <v>214</v>
+      </c>
+      <c r="G1327" t="n">
+        <v>278</v>
+      </c>
+      <c r="H1327" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1327" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1327" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1327" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1327" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>G084</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>761 Yab-Yum (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1328" t="n">
+        <v>71</v>
+      </c>
+      <c r="G1328" t="n">
+        <v>92</v>
+      </c>
+      <c r="H1328" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1328" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1328" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1328" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1328" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>G085</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>841 Space Whale (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1329" t="n">
+        <v>4675</v>
+      </c>
+      <c r="G1329" t="n">
+        <v>6078</v>
+      </c>
+      <c r="H1329" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1329" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1329" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1329" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1329" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>G086</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>841 Space Whale (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1330" t="n">
+        <v>322</v>
+      </c>
+      <c r="G1330" t="n">
+        <v>419</v>
+      </c>
+      <c r="H1330" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1330" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1330" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1330" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1330" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>G087</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>841 Space Whale (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1331" t="n">
+        <v>148</v>
+      </c>
+      <c r="G1331" t="n">
+        <v>192</v>
+      </c>
+      <c r="H1331" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1331" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1331" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1331" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1331" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>G088</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>886 Yato-no-Kami (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1332" t="n">
+        <v>1811</v>
+      </c>
+      <c r="G1332" t="n">
+        <v>2354</v>
+      </c>
+      <c r="H1332" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1332" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1332" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1332" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1332" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>G089</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>886 Yato-no-Kami (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1333" t="n">
+        <v>258</v>
+      </c>
+      <c r="G1333" t="n">
+        <v>335</v>
+      </c>
+      <c r="H1333" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1333" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1333" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1333" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1333" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>G090</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>886 Yato-no-Kami (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1334" t="n">
+        <v>81</v>
+      </c>
+      <c r="G1334" t="n">
+        <v>105</v>
+      </c>
+      <c r="H1334" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1334" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1334" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1334" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1334" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>G091</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>919 Highway Star (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1335" t="n">
+        <v>5871</v>
+      </c>
+      <c r="G1335" t="n">
+        <v>11448</v>
+      </c>
+      <c r="H1335" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1335" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1335" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1335" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1335" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>G092</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>919 Highway Star (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1336" t="n">
+        <v>348</v>
+      </c>
+      <c r="G1336" t="n">
+        <v>588</v>
+      </c>
+      <c r="H1336" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1336" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1336" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1336" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1336" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>G093</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>919 Highway Star (common, St15)</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1337" t="n">
+        <v>128</v>
+      </c>
+      <c r="G1337" t="n">
+        <v>216</v>
+      </c>
+      <c r="H1337" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1337" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1337" t="inlineStr">
+        <is>
+          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+        </is>
+      </c>
+      <c r="K1337" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1337" t="inlineStr">
+        <is>
+          <t>decided</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1337"/>
+  <dimension ref="A1:L1338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35151,7 +35151,7 @@
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>0x37e7</t>
+          <t>0x36e7</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
@@ -35161,12 +35161,12 @@
       </c>
       <c r="I620" t="inlineStr">
         <is>
-          <t>J31, F15</t>
+          <t>J31, F15, T07</t>
         </is>
       </c>
       <c r="J620" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story; poison opened (T07, the user 2026-10-09: damage over time must serve against bosses without trivialising them): healer's Poison cast until it lands takes 23% of the boss HP over the fight (tools/skill_value.py play, check_runs), under a quarter. Kept immune: Ghast, Doll, Countess of Vrachia (undead or doll), Beatrice (C26 already 27% through Michelle), Heartless Avenger (C30: 32%, the fight halved)</t>
         </is>
       </c>
       <c r="K620" t="inlineStr">
@@ -36462,7 +36462,7 @@
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>0x1163</t>
+          <t>0x1063</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -36472,12 +36472,12 @@
       </c>
       <c r="I643" t="inlineStr">
         <is>
-          <t>J31, F15</t>
+          <t>J31, F15, T07</t>
         </is>
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story; poison opened (T07, the user 2026-10-09: damage over time must serve against bosses without trivialising them): healer's Poison cast until it lands takes 20% of the boss HP over the fight (tools/skill_value.py play, check_runs), under a quarter. Kept immune: Ghast, Doll, Countess of Vrachia (undead or doll), Beatrice (C26 already 27% through Michelle), Heartless Avenger (C30: 32%, the fight halved)</t>
         </is>
       </c>
       <c r="K643" t="inlineStr">
@@ -37089,7 +37089,7 @@
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>0x11e7</t>
+          <t>0x10e7</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -37099,12 +37099,12 @@
       </c>
       <c r="I654" t="inlineStr">
         <is>
-          <t>J31, F15</t>
+          <t>J31, F15, T07</t>
         </is>
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story; poison opened (T07, the user 2026-10-09: damage over time must serve against bosses without trivialising them): healer's Poison cast until it lands takes 25% of the boss HP over the fight (tools/skill_value.py play, check_runs), under a quarter. Kept immune: Ghast, Doll, Countess of Vrachia (undead or doll), Beatrice (C26 already 27% through Michelle), Heartless Avenger (C30: 32%, the fight halved)</t>
         </is>
       </c>
       <c r="K654" t="inlineStr">
@@ -37317,7 +37317,7 @@
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>0x35e2</t>
+          <t>0x34e2</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -37327,12 +37327,12 @@
       </c>
       <c r="I658" t="inlineStr">
         <is>
-          <t>J31, F15</t>
+          <t>J31, F15, T07</t>
         </is>
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story; poison opened (T07, the user 2026-10-09: damage over time must serve against bosses without trivialising them): healer's Poison cast until it lands takes 16% of the boss HP over the fight (tools/skill_value.py play, check_runs), under a quarter. Kept immune: Ghast, Doll, Countess of Vrachia (undead or doll), Beatrice (C26 already 27% through Michelle), Heartless Avenger (C30: 32%, the fight halved)</t>
         </is>
       </c>
       <c r="K658" t="inlineStr">
@@ -39198,7 +39198,7 @@
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>0x1766</t>
+          <t>0x1666</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
@@ -39208,12 +39208,12 @@
       </c>
       <c r="I691" t="inlineStr">
         <is>
-          <t>J31, F15</t>
+          <t>J31, F15, T07</t>
         </is>
       </c>
       <c r="J691" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story; poison opened (T07, the user 2026-10-09: damage over time must serve against bosses without trivialising them): healer's Poison cast until it lands takes 25% of the boss HP over the fight (tools/skill_value.py play, check_runs), under a quarter. Kept immune: Ghast, Doll, Countess of Vrachia (undead or doll), Beatrice (C26 already 27% through Michelle), Heartless Avenger (C30: 32%, the fight halved)</t>
         </is>
       </c>
       <c r="K691" t="inlineStr">
@@ -74677,6 +74677,63 @@
         </is>
       </c>
       <c r="L1337" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>A239</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>961 Atialuco (C40)</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>immunity flags (0x3C)</t>
+        </is>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>0x35fe</t>
+        </is>
+      </c>
+      <c r="G1338" t="inlineStr">
+        <is>
+          <t>0x34fe</t>
+        </is>
+      </c>
+      <c r="H1338" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="I1338" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="J1338" t="inlineStr">
+        <is>
+          <t>Poison opened (T07, the user 2026-10-09: damage over time must serve against bosses without trivialising them): healer's Poison cast until it lands takes 7% of the boss HP over the fight (tools/skill_value.py play, check_runs), under a quarter. Kept immune: Ghast, Doll, Countess of Vrachia (undead or doll), Beatrice (C26 already 27% through Michelle), Heartless Avenger (C30: 32%, the fight halved)</t>
+        </is>
+      </c>
+      <c r="K1338" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L1338" t="inlineStr">
         <is>
           <t>decided</t>
         </is>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -69792,7 +69792,7 @@
       </c>
       <c r="J1245" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C17 easier (wins / length / lowest HP: vanilla 100% / 47.8 / 52%, variant 100% / 32.5 / 53%); HP x1.20, ATK and INT x1.00 bring it back into the window of vanilla (100% / 39.5 / 52%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C17 easier (wins / length / lowest HP: vanilla 100% / 47.8 / 52%, variant 100% / 32.5 / 53%); HP x1.20, ATK and INT x1.00 bring it back into the window of vanilla (100% / 39.5 / 52%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1245" t="inlineStr">
@@ -69802,7 +69802,7 @@
       </c>
       <c r="L1245" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -69845,7 +69845,7 @@
       </c>
       <c r="J1246" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C19 easier (wins / length / lowest HP: vanilla 100% / 7.8 / 66%, variant 92% / 5.7 / 64%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (92% / 6.2 / 63%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C19 easier (wins / length / lowest HP: vanilla 100% / 7.8 / 66%, variant 92% / 5.7 / 64%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (92% / 6.2 / 63%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1246" t="inlineStr">
@@ -69855,7 +69855,7 @@
       </c>
       <c r="L1246" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -69898,7 +69898,7 @@
       </c>
       <c r="J1247" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C21 easier (wins / length / lowest HP: vanilla 100% / 14.8 / 60%, variant 100% / 9.8 / 65%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (100% / 11.3 / 63%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C21 easier (wins / length / lowest HP: vanilla 100% / 14.8 / 60%, variant 100% / 9.8 / 65%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (100% / 11.3 / 63%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1247" t="inlineStr">
@@ -69908,7 +69908,7 @@
       </c>
       <c r="L1247" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -69951,7 +69951,7 @@
       </c>
       <c r="J1248" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C21 easier (wins / length / lowest HP: vanilla 100% / 14.8 / 60%, variant 100% / 9.8 / 65%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (100% / 11.3 / 63%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C21 easier (wins / length / lowest HP: vanilla 100% / 14.8 / 60%, variant 100% / 9.8 / 65%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (100% / 11.3 / 63%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1248" t="inlineStr">
@@ -69961,7 +69961,7 @@
       </c>
       <c r="L1248" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -70004,7 +70004,7 @@
       </c>
       <c r="J1249" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C21 easier (wins / length / lowest HP: vanilla 100% / 14.8 / 60%, variant 100% / 9.8 / 65%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (100% / 11.3 / 63%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C21 easier (wins / length / lowest HP: vanilla 100% / 14.8 / 60%, variant 100% / 9.8 / 65%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (100% / 11.3 / 63%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1249" t="inlineStr">
@@ -70014,7 +70014,7 @@
       </c>
       <c r="L1249" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -70057,7 +70057,7 @@
       </c>
       <c r="J1250" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C24 easier (wins / length / lowest HP: vanilla 100% / 6.1 / 63%, variant 100% / 4.2 / 72%); HP x1.20, ATK and INT x1.00 bring it back into the window of vanilla (100% / 4.8 / 71%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C24 easier (wins / length / lowest HP: vanilla 100% / 6.1 / 63%, variant 100% / 4.2 / 72%); HP x1.20, ATK and INT x1.00 bring it back into the window of vanilla (100% / 4.8 / 71%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1250" t="inlineStr">
@@ -70067,7 +70067,7 @@
       </c>
       <c r="L1250" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -70110,7 +70110,7 @@
       </c>
       <c r="J1251" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C26 easier (wins / length / lowest HP: vanilla 85% / 24.9 / 47%, variant 100% / 9.4 / 61%); HP x1.80, ATK and INT x1.16 bring it back into the window of vanilla (95% / 24.0 / 47%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C26 easier (wins / length / lowest HP: vanilla 85% / 24.9 / 47%, variant 100% / 9.4 / 61%); HP x1.80, ATK and INT x1.16 bring it back into the window of vanilla (95% / 24.0 / 47%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1251" t="inlineStr">
@@ -70120,7 +70120,7 @@
       </c>
       <c r="L1251" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -70269,7 +70269,7 @@
       </c>
       <c r="J1254" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C26 easier (wins / length / lowest HP: vanilla 85% / 24.9 / 47%, variant 100% / 9.4 / 61%); HP x1.80, ATK and INT x1.16 bring it back into the window of vanilla (95% / 24.0 / 47%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C26 easier (wins / length / lowest HP: vanilla 85% / 24.9 / 47%, variant 100% / 9.4 / 61%); HP x1.80, ATK and INT x1.16 bring it back into the window of vanilla (95% / 24.0 / 47%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1254" t="inlineStr">
@@ -70279,7 +70279,7 @@
       </c>
       <c r="L1254" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -70428,7 +70428,7 @@
       </c>
       <c r="J1257" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C27 easier (wins / length / lowest HP: vanilla 100% / 5.0 / 83%, variant 100% / 3.6 / 88%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (100% / 3.8 / 89%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C27 easier (wins / length / lowest HP: vanilla 100% / 5.0 / 83%, variant 100% / 3.6 / 88%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (100% / 3.8 / 89%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1257" t="inlineStr">
@@ -70438,7 +70438,7 @@
       </c>
       <c r="L1257" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -70481,7 +70481,7 @@
       </c>
       <c r="J1258" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C28 easier (wins / length / lowest HP: vanilla 95% / 13.2 / 35%, variant 98% / 8.3 / 47%); HP x1.20, ATK and INT x1.00 bring it back into the window of vanilla (95% / 10.2 / 43%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C28 easier (wins / length / lowest HP: vanilla 95% / 13.2 / 35%, variant 98% / 8.3 / 47%); HP x1.20, ATK and INT x1.00 bring it back into the window of vanilla (95% / 10.2 / 43%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1258" t="inlineStr">
@@ -70491,7 +70491,7 @@
       </c>
       <c r="L1258" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -70534,7 +70534,7 @@
       </c>
       <c r="J1259" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C29 easier (wins / length / lowest HP: vanilla 15% / 39.5 / 13%, variant 40% / 27.2 / 23%); HP x1.30, ATK and INT x1.00 bring it back into the window of vanilla (20% / 33.7 / 11%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C29 easier (wins / length / lowest HP: vanilla 15% / 39.5 / 13%, variant 40% / 27.2 / 23%); HP x1.30, ATK and INT x1.00 bring it back into the window of vanilla (20% / 33.7 / 11%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1259" t="inlineStr">
@@ -70544,7 +70544,7 @@
       </c>
       <c r="L1259" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -70587,7 +70587,7 @@
       </c>
       <c r="J1260" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C32 easier (wins / length / lowest HP: vanilla 92% / 20.6 / 45%, variant 100% / 12.7 / 61%); HP x1.45, ATK and INT x1.00 bring it back into the window of vanilla (100% / 20.7 / 51%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C32 easier (wins / length / lowest HP: vanilla 92% / 20.6 / 45%, variant 100% / 12.7 / 61%); HP x1.45, ATK and INT x1.00 bring it back into the window of vanilla (100% / 20.7 / 51%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1260" t="inlineStr">
@@ -70597,7 +70597,7 @@
       </c>
       <c r="L1260" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -70640,7 +70640,7 @@
       </c>
       <c r="J1261" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C34 easier (wins / length / lowest HP: vanilla 100% / 41.3 / 59%, variant 100% / 22.6 / 64%); HP x1.20, ATK and INT x1.00 bring it back into the window of vanilla (100% / 31.0 / 60%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C34 easier (wins / length / lowest HP: vanilla 100% / 41.3 / 59%, variant 100% / 22.6 / 64%); HP x1.20, ATK and INT x1.00 bring it back into the window of vanilla (100% / 31.0 / 60%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1261" t="inlineStr">
@@ -70650,7 +70650,7 @@
       </c>
       <c r="L1261" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -70693,7 +70693,7 @@
       </c>
       <c r="J1262" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C34 easier (wins / length / lowest HP: vanilla 100% / 41.3 / 59%, variant 100% / 22.6 / 64%); HP x1.20, ATK and INT x1.00 bring it back into the window of vanilla (100% / 31.0 / 60%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C34 easier (wins / length / lowest HP: vanilla 100% / 41.3 / 59%, variant 100% / 22.6 / 64%); HP x1.20, ATK and INT x1.00 bring it back into the window of vanilla (100% / 31.0 / 60%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1262" t="inlineStr">
@@ -70703,7 +70703,7 @@
       </c>
       <c r="L1262" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -70746,7 +70746,7 @@
       </c>
       <c r="J1263" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C36 easier (wins / length / lowest HP: vanilla 90% / 17.4 / 0%, variant 95% / 12.6 / 0%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (98% / 14.0 / 1%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C36 easier (wins / length / lowest HP: vanilla 90% / 17.4 / 0%, variant 95% / 12.6 / 0%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (98% / 14.0 / 1%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1263" t="inlineStr">
@@ -70756,7 +70756,7 @@
       </c>
       <c r="L1263" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -70799,7 +70799,7 @@
       </c>
       <c r="J1264" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C37 easier (wins / length / lowest HP: vanilla 100% / 14.4 / 60%, variant 100% / 9.7 / 62%); HP x1.20, ATK and INT x1.00 bring it back into the window of vanilla (100% / 12.0 / 60%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C37 easier (wins / length / lowest HP: vanilla 100% / 14.4 / 60%, variant 100% / 9.7 / 62%); HP x1.20, ATK and INT x1.00 bring it back into the window of vanilla (100% / 12.0 / 60%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1264" t="inlineStr">
@@ -70809,7 +70809,7 @@
       </c>
       <c r="L1264" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -70852,7 +70852,7 @@
       </c>
       <c r="J1265" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C38 easier (wins / length / lowest HP: vanilla 60% / 18.1 / 27%, variant 92% / 11.8 / 55%); HP x1.45, ATK and INT x1.00 bring it back into the window of vanilla (68% / 18.4 / 36%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C38 easier (wins / length / lowest HP: vanilla 60% / 18.1 / 27%, variant 92% / 11.8 / 55%); HP x1.45, ATK and INT x1.00 bring it back into the window of vanilla (68% / 18.4 / 36%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1265" t="inlineStr">
@@ -70862,7 +70862,7 @@
       </c>
       <c r="L1265" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -70905,7 +70905,7 @@
       </c>
       <c r="J1266" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C40 easier (wins / length / lowest HP: vanilla 75% / 37.1 / 26%, variant 95% / 23.5 / 41%); HP x1.45, ATK and INT x1.00 bring it back into the window of vanilla (85% / 41.0 / 31%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C40 easier (wins / length / lowest HP: vanilla 75% / 37.1 / 26%, variant 95% / 23.5 / 41%); HP x1.45, ATK and INT x1.00 bring it back into the window of vanilla (85% / 41.0 / 31%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1266" t="inlineStr">
@@ -70915,7 +70915,7 @@
       </c>
       <c r="L1266" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -70958,7 +70958,7 @@
       </c>
       <c r="J1267" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C40 easier (wins / length / lowest HP: vanilla 75% / 37.1 / 26%, variant 95% / 23.5 / 41%); HP x1.45, ATK and INT x1.00 bring it back into the window of vanilla (85% / 41.0 / 31%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C40 easier (wins / length / lowest HP: vanilla 75% / 37.1 / 26%, variant 95% / 23.5 / 41%); HP x1.45, ATK and INT x1.00 bring it back into the window of vanilla (85% / 41.0 / 31%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1267" t="inlineStr">
@@ -70968,7 +70968,7 @@
       </c>
       <c r="L1267" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -71011,7 +71011,7 @@
       </c>
       <c r="J1268" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made P08 easier (wins / length / lowest HP: vanilla 100% / 6.2 / 88%, variant 100% / 4.5 / 90%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (100% / 4.9 / 89%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made P08 easier (wins / length / lowest HP: vanilla 100% / 6.2 / 88%, variant 100% / 4.5 / 90%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (100% / 4.9 / 89%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1268" t="inlineStr">
@@ -71021,7 +71021,7 @@
       </c>
       <c r="L1268" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -71064,7 +71064,7 @@
       </c>
       <c r="J1269" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made P24 easier (wins / length / lowest HP: vanilla 100% / 4.9 / 58%, variant 100% / 3.6 / 62%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (98% / 4.0 / 57%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made P24 easier (wins / length / lowest HP: vanilla 100% / 4.9 / 58%, variant 100% / 3.6 / 62%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (98% / 4.0 / 57%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1269" t="inlineStr">
@@ -71074,7 +71074,7 @@
       </c>
       <c r="L1269" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -71117,7 +71117,7 @@
       </c>
       <c r="J1270" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made P24 easier (wins / length / lowest HP: vanilla 100% / 4.9 / 58%, variant 100% / 3.6 / 62%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (98% / 4.0 / 57%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made P24 easier (wins / length / lowest HP: vanilla 100% / 4.9 / 58%, variant 100% / 3.6 / 62%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (98% / 4.0 / 57%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1270" t="inlineStr">
@@ -71127,7 +71127,7 @@
       </c>
       <c r="L1270" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -71170,7 +71170,7 @@
       </c>
       <c r="J1271" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made P24 easier (wins / length / lowest HP: vanilla 100% / 4.9 / 58%, variant 100% / 3.6 / 62%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (98% / 4.0 / 57%). Only enemies of no random formation</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made P24 easier (wins / length / lowest HP: vanilla 100% / 4.9 / 58%, variant 100% / 3.6 / 62%); HP x1.10, ATK and INT x1.00 bring it back into the window of vanilla (98% / 4.0 / 57%). Only enemies of no random formation [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1271" t="inlineStr">
@@ -71180,7 +71180,7 @@
       </c>
       <c r="L1271" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -71223,7 +71223,7 @@
       </c>
       <c r="J1272" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py, wider search asked by the user): C30, two fights in a row, was easier on the variant (wins / length / lowest HP: vanilla 90% / 44.4 / 45%, variant 95% / 32.8 / 47%); HP x1.30 with ATK and INT x0.92 bring it back into the window of vanilla (88% / 54.7 / 43%); HP alone made it far harder (42% wins)</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py, wider search asked by the user): C30, two fights in a row, was easier on the variant (wins / length / lowest HP: vanilla 90% / 44.4 / 45%, variant 95% / 32.8 / 47%); HP x1.30 with ATK and INT x0.92 bring it back into the window of vanilla (88% / 54.7 / 43%); HP alone made it far harder (42% wins) [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1272" t="inlineStr">
@@ -71233,7 +71233,7 @@
       </c>
       <c r="L1272" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -71382,7 +71382,7 @@
       </c>
       <c r="J1275" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py, wider search asked by the user): C30, two fights in a row, was easier on the variant (wins / length / lowest HP: vanilla 90% / 44.4 / 45%, variant 95% / 32.8 / 47%); HP x1.30 with ATK and INT x0.92 bring it back into the window of vanilla (88% / 54.7 / 43%); HP alone made it far harder (42% wins)</t>
+          <t>Difficulty kept (R08, R10; tools/boss_fit.py, wider search asked by the user): C30, two fights in a row, was easier on the variant (wins / length / lowest HP: vanilla 90% / 44.4 / 45%, variant 95% / 32.8 / 47%); HP x1.30 with ATK and INT x0.92 bring it back into the window of vanilla (88% / 54.7 / 43%); HP alone made it far harder (42% wins) [Dropped per user directive: HP inflation caused artificial fight length]</t>
         </is>
       </c>
       <c r="K1275" t="inlineStr">
@@ -71392,7 +71392,7 @@
       </c>
       <c r="L1275" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -30116,7 +30116,7 @@
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>J06, F10</t>
+          <t>J06, F10, F87</t>
         </is>
       </c>
       <c r="J530" t="inlineStr">
@@ -30173,7 +30173,7 @@
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>J06, F10</t>
+          <t>J06, F10, F87</t>
         </is>
       </c>
       <c r="J531" t="inlineStr">
@@ -30230,7 +30230,7 @@
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>J06, F10</t>
+          <t>J06, F10, F87</t>
         </is>
       </c>
       <c r="J532" t="inlineStr">
@@ -30287,7 +30287,7 @@
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>J06, F10</t>
+          <t>J06, F10, F87</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1338"/>
+  <dimension ref="A1:L1368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74739,6 +74739,1616 @@
         </is>
       </c>
     </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>sealbooks</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>Grand Sealbook [Melek Taus] (0955)</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>secondary enchantment</t>
+        </is>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>ench_cnt=1 (222 only)</t>
+        </is>
+      </c>
+      <c r="G1339" t="inlineStr">
+        <is>
+          <t>ench_cnt=2 (222 Front line ATK, 268 Critical UP)</t>
+        </is>
+      </c>
+      <c r="H1339" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1339" t="inlineStr">
+        <is>
+          <t>F89</t>
+        </is>
+      </c>
+      <c r="J1339" t="inlineStr">
+        <is>
+          <t>Postgame Grand Sealbook given complementary offensive secondary enchantment (Critical rate UP) via native engine loop.</t>
+        </is>
+      </c>
+      <c r="K1339" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1339" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>sealbooks</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>Grand Sealbook [Samael] (0951)</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>secondary enchantment</t>
+        </is>
+      </c>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>ench_cnt=1 (224 only)</t>
+        </is>
+      </c>
+      <c r="G1340" t="inlineStr">
+        <is>
+          <t>ench_cnt=2 (224 Back line INT, 248 Spell TP Down)</t>
+        </is>
+      </c>
+      <c r="H1340" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1340" t="inlineStr">
+        <is>
+          <t>F89</t>
+        </is>
+      </c>
+      <c r="J1340" t="inlineStr">
+        <is>
+          <t>Postgame Grand Sealbook given magic sustain secondary enchantment (TP Cost for spells DOWN) via native engine loop.</t>
+        </is>
+      </c>
+      <c r="K1340" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1340" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>sealbooks</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>Grand Sealbook [Sukuna-Hikona] (0775)</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>secondary enchantment</t>
+        </is>
+      </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>ench_cnt=1 (281 only)</t>
+        </is>
+      </c>
+      <c r="G1341" t="inlineStr">
+        <is>
+          <t>ench_cnt=2 (281 Back line DEX+AGI, 246 Tech TP Down)</t>
+        </is>
+      </c>
+      <c r="H1341" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1341" t="inlineStr">
+        <is>
+          <t>F89</t>
+        </is>
+      </c>
+      <c r="J1341" t="inlineStr">
+        <is>
+          <t>Postgame Grand Sealbook given technique sustain secondary enchantment (TP Cost for techniques DOWN) via native engine loop.</t>
+        </is>
+      </c>
+      <c r="K1341" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1341" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>sealbooks</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>Grand Sealbook [Genbu] (0801)</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>secondary enchantment</t>
+        </is>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>ench_cnt=1 (223 only)</t>
+        </is>
+      </c>
+      <c r="G1342" t="inlineStr">
+        <is>
+          <t>ench_cnt=2 (223 Front line ATK+DEF, 257 Defend HP recovery)</t>
+        </is>
+      </c>
+      <c r="H1342" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1342" t="inlineStr">
+        <is>
+          <t>F89</t>
+        </is>
+      </c>
+      <c r="J1342" t="inlineStr">
+        <is>
+          <t>Postgame Grand Sealbook given defensive sustain secondary enchantment (HP recovers while defending) via native engine loop.</t>
+        </is>
+      </c>
+      <c r="K1342" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1342" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>sealbooks</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>Grand Sealbook [Murasaki Shikibu] (0722)</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>secondary enchantment</t>
+        </is>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>ench_cnt=1 (292 only)</t>
+        </is>
+      </c>
+      <c r="G1343" t="inlineStr">
+        <is>
+          <t>ench_cnt=2 (292 Defend TP recovery, 265 Ailment dissipation UP)</t>
+        </is>
+      </c>
+      <c r="H1343" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1343" t="inlineStr">
+        <is>
+          <t>F89</t>
+        </is>
+      </c>
+      <c r="J1343" t="inlineStr">
+        <is>
+          <t>Postgame Grand Sealbook given ailment mitigation secondary enchantment (Rate of status ailments dissipation UP) via native engine loop.</t>
+        </is>
+      </c>
+      <c r="K1343" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1343" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>enchantments</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>EnchantData_0024 (All stats +1)</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>stacking flag (0x20 bit 0)</t>
+        </is>
+      </c>
+      <c r="F1344" t="n">
+        <v>428</v>
+      </c>
+      <c r="G1344" t="n">
+        <v>429</v>
+      </c>
+      <c r="H1344" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1344" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="J1344" t="inlineStr">
+        <is>
+          <t>Bit 0 at 0x20 in EnchantData enabled, matching IDs 0-23 so All Stats +1 stacks across multiple equipped pieces.</t>
+        </is>
+      </c>
+      <c r="K1344" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1344" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>enchantments</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>EnchantData_0025 (All stats +3)</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>stacking flag (0x20 bit 0)</t>
+        </is>
+      </c>
+      <c r="F1345" t="n">
+        <v>428</v>
+      </c>
+      <c r="G1345" t="n">
+        <v>429</v>
+      </c>
+      <c r="H1345" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1345" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="J1345" t="inlineStr">
+        <is>
+          <t>Bit 0 at 0x20 in EnchantData enabled so All Stats +3 stacks across multiple equipped pieces.</t>
+        </is>
+      </c>
+      <c r="K1345" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1345" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>enchantments</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>EnchantData_0026 (All stats +6)</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>stacking flag (0x20 bit 0)</t>
+        </is>
+      </c>
+      <c r="F1346" t="n">
+        <v>428</v>
+      </c>
+      <c r="G1346" t="n">
+        <v>429</v>
+      </c>
+      <c r="H1346" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1346" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="J1346" t="inlineStr">
+        <is>
+          <t>Bit 0 at 0x20 in EnchantData enabled so All Stats +6 stacks across multiple equipped pieces.</t>
+        </is>
+      </c>
+      <c r="K1346" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1346" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>enchantments</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>EnchantData_0027 (All stats +9)</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>stacking flag (0x20 bit 0)</t>
+        </is>
+      </c>
+      <c r="F1347" t="n">
+        <v>428</v>
+      </c>
+      <c r="G1347" t="n">
+        <v>429</v>
+      </c>
+      <c r="H1347" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1347" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="J1347" t="inlineStr">
+        <is>
+          <t>Bit 0 at 0x20 in EnchantData enabled so All Stats +9 stacks across multiple equipped pieces.</t>
+        </is>
+      </c>
+      <c r="K1347" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1347" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>enchantments</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>EnchantData_0028 (All stats +12)</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>stacking flag (0x20 bit 0)</t>
+        </is>
+      </c>
+      <c r="F1348" t="n">
+        <v>428</v>
+      </c>
+      <c r="G1348" t="n">
+        <v>429</v>
+      </c>
+      <c r="H1348" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1348" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="J1348" t="inlineStr">
+        <is>
+          <t>Bit 0 at 0x20 in EnchantData enabled so All Stats +12 stacks across multiple equipped pieces.</t>
+        </is>
+      </c>
+      <c r="K1348" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1348" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>331 Overdue (P06)</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>equipment drop rate</t>
+        </is>
+      </c>
+      <c r="F1349" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1349" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1349" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1349" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1349" t="inlineStr">
+        <is>
+          <t>Postgame boss rarest equipment drop rate gently raised from 1% to 3% to alleviate excessive reload grinding.</t>
+        </is>
+      </c>
+      <c r="K1349" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1349" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>751 Azathoth (P18)</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>equipment drop rate</t>
+        </is>
+      </c>
+      <c r="F1350" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1350" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1350" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1350" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1350" t="inlineStr">
+        <is>
+          <t>Postgame boss rarest equipment drop rate gently raised from 1% to 3% to alleviate excessive reload grinding.</t>
+        </is>
+      </c>
+      <c r="K1350" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1350" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>862 Last Judgment (P24)</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>equipment drop rate</t>
+        </is>
+      </c>
+      <c r="F1351" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1351" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1351" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1351" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1351" t="inlineStr">
+        <is>
+          <t>Postgame superboss rarest equipment drop rate gently raised from 1% to 3%.</t>
+        </is>
+      </c>
+      <c r="K1351" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1351" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>P014</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>921 Hell's Angel</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>equipment drop rate</t>
+        </is>
+      </c>
+      <c r="F1352" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1352" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1352" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1352" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1352" t="inlineStr">
+        <is>
+          <t>Postgame superboss rarest equipment drop rate gently raised from 1% to 3%.</t>
+        </is>
+      </c>
+      <c r="K1352" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1352" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>P015</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>951 Samael</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>equipment drop rate</t>
+        </is>
+      </c>
+      <c r="F1353" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1353" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1353" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1353" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1353" t="inlineStr">
+        <is>
+          <t>Postgame superboss rarest equipment drop rate gently raised from 1% to 3%.</t>
+        </is>
+      </c>
+      <c r="K1353" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1353" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>P016</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>955 Melek Taus</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>equipment drop rate</t>
+        </is>
+      </c>
+      <c r="F1354" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1354" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1354" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1354" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1354" t="inlineStr">
+        <is>
+          <t>Postgame superboss rarest equipment drop rate gently raised from 1% to 3%.</t>
+        </is>
+      </c>
+      <c r="K1354" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1354" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>P017</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>775 Sukuna-Hikona</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>equipment drop rate</t>
+        </is>
+      </c>
+      <c r="F1355" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1355" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1355" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1355" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1355" t="inlineStr">
+        <is>
+          <t>Postgame rare equipment drop rate gently raised from 2% to 5%.</t>
+        </is>
+      </c>
+      <c r="K1355" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1355" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>801 Genbu</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>equipment drop rate</t>
+        </is>
+      </c>
+      <c r="F1356" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1356" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1356" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1356" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1356" t="inlineStr">
+        <is>
+          <t>Postgame rare equipment drop rate gently raised from 2% to 5%.</t>
+        </is>
+      </c>
+      <c r="K1356" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1356" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>712 Iktomi</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>equipment drop rate</t>
+        </is>
+      </c>
+      <c r="F1357" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1357" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1357" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1357" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1357" t="inlineStr">
+        <is>
+          <t>Postgame rare equipment drop rate gently raised from 2% to 5%.</t>
+        </is>
+      </c>
+      <c r="K1357" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1357" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>P020</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>722 Murasaki Shikibu</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>equipment drop rate</t>
+        </is>
+      </c>
+      <c r="F1358" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1358" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1358" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1358" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1358" t="inlineStr">
+        <is>
+          <t>Postgame rare equipment drop rate gently raised from 2% to 5%.</t>
+        </is>
+      </c>
+      <c r="K1358" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1358" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>P021</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>848 Qitian Dasheng</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>equipment drop rate</t>
+        </is>
+      </c>
+      <c r="F1359" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1359" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1359" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1359" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1359" t="inlineStr">
+        <is>
+          <t>Postgame rare equipment drop rate gently raised from 2% to 5%.</t>
+        </is>
+      </c>
+      <c r="K1359" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1359" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>P022</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>887 Nuwa</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>equipment drop rate</t>
+        </is>
+      </c>
+      <c r="F1360" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1360" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1360" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1360" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1360" t="inlineStr">
+        <is>
+          <t>Postgame rare equipment drop rate gently raised from 2% to 5%.</t>
+        </is>
+      </c>
+      <c r="K1360" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1360" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>P023</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>890 Kuchinawa</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>equipment drop rate</t>
+        </is>
+      </c>
+      <c r="F1361" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1361" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1361" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1361" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1361" t="inlineStr">
+        <is>
+          <t>Postgame rare equipment drop rate gently raised from 2% to 5%.</t>
+        </is>
+      </c>
+      <c r="K1361" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1361" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>P024</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>6 Garasha</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>equipment drop rate</t>
+        </is>
+      </c>
+      <c r="F1362" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1362" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1362" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1362" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1362" t="inlineStr">
+        <is>
+          <t>Rare equipment drop rate gently raised from 2% to 5%.</t>
+        </is>
+      </c>
+      <c r="K1362" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1362" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>P025</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>7 Ryoma</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>equipment drop rate</t>
+        </is>
+      </c>
+      <c r="F1363" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1363" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1363" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1363" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1363" t="inlineStr">
+        <is>
+          <t>Rare equipment drop rate gently raised from 2% to 5%.</t>
+        </is>
+      </c>
+      <c r="K1363" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1363" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>P026</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>QuestData_0000 (Fruit Fighter)</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1364" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1364" t="n">
+        <v>45</v>
+      </c>
+      <c r="H1364" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1364" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1364" t="inlineStr">
+        <is>
+          <t>Early progression quest gold raised by +50% to ease early consumable and gear acquisition.</t>
+        </is>
+      </c>
+      <c r="K1364" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1364" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>P027</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>QuestData_0005 (Pest Control)</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1365" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1365" t="n">
+        <v>60</v>
+      </c>
+      <c r="H1365" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1365" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1365" t="inlineStr">
+        <is>
+          <t>Early progression quest gold raised by +43% to ease early consumable and gear acquisition.</t>
+        </is>
+      </c>
+      <c r="K1365" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1365" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>P028</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>QuestData_0050 (Last-Minute Souvenir)</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1366" t="n">
+        <v>350</v>
+      </c>
+      <c r="G1366" t="n">
+        <v>500</v>
+      </c>
+      <c r="H1366" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1366" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1366" t="inlineStr">
+        <is>
+          <t>Midgame quest gold raised by +43% to incentivize quest completion for lagging parties.</t>
+        </is>
+      </c>
+      <c r="K1366" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1366" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>P029</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>QuestData_0100 (Midgame Hunting Quest)</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1367" t="n">
+        <v>585</v>
+      </c>
+      <c r="G1367" t="n">
+        <v>850</v>
+      </c>
+      <c r="H1367" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1367" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1367" t="inlineStr">
+        <is>
+          <t>Midgame quest gold raised by +45% to incentivize quest completion for lagging parties.</t>
+        </is>
+      </c>
+      <c r="K1367" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1367" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>P030</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>QuestData_0200 (Late Game Hunting Quest)</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1368" t="n">
+        <v>599</v>
+      </c>
+      <c r="G1368" t="n">
+        <v>900</v>
+      </c>
+      <c r="H1368" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1368" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1368" t="inlineStr">
+        <is>
+          <t>Late game quest gold raised by +50% to incentivize quest completion for lagging parties.</t>
+        </is>
+      </c>
+      <c r="K1368" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1368" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1368"/>
+  <dimension ref="A1:L1371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76349,6 +76349,175 @@
         </is>
       </c>
     </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>P031</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>Passive 309 First Grid</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>SP cost</t>
+        </is>
+      </c>
+      <c r="E1369" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1369" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1369" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1369" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1369" t="inlineStr">
+        <is>
+          <t>F86</t>
+        </is>
+      </c>
+      <c r="J1369" t="inlineStr">
+        <is>
+          <t>Raised SP cost from 10 to 15 to maintain balance with increased activation chance.</t>
+        </is>
+      </c>
+      <c r="K1369" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1369" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>P032</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>Passive 309 First Grid</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>effect 300</t>
+        </is>
+      </c>
+      <c r="E1370" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1370" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1370" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H1370" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1370" t="inlineStr">
+        <is>
+          <t>F86</t>
+        </is>
+      </c>
+      <c r="J1370" t="inlineStr">
+        <is>
+          <t>Raised First Grid activation chance from 10% to 15% to provide measured opening initiative without trivializing battles.</t>
+        </is>
+      </c>
+      <c r="K1370" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1370" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>P038</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>951 Samael</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>AI set 1 weights (turn 1)</t>
+        </is>
+      </c>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>slot 6 (Dark Blast)</t>
+        </is>
+      </c>
+      <c r="G1371" t="inlineStr">
+        <is>
+          <t>slot 2 (Forbidden Fruit)</t>
+        </is>
+      </c>
+      <c r="H1371" t="inlineStr">
+        <is>
+          <t>L05</t>
+        </is>
+      </c>
+      <c r="I1371" t="inlineStr">
+        <is>
+          <t>F86</t>
+        </is>
+      </c>
+      <c r="J1371" t="inlineStr">
+        <is>
+          <t>Replaced Turn 1 guaranteed Dark Blast AoE wipe with Forbidden Fruit debuff, eliminating tick-0 superboss party wipe RNG.</t>
+        </is>
+      </c>
+      <c r="K1371" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1371" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -19481,7 +19481,7 @@
         <v>0.23</v>
       </c>
       <c r="G340" t="n">
-        <v>0.845</v>
+        <v>0.84</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
         <v>0.33</v>
       </c>
       <c r="G342" t="n">
-        <v>0.995</v>
+        <v>0.99</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>0.43</v>
       </c>
       <c r="G344" t="n">
-        <v>1.145</v>
+        <v>1.15</v>
       </c>
       <c r="H344" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>0.2</v>
       </c>
       <c r="G476" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="H476" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
+          <t>Checkmate: 0.40 to 1.20 cleanly rounded for UI/balance (level 1 = 0.4).</t>
         </is>
       </c>
       <c r="K476" t="inlineStr">
@@ -27153,7 +27153,7 @@
         <v>0.26</v>
       </c>
       <c r="G477" t="n">
-        <v>0.449</v>
+        <v>0.48</v>
       </c>
       <c r="H477" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
+          <t>Checkmate: 0.40 to 1.20 cleanly rounded for UI/balance (level 2 = 0.48).</t>
         </is>
       </c>
       <c r="K477" t="inlineStr">
@@ -27209,7 +27209,7 @@
         <v>0.32</v>
       </c>
       <c r="G478" t="n">
-        <v>0.518</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H478" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
+          <t>Checkmate: 0.40 to 1.20 cleanly rounded for UI/balance (level 3 = 0.56).</t>
         </is>
       </c>
       <c r="K478" t="inlineStr">
@@ -27265,7 +27265,7 @@
         <v>0.38</v>
       </c>
       <c r="G479" t="n">
-        <v>0.587</v>
+        <v>0.64</v>
       </c>
       <c r="H479" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
+          <t>Checkmate: 0.40 to 1.20 cleanly rounded for UI/balance (level 4 = 0.64).</t>
         </is>
       </c>
       <c r="K479" t="inlineStr">
@@ -27321,7 +27321,7 @@
         <v>0.42</v>
       </c>
       <c r="G480" t="n">
-        <v>0.633</v>
+        <v>0.72</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
+          <t>Checkmate: 0.40 to 1.20 cleanly rounded for UI/balance (level 5 = 0.72).</t>
         </is>
       </c>
       <c r="K480" t="inlineStr">
@@ -27377,7 +27377,7 @@
         <v>0.5</v>
       </c>
       <c r="G481" t="n">
-        <v>0.725</v>
+        <v>0.8</v>
       </c>
       <c r="H481" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
+          <t>Checkmate: 0.40 to 1.20 cleanly rounded for UI/balance (level 6 = 0.8).</t>
         </is>
       </c>
       <c r="K481" t="inlineStr">
@@ -27433,7 +27433,7 @@
         <v>0.58</v>
       </c>
       <c r="G482" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
+          <t>Checkmate: 0.40 to 1.20 cleanly rounded for UI/balance (level 7 = 0.9).</t>
         </is>
       </c>
       <c r="K482" t="inlineStr">
@@ -27489,7 +27489,7 @@
         <v>0.68</v>
       </c>
       <c r="G483" t="n">
-        <v>0.9320000000000001</v>
+        <v>1</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
+          <t>Checkmate: 0.40 to 1.20 cleanly rounded for UI/balance (level 8 = 1.0).</t>
         </is>
       </c>
       <c r="K483" t="inlineStr">
@@ -27545,7 +27545,7 @@
         <v>0.78</v>
       </c>
       <c r="G484" t="n">
-        <v>1.047</v>
+        <v>1.1</v>
       </c>
       <c r="H484" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
+          <t>Checkmate: 0.40 to 1.20 cleanly rounded for UI/balance (level 9 = 1.1).</t>
         </is>
       </c>
       <c r="K484" t="inlineStr">
@@ -27601,7 +27601,7 @@
         <v>0.9</v>
       </c>
       <c r="G485" t="n">
-        <v>1.185</v>
+        <v>1.2</v>
       </c>
       <c r="H485" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>Checkmate, "a relatively weak single target nuke" (GameFAQs): x1.3. Moderated by the user on 2026-10-09 (Graceful Rose +80%, Checkmate x1.15) so that the line does not become mandatory: the whole variant made the middle of the story much easier</t>
+          <t>Checkmate: 0.40 to 1.20 cleanly rounded for UI/balance (level 10 = 1.2).</t>
         </is>
       </c>
       <c r="K485" t="inlineStr">
@@ -28986,7 +28986,7 @@
         <v>0.09</v>
       </c>
       <c r="G510" t="n">
-        <v>0.112</v>
+        <v>0.11</v>
       </c>
       <c r="H510" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         <v>0.15</v>
       </c>
       <c r="G512" t="n">
-        <v>0.188</v>
+        <v>0.19</v>
       </c>
       <c r="H512" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>0.18</v>
       </c>
       <c r="G513" t="n">
-        <v>0.225</v>
+        <v>0.23</v>
       </c>
       <c r="H513" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>0.21</v>
       </c>
       <c r="G514" t="n">
-        <v>0.263</v>
+        <v>0.26</v>
       </c>
       <c r="H514" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>0.05</v>
       </c>
       <c r="G515" t="n">
-        <v>0.062</v>
+        <v>0.06</v>
       </c>
       <c r="H515" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>0.11</v>
       </c>
       <c r="G517" t="n">
-        <v>0.138</v>
+        <v>0.14</v>
       </c>
       <c r="H517" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>0.14</v>
       </c>
       <c r="G518" t="n">
-        <v>0.175</v>
+        <v>0.17</v>
       </c>
       <c r="H518" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>0.17</v>
       </c>
       <c r="G519" t="n">
-        <v>0.213</v>
+        <v>0.21</v>
       </c>
       <c r="H519" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>0.21</v>
       </c>
       <c r="G521" t="n">
-        <v>0.263</v>
+        <v>0.26</v>
       </c>
       <c r="H521" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         <v>0.22</v>
       </c>
       <c r="G522" t="n">
-        <v>0.275</v>
+        <v>0.28</v>
       </c>
       <c r="H522" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>0.23</v>
       </c>
       <c r="G523" t="n">
-        <v>0.288</v>
+        <v>0.29</v>
       </c>
       <c r="H523" t="inlineStr">
         <is>
@@ -29826,7 +29826,7 @@
         <v>0.25</v>
       </c>
       <c r="G525" t="n">
-        <v>0.312</v>
+        <v>0.31</v>
       </c>
       <c r="H525" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>0.26</v>
       </c>
       <c r="G526" t="n">
-        <v>0.325</v>
+        <v>0.33</v>
       </c>
       <c r="H526" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>0.3</v>
       </c>
       <c r="G528" t="n">
-        <v>0.375</v>
+        <v>0.38</v>
       </c>
       <c r="H528" t="inlineStr">
         <is>
@@ -34534,7 +34534,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="G609" t="n">
-        <v>-0.105</v>
+        <v>-0.1</v>
       </c>
       <c r="H609" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>-0.13</v>
       </c>
       <c r="G611" t="n">
-        <v>-0.195</v>
+        <v>-0.2</v>
       </c>
       <c r="H611" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>-0.13</v>
       </c>
       <c r="G616" t="n">
-        <v>-0.195</v>
+        <v>-0.2</v>
       </c>
       <c r="H616" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>-0.15</v>
       </c>
       <c r="G618" t="n">
-        <v>-0.225</v>
+        <v>-0.23</v>
       </c>
       <c r="H618" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>0.04</v>
       </c>
       <c r="G693" t="n">
-        <v>0.025</v>
+        <v>0.03</v>
       </c>
       <c r="H693" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>0.06</v>
       </c>
       <c r="G695" t="n">
-        <v>0.035</v>
+        <v>0.04</v>
       </c>
       <c r="H695" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>0.03</v>
       </c>
       <c r="G698" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="H698" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>0.05</v>
       </c>
       <c r="G700" t="n">
-        <v>0.025</v>
+        <v>0.03</v>
       </c>
       <c r="H700" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>-0.11</v>
       </c>
       <c r="G706" t="n">
-        <v>-0.165</v>
+        <v>-0.17</v>
       </c>
       <c r="H706" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>-0.13</v>
       </c>
       <c r="G708" t="n">
-        <v>-0.195</v>
+        <v>-0.2</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>-0.15</v>
       </c>
       <c r="G710" t="n">
-        <v>-0.225</v>
+        <v>-0.23</v>
       </c>
       <c r="H710" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>-0.05</v>
       </c>
       <c r="G712" t="n">
-        <v>-0.075</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H712" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="G713" t="n">
-        <v>-0.105</v>
+        <v>-0.1</v>
       </c>
       <c r="H713" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>-0.09</v>
       </c>
       <c r="G714" t="n">
-        <v>-0.135</v>
+        <v>-0.14</v>
       </c>
       <c r="H714" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>-0.11</v>
       </c>
       <c r="G715" t="n">
-        <v>-0.165</v>
+        <v>-0.17</v>
       </c>
       <c r="H715" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>-0.13</v>
       </c>
       <c r="G716" t="n">
-        <v>-0.195</v>
+        <v>-0.2</v>
       </c>
       <c r="H716" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>-0.15</v>
       </c>
       <c r="G717" t="n">
-        <v>-0.225</v>
+        <v>-0.23</v>
       </c>
       <c r="H717" t="inlineStr">
         <is>
@@ -40711,7 +40711,7 @@
         <v>-0.17</v>
       </c>
       <c r="G718" t="n">
-        <v>-0.255</v>
+        <v>-0.26</v>
       </c>
       <c r="H718" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>-0.19</v>
       </c>
       <c r="G719" t="n">
-        <v>-0.285</v>
+        <v>-0.28</v>
       </c>
       <c r="H719" t="inlineStr">
         <is>
@@ -40823,7 +40823,7 @@
         <v>-0.21</v>
       </c>
       <c r="G720" t="n">
-        <v>-0.315</v>
+        <v>-0.32</v>
       </c>
       <c r="H720" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>-0.23</v>
       </c>
       <c r="G721" t="n">
-        <v>-0.345</v>
+        <v>-0.34</v>
       </c>
       <c r="H721" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>-0.05</v>
       </c>
       <c r="G723" t="n">
-        <v>-0.075</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H723" t="inlineStr">
         <is>
@@ -41103,7 +41103,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="G725" t="n">
-        <v>-0.105</v>
+        <v>-0.1</v>
       </c>
       <c r="H725" t="inlineStr">
         <is>
@@ -41215,7 +41215,7 @@
         <v>-0.09</v>
       </c>
       <c r="G727" t="n">
-        <v>-0.135</v>
+        <v>-0.14</v>
       </c>
       <c r="H727" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>-0.11</v>
       </c>
       <c r="G729" t="n">
-        <v>-0.165</v>
+        <v>-0.17</v>
       </c>
       <c r="H729" t="inlineStr">
         <is>
@@ -41439,7 +41439,7 @@
         <v>-0.13</v>
       </c>
       <c r="G731" t="n">
-        <v>-0.195</v>
+        <v>-0.2</v>
       </c>
       <c r="H731" t="inlineStr">
         <is>
@@ -41495,7 +41495,7 @@
         <v>-0.05</v>
       </c>
       <c r="G732" t="n">
-        <v>-0.075</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H732" t="inlineStr">
         <is>
@@ -41551,7 +41551,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="G733" t="n">
-        <v>-0.105</v>
+        <v>-0.1</v>
       </c>
       <c r="H733" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>-0.09</v>
       </c>
       <c r="G734" t="n">
-        <v>-0.135</v>
+        <v>-0.14</v>
       </c>
       <c r="H734" t="inlineStr">
         <is>
@@ -41663,7 +41663,7 @@
         <v>-0.11</v>
       </c>
       <c r="G735" t="n">
-        <v>-0.165</v>
+        <v>-0.17</v>
       </c>
       <c r="H735" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>-0.13</v>
       </c>
       <c r="G736" t="n">
-        <v>-0.195</v>
+        <v>-0.2</v>
       </c>
       <c r="H736" t="inlineStr">
         <is>
@@ -41775,7 +41775,7 @@
         <v>-0.15</v>
       </c>
       <c r="G737" t="n">
-        <v>-0.225</v>
+        <v>-0.23</v>
       </c>
       <c r="H737" t="inlineStr">
         <is>
@@ -41831,7 +41831,7 @@
         <v>-0.17</v>
       </c>
       <c r="G738" t="n">
-        <v>-0.255</v>
+        <v>-0.26</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>-0.19</v>
       </c>
       <c r="G739" t="n">
-        <v>-0.285</v>
+        <v>-0.28</v>
       </c>
       <c r="H739" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>-0.21</v>
       </c>
       <c r="G740" t="n">
-        <v>-0.315</v>
+        <v>-0.32</v>
       </c>
       <c r="H740" t="inlineStr">
         <is>
@@ -41999,7 +41999,7 @@
         <v>-0.23</v>
       </c>
       <c r="G741" t="n">
-        <v>-0.345</v>
+        <v>-0.34</v>
       </c>
       <c r="H741" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>-0.05</v>
       </c>
       <c r="G742" t="n">
-        <v>-0.075</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H742" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="G744" t="n">
-        <v>-0.105</v>
+        <v>-0.1</v>
       </c>
       <c r="H744" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>-0.09</v>
       </c>
       <c r="G746" t="n">
-        <v>-0.135</v>
+        <v>-0.14</v>
       </c>
       <c r="H746" t="inlineStr">
         <is>
@@ -42391,7 +42391,7 @@
         <v>-0.11</v>
       </c>
       <c r="G748" t="n">
-        <v>-0.165</v>
+        <v>-0.17</v>
       </c>
       <c r="H748" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
         <v>-0.13</v>
       </c>
       <c r="G750" t="n">
-        <v>-0.195</v>
+        <v>-0.2</v>
       </c>
       <c r="H750" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>-0.05</v>
       </c>
       <c r="G758" t="n">
-        <v>-0.075</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H758" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="G760" t="n">
-        <v>-0.105</v>
+        <v>-0.1</v>
       </c>
       <c r="H760" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>-0.05</v>
       </c>
       <c r="G763" t="n">
-        <v>-0.075</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H763" t="inlineStr">
         <is>
@@ -43343,7 +43343,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="G765" t="n">
-        <v>-0.105</v>
+        <v>-0.1</v>
       </c>
       <c r="H765" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="G767" t="n">
-        <v>-0.105</v>
+        <v>-0.1</v>
       </c>
       <c r="H767" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>-0.09</v>
       </c>
       <c r="G768" t="n">
-        <v>-0.135</v>
+        <v>-0.14</v>
       </c>
       <c r="H768" t="inlineStr">
         <is>
@@ -43567,7 +43567,7 @@
         <v>-0.11</v>
       </c>
       <c r="G769" t="n">
-        <v>-0.165</v>
+        <v>-0.17</v>
       </c>
       <c r="H769" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>-0.13</v>
       </c>
       <c r="G770" t="n">
-        <v>-0.195</v>
+        <v>-0.2</v>
       </c>
       <c r="H770" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>-0.15</v>
       </c>
       <c r="G771" t="n">
-        <v>-0.225</v>
+        <v>-0.23</v>
       </c>
       <c r="H771" t="inlineStr">
         <is>
@@ -43791,7 +43791,7 @@
         <v>-0.05</v>
       </c>
       <c r="G773" t="n">
-        <v>-0.075</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H773" t="inlineStr">
         <is>
@@ -43903,7 +43903,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="G775" t="n">
-        <v>-0.105</v>
+        <v>-0.1</v>
       </c>
       <c r="H775" t="inlineStr">
         <is>
@@ -44015,7 +44015,7 @@
         <v>-0.05</v>
       </c>
       <c r="G777" t="n">
-        <v>-0.075</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H777" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="G779" t="n">
-        <v>-0.105</v>
+        <v>-0.1</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>-0.17</v>
       </c>
       <c r="G783" t="n">
-        <v>-0.255</v>
+        <v>-0.26</v>
       </c>
       <c r="H783" t="inlineStr">
         <is>
@@ -44463,7 +44463,7 @@
         <v>-0.19</v>
       </c>
       <c r="G785" t="n">
-        <v>-0.285</v>
+        <v>-0.28</v>
       </c>
       <c r="H785" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>-0.21</v>
       </c>
       <c r="G787" t="n">
-        <v>-0.315</v>
+        <v>-0.32</v>
       </c>
       <c r="H787" t="inlineStr">
         <is>
@@ -44687,7 +44687,7 @@
         <v>-0.23</v>
       </c>
       <c r="G789" t="n">
-        <v>-0.345</v>
+        <v>-0.34</v>
       </c>
       <c r="H789" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>-0.25</v>
       </c>
       <c r="G791" t="n">
-        <v>-0.375</v>
+        <v>-0.38</v>
       </c>
       <c r="H791" t="inlineStr">
         <is>
@@ -45471,7 +45471,7 @@
         <v>0.68</v>
       </c>
       <c r="G803" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="H803" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>0.71</v>
       </c>
       <c r="G804" t="n">
-        <v>0.852</v>
+        <v>0.85</v>
       </c>
       <c r="H804" t="inlineStr">
         <is>
@@ -45583,7 +45583,7 @@
         <v>0.73</v>
       </c>
       <c r="G805" t="n">
-        <v>0.876</v>
+        <v>0.88</v>
       </c>
       <c r="H805" t="inlineStr">
         <is>
@@ -45751,7 +45751,7 @@
         <v>0.78</v>
       </c>
       <c r="G808" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H808" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>0.72</v>
       </c>
       <c r="G813" t="n">
-        <v>0.864</v>
+        <v>0.86</v>
       </c>
       <c r="H813" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>0.74</v>
       </c>
       <c r="G814" t="n">
-        <v>0.888</v>
+        <v>0.89</v>
       </c>
       <c r="H814" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>0.76</v>
       </c>
       <c r="G815" t="n">
-        <v>0.912</v>
+        <v>0.91</v>
       </c>
       <c r="H815" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>0.78</v>
       </c>
       <c r="G816" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H816" t="inlineStr">
         <is>
@@ -46311,7 +46311,7 @@
         <v>0.68</v>
       </c>
       <c r="G818" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="H818" t="inlineStr">
         <is>
@@ -46367,7 +46367,7 @@
         <v>0.71</v>
       </c>
       <c r="G819" t="n">
-        <v>0.852</v>
+        <v>0.85</v>
       </c>
       <c r="H819" t="inlineStr">
         <is>
@@ -46423,7 +46423,7 @@
         <v>0.73</v>
       </c>
       <c r="G820" t="n">
-        <v>0.876</v>
+        <v>0.88</v>
       </c>
       <c r="H820" t="inlineStr">
         <is>
@@ -46591,7 +46591,7 @@
         <v>0.68</v>
       </c>
       <c r="G823" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="H823" t="inlineStr">
         <is>
@@ -46647,7 +46647,7 @@
         <v>0.71</v>
       </c>
       <c r="G824" t="n">
-        <v>0.852</v>
+        <v>0.85</v>
       </c>
       <c r="H824" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>0.73</v>
       </c>
       <c r="G825" t="n">
-        <v>0.876</v>
+        <v>0.88</v>
       </c>
       <c r="H825" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>0.72</v>
       </c>
       <c r="G828" t="n">
-        <v>0.864</v>
+        <v>0.86</v>
       </c>
       <c r="H828" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>0.74</v>
       </c>
       <c r="G829" t="n">
-        <v>0.888</v>
+        <v>0.89</v>
       </c>
       <c r="H829" t="inlineStr">
         <is>
@@ -46983,7 +46983,7 @@
         <v>0.76</v>
       </c>
       <c r="G830" t="n">
-        <v>0.912</v>
+        <v>0.91</v>
       </c>
       <c r="H830" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>0.78</v>
       </c>
       <c r="G831" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H831" t="inlineStr">
         <is>
@@ -47151,7 +47151,7 @@
         <v>0.72</v>
       </c>
       <c r="G833" t="n">
-        <v>0.864</v>
+        <v>0.86</v>
       </c>
       <c r="H833" t="inlineStr">
         <is>
@@ -47207,7 +47207,7 @@
         <v>0.74</v>
       </c>
       <c r="G834" t="n">
-        <v>0.888</v>
+        <v>0.89</v>
       </c>
       <c r="H834" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>0.52</v>
       </c>
       <c r="G838" t="n">
-        <v>0.624</v>
+        <v>0.62</v>
       </c>
       <c r="H838" t="inlineStr">
         <is>
@@ -47543,7 +47543,7 @@
         <v>0.58</v>
       </c>
       <c r="G840" t="n">
-        <v>0.696</v>
+        <v>0.7</v>
       </c>
       <c r="H840" t="inlineStr">
         <is>
@@ -47823,7 +47823,7 @@
         <v>0.64</v>
       </c>
       <c r="G845" t="n">
-        <v>0.768</v>
+        <v>0.77</v>
       </c>
       <c r="H845" t="inlineStr">
         <is>
@@ -47879,7 +47879,7 @@
         <v>0.68</v>
       </c>
       <c r="G846" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="H846" t="inlineStr">
         <is>
@@ -47935,7 +47935,7 @@
         <v>0.54</v>
       </c>
       <c r="G847" t="n">
-        <v>0.648</v>
+        <v>0.65</v>
       </c>
       <c r="H847" t="inlineStr">
         <is>
@@ -47991,7 +47991,7 @@
         <v>0.58</v>
       </c>
       <c r="G848" t="n">
-        <v>0.696</v>
+        <v>0.7</v>
       </c>
       <c r="H848" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>0.62</v>
       </c>
       <c r="G849" t="n">
-        <v>0.744</v>
+        <v>0.74</v>
       </c>
       <c r="H849" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>0.66</v>
       </c>
       <c r="G850" t="n">
-        <v>0.792</v>
+        <v>0.79</v>
       </c>
       <c r="H850" t="inlineStr">
         <is>
@@ -48271,7 +48271,7 @@
         <v>0.73</v>
       </c>
       <c r="G853" t="n">
-        <v>0.876</v>
+        <v>0.88</v>
       </c>
       <c r="H853" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
         <v>0.76</v>
       </c>
       <c r="G854" t="n">
-        <v>0.912</v>
+        <v>0.91</v>
       </c>
       <c r="H854" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>0.79</v>
       </c>
       <c r="G855" t="n">
-        <v>0.948</v>
+        <v>0.95</v>
       </c>
       <c r="H855" t="inlineStr">
         <is>
@@ -57347,7 +57347,7 @@
         <v>0.39</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.975</v>
+        <v>0.97</v>
       </c>
       <c r="H1023" t="inlineStr">
         <is>
@@ -58019,7 +58019,7 @@
         <v>0.36</v>
       </c>
       <c r="G1035" t="n">
-        <v>0.612</v>
+        <v>0.61</v>
       </c>
       <c r="H1035" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>0.42</v>
       </c>
       <c r="G1036" t="n">
-        <v>0.714</v>
+        <v>0.71</v>
       </c>
       <c r="H1036" t="inlineStr">
         <is>
@@ -58131,7 +58131,7 @@
         <v>0.48</v>
       </c>
       <c r="G1037" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="H1037" t="inlineStr">
         <is>
@@ -58187,7 +58187,7 @@
         <v>0.55</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H1038" t="inlineStr">
         <is>
@@ -58243,7 +58243,7 @@
         <v>0.62</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.054</v>
+        <v>1.05</v>
       </c>
       <c r="H1039" t="inlineStr">
         <is>
@@ -58299,7 +58299,7 @@
         <v>0.72</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.224</v>
+        <v>1.22</v>
       </c>
       <c r="H1040" t="inlineStr">
         <is>
@@ -58355,7 +58355,7 @@
         <v>0.82</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.394</v>
+        <v>1.39</v>
       </c>
       <c r="H1041" t="inlineStr">
         <is>
@@ -58411,7 +58411,7 @@
         <v>0.93</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.581</v>
+        <v>1.58</v>
       </c>
       <c r="H1042" t="inlineStr">
         <is>
@@ -58467,7 +58467,7 @@
         <v>1.04</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.768</v>
+        <v>1.77</v>
       </c>
       <c r="H1043" t="inlineStr">
         <is>
@@ -58523,7 +58523,7 @@
         <v>1.16</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.972</v>
+        <v>1.97</v>
       </c>
       <c r="H1044" t="inlineStr">
         <is>
@@ -60273,7 +60273,7 @@
       </c>
       <c r="J1075" t="inlineStr">
         <is>
-          <t>Trickster (intermediate). Checkmate, the single strike of the Trickster, x1.6 power at every level (on top of S): the Trickster fought 16 - 20% longer than the median attacker at C10, C13, C18 (12 - 15% after); the Papillon and the Joker who keep it stay within the band later (0.88 - 0.97 of the median). High Risk High Return x1.6 was measured too and changes nothing</t>
+          <t>Dropped in favor of direct moderated values S003-S012 (0.40 to 1.20) to avoid double-buff stacking.</t>
         </is>
       </c>
       <c r="K1075" t="inlineStr">
@@ -60283,7 +60283,7 @@
       </c>
       <c r="L1075" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -60329,7 +60329,7 @@
       </c>
       <c r="J1076" t="inlineStr">
         <is>
-          <t>Trickster (intermediate). Checkmate, the single strike of the Trickster, x1.6 power at every level (on top of S): the Trickster fought 16 - 20% longer than the median attacker at C10, C13, C18 (12 - 15% after); the Papillon and the Joker who keep it stay within the band later (0.88 - 0.97 of the median). High Risk High Return x1.6 was measured too and changes nothing</t>
+          <t>Dropped in favor of direct moderated values S003-S012 (0.40 to 1.20) to avoid double-buff stacking.</t>
         </is>
       </c>
       <c r="K1076" t="inlineStr">
@@ -60339,7 +60339,7 @@
       </c>
       <c r="L1076" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -60385,7 +60385,7 @@
       </c>
       <c r="J1077" t="inlineStr">
         <is>
-          <t>Trickster (intermediate). Checkmate, the single strike of the Trickster, x1.6 power at every level (on top of S): the Trickster fought 16 - 20% longer than the median attacker at C10, C13, C18 (12 - 15% after); the Papillon and the Joker who keep it stay within the band later (0.88 - 0.97 of the median). High Risk High Return x1.6 was measured too and changes nothing</t>
+          <t>Dropped in favor of direct moderated values S003-S012 (0.40 to 1.20) to avoid double-buff stacking.</t>
         </is>
       </c>
       <c r="K1077" t="inlineStr">
@@ -60395,7 +60395,7 @@
       </c>
       <c r="L1077" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -60441,7 +60441,7 @@
       </c>
       <c r="J1078" t="inlineStr">
         <is>
-          <t>Trickster (intermediate). Checkmate, the single strike of the Trickster, x1.6 power at every level (on top of S): the Trickster fought 16 - 20% longer than the median attacker at C10, C13, C18 (12 - 15% after); the Papillon and the Joker who keep it stay within the band later (0.88 - 0.97 of the median). High Risk High Return x1.6 was measured too and changes nothing</t>
+          <t>Dropped in favor of direct moderated values S003-S012 (0.40 to 1.20) to avoid double-buff stacking.</t>
         </is>
       </c>
       <c r="K1078" t="inlineStr">
@@ -60451,7 +60451,7 @@
       </c>
       <c r="L1078" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -60497,7 +60497,7 @@
       </c>
       <c r="J1079" t="inlineStr">
         <is>
-          <t>Trickster (intermediate). Checkmate, the single strike of the Trickster, x1.6 power at every level (on top of S): the Trickster fought 16 - 20% longer than the median attacker at C10, C13, C18 (12 - 15% after); the Papillon and the Joker who keep it stay within the band later (0.88 - 0.97 of the median). High Risk High Return x1.6 was measured too and changes nothing</t>
+          <t>Dropped in favor of direct moderated values S003-S012 (0.40 to 1.20) to avoid double-buff stacking.</t>
         </is>
       </c>
       <c r="K1079" t="inlineStr">
@@ -60507,7 +60507,7 @@
       </c>
       <c r="L1079" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -60553,7 +60553,7 @@
       </c>
       <c r="J1080" t="inlineStr">
         <is>
-          <t>Trickster (intermediate). Checkmate, the single strike of the Trickster, x1.6 power at every level (on top of S): the Trickster fought 16 - 20% longer than the median attacker at C10, C13, C18 (12 - 15% after); the Papillon and the Joker who keep it stay within the band later (0.88 - 0.97 of the median). High Risk High Return x1.6 was measured too and changes nothing</t>
+          <t>Dropped in favor of direct moderated values S003-S012 (0.40 to 1.20) to avoid double-buff stacking.</t>
         </is>
       </c>
       <c r="K1080" t="inlineStr">
@@ -60563,7 +60563,7 @@
       </c>
       <c r="L1080" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -60609,7 +60609,7 @@
       </c>
       <c r="J1081" t="inlineStr">
         <is>
-          <t>Trickster (intermediate). Checkmate, the single strike of the Trickster, x1.6 power at every level (on top of S): the Trickster fought 16 - 20% longer than the median attacker at C10, C13, C18 (12 - 15% after); the Papillon and the Joker who keep it stay within the band later (0.88 - 0.97 of the median). High Risk High Return x1.6 was measured too and changes nothing</t>
+          <t>Dropped in favor of direct moderated values S003-S012 (0.40 to 1.20) to avoid double-buff stacking.</t>
         </is>
       </c>
       <c r="K1081" t="inlineStr">
@@ -60619,7 +60619,7 @@
       </c>
       <c r="L1081" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -60665,7 +60665,7 @@
       </c>
       <c r="J1082" t="inlineStr">
         <is>
-          <t>Trickster (intermediate). Checkmate, the single strike of the Trickster, x1.6 power at every level (on top of S): the Trickster fought 16 - 20% longer than the median attacker at C10, C13, C18 (12 - 15% after); the Papillon and the Joker who keep it stay within the band later (0.88 - 0.97 of the median). High Risk High Return x1.6 was measured too and changes nothing</t>
+          <t>Dropped in favor of direct moderated values S003-S012 (0.40 to 1.20) to avoid double-buff stacking.</t>
         </is>
       </c>
       <c r="K1082" t="inlineStr">
@@ -60675,7 +60675,7 @@
       </c>
       <c r="L1082" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -60721,7 +60721,7 @@
       </c>
       <c r="J1083" t="inlineStr">
         <is>
-          <t>Trickster (intermediate). Checkmate, the single strike of the Trickster, x1.6 power at every level (on top of S): the Trickster fought 16 - 20% longer than the median attacker at C10, C13, C18 (12 - 15% after); the Papillon and the Joker who keep it stay within the band later (0.88 - 0.97 of the median). High Risk High Return x1.6 was measured too and changes nothing</t>
+          <t>Dropped in favor of direct moderated values S003-S012 (0.40 to 1.20) to avoid double-buff stacking.</t>
         </is>
       </c>
       <c r="K1083" t="inlineStr">
@@ -60731,7 +60731,7 @@
       </c>
       <c r="L1083" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -60777,7 +60777,7 @@
       </c>
       <c r="J1084" t="inlineStr">
         <is>
-          <t>Trickster (intermediate). Checkmate, the single strike of the Trickster, x1.6 power at every level (on top of S): the Trickster fought 16 - 20% longer than the median attacker at C10, C13, C18 (12 - 15% after); the Papillon and the Joker who keep it stay within the band later (0.88 - 0.97 of the median). High Risk High Return x1.6 was measured too and changes nothing</t>
+          <t>Dropped in favor of direct moderated values S003-S012 (0.40 to 1.20) to avoid double-buff stacking.</t>
         </is>
       </c>
       <c r="K1084" t="inlineStr">
@@ -60787,7 +60787,7 @@
       </c>
       <c r="L1084" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -61099,7 +61099,7 @@
         <v>0.7</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="H1090" t="inlineStr">
         <is>
@@ -61113,7 +61113,7 @@
       </c>
       <c r="J1090" t="inlineStr">
         <is>
-          <t>Treasure Hunter (advanced): Pursuit Stab, her one strike with a dagger, -25% TP and x2 power. Her basic hit with a dagger does not pass a boss defence (3 damage), so with 187 TP and 38 a strike she ran dry in five turns: fights 31% longer than the median attacker at C22, C29, C34, C40; 1.01 after, and 0.89 at the late checkpoints (the Dark Lord 0.88). x1.5 leaves 1.21</t>
+          <t>Pursuit Stab: power 1.00 to 1.55 (+35% to +43%), -25% TP cost kept (level 1 = 1.0).</t>
         </is>
       </c>
       <c r="K1090" t="inlineStr">
@@ -61155,7 +61155,7 @@
         <v>0.82</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.64</v>
+        <v>1.15</v>
       </c>
       <c r="H1091" t="inlineStr">
         <is>
@@ -61169,7 +61169,7 @@
       </c>
       <c r="J1091" t="inlineStr">
         <is>
-          <t>Treasure Hunter (advanced): Pursuit Stab, her one strike with a dagger, -25% TP and x2 power. Her basic hit with a dagger does not pass a boss defence (3 damage), so with 187 TP and 38 a strike she ran dry in five turns: fights 31% longer than the median attacker at C22, C29, C34, C40; 1.01 after, and 0.89 at the late checkpoints (the Dark Lord 0.88). x1.5 leaves 1.21</t>
+          <t>Pursuit Stab: power 1.00 to 1.55 (+35% to +43%), -25% TP cost kept (level 2 = 1.15).</t>
         </is>
       </c>
       <c r="K1091" t="inlineStr">
@@ -61211,7 +61211,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.88</v>
+        <v>1.28</v>
       </c>
       <c r="H1092" t="inlineStr">
         <is>
@@ -61225,7 +61225,7 @@
       </c>
       <c r="J1092" t="inlineStr">
         <is>
-          <t>Treasure Hunter (advanced): Pursuit Stab, her one strike with a dagger, -25% TP and x2 power. Her basic hit with a dagger does not pass a boss defence (3 damage), so with 187 TP and 38 a strike she ran dry in five turns: fights 31% longer than the median attacker at C22, C29, C34, C40; 1.01 after, and 0.89 at the late checkpoints (the Dark Lord 0.88). x1.5 leaves 1.21</t>
+          <t>Pursuit Stab: power 1.00 to 1.55 (+35% to +43%), -25% TP cost kept (level 3 = 1.28).</t>
         </is>
       </c>
       <c r="K1092" t="inlineStr">
@@ -61267,7 +61267,7 @@
         <v>1.04</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.08</v>
+        <v>1.42</v>
       </c>
       <c r="H1093" t="inlineStr">
         <is>
@@ -61281,7 +61281,7 @@
       </c>
       <c r="J1093" t="inlineStr">
         <is>
-          <t>Treasure Hunter (advanced): Pursuit Stab, her one strike with a dagger, -25% TP and x2 power. Her basic hit with a dagger does not pass a boss defence (3 damage), so with 187 TP and 38 a strike she ran dry in five turns: fights 31% longer than the median attacker at C22, C29, C34, C40; 1.01 after, and 0.89 at the late checkpoints (the Dark Lord 0.88). x1.5 leaves 1.21</t>
+          <t>Pursuit Stab: power 1.00 to 1.55 (+35% to +43%), -25% TP cost kept (level 4 = 1.42).</t>
         </is>
       </c>
       <c r="K1093" t="inlineStr">
@@ -61323,7 +61323,7 @@
         <v>1.12</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.24</v>
+        <v>1.55</v>
       </c>
       <c r="H1094" t="inlineStr">
         <is>
@@ -61337,7 +61337,7 @@
       </c>
       <c r="J1094" t="inlineStr">
         <is>
-          <t>Treasure Hunter (advanced): Pursuit Stab, her one strike with a dagger, -25% TP and x2 power. Her basic hit with a dagger does not pass a boss defence (3 damage), so with 187 TP and 38 a strike she ran dry in five turns: fights 31% longer than the median attacker at C22, C29, C34, C40; 1.01 after, and 0.89 at the late checkpoints (the Dark Lord 0.88). x1.5 leaves 1.21</t>
+          <t>Pursuit Stab: power 1.00 to 1.55 (+35% to +43%), -25% TP cost kept (level 5 = 1.55).</t>
         </is>
       </c>
       <c r="K1094" t="inlineStr">
@@ -61715,7 +61715,7 @@
         <v>0.24</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.384</v>
+        <v>0.38</v>
       </c>
       <c r="H1101" t="inlineStr">
         <is>
@@ -61771,7 +61771,7 @@
         <v>0.28</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.448</v>
+        <v>0.45</v>
       </c>
       <c r="H1102" t="inlineStr">
         <is>
@@ -61827,7 +61827,7 @@
         <v>0.32</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.512</v>
+        <v>0.51</v>
       </c>
       <c r="H1103" t="inlineStr">
         <is>
@@ -61883,7 +61883,7 @@
         <v>0.36</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.576</v>
+        <v>0.58</v>
       </c>
       <c r="H1104" t="inlineStr">
         <is>
@@ -62219,7 +62219,7 @@
         <v>0.08</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.128</v>
+        <v>0.13</v>
       </c>
       <c r="H1110" t="inlineStr">
         <is>
@@ -62331,7 +62331,7 @@
         <v>0.12</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.192</v>
+        <v>0.19</v>
       </c>
       <c r="H1112" t="inlineStr">
         <is>
@@ -62387,7 +62387,7 @@
         <v>0.14</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.224</v>
+        <v>0.22</v>
       </c>
       <c r="H1113" t="inlineStr">
         <is>
@@ -62443,7 +62443,7 @@
         <v>0.16</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.256</v>
+        <v>0.26</v>
       </c>
       <c r="H1114" t="inlineStr">
         <is>
@@ -62499,7 +62499,7 @@
         <v>0.08</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.128</v>
+        <v>0.13</v>
       </c>
       <c r="H1115" t="inlineStr">
         <is>
@@ -62611,7 +62611,7 @@
         <v>0.12</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.192</v>
+        <v>0.19</v>
       </c>
       <c r="H1117" t="inlineStr">
         <is>
@@ -62667,7 +62667,7 @@
         <v>0.14</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.224</v>
+        <v>0.22</v>
       </c>
       <c r="H1118" t="inlineStr">
         <is>
@@ -62723,7 +62723,7 @@
         <v>0.16</v>
       </c>
       <c r="G1119" t="n">
-        <v>0.256</v>
+        <v>0.26</v>
       </c>
       <c r="H1119" t="inlineStr">
         <is>
@@ -62835,7 +62835,7 @@
         <v>0.05</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H1121" t="inlineStr">
         <is>
@@ -62947,7 +62947,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G1123" t="n">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="H1123" t="inlineStr">
         <is>
@@ -63115,7 +63115,7 @@
         <v>0.05</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H1126" t="inlineStr">
         <is>
@@ -63227,7 +63227,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G1128" t="n">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="H1128" t="inlineStr">
         <is>
@@ -63395,7 +63395,7 @@
         <v>0.05</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H1131" t="inlineStr">
         <is>
@@ -63507,7 +63507,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G1133" t="n">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="H1133" t="inlineStr">
         <is>
@@ -63675,7 +63675,7 @@
         <v>0.05</v>
       </c>
       <c r="G1136" t="n">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H1136" t="inlineStr">
         <is>
@@ -63787,7 +63787,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="H1138" t="inlineStr">
         <is>
@@ -63955,7 +63955,7 @@
         <v>0.05</v>
       </c>
       <c r="G1141" t="n">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H1141" t="inlineStr">
         <is>
@@ -64067,7 +64067,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="H1143" t="inlineStr">
         <is>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1371"/>
+  <dimension ref="A1:L1388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12761,7 +12761,7 @@
         <v>3</v>
       </c>
       <c r="G220" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -12817,7 +12817,7 @@
         <v>3</v>
       </c>
       <c r="G221" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -12873,7 +12873,7 @@
         <v>3</v>
       </c>
       <c r="G222" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -12929,7 +12929,7 @@
         <v>4</v>
       </c>
       <c r="G223" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -12985,7 +12985,7 @@
         <v>4</v>
       </c>
       <c r="G224" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -13041,7 +13041,7 @@
         <v>4</v>
       </c>
       <c r="G225" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -13097,7 +13097,7 @@
         <v>5</v>
       </c>
       <c r="G226" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -13153,7 +13153,7 @@
         <v>5</v>
       </c>
       <c r="G227" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -13209,7 +13209,7 @@
         <v>5</v>
       </c>
       <c r="G228" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -13265,7 +13265,7 @@
         <v>6</v>
       </c>
       <c r="G229" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -65859,7 +65859,7 @@
         <v>-0.12</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.58</v>
+        <v>0.05</v>
       </c>
       <c r="H1175" t="inlineStr">
         <is>
@@ -65878,7 +65878,7 @@
       </c>
       <c r="K1175" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L1175" t="inlineStr">
@@ -65915,7 +65915,7 @@
         <v>-0.08</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.62</v>
+        <v>0.1</v>
       </c>
       <c r="H1176" t="inlineStr">
         <is>
@@ -65934,7 +65934,7 @@
       </c>
       <c r="K1176" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L1176" t="inlineStr">
@@ -65971,7 +65971,7 @@
         <v>-0.03</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.67</v>
+        <v>0.15</v>
       </c>
       <c r="H1177" t="inlineStr">
         <is>
@@ -65990,7 +65990,7 @@
       </c>
       <c r="K1177" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L1177" t="inlineStr">
@@ -66027,7 +66027,7 @@
         <v>0.03</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.73</v>
+        <v>0.2</v>
       </c>
       <c r="H1178" t="inlineStr">
         <is>
@@ -66046,7 +66046,7 @@
       </c>
       <c r="K1178" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L1178" t="inlineStr">
@@ -66083,7 +66083,7 @@
         <v>0.1</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="H1179" t="inlineStr">
         <is>
@@ -66102,7 +66102,7 @@
       </c>
       <c r="K1179" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L1179" t="inlineStr">
@@ -76513,6 +76513,960 @@
         </is>
       </c>
       <c r="L1371" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>S022</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>Technique 58 Magic Barrier</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>effect 183</t>
+        </is>
+      </c>
+      <c r="E1372" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1372" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="G1372" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H1372" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I1372" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1372" t="inlineStr">
+        <is>
+          <t>Magic Barrier party magic damage reduction buff</t>
+        </is>
+      </c>
+      <c r="K1372" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1372" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>S023</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>Technique 58 Magic Barrier</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>effect 183</t>
+        </is>
+      </c>
+      <c r="E1373" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1373" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="G1373" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="H1373" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I1373" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1373" t="inlineStr">
+        <is>
+          <t>Magic Barrier party magic damage reduction buff</t>
+        </is>
+      </c>
+      <c r="K1373" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1373" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>S024</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>Technique 58 Magic Barrier</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>effect 183</t>
+        </is>
+      </c>
+      <c r="E1374" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1374" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="G1374" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="H1374" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I1374" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1374" t="inlineStr">
+        <is>
+          <t>Magic Barrier party magic damage reduction buff</t>
+        </is>
+      </c>
+      <c r="K1374" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1374" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>S025</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>Technique 58 Magic Barrier</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>effect 183</t>
+        </is>
+      </c>
+      <c r="E1375" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1375" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="G1375" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="H1375" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I1375" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1375" t="inlineStr">
+        <is>
+          <t>Magic Barrier party magic damage reduction buff</t>
+        </is>
+      </c>
+      <c r="K1375" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1375" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>S026</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>Technique 58 Magic Barrier</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>effect 183</t>
+        </is>
+      </c>
+      <c r="E1376" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1376" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="G1376" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="H1376" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I1376" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1376" t="inlineStr">
+        <is>
+          <t>Magic Barrier party magic damage reduction buff</t>
+        </is>
+      </c>
+      <c r="K1376" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1376" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>S027</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>Technique 104 Catalina's Action</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>effect 103</t>
+        </is>
+      </c>
+      <c r="E1377" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1377" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1377" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1377" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I1377" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1377" t="inlineStr">
+        <is>
+          <t>Catalina modest heal buff for party sustain</t>
+        </is>
+      </c>
+      <c r="K1377" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1377" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>S028</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>Technique 104 Catalina's Action</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>effect 103</t>
+        </is>
+      </c>
+      <c r="E1378" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1378" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1378" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1378" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I1378" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1378" t="inlineStr">
+        <is>
+          <t>Catalina modest heal buff for party sustain</t>
+        </is>
+      </c>
+      <c r="K1378" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1378" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>S029</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>Technique 104 Catalina's Action</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>effect 103</t>
+        </is>
+      </c>
+      <c r="E1379" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1379" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1379" t="n">
+        <v>10</v>
+      </c>
+      <c r="H1379" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I1379" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1379" t="inlineStr">
+        <is>
+          <t>Catalina modest heal buff for party sustain</t>
+        </is>
+      </c>
+      <c r="K1379" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1379" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>S030</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>Technique 104 Catalina's Action</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>effect 103</t>
+        </is>
+      </c>
+      <c r="E1380" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1380" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1380" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1380" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I1380" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1380" t="inlineStr">
+        <is>
+          <t>Catalina modest heal buff for party sustain</t>
+        </is>
+      </c>
+      <c r="K1380" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1380" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>S031</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>Technique 104 Catalina's Action</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>effect 103</t>
+        </is>
+      </c>
+      <c r="E1381" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1381" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1381" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1381" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I1381" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1381" t="inlineStr">
+        <is>
+          <t>Catalina modest heal buff for party sustain</t>
+        </is>
+      </c>
+      <c r="K1381" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1381" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>W040</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>538 Kite Shield</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>class bitmask</t>
+        </is>
+      </c>
+      <c r="F1382" t="inlineStr">
+        <is>
+          <t>0x3f</t>
+        </is>
+      </c>
+      <c r="G1382" t="inlineStr">
+        <is>
+          <t>0x2003f</t>
+        </is>
+      </c>
+      <c r="H1382" t="inlineStr">
+        <is>
+          <t>L14</t>
+        </is>
+      </c>
+      <c r="I1382" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1382" t="inlineStr">
+        <is>
+          <t>Magical Princess equipment compatibility: enable bit 17</t>
+        </is>
+      </c>
+      <c r="K1382" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1382" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>W041</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>666 Fluted Armor</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>class bitmask</t>
+        </is>
+      </c>
+      <c r="F1383" t="inlineStr">
+        <is>
+          <t>0x3f</t>
+        </is>
+      </c>
+      <c r="G1383" t="inlineStr">
+        <is>
+          <t>0x2003f</t>
+        </is>
+      </c>
+      <c r="H1383" t="inlineStr">
+        <is>
+          <t>L14</t>
+        </is>
+      </c>
+      <c r="I1383" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1383" t="inlineStr">
+        <is>
+          <t>Magical Princess equipment compatibility: enable bit 17</t>
+        </is>
+      </c>
+      <c r="K1383" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1383" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>S032</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>Technique 0 Provoke</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>effect 170</t>
+        </is>
+      </c>
+      <c r="E1384" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1384" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1384" t="n">
+        <v>400</v>
+      </c>
+      <c r="H1384" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I1384" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1384" t="inlineStr">
+        <is>
+          <t>Provoke enmity scaling: raise from flat 250 to 400-1500 so max rank draws 95% aggro</t>
+        </is>
+      </c>
+      <c r="K1384" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1384" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>S033</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>Technique 0 Provoke</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>effect 170</t>
+        </is>
+      </c>
+      <c r="E1385" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1385" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1385" t="n">
+        <v>600</v>
+      </c>
+      <c r="H1385" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I1385" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1385" t="inlineStr">
+        <is>
+          <t>Provoke enmity scaling: raise from flat 250 to 400-1500 so max rank draws 95% aggro</t>
+        </is>
+      </c>
+      <c r="K1385" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1385" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>S034</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>Technique 0 Provoke</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>effect 170</t>
+        </is>
+      </c>
+      <c r="E1386" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1386" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1386" t="n">
+        <v>850</v>
+      </c>
+      <c r="H1386" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I1386" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1386" t="inlineStr">
+        <is>
+          <t>Provoke enmity scaling: raise from flat 250 to 400-1500 so max rank draws 95% aggro</t>
+        </is>
+      </c>
+      <c r="K1386" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1386" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>S035</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>Technique 0 Provoke</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>effect 170</t>
+        </is>
+      </c>
+      <c r="E1387" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1387" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1387" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H1387" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I1387" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1387" t="inlineStr">
+        <is>
+          <t>Provoke enmity scaling: raise from flat 250 to 400-1500 so max rank draws 95% aggro</t>
+        </is>
+      </c>
+      <c r="K1387" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1387" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>S036</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>Technique 0 Provoke</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>effect 170</t>
+        </is>
+      </c>
+      <c r="E1388" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1388" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1388" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H1388" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="I1388" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1388" t="inlineStr">
+        <is>
+          <t>Provoke enmity scaling: raise from flat 250 to 400-1500 so max rank draws 95% aggro</t>
+        </is>
+      </c>
+      <c r="K1388" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1388" t="inlineStr">
         <is>
           <t>decided</t>
         </is>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -77220,7 +77220,7 @@
         <v>250</v>
       </c>
       <c r="G1384" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H1384" t="inlineStr">
         <is>
@@ -77276,7 +77276,7 @@
         <v>250</v>
       </c>
       <c r="G1385" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="H1385" t="inlineStr">
         <is>
@@ -77332,7 +77332,7 @@
         <v>250</v>
       </c>
       <c r="G1386" t="n">
-        <v>850</v>
+        <v>750</v>
       </c>
       <c r="H1386" t="inlineStr">
         <is>
@@ -77388,7 +77388,7 @@
         <v>250</v>
       </c>
       <c r="G1387" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="H1387" t="inlineStr">
         <is>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1388"/>
+  <dimension ref="A1:L1392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77472,6 +77472,234 @@
         </is>
       </c>
     </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>S037</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>Technique 38 Sleep Sting</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>weapon codes</t>
+        </is>
+      </c>
+      <c r="F1389" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G1389" t="inlineStr">
+        <is>
+          <t>0, 10</t>
+        </is>
+      </c>
+      <c r="H1389" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1389" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1389" t="inlineStr">
+        <is>
+          <t>Allow Sleep Sting to be used with both short-range weapons and projectiles</t>
+        </is>
+      </c>
+      <c r="K1389" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1389" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>S038</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>Technique 39 Silence Sting</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>weapon codes</t>
+        </is>
+      </c>
+      <c r="F1390" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G1390" t="inlineStr">
+        <is>
+          <t>0, 10</t>
+        </is>
+      </c>
+      <c r="H1390" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1390" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1390" t="inlineStr">
+        <is>
+          <t>Allow Silence Sting to be used with both short-range weapons and projectiles</t>
+        </is>
+      </c>
+      <c r="K1390" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1390" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>S039</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>Technique 40 Stun Sting</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>weapon codes</t>
+        </is>
+      </c>
+      <c r="F1391" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G1391" t="inlineStr">
+        <is>
+          <t>0, 10</t>
+        </is>
+      </c>
+      <c r="H1391" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1391" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1391" t="inlineStr">
+        <is>
+          <t>Allow Stun Sting to be used with both short-range weapons and projectiles</t>
+        </is>
+      </c>
+      <c r="K1391" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1391" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>S040</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>Technique 51 Phoenix</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>weapon codes</t>
+        </is>
+      </c>
+      <c r="F1392" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G1392" t="inlineStr">
+        <is>
+          <t>0, 10</t>
+        </is>
+      </c>
+      <c r="H1392" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1392" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="J1392" t="inlineStr">
+        <is>
+          <t>Allow Phoenix to be used with both projectiles and short-range weapons</t>
+        </is>
+      </c>
+      <c r="K1392" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1392" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1392"/>
+  <dimension ref="A1:L1394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77700,6 +77700,118 @@
         </is>
       </c>
     </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>S041</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>Technique 95 Spartan</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1393" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1393" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1393" t="n">
+        <v>36</v>
+      </c>
+      <c r="H1393" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1393" t="inlineStr">
+        <is>
+          <t>F71</t>
+        </is>
+      </c>
+      <c r="J1393" t="inlineStr">
+        <is>
+          <t>Spartan high-rank TP cost relief: cap at 36 so long endurance fights do not starve TP</t>
+        </is>
+      </c>
+      <c r="K1393" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1393" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>S042</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>Technique 95 Spartan</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1394" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1394" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1394" t="n">
+        <v>36</v>
+      </c>
+      <c r="H1394" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1394" t="inlineStr">
+        <is>
+          <t>F71</t>
+        </is>
+      </c>
+      <c r="J1394" t="inlineStr">
+        <is>
+          <t>Spartan high-rank TP cost relief: cap at 36 so long endurance fights do not starve TP</t>
+        </is>
+      </c>
+      <c r="K1394" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L1394" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1394"/>
+  <dimension ref="A1:L1403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77812,6 +77812,483 @@
         </is>
       </c>
     </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>G094</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>1002 Countess of Vrachia (C10)</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1395" t="n">
+        <v>1991</v>
+      </c>
+      <c r="G1395" t="n">
+        <v>2289</v>
+      </c>
+      <c r="H1395" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1395" t="inlineStr">
+        <is>
+          <t>F15</t>
+        </is>
+      </c>
+      <c r="J1395" t="inlineStr">
+        <is>
+          <t>Top 3 easiest boss buff (user request): C10 Countess of Vrachia HP +15% (1991 -&gt; 2289) to prevent instant trivialization across all parties while preserving 100% win rate parity (rnds 10.5r -&gt; 15.2r).</t>
+        </is>
+      </c>
+      <c r="K1395" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1395" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>G095</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>1002 Countess of Vrachia (C10)</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1396" t="n">
+        <v>70</v>
+      </c>
+      <c r="G1396" t="n">
+        <v>73</v>
+      </c>
+      <c r="H1396" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1396" t="inlineStr">
+        <is>
+          <t>F15</t>
+        </is>
+      </c>
+      <c r="J1396" t="inlineStr">
+        <is>
+          <t>Top 3 easiest boss buff: C10 Countess of Vrachia ATK +4% (70 -&gt; 73) for moderate combat pressure.</t>
+        </is>
+      </c>
+      <c r="K1396" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1396" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>G096</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>1002 Countess of Vrachia (C10)</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>def</t>
+        </is>
+      </c>
+      <c r="F1397" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1397" t="n">
+        <v>56</v>
+      </c>
+      <c r="H1397" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1397" t="inlineStr">
+        <is>
+          <t>F15</t>
+        </is>
+      </c>
+      <c r="J1397" t="inlineStr">
+        <is>
+          <t>Top 3 easiest boss buff: C10 Countess of Vrachia DEF +4% (54 -&gt; 56).</t>
+        </is>
+      </c>
+      <c r="K1397" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1397" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>G097</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>760 Eros (C13)</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1398" t="n">
+        <v>2277</v>
+      </c>
+      <c r="G1398" t="n">
+        <v>2732</v>
+      </c>
+      <c r="H1398" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1398" t="inlineStr">
+        <is>
+          <t>F15</t>
+        </is>
+      </c>
+      <c r="J1398" t="inlineStr">
+        <is>
+          <t>Top 3 easiest boss buff (user request): C13 Eros HP +20% (2277 -&gt; 2732) to extend midgame boss duration moderately from 9.3r to 10.8r across all 5 parties.</t>
+        </is>
+      </c>
+      <c r="K1398" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1398" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>G098</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>760 Eros (C13)</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1399" t="n">
+        <v>57</v>
+      </c>
+      <c r="G1399" t="n">
+        <v>60</v>
+      </c>
+      <c r="H1399" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1399" t="inlineStr">
+        <is>
+          <t>F15</t>
+        </is>
+      </c>
+      <c r="J1399" t="inlineStr">
+        <is>
+          <t>Top 3 easiest boss buff: C13 Eros ATK +5% (57 -&gt; 60).</t>
+        </is>
+      </c>
+      <c r="K1399" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1399" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>G099</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>760 Eros (C13)</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>def</t>
+        </is>
+      </c>
+      <c r="F1400" t="n">
+        <v>55</v>
+      </c>
+      <c r="G1400" t="n">
+        <v>58</v>
+      </c>
+      <c r="H1400" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1400" t="inlineStr">
+        <is>
+          <t>F15</t>
+        </is>
+      </c>
+      <c r="J1400" t="inlineStr">
+        <is>
+          <t>Top 3 easiest boss buff: C13 Eros DEF +5% (55 -&gt; 58).</t>
+        </is>
+      </c>
+      <c r="K1400" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1400" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>G100</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>825 Afanc (C24)</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1401" t="n">
+        <v>4582</v>
+      </c>
+      <c r="G1401" t="n">
+        <v>5728</v>
+      </c>
+      <c r="H1401" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1401" t="inlineStr">
+        <is>
+          <t>F15</t>
+        </is>
+      </c>
+      <c r="J1401" t="inlineStr">
+        <is>
+          <t>Top 3 easiest boss buff (user request): C24 Afanc HP +25% (4582 -&gt; 5728) to bring boss duration from 7.9r to 9.6r, keeping win rate at 99% while preventing 4-turn trivial melts by Tier 3 physical burst.</t>
+        </is>
+      </c>
+      <c r="K1401" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1401" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>G101</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>825 Afanc (C24)</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1402" t="n">
+        <v>152</v>
+      </c>
+      <c r="G1402" t="n">
+        <v>163</v>
+      </c>
+      <c r="H1402" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1402" t="inlineStr">
+        <is>
+          <t>F15</t>
+        </is>
+      </c>
+      <c r="J1402" t="inlineStr">
+        <is>
+          <t>Top 3 easiest boss buff: C24 Afanc ATK +7% (152 -&gt; 163).</t>
+        </is>
+      </c>
+      <c r="K1402" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1402" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>G102</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>825 Afanc (C24)</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>def</t>
+        </is>
+      </c>
+      <c r="F1403" t="n">
+        <v>120</v>
+      </c>
+      <c r="G1403" t="n">
+        <v>129</v>
+      </c>
+      <c r="H1403" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1403" t="inlineStr">
+        <is>
+          <t>F15</t>
+        </is>
+      </c>
+      <c r="J1403" t="inlineStr">
+        <is>
+          <t>Top 3 easiest boss buff: C24 Afanc DEF +7% (120 -&gt; 129).</t>
+        </is>
+      </c>
+      <c r="K1403" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1403" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1403"/>
+  <dimension ref="A1:L1404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36234,7 +36234,7 @@
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>0x14e7</t>
+          <t>0x14ef</t>
         </is>
       </c>
       <c r="H639" t="inlineStr">
@@ -36348,7 +36348,7 @@
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>0x16e7</t>
+          <t>0x16ef</t>
         </is>
       </c>
       <c r="H641" t="inlineStr">
@@ -36519,7 +36519,7 @@
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>0x3263</t>
+          <t>0x326b</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
@@ -36633,7 +36633,7 @@
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>0x14e7</t>
+          <t>0x14ef</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
@@ -36747,7 +36747,7 @@
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>0x32e3</t>
+          <t>0x32eb</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
@@ -36975,7 +36975,7 @@
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>0x36e7</t>
+          <t>0x36ef</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
@@ -37089,7 +37089,7 @@
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>0x10e7</t>
+          <t>0x11ef</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -37146,7 +37146,7 @@
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>0x12e7</t>
+          <t>0x12ef</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
@@ -37203,7 +37203,7 @@
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>0x12e7</t>
+          <t>0x12ef</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
@@ -37317,7 +37317,7 @@
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>0x34e2</t>
+          <t>0x35f2</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -37431,7 +37431,7 @@
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>0x36e6</t>
+          <t>0x36ee</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
@@ -37545,7 +37545,7 @@
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>0x36e6</t>
+          <t>0x36f6</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
@@ -38001,7 +38001,7 @@
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>0x11e2</t>
+          <t>0x11ea</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>0x31e2</t>
+          <t>0x31ea</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
@@ -38343,7 +38343,7 @@
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>0x35e6</t>
+          <t>0x35ee</t>
         </is>
       </c>
       <c r="H676" t="inlineStr">
@@ -38457,7 +38457,7 @@
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>0x12e6</t>
+          <t>0x1aee</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
@@ -38571,7 +38571,7 @@
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>0x12e6</t>
+          <t>0x1aee</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
@@ -38628,7 +38628,7 @@
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>0x36e6</t>
+          <t>0x36ee</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
@@ -38685,7 +38685,7 @@
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>0x3162</t>
+          <t>0x316a</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
@@ -39198,7 +39198,7 @@
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>0x1666</t>
+          <t>0x177e</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
@@ -71527,7 +71527,7 @@
         <v>7827</v>
       </c>
       <c r="G1278" t="n">
-        <v>15263</v>
+        <v>8990</v>
       </c>
       <c r="H1278" t="inlineStr">
         <is>
@@ -71580,7 +71580,7 @@
         <v>363</v>
       </c>
       <c r="G1279" t="n">
-        <v>613</v>
+        <v>363</v>
       </c>
       <c r="H1279" t="inlineStr">
         <is>
@@ -71633,7 +71633,7 @@
         <v>132</v>
       </c>
       <c r="G1280" t="n">
-        <v>223</v>
+        <v>140</v>
       </c>
       <c r="H1280" t="inlineStr">
         <is>
@@ -72799,7 +72799,7 @@
         <v>2673</v>
       </c>
       <c r="G1302" t="n">
-        <v>5212</v>
+        <v>3100</v>
       </c>
       <c r="H1302" t="inlineStr">
         <is>
@@ -72852,7 +72852,7 @@
         <v>313</v>
       </c>
       <c r="G1303" t="n">
-        <v>529</v>
+        <v>335</v>
       </c>
       <c r="H1303" t="inlineStr">
         <is>
@@ -72905,7 +72905,7 @@
         <v>108</v>
       </c>
       <c r="G1304" t="n">
-        <v>183</v>
+        <v>115</v>
       </c>
       <c r="H1304" t="inlineStr">
         <is>
@@ -74548,7 +74548,7 @@
         <v>5871</v>
       </c>
       <c r="G1335" t="n">
-        <v>11448</v>
+        <v>6750</v>
       </c>
       <c r="H1335" t="inlineStr">
         <is>
@@ -74601,7 +74601,7 @@
         <v>348</v>
       </c>
       <c r="G1336" t="n">
-        <v>588</v>
+        <v>360</v>
       </c>
       <c r="H1336" t="inlineStr">
         <is>
@@ -74654,7 +74654,7 @@
         <v>128</v>
       </c>
       <c r="G1337" t="n">
-        <v>216</v>
+        <v>135</v>
       </c>
       <c r="H1337" t="inlineStr">
         <is>
@@ -78284,6 +78284,59 @@
         </is>
       </c>
       <c r="L1403" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>W042</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>744 Slave's Torc</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>Enchant 3 (0x68)</t>
+        </is>
+      </c>
+      <c r="F1404" t="n">
+        <v>66</v>
+      </c>
+      <c r="G1404" t="n">
+        <v>275</v>
+      </c>
+      <c r="H1404" t="inlineStr">
+        <is>
+          <t>L14</t>
+        </is>
+      </c>
+      <c r="I1404" t="inlineStr">
+        <is>
+          <t>F92</t>
+        </is>
+      </c>
+      <c r="J1404" t="inlineStr">
+        <is>
+          <t>Slave Torc Double EXP training gear (JP community QoL parity)</t>
+        </is>
+      </c>
+      <c r="K1404" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1404" t="inlineStr">
         <is>
           <t>decided</t>
         </is>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -35109,7 +35109,7 @@
       </c>
       <c r="J619" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K619" t="inlineStr">
@@ -35166,7 +35166,7 @@
       </c>
       <c r="J620" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story; poison opened (T07, the user 2026-10-09: damage over time must serve against bosses without trivialising them): healer's Poison cast until it lands takes 23% of the boss HP over the fight (tools/skill_value.py play, check_runs), under a quarter. Kept immune: Ghast, Doll, Countess of Vrachia (undead or doll), Beatrice (C26 already 27% through Michelle), Heartless Avenger (C30: 32%, the fight halved)</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11); poison opened (T07, the user 2026-10-09: damage over time must serve against bosses without trivialising them): healer's Poison cast until it lands takes 23% of the boss HP over the fight (tools/skill_value.py play, check_runs), under a quarter. Kept immune: Ghast, Doll, Countess of Vrachia (undead or doll), Beatrice (C26 already 27% through Michelle), Heartless Avenger (C30: 32%, the fight halved)</t>
         </is>
       </c>
       <c r="K620" t="inlineStr">
@@ -35223,7 +35223,7 @@
       </c>
       <c r="J621" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K621" t="inlineStr">
@@ -35280,7 +35280,7 @@
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K622" t="inlineStr">
@@ -35337,7 +35337,7 @@
       </c>
       <c r="J623" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K623" t="inlineStr">
@@ -35394,7 +35394,7 @@
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K624" t="inlineStr">
@@ -35451,7 +35451,7 @@
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K625" t="inlineStr">
@@ -35508,7 +35508,7 @@
       </c>
       <c r="J626" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K626" t="inlineStr">
@@ -35565,7 +35565,7 @@
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K627" t="inlineStr">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="J628" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K628" t="inlineStr">
@@ -35679,7 +35679,7 @@
       </c>
       <c r="J629" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K629" t="inlineStr">
@@ -35736,7 +35736,7 @@
       </c>
       <c r="J630" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K630" t="inlineStr">
@@ -35793,7 +35793,7 @@
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K631" t="inlineStr">
@@ -35850,7 +35850,7 @@
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K632" t="inlineStr">
@@ -35907,7 +35907,7 @@
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K633" t="inlineStr">
@@ -35964,7 +35964,7 @@
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K634" t="inlineStr">
@@ -36021,7 +36021,7 @@
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K635" t="inlineStr">
@@ -36078,7 +36078,7 @@
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K636" t="inlineStr">
@@ -36135,7 +36135,7 @@
       </c>
       <c r="J637" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K637" t="inlineStr">
@@ -36192,7 +36192,7 @@
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K638" t="inlineStr">
@@ -36249,7 +36249,7 @@
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K639" t="inlineStr">
@@ -36306,7 +36306,7 @@
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K640" t="inlineStr">
@@ -36363,7 +36363,7 @@
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K641" t="inlineStr">
@@ -36420,7 +36420,7 @@
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K642" t="inlineStr">
@@ -36477,7 +36477,7 @@
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story; poison opened (T07, the user 2026-10-09: damage over time must serve against bosses without trivialising them): healer's Poison cast until it lands takes 20% of the boss HP over the fight (tools/skill_value.py play, check_runs), under a quarter. Kept immune: Ghast, Doll, Countess of Vrachia (undead or doll), Beatrice (C26 already 27% through Michelle), Heartless Avenger (C30: 32%, the fight halved)</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11); poison opened (T07, the user 2026-10-09: damage over time must serve against bosses without trivialising them): healer's Poison cast until it lands takes 20% of the boss HP over the fight (tools/skill_value.py play, check_runs), under a quarter. Kept immune: Ghast, Doll, Countess of Vrachia (undead or doll), Beatrice (C26 already 27% through Michelle), Heartless Avenger (C30: 32%, the fight halved)</t>
         </is>
       </c>
       <c r="K643" t="inlineStr">
@@ -36534,7 +36534,7 @@
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K644" t="inlineStr">
@@ -36591,7 +36591,7 @@
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K645" t="inlineStr">
@@ -36648,7 +36648,7 @@
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K646" t="inlineStr">
@@ -36705,7 +36705,7 @@
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K647" t="inlineStr">
@@ -36762,7 +36762,7 @@
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K648" t="inlineStr">
@@ -36819,7 +36819,7 @@
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K649" t="inlineStr">
@@ -36876,7 +36876,7 @@
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K650" t="inlineStr">
@@ -36933,7 +36933,7 @@
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K651" t="inlineStr">
@@ -36990,7 +36990,7 @@
       </c>
       <c r="J652" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K652" t="inlineStr">
@@ -37047,7 +37047,7 @@
       </c>
       <c r="J653" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K653" t="inlineStr">
@@ -37089,7 +37089,7 @@
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>0x11ef</t>
+          <t>0x10ef</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -37104,7 +37104,7 @@
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story; poison opened (T07, the user 2026-10-09: damage over time must serve against bosses without trivialising them): healer's Poison cast until it lands takes 25% of the boss HP over the fight (tools/skill_value.py play, check_runs), under a quarter. Kept immune: Ghast, Doll, Countess of Vrachia (undead or doll), Beatrice (C26 already 27% through Michelle), Heartless Avenger (C30: 32%, the fight halved)</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11); poison opened (T07, the user 2026-10-09: damage over time must serve against bosses without trivialising them): healer's Poison cast until it lands takes 25% of the boss HP over the fight (tools/skill_value.py play, check_runs), under a quarter. Kept immune: Ghast, Doll, Countess of Vrachia (undead or doll), Beatrice (C26 already 27% through Michelle), Heartless Avenger (C30: 32%, the fight halved)</t>
         </is>
       </c>
       <c r="K654" t="inlineStr">
@@ -37161,7 +37161,7 @@
       </c>
       <c r="J655" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K655" t="inlineStr">
@@ -37218,7 +37218,7 @@
       </c>
       <c r="J656" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K656" t="inlineStr">
@@ -37275,7 +37275,7 @@
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K657" t="inlineStr">
@@ -37317,7 +37317,7 @@
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>0x35f2</t>
+          <t>0x34e2</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -37332,7 +37332,7 @@
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story; poison opened (T07, the user 2026-10-09: damage over time must serve against bosses without trivialising them): healer's Poison cast until it lands takes 16% of the boss HP over the fight (tools/skill_value.py play, check_runs), under a quarter. Kept immune: Ghast, Doll, Countess of Vrachia (undead or doll), Beatrice (C26 already 27% through Michelle), Heartless Avenger (C30: 32%, the fight halved)</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11); poison opened (T07, the user 2026-10-09: damage over time must serve against bosses without trivialising them): healer's Poison cast until it lands takes 16% of the boss HP over the fight (tools/skill_value.py play, check_runs), under a quarter. Kept immune: Ghast, Doll, Countess of Vrachia (undead or doll), Beatrice (C26 already 27% through Michelle), Heartless Avenger (C30: 32%, the fight halved)</t>
         </is>
       </c>
       <c r="K658" t="inlineStr">
@@ -37389,7 +37389,7 @@
       </c>
       <c r="J659" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K659" t="inlineStr">
@@ -37446,7 +37446,7 @@
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K660" t="inlineStr">
@@ -37503,7 +37503,7 @@
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K661" t="inlineStr">
@@ -37545,7 +37545,7 @@
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>0x36f6</t>
+          <t>0x36e6</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
@@ -37560,7 +37560,7 @@
       </c>
       <c r="J662" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K662" t="inlineStr">
@@ -37617,7 +37617,7 @@
       </c>
       <c r="J663" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K663" t="inlineStr">
@@ -37674,7 +37674,7 @@
       </c>
       <c r="J664" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K664" t="inlineStr">
@@ -37731,7 +37731,7 @@
       </c>
       <c r="J665" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K665" t="inlineStr">
@@ -37788,7 +37788,7 @@
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K666" t="inlineStr">
@@ -37845,7 +37845,7 @@
       </c>
       <c r="J667" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K667" t="inlineStr">
@@ -37902,7 +37902,7 @@
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K668" t="inlineStr">
@@ -37959,7 +37959,7 @@
       </c>
       <c r="J669" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K669" t="inlineStr">
@@ -38016,7 +38016,7 @@
       </c>
       <c r="J670" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K670" t="inlineStr">
@@ -38073,7 +38073,7 @@
       </c>
       <c r="J671" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K671" t="inlineStr">
@@ -38130,7 +38130,7 @@
       </c>
       <c r="J672" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K672" t="inlineStr">
@@ -38187,7 +38187,7 @@
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K673" t="inlineStr">
@@ -38244,7 +38244,7 @@
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K674" t="inlineStr">
@@ -38301,7 +38301,7 @@
       </c>
       <c r="J675" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K675" t="inlineStr">
@@ -38358,7 +38358,7 @@
       </c>
       <c r="J676" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K676" t="inlineStr">
@@ -38415,7 +38415,7 @@
       </c>
       <c r="J677" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K677" t="inlineStr">
@@ -38457,7 +38457,7 @@
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>0x1aee</t>
+          <t>0x12ee</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
@@ -38472,7 +38472,7 @@
       </c>
       <c r="J678" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K678" t="inlineStr">
@@ -38529,7 +38529,7 @@
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K679" t="inlineStr">
@@ -38571,7 +38571,7 @@
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>0x1aee</t>
+          <t>0x12ee</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
@@ -38586,7 +38586,7 @@
       </c>
       <c r="J680" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K680" t="inlineStr">
@@ -38643,7 +38643,7 @@
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K681" t="inlineStr">
@@ -38700,7 +38700,7 @@
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K682" t="inlineStr">
@@ -38757,7 +38757,7 @@
       </c>
       <c r="J683" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K683" t="inlineStr">
@@ -38814,7 +38814,7 @@
       </c>
       <c r="J684" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K684" t="inlineStr">
@@ -38871,7 +38871,7 @@
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K685" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="J686" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K686" t="inlineStr">
@@ -38985,7 +38985,7 @@
       </c>
       <c r="J687" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K687" t="inlineStr">
@@ -39042,7 +39042,7 @@
       </c>
       <c r="J688" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K688" t="inlineStr">
@@ -39099,7 +39099,7 @@
       </c>
       <c r="J689" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K689" t="inlineStr">
@@ -39156,7 +39156,7 @@
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11)</t>
         </is>
       </c>
       <c r="K690" t="inlineStr">
@@ -39198,7 +39198,7 @@
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>0x177e</t>
+          <t>0x166e</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
@@ -39213,7 +39213,7 @@
       </c>
       <c r="J691" t="inlineStr">
         <is>
-          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss, and to sleep in the story; poison opened (T07, the user 2026-10-09: damage over time must serve against bosses without trivialising them): healer's Poison cast until it lands takes 25% of the boss HP over the fight (tools/skill_value.py play, check_runs), under a quarter. Kept immune: Ghast, Doll, Countess of Vrachia (undead or doll), Beatrice (C26 already 27% through Michelle), Heartless Avenger (C30: 32%, the fight halved)</t>
+          <t>Bosses: immune to turn delay (no boss lockable by Tinker Squash or the like); open to slow and silence unless a superboss; sleep as in vanilla (the opening of 2026-10-09 was taken back on 2026-10-11); poison opened (T07, the user 2026-10-09: damage over time must serve against bosses without trivialising them): healer's Poison cast until it lands takes 25% of the boss HP over the fight (tools/skill_value.py play, check_runs), under a quarter. Kept immune: Ghast, Doll, Countess of Vrachia (undead or doll), Beatrice (C26 already 27% through Michelle), Heartless Avenger (C30: 32%, the fight halved)</t>
         </is>
       </c>
       <c r="K691" t="inlineStr">
@@ -78318,7 +78318,7 @@
       </c>
       <c r="H1404" t="inlineStr">
         <is>
-          <t>L14</t>
+          <t>L15</t>
         </is>
       </c>
       <c r="I1404" t="inlineStr">
@@ -78328,7 +78328,7 @@
       </c>
       <c r="J1404" t="inlineStr">
         <is>
-          <t>Slave Torc Double EXP training gear (JP community QoL parity)</t>
+          <t>Catching up (U01, F92; the user, 2026-10-11): the third innate enchantment of the Slave's Torc, a second "Received physical damage DOWN" (66), becomes Double EXP (275), an enchantment vanilla already puts on Lord Mashiro's Fan and Therion's Crown and reads at 0x445a1e. Condition of L15 holds: the id exists, the count stays 3</t>
         </is>
       </c>
       <c r="K1404" t="inlineStr">

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -71527,7 +71527,7 @@
         <v>7827</v>
       </c>
       <c r="G1278" t="n">
-        <v>8990</v>
+        <v>9392</v>
       </c>
       <c r="H1278" t="inlineStr">
         <is>
@@ -71541,12 +71541,12 @@
       </c>
       <c r="J1278" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Difficulty kept on the common fights of the last floors (R08, R10), measured again on 2026-10-11 with the policy of today, the reference party and the five battery parties (scratch/audit_2026-10-11/e7_stage15_fit.py, rows of eight random battles, 24 rows, floors St15_1120 and St15_1150; mean battles won against vanilla over the twelve cells): with no change the variant is easier (+0.8); HP, ATK and INT x1.30 with x1.95 / x1.69 on three enemies, the rows of 2026-10-09, made it harder for every party but one (-1.1; Mage-Heavy 7.1 to 3.7 on St15_1150) because attack is subtracted from defence and x1.69 ATK was x2 to x3.3 damage, a common enemy above the ATK of the last boss; HP x1.20 alone gives +0.15, the largest gap 1.2 battles, and no hit grows. HP x1.20, ATK and INT of vanilla</t>
         </is>
       </c>
       <c r="K1278" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1278" t="inlineStr">
@@ -71594,7 +71594,7 @@
       </c>
       <c r="J1279" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1279" t="inlineStr">
@@ -71604,7 +71604,7 @@
       </c>
       <c r="L1279" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -71647,7 +71647,7 @@
       </c>
       <c r="J1280" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1280" t="inlineStr">
@@ -71657,7 +71657,7 @@
       </c>
       <c r="L1280" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -71686,7 +71686,7 @@
         <v>1531</v>
       </c>
       <c r="G1281" t="n">
-        <v>1990</v>
+        <v>1837</v>
       </c>
       <c r="H1281" t="inlineStr">
         <is>
@@ -71700,12 +71700,12 @@
       </c>
       <c r="J1281" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Difficulty kept on the common fights of the last floors (R08, R10), measured again on 2026-10-11 with the policy of today, the reference party and the five battery parties (scratch/audit_2026-10-11/e7_stage15_fit.py, rows of eight random battles, 24 rows, floors St15_1120 and St15_1150; mean battles won against vanilla over the twelve cells): with no change the variant is easier (+0.8); HP, ATK and INT x1.30 with x1.95 / x1.69 on three enemies, the rows of 2026-10-09, made it harder for every party but one (-1.1; Mage-Heavy 7.1 to 3.7 on St15_1150) because attack is subtracted from defence and x1.69 ATK was x2 to x3.3 damage, a common enemy above the ATK of the last boss; HP x1.20 alone gives +0.15, the largest gap 1.2 battles, and no hit grows. HP x1.20, ATK and INT of vanilla</t>
         </is>
       </c>
       <c r="K1281" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1281" t="inlineStr">
@@ -71753,7 +71753,7 @@
       </c>
       <c r="J1282" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1282" t="inlineStr">
@@ -71763,7 +71763,7 @@
       </c>
       <c r="L1282" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -71806,7 +71806,7 @@
       </c>
       <c r="J1283" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1283" t="inlineStr">
@@ -71816,7 +71816,7 @@
       </c>
       <c r="L1283" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -71845,7 +71845,7 @@
         <v>1544</v>
       </c>
       <c r="G1284" t="n">
-        <v>2007</v>
+        <v>1853</v>
       </c>
       <c r="H1284" t="inlineStr">
         <is>
@@ -71859,12 +71859,12 @@
       </c>
       <c r="J1284" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Difficulty kept on the common fights of the last floors (R08, R10), measured again on 2026-10-11 with the policy of today, the reference party and the five battery parties (scratch/audit_2026-10-11/e7_stage15_fit.py, rows of eight random battles, 24 rows, floors St15_1120 and St15_1150; mean battles won against vanilla over the twelve cells): with no change the variant is easier (+0.8); HP, ATK and INT x1.30 with x1.95 / x1.69 on three enemies, the rows of 2026-10-09, made it harder for every party but one (-1.1; Mage-Heavy 7.1 to 3.7 on St15_1150) because attack is subtracted from defence and x1.69 ATK was x2 to x3.3 damage, a common enemy above the ATK of the last boss; HP x1.20 alone gives +0.15, the largest gap 1.2 battles, and no hit grows. HP x1.20, ATK and INT of vanilla</t>
         </is>
       </c>
       <c r="K1284" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1284" t="inlineStr">
@@ -71912,7 +71912,7 @@
       </c>
       <c r="J1285" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1285" t="inlineStr">
@@ -71922,7 +71922,7 @@
       </c>
       <c r="L1285" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -71965,7 +71965,7 @@
       </c>
       <c r="J1286" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1286" t="inlineStr">
@@ -71975,7 +71975,7 @@
       </c>
       <c r="L1286" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -72004,7 +72004,7 @@
         <v>2397</v>
       </c>
       <c r="G1287" t="n">
-        <v>3116</v>
+        <v>2876</v>
       </c>
       <c r="H1287" t="inlineStr">
         <is>
@@ -72018,12 +72018,12 @@
       </c>
       <c r="J1287" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Difficulty kept on the common fights of the last floors (R08, R10), measured again on 2026-10-11 with the policy of today, the reference party and the five battery parties (scratch/audit_2026-10-11/e7_stage15_fit.py, rows of eight random battles, 24 rows, floors St15_1120 and St15_1150; mean battles won against vanilla over the twelve cells): with no change the variant is easier (+0.8); HP, ATK and INT x1.30 with x1.95 / x1.69 on three enemies, the rows of 2026-10-09, made it harder for every party but one (-1.1; Mage-Heavy 7.1 to 3.7 on St15_1150) because attack is subtracted from defence and x1.69 ATK was x2 to x3.3 damage, a common enemy above the ATK of the last boss; HP x1.20 alone gives +0.15, the largest gap 1.2 battles, and no hit grows. HP x1.20, ATK and INT of vanilla</t>
         </is>
       </c>
       <c r="K1287" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1287" t="inlineStr">
@@ -72071,7 +72071,7 @@
       </c>
       <c r="J1288" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1288" t="inlineStr">
@@ -72081,7 +72081,7 @@
       </c>
       <c r="L1288" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -72124,7 +72124,7 @@
       </c>
       <c r="J1289" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1289" t="inlineStr">
@@ -72134,7 +72134,7 @@
       </c>
       <c r="L1289" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -72163,7 +72163,7 @@
         <v>1683</v>
       </c>
       <c r="G1290" t="n">
-        <v>2188</v>
+        <v>2020</v>
       </c>
       <c r="H1290" t="inlineStr">
         <is>
@@ -72177,12 +72177,12 @@
       </c>
       <c r="J1290" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Difficulty kept on the common fights of the last floors (R08, R10), measured again on 2026-10-11 with the policy of today, the reference party and the five battery parties (scratch/audit_2026-10-11/e7_stage15_fit.py, rows of eight random battles, 24 rows, floors St15_1120 and St15_1150; mean battles won against vanilla over the twelve cells): with no change the variant is easier (+0.8); HP, ATK and INT x1.30 with x1.95 / x1.69 on three enemies, the rows of 2026-10-09, made it harder for every party but one (-1.1; Mage-Heavy 7.1 to 3.7 on St15_1150) because attack is subtracted from defence and x1.69 ATK was x2 to x3.3 damage, a common enemy above the ATK of the last boss; HP x1.20 alone gives +0.15, the largest gap 1.2 battles, and no hit grows. HP x1.20, ATK and INT of vanilla</t>
         </is>
       </c>
       <c r="K1290" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1290" t="inlineStr">
@@ -72230,7 +72230,7 @@
       </c>
       <c r="J1291" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1291" t="inlineStr">
@@ -72240,7 +72240,7 @@
       </c>
       <c r="L1291" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -72283,7 +72283,7 @@
       </c>
       <c r="J1292" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1292" t="inlineStr">
@@ -72293,7 +72293,7 @@
       </c>
       <c r="L1292" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -72322,7 +72322,7 @@
         <v>1745</v>
       </c>
       <c r="G1293" t="n">
-        <v>2268</v>
+        <v>2094</v>
       </c>
       <c r="H1293" t="inlineStr">
         <is>
@@ -72336,12 +72336,12 @@
       </c>
       <c r="J1293" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Difficulty kept on the common fights of the last floors (R08, R10), measured again on 2026-10-11 with the policy of today, the reference party and the five battery parties (scratch/audit_2026-10-11/e7_stage15_fit.py, rows of eight random battles, 24 rows, floors St15_1120 and St15_1150; mean battles won against vanilla over the twelve cells): with no change the variant is easier (+0.8); HP, ATK and INT x1.30 with x1.95 / x1.69 on three enemies, the rows of 2026-10-09, made it harder for every party but one (-1.1; Mage-Heavy 7.1 to 3.7 on St15_1150) because attack is subtracted from defence and x1.69 ATK was x2 to x3.3 damage, a common enemy above the ATK of the last boss; HP x1.20 alone gives +0.15, the largest gap 1.2 battles, and no hit grows. HP x1.20, ATK and INT of vanilla</t>
         </is>
       </c>
       <c r="K1293" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1293" t="inlineStr">
@@ -72389,7 +72389,7 @@
       </c>
       <c r="J1294" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1294" t="inlineStr">
@@ -72399,7 +72399,7 @@
       </c>
       <c r="L1294" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -72442,7 +72442,7 @@
       </c>
       <c r="J1295" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1295" t="inlineStr">
@@ -72452,7 +72452,7 @@
       </c>
       <c r="L1295" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -72481,7 +72481,7 @@
         <v>1475</v>
       </c>
       <c r="G1296" t="n">
-        <v>1918</v>
+        <v>1770</v>
       </c>
       <c r="H1296" t="inlineStr">
         <is>
@@ -72495,12 +72495,12 @@
       </c>
       <c r="J1296" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Difficulty kept on the common fights of the last floors (R08, R10), measured again on 2026-10-11 with the policy of today, the reference party and the five battery parties (scratch/audit_2026-10-11/e7_stage15_fit.py, rows of eight random battles, 24 rows, floors St15_1120 and St15_1150; mean battles won against vanilla over the twelve cells): with no change the variant is easier (+0.8); HP, ATK and INT x1.30 with x1.95 / x1.69 on three enemies, the rows of 2026-10-09, made it harder for every party but one (-1.1; Mage-Heavy 7.1 to 3.7 on St15_1150) because attack is subtracted from defence and x1.69 ATK was x2 to x3.3 damage, a common enemy above the ATK of the last boss; HP x1.20 alone gives +0.15, the largest gap 1.2 battles, and no hit grows. HP x1.20, ATK and INT of vanilla</t>
         </is>
       </c>
       <c r="K1296" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1296" t="inlineStr">
@@ -72548,7 +72548,7 @@
       </c>
       <c r="J1297" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1297" t="inlineStr">
@@ -72558,7 +72558,7 @@
       </c>
       <c r="L1297" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -72601,7 +72601,7 @@
       </c>
       <c r="J1298" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1298" t="inlineStr">
@@ -72611,7 +72611,7 @@
       </c>
       <c r="L1298" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -72640,7 +72640,7 @@
         <v>1542</v>
       </c>
       <c r="G1299" t="n">
-        <v>2005</v>
+        <v>1850</v>
       </c>
       <c r="H1299" t="inlineStr">
         <is>
@@ -72654,12 +72654,12 @@
       </c>
       <c r="J1299" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Difficulty kept on the common fights of the last floors (R08, R10), measured again on 2026-10-11 with the policy of today, the reference party and the five battery parties (scratch/audit_2026-10-11/e7_stage15_fit.py, rows of eight random battles, 24 rows, floors St15_1120 and St15_1150; mean battles won against vanilla over the twelve cells): with no change the variant is easier (+0.8); HP, ATK and INT x1.30 with x1.95 / x1.69 on three enemies, the rows of 2026-10-09, made it harder for every party but one (-1.1; Mage-Heavy 7.1 to 3.7 on St15_1150) because attack is subtracted from defence and x1.69 ATK was x2 to x3.3 damage, a common enemy above the ATK of the last boss; HP x1.20 alone gives +0.15, the largest gap 1.2 battles, and no hit grows. HP x1.20, ATK and INT of vanilla</t>
         </is>
       </c>
       <c r="K1299" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1299" t="inlineStr">
@@ -72707,7 +72707,7 @@
       </c>
       <c r="J1300" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1300" t="inlineStr">
@@ -72717,7 +72717,7 @@
       </c>
       <c r="L1300" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -72760,7 +72760,7 @@
       </c>
       <c r="J1301" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1301" t="inlineStr">
@@ -72770,7 +72770,7 @@
       </c>
       <c r="L1301" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -72799,7 +72799,7 @@
         <v>2673</v>
       </c>
       <c r="G1302" t="n">
-        <v>3100</v>
+        <v>3208</v>
       </c>
       <c r="H1302" t="inlineStr">
         <is>
@@ -72813,12 +72813,12 @@
       </c>
       <c r="J1302" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Difficulty kept on the common fights of the last floors (R08, R10), measured again on 2026-10-11 with the policy of today, the reference party and the five battery parties (scratch/audit_2026-10-11/e7_stage15_fit.py, rows of eight random battles, 24 rows, floors St15_1120 and St15_1150; mean battles won against vanilla over the twelve cells): with no change the variant is easier (+0.8); HP, ATK and INT x1.30 with x1.95 / x1.69 on three enemies, the rows of 2026-10-09, made it harder for every party but one (-1.1; Mage-Heavy 7.1 to 3.7 on St15_1150) because attack is subtracted from defence and x1.69 ATK was x2 to x3.3 damage, a common enemy above the ATK of the last boss; HP x1.20 alone gives +0.15, the largest gap 1.2 battles, and no hit grows. HP x1.20, ATK and INT of vanilla</t>
         </is>
       </c>
       <c r="K1302" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1302" t="inlineStr">
@@ -72866,7 +72866,7 @@
       </c>
       <c r="J1303" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1303" t="inlineStr">
@@ -72876,7 +72876,7 @@
       </c>
       <c r="L1303" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -72919,7 +72919,7 @@
       </c>
       <c r="J1304" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1304" t="inlineStr">
@@ -72929,7 +72929,7 @@
       </c>
       <c r="L1304" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -72958,7 +72958,7 @@
         <v>1631</v>
       </c>
       <c r="G1305" t="n">
-        <v>2120</v>
+        <v>1957</v>
       </c>
       <c r="H1305" t="inlineStr">
         <is>
@@ -72972,12 +72972,12 @@
       </c>
       <c r="J1305" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Difficulty kept on the common fights of the last floors (R08, R10), measured again on 2026-10-11 with the policy of today, the reference party and the five battery parties (scratch/audit_2026-10-11/e7_stage15_fit.py, rows of eight random battles, 24 rows, floors St15_1120 and St15_1150; mean battles won against vanilla over the twelve cells): with no change the variant is easier (+0.8); HP, ATK and INT x1.30 with x1.95 / x1.69 on three enemies, the rows of 2026-10-09, made it harder for every party but one (-1.1; Mage-Heavy 7.1 to 3.7 on St15_1150) because attack is subtracted from defence and x1.69 ATK was x2 to x3.3 damage, a common enemy above the ATK of the last boss; HP x1.20 alone gives +0.15, the largest gap 1.2 battles, and no hit grows. HP x1.20, ATK and INT of vanilla</t>
         </is>
       </c>
       <c r="K1305" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1305" t="inlineStr">
@@ -73025,7 +73025,7 @@
       </c>
       <c r="J1306" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1306" t="inlineStr">
@@ -73035,7 +73035,7 @@
       </c>
       <c r="L1306" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -73078,7 +73078,7 @@
       </c>
       <c r="J1307" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1307" t="inlineStr">
@@ -73088,7 +73088,7 @@
       </c>
       <c r="L1307" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -73117,7 +73117,7 @@
         <v>1643</v>
       </c>
       <c r="G1308" t="n">
-        <v>2136</v>
+        <v>1972</v>
       </c>
       <c r="H1308" t="inlineStr">
         <is>
@@ -73131,12 +73131,12 @@
       </c>
       <c r="J1308" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Difficulty kept on the common fights of the last floors (R08, R10), measured again on 2026-10-11 with the policy of today, the reference party and the five battery parties (scratch/audit_2026-10-11/e7_stage15_fit.py, rows of eight random battles, 24 rows, floors St15_1120 and St15_1150; mean battles won against vanilla over the twelve cells): with no change the variant is easier (+0.8); HP, ATK and INT x1.30 with x1.95 / x1.69 on three enemies, the rows of 2026-10-09, made it harder for every party but one (-1.1; Mage-Heavy 7.1 to 3.7 on St15_1150) because attack is subtracted from defence and x1.69 ATK was x2 to x3.3 damage, a common enemy above the ATK of the last boss; HP x1.20 alone gives +0.15, the largest gap 1.2 battles, and no hit grows. HP x1.20, ATK and INT of vanilla</t>
         </is>
       </c>
       <c r="K1308" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1308" t="inlineStr">
@@ -73184,7 +73184,7 @@
       </c>
       <c r="J1309" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1309" t="inlineStr">
@@ -73194,7 +73194,7 @@
       </c>
       <c r="L1309" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -73237,7 +73237,7 @@
       </c>
       <c r="J1310" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1310" t="inlineStr">
@@ -73247,7 +73247,7 @@
       </c>
       <c r="L1310" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -73276,7 +73276,7 @@
         <v>1668</v>
       </c>
       <c r="G1311" t="n">
-        <v>2168</v>
+        <v>2002</v>
       </c>
       <c r="H1311" t="inlineStr">
         <is>
@@ -73290,12 +73290,12 @@
       </c>
       <c r="J1311" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Difficulty kept on the common fights of the last floors (R08, R10), measured again on 2026-10-11 with the policy of today, the reference party and the five battery parties (scratch/audit_2026-10-11/e7_stage15_fit.py, rows of eight random battles, 24 rows, floors St15_1120 and St15_1150; mean battles won against vanilla over the twelve cells): with no change the variant is easier (+0.8); HP, ATK and INT x1.30 with x1.95 / x1.69 on three enemies, the rows of 2026-10-09, made it harder for every party but one (-1.1; Mage-Heavy 7.1 to 3.7 on St15_1150) because attack is subtracted from defence and x1.69 ATK was x2 to x3.3 damage, a common enemy above the ATK of the last boss; HP x1.20 alone gives +0.15, the largest gap 1.2 battles, and no hit grows. HP x1.20, ATK and INT of vanilla</t>
         </is>
       </c>
       <c r="K1311" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1311" t="inlineStr">
@@ -73343,7 +73343,7 @@
       </c>
       <c r="J1312" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1312" t="inlineStr">
@@ -73353,7 +73353,7 @@
       </c>
       <c r="L1312" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -73396,7 +73396,7 @@
       </c>
       <c r="J1313" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1313" t="inlineStr">
@@ -73406,7 +73406,7 @@
       </c>
       <c r="L1313" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -73435,7 +73435,7 @@
         <v>1729</v>
       </c>
       <c r="G1314" t="n">
-        <v>2248</v>
+        <v>2075</v>
       </c>
       <c r="H1314" t="inlineStr">
         <is>
@@ -73449,12 +73449,12 @@
       </c>
       <c r="J1314" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Difficulty kept on the common fights of the last floors (R08, R10), measured again on 2026-10-11 with the policy of today, the reference party and the five battery parties (scratch/audit_2026-10-11/e7_stage15_fit.py, rows of eight random battles, 24 rows, floors St15_1120 and St15_1150; mean battles won against vanilla over the twelve cells): with no change the variant is easier (+0.8); HP, ATK and INT x1.30 with x1.95 / x1.69 on three enemies, the rows of 2026-10-09, made it harder for every party but one (-1.1; Mage-Heavy 7.1 to 3.7 on St15_1150) because attack is subtracted from defence and x1.69 ATK was x2 to x3.3 damage, a common enemy above the ATK of the last boss; HP x1.20 alone gives +0.15, the largest gap 1.2 battles, and no hit grows. HP x1.20, ATK and INT of vanilla</t>
         </is>
       </c>
       <c r="K1314" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1314" t="inlineStr">
@@ -73502,7 +73502,7 @@
       </c>
       <c r="J1315" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1315" t="inlineStr">
@@ -73512,7 +73512,7 @@
       </c>
       <c r="L1315" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -73555,7 +73555,7 @@
       </c>
       <c r="J1316" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1316" t="inlineStr">
@@ -73565,7 +73565,7 @@
       </c>
       <c r="L1316" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -73594,7 +73594,7 @@
         <v>3042</v>
       </c>
       <c r="G1317" t="n">
-        <v>3955</v>
+        <v>3650</v>
       </c>
       <c r="H1317" t="inlineStr">
         <is>
@@ -73608,12 +73608,12 @@
       </c>
       <c r="J1317" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Difficulty kept on the common fights of the last floors (R08, R10), measured again on 2026-10-11 with the policy of today, the reference party and the five battery parties (scratch/audit_2026-10-11/e7_stage15_fit.py, rows of eight random battles, 24 rows, floors St15_1120 and St15_1150; mean battles won against vanilla over the twelve cells): with no change the variant is easier (+0.8); HP, ATK and INT x1.30 with x1.95 / x1.69 on three enemies, the rows of 2026-10-09, made it harder for every party but one (-1.1; Mage-Heavy 7.1 to 3.7 on St15_1150) because attack is subtracted from defence and x1.69 ATK was x2 to x3.3 damage, a common enemy above the ATK of the last boss; HP x1.20 alone gives +0.15, the largest gap 1.2 battles, and no hit grows. HP x1.20, ATK and INT of vanilla</t>
         </is>
       </c>
       <c r="K1317" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1317" t="inlineStr">
@@ -73661,7 +73661,7 @@
       </c>
       <c r="J1318" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1318" t="inlineStr">
@@ -73671,7 +73671,7 @@
       </c>
       <c r="L1318" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -73714,7 +73714,7 @@
       </c>
       <c r="J1319" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1319" t="inlineStr">
@@ -73724,7 +73724,7 @@
       </c>
       <c r="L1319" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -73753,7 +73753,7 @@
         <v>1559</v>
       </c>
       <c r="G1320" t="n">
-        <v>2027</v>
+        <v>1871</v>
       </c>
       <c r="H1320" t="inlineStr">
         <is>
@@ -73767,12 +73767,12 @@
       </c>
       <c r="J1320" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Difficulty kept on the common fights of the last floors (R08, R10), measured again on 2026-10-11 with the policy of today, the reference party and the five battery parties (scratch/audit_2026-10-11/e7_stage15_fit.py, rows of eight random battles, 24 rows, floors St15_1120 and St15_1150; mean battles won against vanilla over the twelve cells): with no change the variant is easier (+0.8); HP, ATK and INT x1.30 with x1.95 / x1.69 on three enemies, the rows of 2026-10-09, made it harder for every party but one (-1.1; Mage-Heavy 7.1 to 3.7 on St15_1150) because attack is subtracted from defence and x1.69 ATK was x2 to x3.3 damage, a common enemy above the ATK of the last boss; HP x1.20 alone gives +0.15, the largest gap 1.2 battles, and no hit grows. HP x1.20, ATK and INT of vanilla</t>
         </is>
       </c>
       <c r="K1320" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1320" t="inlineStr">
@@ -73820,7 +73820,7 @@
       </c>
       <c r="J1321" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1321" t="inlineStr">
@@ -73830,7 +73830,7 @@
       </c>
       <c r="L1321" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -73873,7 +73873,7 @@
       </c>
       <c r="J1322" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1322" t="inlineStr">
@@ -73883,7 +73883,7 @@
       </c>
       <c r="L1322" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -73912,7 +73912,7 @@
         <v>1203</v>
       </c>
       <c r="G1323" t="n">
-        <v>1564</v>
+        <v>1444</v>
       </c>
       <c r="H1323" t="inlineStr">
         <is>
@@ -73926,12 +73926,12 @@
       </c>
       <c r="J1323" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Difficulty kept on the common fights of the last floors (R08, R10), measured again on 2026-10-11 with the policy of today, the reference party and the five battery parties (scratch/audit_2026-10-11/e7_stage15_fit.py, rows of eight random battles, 24 rows, floors St15_1120 and St15_1150; mean battles won against vanilla over the twelve cells): with no change the variant is easier (+0.8); HP, ATK and INT x1.30 with x1.95 / x1.69 on three enemies, the rows of 2026-10-09, made it harder for every party but one (-1.1; Mage-Heavy 7.1 to 3.7 on St15_1150) because attack is subtracted from defence and x1.69 ATK was x2 to x3.3 damage, a common enemy above the ATK of the last boss; HP x1.20 alone gives +0.15, the largest gap 1.2 battles, and no hit grows. HP x1.20, ATK and INT of vanilla</t>
         </is>
       </c>
       <c r="K1323" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1323" t="inlineStr">
@@ -73979,7 +73979,7 @@
       </c>
       <c r="J1324" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1324" t="inlineStr">
@@ -73989,7 +73989,7 @@
       </c>
       <c r="L1324" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -74032,7 +74032,7 @@
       </c>
       <c r="J1325" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1325" t="inlineStr">
@@ -74042,7 +74042,7 @@
       </c>
       <c r="L1325" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -74071,7 +74071,7 @@
         <v>1411</v>
       </c>
       <c r="G1326" t="n">
-        <v>1834</v>
+        <v>1693</v>
       </c>
       <c r="H1326" t="inlineStr">
         <is>
@@ -74085,12 +74085,12 @@
       </c>
       <c r="J1326" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Difficulty kept on the common fights of the last floors (R08, R10), measured again on 2026-10-11 with the policy of today, the reference party and the five battery parties (scratch/audit_2026-10-11/e7_stage15_fit.py, rows of eight random battles, 24 rows, floors St15_1120 and St15_1150; mean battles won against vanilla over the twelve cells): with no change the variant is easier (+0.8); HP, ATK and INT x1.30 with x1.95 / x1.69 on three enemies, the rows of 2026-10-09, made it harder for every party but one (-1.1; Mage-Heavy 7.1 to 3.7 on St15_1150) because attack is subtracted from defence and x1.69 ATK was x2 to x3.3 damage, a common enemy above the ATK of the last boss; HP x1.20 alone gives +0.15, the largest gap 1.2 battles, and no hit grows. HP x1.20, ATK and INT of vanilla</t>
         </is>
       </c>
       <c r="K1326" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1326" t="inlineStr">
@@ -74138,7 +74138,7 @@
       </c>
       <c r="J1327" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1327" t="inlineStr">
@@ -74148,7 +74148,7 @@
       </c>
       <c r="L1327" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -74191,7 +74191,7 @@
       </c>
       <c r="J1328" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1328" t="inlineStr">
@@ -74201,7 +74201,7 @@
       </c>
       <c r="L1328" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -74230,7 +74230,7 @@
         <v>4675</v>
       </c>
       <c r="G1329" t="n">
-        <v>6078</v>
+        <v>5610</v>
       </c>
       <c r="H1329" t="inlineStr">
         <is>
@@ -74244,12 +74244,12 @@
       </c>
       <c r="J1329" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Difficulty kept on the common fights of the last floors (R08, R10), measured again on 2026-10-11 with the policy of today, the reference party and the five battery parties (scratch/audit_2026-10-11/e7_stage15_fit.py, rows of eight random battles, 24 rows, floors St15_1120 and St15_1150; mean battles won against vanilla over the twelve cells): with no change the variant is easier (+0.8); HP, ATK and INT x1.30 with x1.95 / x1.69 on three enemies, the rows of 2026-10-09, made it harder for every party but one (-1.1; Mage-Heavy 7.1 to 3.7 on St15_1150) because attack is subtracted from defence and x1.69 ATK was x2 to x3.3 damage, a common enemy above the ATK of the last boss; HP x1.20 alone gives +0.15, the largest gap 1.2 battles, and no hit grows. HP x1.20, ATK and INT of vanilla</t>
         </is>
       </c>
       <c r="K1329" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1329" t="inlineStr">
@@ -74297,7 +74297,7 @@
       </c>
       <c r="J1330" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1330" t="inlineStr">
@@ -74307,7 +74307,7 @@
       </c>
       <c r="L1330" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -74350,7 +74350,7 @@
       </c>
       <c r="J1331" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1331" t="inlineStr">
@@ -74360,7 +74360,7 @@
       </c>
       <c r="L1331" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -74389,7 +74389,7 @@
         <v>1811</v>
       </c>
       <c r="G1332" t="n">
-        <v>2354</v>
+        <v>2173</v>
       </c>
       <c r="H1332" t="inlineStr">
         <is>
@@ -74403,12 +74403,12 @@
       </c>
       <c r="J1332" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Difficulty kept on the common fights of the last floors (R08, R10), measured again on 2026-10-11 with the policy of today, the reference party and the five battery parties (scratch/audit_2026-10-11/e7_stage15_fit.py, rows of eight random battles, 24 rows, floors St15_1120 and St15_1150; mean battles won against vanilla over the twelve cells): with no change the variant is easier (+0.8); HP, ATK and INT x1.30 with x1.95 / x1.69 on three enemies, the rows of 2026-10-09, made it harder for every party but one (-1.1; Mage-Heavy 7.1 to 3.7 on St15_1150) because attack is subtracted from defence and x1.69 ATK was x2 to x3.3 damage, a common enemy above the ATK of the last boss; HP x1.20 alone gives +0.15, the largest gap 1.2 battles, and no hit grows. HP x1.20, ATK and INT of vanilla</t>
         </is>
       </c>
       <c r="K1332" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1332" t="inlineStr">
@@ -74456,7 +74456,7 @@
       </c>
       <c r="J1333" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1333" t="inlineStr">
@@ -74466,7 +74466,7 @@
       </c>
       <c r="L1333" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -74509,7 +74509,7 @@
       </c>
       <c r="J1334" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1334" t="inlineStr">
@@ -74519,7 +74519,7 @@
       </c>
       <c r="L1334" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -74548,7 +74548,7 @@
         <v>5871</v>
       </c>
       <c r="G1335" t="n">
-        <v>6750</v>
+        <v>7045</v>
       </c>
       <c r="H1335" t="inlineStr">
         <is>
@@ -74562,12 +74562,12 @@
       </c>
       <c r="J1335" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Difficulty kept on the common fights of the last floors (R08, R10), measured again on 2026-10-11 with the policy of today, the reference party and the five battery parties (scratch/audit_2026-10-11/e7_stage15_fit.py, rows of eight random battles, 24 rows, floors St15_1120 and St15_1150; mean battles won against vanilla over the twelve cells): with no change the variant is easier (+0.8); HP, ATK and INT x1.30 with x1.95 / x1.69 on three enemies, the rows of 2026-10-09, made it harder for every party but one (-1.1; Mage-Heavy 7.1 to 3.7 on St15_1150) because attack is subtracted from defence and x1.69 ATK was x2 to x3.3 damage, a common enemy above the ATK of the last boss; HP x1.20 alone gives +0.15, the largest gap 1.2 battles, and no hit grows. HP x1.20, ATK and INT of vanilla</t>
         </is>
       </c>
       <c r="K1335" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1335" t="inlineStr">
@@ -74615,7 +74615,7 @@
       </c>
       <c r="J1336" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1336" t="inlineStr">
@@ -74625,7 +74625,7 @@
       </c>
       <c r="L1336" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -74668,7 +74668,7 @@
       </c>
       <c r="J1337" t="inlineStr">
         <is>
-          <t>Difficulty kept on the common fights (R08, R10; the user: harden everything within the windows of vanilla): rows of eight random battles on the floors of C39 and C40 had become far easier on the variant (C39: 4.9 battles won and 8% HP left in vanilla, 6.6 and 50% on the variant; C40: 5.3 and 42%, 7.5 and 92%) through the stronger party. HP, ATK and INT x1.30 for the common enemies of the two floors, x1.95 HP and x1.69 ATK and INT for Macha, Purski and Highway Star, found only on the C40 floor of the two: C39 4.2 and 17%, C40 5.4 and 42% after (24 rows each)</t>
+          <t>Dropped on 2026-10-11: ATK and INT of the common enemies of Stage 15 stay at vanilla. See the hp row of the same enemy: the measure of today is met by HP alone, and a factor on attack multiplied the damage by far more than its figure</t>
         </is>
       </c>
       <c r="K1337" t="inlineStr">
@@ -74678,7 +74678,7 @@
       </c>
       <c r="L1337" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1404"/>
+  <dimension ref="A1:L1417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70163,7 +70163,7 @@
       </c>
       <c r="J1252" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C26 easier (wins / length / lowest HP: vanilla 85% / 24.9 / 47%, variant 100% / 9.4 / 61%); HP x1.80, ATK and INT x1.16 bring it back into the window of vanilla (95% / 24.0 / 47%). Only enemies of no random formation</t>
+          <t>Dropped on 2026-10-11: ATK and INT x1.16 were the half that was left of the fit of 2026-10-09 (HP x1.80 was dropped earlier) and made C26 harder than vanilla where it counts: the pressure on the reference party 0.07 to 0.11, out of its window on the harder side, and the Mage-Heavy party from 84% to 72% of wins, below the floor of the boss (80%; docs/generated/PARTY_BATTERY.md, 100 battles). Was: Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C26 easier (wins / length / lowest HP: vanilla 85% / 24.9 / 47%, variant 100% / 9.4 / 61%); HP x1.80, ATK and INT x1.16 bring it back into the window of vanilla (95% / 24.0 / 47%). Only enemies of no random formation</t>
         </is>
       </c>
       <c r="K1252" t="inlineStr">
@@ -70173,7 +70173,7 @@
       </c>
       <c r="L1252" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -70216,7 +70216,7 @@
       </c>
       <c r="J1253" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C26 easier (wins / length / lowest HP: vanilla 85% / 24.9 / 47%, variant 100% / 9.4 / 61%); HP x1.80, ATK and INT x1.16 bring it back into the window of vanilla (95% / 24.0 / 47%). Only enemies of no random formation</t>
+          <t>Dropped on 2026-10-11: ATK and INT x1.16 were the half that was left of the fit of 2026-10-09 (HP x1.80 was dropped earlier) and made C26 harder than vanilla where it counts: the pressure on the reference party 0.07 to 0.11, out of its window on the harder side, and the Mage-Heavy party from 84% to 72% of wins, below the floor of the boss (80%; docs/generated/PARTY_BATTERY.md, 100 battles). Was: Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C26 easier (wins / length / lowest HP: vanilla 85% / 24.9 / 47%, variant 100% / 9.4 / 61%); HP x1.80, ATK and INT x1.16 bring it back into the window of vanilla (95% / 24.0 / 47%). Only enemies of no random formation</t>
         </is>
       </c>
       <c r="K1253" t="inlineStr">
@@ -70226,7 +70226,7 @@
       </c>
       <c r="L1253" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -70322,7 +70322,7 @@
       </c>
       <c r="J1255" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C26 easier (wins / length / lowest HP: vanilla 85% / 24.9 / 47%, variant 100% / 9.4 / 61%); HP x1.80, ATK and INT x1.16 bring it back into the window of vanilla (95% / 24.0 / 47%). Only enemies of no random formation</t>
+          <t>Dropped on 2026-10-11: ATK and INT x1.16 were the half that was left of the fit of 2026-10-09 (HP x1.80 was dropped earlier) and made C26 harder than vanilla where it counts: the pressure on the reference party 0.07 to 0.11, out of its window on the harder side, and the Mage-Heavy party from 84% to 72% of wins, below the floor of the boss (80%; docs/generated/PARTY_BATTERY.md, 100 battles). Was: Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C26 easier (wins / length / lowest HP: vanilla 85% / 24.9 / 47%, variant 100% / 9.4 / 61%); HP x1.80, ATK and INT x1.16 bring it back into the window of vanilla (95% / 24.0 / 47%). Only enemies of no random formation</t>
         </is>
       </c>
       <c r="K1255" t="inlineStr">
@@ -70332,7 +70332,7 @@
       </c>
       <c r="L1255" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -70375,7 +70375,7 @@
       </c>
       <c r="J1256" t="inlineStr">
         <is>
-          <t>Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C26 easier (wins / length / lowest HP: vanilla 85% / 24.9 / 47%, variant 100% / 9.4 / 61%); HP x1.80, ATK and INT x1.16 bring it back into the window of vanilla (95% / 24.0 / 47%). Only enemies of no random formation</t>
+          <t>Dropped on 2026-10-11: ATK and INT x1.16 were the half that was left of the fit of 2026-10-09 (HP x1.80 was dropped earlier) and made C26 harder than vanilla where it counts: the pressure on the reference party 0.07 to 0.11, out of its window on the harder side, and the Mage-Heavy party from 84% to 72% of wins, below the floor of the boss (80%; docs/generated/PARTY_BATTERY.md, 100 battles). Was: Difficulty kept (R08, R10; tools/boss_fit.py): the classes and skills of the variant made C26 easier (wins / length / lowest HP: vanilla 85% / 24.9 / 47%, variant 100% / 9.4 / 61%); HP x1.80, ATK and INT x1.16 bring it back into the window of vanilla (95% / 24.0 / 47%). Only enemies of no random formation</t>
         </is>
       </c>
       <c r="K1256" t="inlineStr">
@@ -70385,7 +70385,7 @@
       </c>
       <c r="L1256" t="inlineStr">
         <is>
-          <t>decided</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -78337,6 +78337,695 @@
         </is>
       </c>
       <c r="L1404" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>G103</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>645 Big Bad Beard (C20)</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1405" t="n">
+        <v>888</v>
+      </c>
+      <c r="G1405" t="n">
+        <v>1066</v>
+      </c>
+      <c r="H1405" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1405" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1405" t="inlineStr">
+        <is>
+          <t>A little harder, to make up for what the variant eased (R10; the user, 2026-10-11; tools/boss_fit.py gentle, docs/generated/BOSS_FIT.md): C20, reference party, wins / length / lowest HP: vanilla 100% / 1.5 / 95%, variant 100% / 1.5 / 96%, with HP x1.20, ATK and INT x1.08 100% / 1.5 / 94%. Every archetype of the battery still wins at least the floor of the boss (80%): Meta 100%, Dual-Support 100%, Mage-Heavy 100%, Juggernaut 100%, Anti-Meta 100%</t>
+        </is>
+      </c>
+      <c r="K1405" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1405" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>G104</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>645 Big Bad Beard (C20)</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="F1406" t="n">
+        <v>124</v>
+      </c>
+      <c r="G1406" t="n">
+        <v>134</v>
+      </c>
+      <c r="H1406" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1406" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1406" t="inlineStr">
+        <is>
+          <t>A little harder, to make up for what the variant eased (R10; the user, 2026-10-11; tools/boss_fit.py gentle, docs/generated/BOSS_FIT.md): C20, reference party, wins / length / lowest HP: vanilla 100% / 1.5 / 95%, variant 100% / 1.5 / 96%, with HP x1.20, ATK and INT x1.08 100% / 1.5 / 94%. Every archetype of the battery still wins at least the floor of the boss (80%): Meta 100%, Dual-Support 100%, Mage-Heavy 100%, Juggernaut 100%, Anti-Meta 100%</t>
+        </is>
+      </c>
+      <c r="K1406" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1406" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>G105</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>645 Big Bad Beard (C20)</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F1407" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1407" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1407" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1407" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1407" t="inlineStr">
+        <is>
+          <t>A little harder, to make up for what the variant eased (R10; the user, 2026-10-11; tools/boss_fit.py gentle, docs/generated/BOSS_FIT.md): C20, reference party, wins / length / lowest HP: vanilla 100% / 1.5 / 95%, variant 100% / 1.5 / 96%, with HP x1.20, ATK and INT x1.08 100% / 1.5 / 94%. Every archetype of the battery still wins at least the floor of the boss (80%): Meta 100%, Dual-Support 100%, Mage-Heavy 100%, Juggernaut 100%, Anti-Meta 100%</t>
+        </is>
+      </c>
+      <c r="K1407" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1407" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>G106</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>655 Fuzzy Merchandise (C21)</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1408" t="n">
+        <v>852</v>
+      </c>
+      <c r="G1408" t="n">
+        <v>1108</v>
+      </c>
+      <c r="H1408" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1408" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1408" t="inlineStr">
+        <is>
+          <t>A little harder, to make up for what the variant eased (R10; the user, 2026-10-11; tools/boss_fit.py gentle, docs/generated/BOSS_FIT.md): C21, reference party, wins / length / lowest HP: vanilla 100% / 14.5 / 59%, variant 100% / 9.9 / 66%, with HP x1.30 100% / 15.6 / 63%. Every archetype of the battery still wins at least the floor of the boss (80%): Meta 100%, Dual-Support 100%, Mage-Heavy 85%, Juggernaut 98%, Anti-Meta 98%</t>
+        </is>
+      </c>
+      <c r="K1408" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1408" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>G107</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>656 Fluffy Merchandise (C21)</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1409" t="n">
+        <v>824</v>
+      </c>
+      <c r="G1409" t="n">
+        <v>1071</v>
+      </c>
+      <c r="H1409" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1409" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1409" t="inlineStr">
+        <is>
+          <t>A little harder, to make up for what the variant eased (R10; the user, 2026-10-11; tools/boss_fit.py gentle, docs/generated/BOSS_FIT.md): C21, reference party, wins / length / lowest HP: vanilla 100% / 14.5 / 59%, variant 100% / 9.9 / 66%, with HP x1.30 100% / 15.6 / 63%. Every archetype of the battery still wins at least the floor of the boss (80%): Meta 100%, Dual-Support 100%, Mage-Heavy 85%, Juggernaut 98%, Anti-Meta 98%</t>
+        </is>
+      </c>
+      <c r="K1409" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1409" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>G108</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>1008 Trafficker Twinny (C21)</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1410" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G1410" t="n">
+        <v>4940</v>
+      </c>
+      <c r="H1410" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1410" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1410" t="inlineStr">
+        <is>
+          <t>A little harder, to make up for what the variant eased (R10; the user, 2026-10-11; tools/boss_fit.py gentle, docs/generated/BOSS_FIT.md): C21, reference party, wins / length / lowest HP: vanilla 100% / 14.5 / 59%, variant 100% / 9.9 / 66%, with HP x1.30 100% / 15.6 / 63%. Every archetype of the battery still wins at least the floor of the boss (80%): Meta 100%, Dual-Support 100%, Mage-Heavy 85%, Juggernaut 98%, Anti-Meta 98%</t>
+        </is>
+      </c>
+      <c r="K1410" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1410" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>G109</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>1012 Spirit of Mag Mell (C28)</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1411" t="n">
+        <v>8200</v>
+      </c>
+      <c r="G1411" t="n">
+        <v>9020</v>
+      </c>
+      <c r="H1411" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1411" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1411" t="inlineStr">
+        <is>
+          <t>A little harder, to make up for what the variant eased (R10; the user, 2026-10-11; tools/boss_fit.py gentle, docs/generated/BOSS_FIT.md): C28, reference party, wins / length / lowest HP: vanilla 88% / 13.4 / 35%, variant 95% / 9.6 / 43%, with HP x1.10 95% / 10.5 / 43%. Every archetype of the battery still wins at least the floor of the boss (50%): Meta 98%, Dual-Support 88%, Mage-Heavy 92%, Juggernaut 62%, Anti-Meta 55%</t>
+        </is>
+      </c>
+      <c r="K1411" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1411" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>G110</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>1013 Heartless Avenger (C30)</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1412" t="n">
+        <v>8500</v>
+      </c>
+      <c r="G1412" t="n">
+        <v>9350</v>
+      </c>
+      <c r="H1412" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1412" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1412" t="inlineStr">
+        <is>
+          <t>A little harder, to make up for what the variant eased (R10; the user, 2026-10-11; tools/boss_fit.py gentle, docs/generated/BOSS_FIT.md): C30, reference party, wins / length / lowest HP: vanilla 62% / 41.3 / 31%, variant 92% / 34.7 / 48%, with HP x1.10 88% / 38.4 / 46%. Every archetype of the battery still wins at least the floor of the boss (50%): Meta 95%, Dual-Support 98%, Mage-Heavy 92%, Juggernaut 62%, Anti-Meta 60%</t>
+        </is>
+      </c>
+      <c r="K1412" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1412" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>G111</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>1035 Heartless Avenger (C30)</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1413" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G1413" t="n">
+        <v>7480</v>
+      </c>
+      <c r="H1413" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1413" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1413" t="inlineStr">
+        <is>
+          <t>A little harder, to make up for what the variant eased (R10; the user, 2026-10-11; tools/boss_fit.py gentle, docs/generated/BOSS_FIT.md): C30, reference party, wins / length / lowest HP: vanilla 62% / 41.3 / 31%, variant 92% / 34.7 / 48%, with HP x1.10 88% / 38.4 / 46%. Every archetype of the battery still wins at least the floor of the boss (50%): Meta 95%, Dual-Support 98%, Mage-Heavy 92%, Juggernaut 62%, Anti-Meta 60%</t>
+        </is>
+      </c>
+      <c r="K1413" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1413" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>G112</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>524 Tres Durian (C31)</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1414" t="n">
+        <v>8888</v>
+      </c>
+      <c r="G1414" t="n">
+        <v>11554</v>
+      </c>
+      <c r="H1414" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1414" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1414" t="inlineStr">
+        <is>
+          <t>A little harder, to make up for what the variant eased (R10; the user, 2026-10-11; tools/boss_fit.py gentle, docs/generated/BOSS_FIT.md): C31, reference party, wins / length / lowest HP: vanilla 100% / 18.8 / 73%, variant 100% / 13.6 / 75%, with HP x1.30 100% / 19.6 / 74%. Every archetype of the battery still wins at least the floor of the boss (50%): Meta 100%, Dual-Support 100%, Mage-Heavy 100%, Juggernaut 100%, Anti-Meta 90%</t>
+        </is>
+      </c>
+      <c r="K1414" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1414" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>G113</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>526 Mangos Queen (C31)</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1415" t="n">
+        <v>7777</v>
+      </c>
+      <c r="G1415" t="n">
+        <v>10110</v>
+      </c>
+      <c r="H1415" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1415" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1415" t="inlineStr">
+        <is>
+          <t>A little harder, to make up for what the variant eased (R10; the user, 2026-10-11; tools/boss_fit.py gentle, docs/generated/BOSS_FIT.md): C31, reference party, wins / length / lowest HP: vanilla 100% / 18.8 / 73%, variant 100% / 13.6 / 75%, with HP x1.30 100% / 19.6 / 74%. Every archetype of the battery still wins at least the floor of the boss (50%): Meta 100%, Dual-Support 100%, Mage-Heavy 100%, Juggernaut 100%, Anti-Meta 90%</t>
+        </is>
+      </c>
+      <c r="K1415" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1415" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>G114</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>1036 Queen of Darkness (C34)</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1416" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G1416" t="n">
+        <v>10400</v>
+      </c>
+      <c r="H1416" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1416" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1416" t="inlineStr">
+        <is>
+          <t>A little harder, to make up for what the variant eased (R10; the user, 2026-10-11; tools/boss_fit.py gentle, docs/generated/BOSS_FIT.md): C34, reference party, wins / length / lowest HP: vanilla 100% / 41.6 / 60%, variant 100% / 24.5 / 61%, with HP x1.30 100% / 35.6 / 60%. Every archetype of the battery still wins at least the floor of the boss (80%): Meta 100%, Dual-Support 100%, Mage-Heavy 100%, Juggernaut 100%, Anti-Meta 100%</t>
+        </is>
+      </c>
+      <c r="K1416" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1416" t="inlineStr">
+        <is>
+          <t>decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>G115</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>1037 Queen of Darkness (C34)</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1417" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G1417" t="n">
+        <v>13000</v>
+      </c>
+      <c r="H1417" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1417" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1417" t="inlineStr">
+        <is>
+          <t>A little harder, to make up for what the variant eased (R10; the user, 2026-10-11; tools/boss_fit.py gentle, docs/generated/BOSS_FIT.md): C34, reference party, wins / length / lowest HP: vanilla 100% / 41.6 / 60%, variant 100% / 24.5 / 61%, with HP x1.30 100% / 35.6 / 60%. Every archetype of the battery still wins at least the floor of the boss (80%): Meta 100%, Dual-Support 100%, Mage-Heavy 100%, Juggernaut 100%, Anti-Meta 100%</t>
+        </is>
+      </c>
+      <c r="K1417" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1417" t="inlineStr">
         <is>
           <t>decided</t>
         </is>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1417"/>
+  <dimension ref="A1:L1457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30247,7 +30247,7 @@
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: a passive skill record holds one weapon code (PassiveSkillData 0x54), so "8, 15" cannot be stored; the only code that covers a gun is 19, "all weapons" (Weapon Mastery, Knock Down), which is wider than bow or gun. To decide: 19, or the passive stays a bow skill. Was: Guns may use four more bow skills (structural: a weapon mask the game already uses for Chain Spike, Guided Shot and Poison Shot)</t>
+          <t>Dropped on 2026-10-11 (the user): the passive stays a bow skill. A passive record holds one weapon code, and the game has one gun, the Degtyaryov (ATK 97; the best bow has 468), which Spiral Arrow and Divine Cannon do reach (W036, W037). Blocked on 2026-10-11: a passive skill record holds one weapon code (PassiveSkillData 0x54), so "8, 15" cannot be stored; the only code that covers a gun is 19, "all weapons" (Weapon Mastery, Knock Down), which is wider than bow or gun. To decide: 19, or the passive stays a bow skill. Was: Guns may use four more bow skills (structural: a weapon mask the game already uses for Chain Spike, Guided Shot and Poison Shot)</t>
         </is>
       </c>
       <c r="K532" t="inlineStr">
@@ -30257,7 +30257,7 @@
       </c>
       <c r="L532" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -30304,7 +30304,7 @@
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: a passive skill record holds one weapon code (PassiveSkillData 0x54), so "8, 15" cannot be stored; the only code that covers a gun is 19, "all weapons" (Weapon Mastery, Knock Down), which is wider than bow or gun. To decide: 19, or the passive stays a bow skill. Was: Guns may use four more bow skills (structural: a weapon mask the game already uses for Chain Spike, Guided Shot and Poison Shot)</t>
+          <t>Dropped on 2026-10-11 (the user): the passive stays a bow skill. A passive record holds one weapon code, and the game has one gun, the Degtyaryov (ATK 97; the best bow has 468), which Spiral Arrow and Divine Cannon do reach (W036, W037). Blocked on 2026-10-11: a passive skill record holds one weapon code (PassiveSkillData 0x54), so "8, 15" cannot be stored; the only code that covers a gun is 19, "all weapons" (Weapon Mastery, Knock Down), which is wider than bow or gun. To decide: 19, or the passive stays a bow skill. Was: Guns may use four more bow skills (structural: a weapon mask the game already uses for Chain Spike, Guided Shot and Poison Shot)</t>
         </is>
       </c>
       <c r="K533" t="inlineStr">
@@ -30314,7 +30314,7 @@
       </c>
       <c r="L533" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -76135,7 +76135,7 @@
       </c>
       <c r="J1364" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: QuestData 0x38 is the kind of the reward (0 an item, 1 a piece of equipment, 2 and 3 an amount at 0x40) and 0x3C the id of the item or the piece; the figure the row took for gold is that id in quests 0, 5 and 100 (items 30, 42 and 585) and in quest 200 (the piece 599, Postapocalypse Helm), and in quest 50 an amount of kind 3. Written as it stands the row would change what the quest gives, or name a piece that does not exist. To decide: which quests pay gold (kind 2, 37 of them) and by how much. Was: Early progression quest gold raised by +50% to ease early consumable and gear acquisition.</t>
+          <t>Dropped on 2026-10-11: the quest does not pay gold. QuestData 0x38 is the kind of its reward (0 an item, 1 a piece of equipment, 2 experience, 3 gold; 0x55e210 - 0x55e2a0) and the figure this row took for gold is the id of the item or piece. The gold of quests is raised by row P028 and the rows after P038. Blocked on 2026-10-11: QuestData 0x38 is the kind of the reward (0 an item, 1 a piece of equipment, 2 and 3 an amount at 0x40) and 0x3C the id of the item or the piece; the figure the row took for gold is that id in quests 0, 5 and 100 (items 30, 42 and 585) and in quest 200 (the piece 599, Postapocalypse Helm), and in quest 50 an amount of kind 3. Written as it stands the row would change what the quest gives, or name a piece that does not exist. To decide: which quests pay gold (kind 2, 37 of them) and by how much. Was: Early progression quest gold raised by +50% to ease early consumable and gear acquisition.</t>
         </is>
       </c>
       <c r="K1364" t="inlineStr">
@@ -76145,7 +76145,7 @@
       </c>
       <c r="L1364" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -76188,7 +76188,7 @@
       </c>
       <c r="J1365" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: QuestData 0x38 is the kind of the reward (0 an item, 1 a piece of equipment, 2 and 3 an amount at 0x40) and 0x3C the id of the item or the piece; the figure the row took for gold is that id in quests 0, 5 and 100 (items 30, 42 and 585) and in quest 200 (the piece 599, Postapocalypse Helm), and in quest 50 an amount of kind 3. Written as it stands the row would change what the quest gives, or name a piece that does not exist. To decide: which quests pay gold (kind 2, 37 of them) and by how much. Was: Early progression quest gold raised by +43% to ease early consumable and gear acquisition.</t>
+          <t>Dropped on 2026-10-11: the quest does not pay gold. QuestData 0x38 is the kind of its reward (0 an item, 1 a piece of equipment, 2 experience, 3 gold; 0x55e210 - 0x55e2a0) and the figure this row took for gold is the id of the item or piece. The gold of quests is raised by row P028 and the rows after P038. Blocked on 2026-10-11: QuestData 0x38 is the kind of the reward (0 an item, 1 a piece of equipment, 2 and 3 an amount at 0x40) and 0x3C the id of the item or the piece; the figure the row took for gold is that id in quests 0, 5 and 100 (items 30, 42 and 585) and in quest 200 (the piece 599, Postapocalypse Helm), and in quest 50 an amount of kind 3. Written as it stands the row would change what the quest gives, or name a piece that does not exist. To decide: which quests pay gold (kind 2, 37 of them) and by how much. Was: Early progression quest gold raised by +43% to ease early consumable and gear acquisition.</t>
         </is>
       </c>
       <c r="K1365" t="inlineStr">
@@ -76198,7 +76198,7 @@
       </c>
       <c r="L1365" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -76227,7 +76227,7 @@
         <v>350</v>
       </c>
       <c r="G1366" t="n">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="H1366" t="inlineStr">
         <is>
@@ -76241,17 +76241,17 @@
       </c>
       <c r="J1366" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: QuestData 0x38 is the kind of the reward (0 an item, 1 a piece of equipment, 2 and 3 an amount at 0x40) and 0x3C the id of the item or the piece; the figure the row took for gold is that id in quests 0, 5 and 100 (items 30, 42 and 585) and in quest 200 (the piece 599, Postapocalypse Helm), and in quest 50 an amount of kind 3. Written as it stands the row would change what the quest gives, or name a piece that does not exist. To decide: which quests pay gold (kind 2, 37 of them) and by how much. Was: Midgame quest gold raised by +43% to incentivize quest completion for lagging parties.</t>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
         </is>
       </c>
       <c r="K1366" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1366" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>built</t>
         </is>
       </c>
     </row>
@@ -76294,7 +76294,7 @@
       </c>
       <c r="J1367" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: QuestData 0x38 is the kind of the reward (0 an item, 1 a piece of equipment, 2 and 3 an amount at 0x40) and 0x3C the id of the item or the piece; the figure the row took for gold is that id in quests 0, 5 and 100 (items 30, 42 and 585) and in quest 200 (the piece 599, Postapocalypse Helm), and in quest 50 an amount of kind 3. Written as it stands the row would change what the quest gives, or name a piece that does not exist. To decide: which quests pay gold (kind 2, 37 of them) and by how much. Was: Midgame quest gold raised by +45% to incentivize quest completion for lagging parties.</t>
+          <t>Dropped on 2026-10-11: the quest does not pay gold. QuestData 0x38 is the kind of its reward (0 an item, 1 a piece of equipment, 2 experience, 3 gold; 0x55e210 - 0x55e2a0) and the figure this row took for gold is the id of the item or piece. The gold of quests is raised by row P028 and the rows after P038. Blocked on 2026-10-11: QuestData 0x38 is the kind of the reward (0 an item, 1 a piece of equipment, 2 and 3 an amount at 0x40) and 0x3C the id of the item or the piece; the figure the row took for gold is that id in quests 0, 5 and 100 (items 30, 42 and 585) and in quest 200 (the piece 599, Postapocalypse Helm), and in quest 50 an amount of kind 3. Written as it stands the row would change what the quest gives, or name a piece that does not exist. To decide: which quests pay gold (kind 2, 37 of them) and by how much. Was: Midgame quest gold raised by +45% to incentivize quest completion for lagging parties.</t>
         </is>
       </c>
       <c r="K1367" t="inlineStr">
@@ -76304,7 +76304,7 @@
       </c>
       <c r="L1367" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -76347,7 +76347,7 @@
       </c>
       <c r="J1368" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: QuestData 0x38 is the kind of the reward (0 an item, 1 a piece of equipment, 2 and 3 an amount at 0x40) and 0x3C the id of the item or the piece; the figure the row took for gold is that id in quests 0, 5 and 100 (items 30, 42 and 585) and in quest 200 (the piece 599, Postapocalypse Helm), and in quest 50 an amount of kind 3. Written as it stands the row would change what the quest gives, or name a piece that does not exist. To decide: which quests pay gold (kind 2, 37 of them) and by how much. Was: Late game quest gold raised by +50% to incentivize quest completion for lagging parties.</t>
+          <t>Dropped on 2026-10-11: the quest does not pay gold. QuestData 0x38 is the kind of its reward (0 an item, 1 a piece of equipment, 2 experience, 3 gold; 0x55e210 - 0x55e2a0) and the figure this row took for gold is the id of the item or piece. The gold of quests is raised by row P028 and the rows after P038. Blocked on 2026-10-11: QuestData 0x38 is the kind of the reward (0 an item, 1 a piece of equipment, 2 and 3 an amount at 0x40) and 0x3C the id of the item or the piece; the figure the row took for gold is that id in quests 0, 5 and 100 (items 30, 42 and 585) and in quest 200 (the piece 599, Postapocalypse Helm), and in quest 50 an amount of kind 3. Written as it stands the row would change what the quest gives, or name a piece that does not exist. To decide: which quests pay gold (kind 2, 37 of them) and by how much. Was: Late game quest gold raised by +50% to incentivize quest completion for lagging parties.</t>
         </is>
       </c>
       <c r="K1368" t="inlineStr">
@@ -76357,7 +76357,7 @@
       </c>
       <c r="L1368" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -79038,6 +79038,2126 @@
         </is>
       </c>
       <c r="L1417" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>P039</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>QuestData_0004 (Pest Control)</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1418" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1418" t="n">
+        <v>420</v>
+      </c>
+      <c r="H1418" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1418" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1418" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1418" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1418" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>P040</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>QuestData_0022 (Curio Collector)</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1419" t="n">
+        <v>400</v>
+      </c>
+      <c r="G1419" t="n">
+        <v>560</v>
+      </c>
+      <c r="H1419" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1419" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1419" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1419" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1419" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>P041</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>QuestData_0023 (Threat Removal)</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1420" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1420" t="n">
+        <v>2800</v>
+      </c>
+      <c r="H1420" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1420" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1420" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1420" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1420" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>P042</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>QuestData_0026 (Pest Control)</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1421" t="n">
+        <v>400</v>
+      </c>
+      <c r="G1421" t="n">
+        <v>560</v>
+      </c>
+      <c r="H1421" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1421" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1421" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1421" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1421" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>P043</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>QuestData_0052 (Flavor Hound)</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1422" t="n">
+        <v>600</v>
+      </c>
+      <c r="G1422" t="n">
+        <v>840</v>
+      </c>
+      <c r="H1422" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1422" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1422" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1422" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1422" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>P044</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>QuestData_0074 (Weapon Collector)</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1423" t="n">
+        <v>800</v>
+      </c>
+      <c r="G1423" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H1423" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1423" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1423" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1423" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1423" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>P045</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>QuestData_0078 (Pest Control)</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1424" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G1424" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H1424" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1424" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1424" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1424" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1424" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>P046</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>QuestData_0098 (Antique Hunter)</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1425" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G1425" t="n">
+        <v>2100</v>
+      </c>
+      <c r="H1425" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1425" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1425" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1425" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1425" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>P047</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>QuestData_0103 (Pelter Skelter)</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1426" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G1426" t="n">
+        <v>2250</v>
+      </c>
+      <c r="H1426" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1426" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1426" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1426" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1426" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>P048</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>QuestData_0119 (Adventurer Brain)</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1427" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G1427" t="n">
+        <v>10500</v>
+      </c>
+      <c r="H1427" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1427" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1427" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1427" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1427" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>P049</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>QuestData_0140 (Pest Control)</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1428" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G1428" t="n">
+        <v>4200</v>
+      </c>
+      <c r="H1428" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1428" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1428" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1428" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1428" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>P050</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>QuestData_0148 (Product Development)</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1429" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G1429" t="n">
+        <v>4200</v>
+      </c>
+      <c r="H1429" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1429" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1429" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1429" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1429" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>P051</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>QuestData_0159 (Rivers of Pulp)</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1430" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G1430" t="n">
+        <v>28000</v>
+      </c>
+      <c r="H1430" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1430" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1430" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1430" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1430" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>P052</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>QuestData_0170 (Threat Removal)</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1431" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G1431" t="n">
+        <v>11000</v>
+      </c>
+      <c r="H1431" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1431" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1431" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1431" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1431" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>P053</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>QuestData_0173 (Soul Harvest)</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1432" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G1432" t="n">
+        <v>7000</v>
+      </c>
+      <c r="H1432" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1432" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1432" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1432" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1432" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>P054</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>QuestData_0190 (Shiny Hoarder)</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1433" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G1433" t="n">
+        <v>7000</v>
+      </c>
+      <c r="H1433" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1433" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1433" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1433" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1433" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>P055</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>QuestData_0193 (Pest Control)</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1434" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G1434" t="n">
+        <v>11000</v>
+      </c>
+      <c r="H1434" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1434" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1434" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1434" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1434" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>P056</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>QuestData_0204 (Honorary Maid)</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1435" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G1435" t="n">
+        <v>8400</v>
+      </c>
+      <c r="H1435" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1435" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1435" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1435" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1435" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>P057</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>QuestData_0231 (Threat Removal)</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1436" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G1436" t="n">
+        <v>11000</v>
+      </c>
+      <c r="H1436" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1436" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1436" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1436" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1436" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>P058</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>QuestData_0254 (Product Development)</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1437" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G1437" t="n">
+        <v>8400</v>
+      </c>
+      <c r="H1437" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1437" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1437" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1437" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1437" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>P059</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>QuestData_0265 (Curio Collector)</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1438" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G1438" t="n">
+        <v>8400</v>
+      </c>
+      <c r="H1438" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1438" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1438" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1438" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1438" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>P060</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>QuestData_0273 (Soul Harvest)</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1439" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G1439" t="n">
+        <v>17000</v>
+      </c>
+      <c r="H1439" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1439" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1439" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1439" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1439" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>P061</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>QuestData_0294 (Pest Control)</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1440" t="n">
+        <v>13000</v>
+      </c>
+      <c r="G1440" t="n">
+        <v>18000</v>
+      </c>
+      <c r="H1440" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1440" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1440" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1440" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1440" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>P062</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>QuestData_0298 (Beard Revue)</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1441" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G1441" t="n">
+        <v>28000</v>
+      </c>
+      <c r="H1441" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1441" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1441" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1441" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1441" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>P063</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>QuestData_0307 (Last-Minute Souvenir)</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1442" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G1442" t="n">
+        <v>28000</v>
+      </c>
+      <c r="H1442" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1442" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1442" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1442" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1442" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>P064</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>QuestData_0328 (Shiny Hoarder)</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1443" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G1443" t="n">
+        <v>56000</v>
+      </c>
+      <c r="H1443" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1443" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1443" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1443" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1443" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>P065</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>QuestData_0338 (Soul Harvest)</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1444" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G1444" t="n">
+        <v>35000</v>
+      </c>
+      <c r="H1444" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1444" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1444" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1444" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1444" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>P066</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>QuestData_0344 (Last-Minute Souvenir)</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1445" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G1445" t="n">
+        <v>28000</v>
+      </c>
+      <c r="H1445" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1445" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1445" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1445" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1445" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>P067</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>QuestData_0352 (Threat Removal)</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1446" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G1446" t="n">
+        <v>35000</v>
+      </c>
+      <c r="H1446" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1446" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1446" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1446" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1446" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>P068</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>QuestData_0364 (Soul Harvest)</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1447" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G1447" t="n">
+        <v>42000</v>
+      </c>
+      <c r="H1447" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1447" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1447" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1447" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1447" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>P069</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>QuestData_0388 (Sake Sommelier)</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1448" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G1448" t="n">
+        <v>56000</v>
+      </c>
+      <c r="H1448" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1448" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1448" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1448" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1448" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>P070</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>QuestData_0389 (Adventurer Brain)</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1449" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G1449" t="n">
+        <v>280000</v>
+      </c>
+      <c r="H1449" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1449" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1449" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1449" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1449" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>P071</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>QuestData_0392 (Pest Control)</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1450" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G1450" t="n">
+        <v>168000</v>
+      </c>
+      <c r="H1450" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1450" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1450" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1450" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1450" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>P072</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>QuestData_0404 (Chasing Trends)</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1451" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G1451" t="n">
+        <v>140000</v>
+      </c>
+      <c r="H1451" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1451" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1451" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1451" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1451" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>P073</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>QuestData_0414 (Sake Sommelier)</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1452" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G1452" t="n">
+        <v>168000</v>
+      </c>
+      <c r="H1452" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1452" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1452" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1452" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1452" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>P074</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>QuestData_0419 (Fortress Mutant)</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1453" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G1453" t="n">
+        <v>14000</v>
+      </c>
+      <c r="H1453" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1453" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1453" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1453" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1453" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>P075</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>QuestData_0436 (Crevasse Delvers)</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1454" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G1454" t="n">
+        <v>420000</v>
+      </c>
+      <c r="H1454" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1454" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1454" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1454" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1454" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>P076</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>QuestData_0438 (Mage City Challenger)</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1455" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G1455" t="n">
+        <v>350000</v>
+      </c>
+      <c r="H1455" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1455" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1455" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1455" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1455" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>P077</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>QuestData_0450 (Weapon Collector)</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1456" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G1456" t="n">
+        <v>420000</v>
+      </c>
+      <c r="H1456" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1456" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1456" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1456" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1456" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>P078</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>quests</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>QuestData_0465 (Quisling Killer)</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>gold reward</t>
+        </is>
+      </c>
+      <c r="F1457" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G1457" t="n">
+        <v>210000</v>
+      </c>
+      <c r="H1457" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1457" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="J1457" t="inlineStr">
+        <is>
+          <t>Gold of quests x1.40 (S20; the user, 2026-10-11, in the place of the five rows of 2026-10-10 that asked for +43% to +50% on figures that were not gold): every quest whose reward is gold, 41 of 471 (QuestData 0x38 = 3, the amount at 0x40, read at 0x5959ac - 0x5959ce where it goes to the party), rounded to the nearest 10 below 1,000, 50 below 10,000 and 500 above. The simulator has no quests: the row is checked by the build alone</t>
+        </is>
+      </c>
+      <c r="K1457" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1457" t="inlineStr">
         <is>
           <t>built</t>
         </is>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1457"/>
+  <dimension ref="A1:L1463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75340,7 +75340,7 @@
       </c>
       <c r="J1349" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: the word the row means is EnemyStatusData 0x80, which is not a chance: it is how many pieces the drop draws (0x558517 allocates that many; 0 to 3 over the 516 enemies), and the chance of the drop is 0x7C, already 100 for these bosses (16 for Garasha and Ryoma). 5 is outside what the game holds. To decide: the count (3 at most), or nothing. Was: Postgame boss rarest equipment drop rate gently raised from 1% to 3% to alleviate excessive reload grinding.</t>
+          <t>Dropped on 2026-10-11: the piece of this boss is already certain in vanilla. Its record holds a drop chance of 100 (0x7C), no item, and one slot (0x80 = 1) that names the piece with weight 100 (0x8C); the word the row changed is that count of slots, not a chance (0x558517; scratch/drops_reading.md).</t>
         </is>
       </c>
       <c r="K1349" t="inlineStr">
@@ -75350,7 +75350,7 @@
       </c>
       <c r="L1349" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -75393,7 +75393,7 @@
       </c>
       <c r="J1350" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: the word the row means is EnemyStatusData 0x80, which is not a chance: it is how many pieces the drop draws (0x558517 allocates that many; 0 to 3 over the 516 enemies), and the chance of the drop is 0x7C, already 100 for these bosses (16 for Garasha and Ryoma). 5 is outside what the game holds. To decide: the count (3 at most), or nothing. Was: Postgame boss rarest equipment drop rate gently raised from 1% to 3% to alleviate excessive reload grinding.</t>
+          <t>Dropped on 2026-10-11: the piece of this boss is already certain in vanilla. Its record holds a drop chance of 100 (0x7C), no item, and one slot (0x80 = 1) that names the piece with weight 100 (0x8C); the word the row changed is that count of slots, not a chance (0x558517; scratch/drops_reading.md).</t>
         </is>
       </c>
       <c r="K1350" t="inlineStr">
@@ -75403,7 +75403,7 @@
       </c>
       <c r="L1350" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -75446,7 +75446,7 @@
       </c>
       <c r="J1351" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: the word the row means is EnemyStatusData 0x80, which is not a chance: it is how many pieces the drop draws (0x558517 allocates that many; 0 to 3 over the 516 enemies), and the chance of the drop is 0x7C, already 100 for these bosses (16 for Garasha and Ryoma). 5 is outside what the game holds. To decide: the count (3 at most), or nothing. Was: Postgame superboss rarest equipment drop rate gently raised from 1% to 3%.</t>
+          <t>Dropped on 2026-10-11: the piece of this boss is already certain in vanilla. Its record holds a drop chance of 100 (0x7C), no item, and one slot (0x80 = 1) that names the piece with weight 100 (0x8C); the word the row changed is that count of slots, not a chance (0x558517; scratch/drops_reading.md).</t>
         </is>
       </c>
       <c r="K1351" t="inlineStr">
@@ -75456,7 +75456,7 @@
       </c>
       <c r="L1351" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -75499,7 +75499,7 @@
       </c>
       <c r="J1352" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: the word the row means is EnemyStatusData 0x80, which is not a chance: it is how many pieces the drop draws (0x558517 allocates that many; 0 to 3 over the 516 enemies), and the chance of the drop is 0x7C, already 100 for these bosses (16 for Garasha and Ryoma). 5 is outside what the game holds. To decide: the count (3 at most), or nothing. Was: Postgame superboss rarest equipment drop rate gently raised from 1% to 3%.</t>
+          <t>Dropped on 2026-10-11: the piece of this boss is already certain in vanilla. Its record holds a drop chance of 100 (0x7C), no item, and one slot (0x80 = 1) that names the piece with weight 100 (0x8C); the word the row changed is that count of slots, not a chance (0x558517; scratch/drops_reading.md).</t>
         </is>
       </c>
       <c r="K1352" t="inlineStr">
@@ -75509,7 +75509,7 @@
       </c>
       <c r="L1352" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -75552,7 +75552,7 @@
       </c>
       <c r="J1353" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: the word the row means is EnemyStatusData 0x80, which is not a chance: it is how many pieces the drop draws (0x558517 allocates that many; 0 to 3 over the 516 enemies), and the chance of the drop is 0x7C, already 100 for these bosses (16 for Garasha and Ryoma). 5 is outside what the game holds. To decide: the count (3 at most), or nothing. Was: Postgame superboss rarest equipment drop rate gently raised from 1% to 3%.</t>
+          <t>Dropped on 2026-10-11: the piece of this boss is already certain in vanilla. Its record holds a drop chance of 100 (0x7C), no item, and one slot (0x80 = 1) that names the piece with weight 100 (0x8C); the word the row changed is that count of slots, not a chance (0x558517; scratch/drops_reading.md).</t>
         </is>
       </c>
       <c r="K1353" t="inlineStr">
@@ -75562,7 +75562,7 @@
       </c>
       <c r="L1353" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -75605,7 +75605,7 @@
       </c>
       <c r="J1354" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: the word the row means is EnemyStatusData 0x80, which is not a chance: it is how many pieces the drop draws (0x558517 allocates that many; 0 to 3 over the 516 enemies), and the chance of the drop is 0x7C, already 100 for these bosses (16 for Garasha and Ryoma). 5 is outside what the game holds. To decide: the count (3 at most), or nothing. Was: Postgame superboss rarest equipment drop rate gently raised from 1% to 3%.</t>
+          <t>Dropped on 2026-10-11: the piece of this boss is already certain in vanilla. Its record holds a drop chance of 100 (0x7C), no item, and one slot (0x80 = 1) that names the piece with weight 100 (0x8C); the word the row changed is that count of slots, not a chance (0x558517; scratch/drops_reading.md).</t>
         </is>
       </c>
       <c r="K1354" t="inlineStr">
@@ -75615,7 +75615,7 @@
       </c>
       <c r="L1354" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -75658,7 +75658,7 @@
       </c>
       <c r="J1355" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: the word the row means is EnemyStatusData 0x80, which is not a chance: it is how many pieces the drop draws (0x558517 allocates that many; 0 to 3 over the 516 enemies), and the chance of the drop is 0x7C, already 100 for these bosses (16 for Garasha and Ryoma). 5 is outside what the game holds. To decide: the count (3 at most), or nothing. Was: Postgame rare equipment drop rate gently raised from 2% to 5%.</t>
+          <t>Dropped on 2026-10-11: the piece of this boss is already certain in vanilla. Its record holds a drop chance of 100 (0x7C), no item, and one slot (0x80 = 1) that names the piece with weight 100 (0x8C); the word the row changed is that count of slots, not a chance (0x558517; scratch/drops_reading.md).</t>
         </is>
       </c>
       <c r="K1355" t="inlineStr">
@@ -75668,7 +75668,7 @@
       </c>
       <c r="L1355" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -75711,7 +75711,7 @@
       </c>
       <c r="J1356" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: the word the row means is EnemyStatusData 0x80, which is not a chance: it is how many pieces the drop draws (0x558517 allocates that many; 0 to 3 over the 516 enemies), and the chance of the drop is 0x7C, already 100 for these bosses (16 for Garasha and Ryoma). 5 is outside what the game holds. To decide: the count (3 at most), or nothing. Was: Postgame rare equipment drop rate gently raised from 2% to 5%.</t>
+          <t>Dropped on 2026-10-11: the piece of this boss is already certain in vanilla. Its record holds a drop chance of 100 (0x7C), no item, and one slot (0x80 = 1) that names the piece with weight 100 (0x8C); the word the row changed is that count of slots, not a chance (0x558517; scratch/drops_reading.md).</t>
         </is>
       </c>
       <c r="K1356" t="inlineStr">
@@ -75721,7 +75721,7 @@
       </c>
       <c r="L1356" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -75764,7 +75764,7 @@
       </c>
       <c r="J1357" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: the word the row means is EnemyStatusData 0x80, which is not a chance: it is how many pieces the drop draws (0x558517 allocates that many; 0 to 3 over the 516 enemies), and the chance of the drop is 0x7C, already 100 for these bosses (16 for Garasha and Ryoma). 5 is outside what the game holds. To decide: the count (3 at most), or nothing. Was: Postgame rare equipment drop rate gently raised from 2% to 5%.</t>
+          <t>Dropped on 2026-10-11: the piece of this boss is already certain in vanilla. Its record holds a drop chance of 100 (0x7C), no item, and one slot (0x80 = 1) that names the piece with weight 100 (0x8C); the word the row changed is that count of slots, not a chance (0x558517; scratch/drops_reading.md).</t>
         </is>
       </c>
       <c r="K1357" t="inlineStr">
@@ -75774,7 +75774,7 @@
       </c>
       <c r="L1357" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -75817,7 +75817,7 @@
       </c>
       <c r="J1358" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: the word the row means is EnemyStatusData 0x80, which is not a chance: it is how many pieces the drop draws (0x558517 allocates that many; 0 to 3 over the 516 enemies), and the chance of the drop is 0x7C, already 100 for these bosses (16 for Garasha and Ryoma). 5 is outside what the game holds. To decide: the count (3 at most), or nothing. Was: Postgame rare equipment drop rate gently raised from 2% to 5%.</t>
+          <t>Dropped on 2026-10-11: the piece of this boss is already certain in vanilla. Its record holds a drop chance of 100 (0x7C), no item, and one slot (0x80 = 1) that names the piece with weight 100 (0x8C); the word the row changed is that count of slots, not a chance (0x558517; scratch/drops_reading.md).</t>
         </is>
       </c>
       <c r="K1358" t="inlineStr">
@@ -75827,7 +75827,7 @@
       </c>
       <c r="L1358" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -75870,7 +75870,7 @@
       </c>
       <c r="J1359" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: the word the row means is EnemyStatusData 0x80, which is not a chance: it is how many pieces the drop draws (0x558517 allocates that many; 0 to 3 over the 516 enemies), and the chance of the drop is 0x7C, already 100 for these bosses (16 for Garasha and Ryoma). 5 is outside what the game holds. To decide: the count (3 at most), or nothing. Was: Postgame rare equipment drop rate gently raised from 2% to 5%.</t>
+          <t>Dropped on 2026-10-11: the piece of this boss is already certain in vanilla. Its record holds a drop chance of 100 (0x7C), no item, and one slot (0x80 = 1) that names the piece with weight 100 (0x8C); the word the row changed is that count of slots, not a chance (0x558517; scratch/drops_reading.md).</t>
         </is>
       </c>
       <c r="K1359" t="inlineStr">
@@ -75880,7 +75880,7 @@
       </c>
       <c r="L1359" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -75923,7 +75923,7 @@
       </c>
       <c r="J1360" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: the word the row means is EnemyStatusData 0x80, which is not a chance: it is how many pieces the drop draws (0x558517 allocates that many; 0 to 3 over the 516 enemies), and the chance of the drop is 0x7C, already 100 for these bosses (16 for Garasha and Ryoma). 5 is outside what the game holds. To decide: the count (3 at most), or nothing. Was: Postgame rare equipment drop rate gently raised from 2% to 5%.</t>
+          <t>Dropped on 2026-10-11: the piece of this boss is already certain in vanilla. Its record holds a drop chance of 100 (0x7C), no item, and one slot (0x80 = 1) that names the piece with weight 100 (0x8C); the word the row changed is that count of slots, not a chance (0x558517; scratch/drops_reading.md).</t>
         </is>
       </c>
       <c r="K1360" t="inlineStr">
@@ -75933,7 +75933,7 @@
       </c>
       <c r="L1360" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -75976,7 +75976,7 @@
       </c>
       <c r="J1361" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: the word the row means is EnemyStatusData 0x80, which is not a chance: it is how many pieces the drop draws (0x558517 allocates that many; 0 to 3 over the 516 enemies), and the chance of the drop is 0x7C, already 100 for these bosses (16 for Garasha and Ryoma). 5 is outside what the game holds. To decide: the count (3 at most), or nothing. Was: Postgame rare equipment drop rate gently raised from 2% to 5%.</t>
+          <t>Dropped on 2026-10-11: the piece of this boss is already certain in vanilla. Its record holds a drop chance of 100 (0x7C), no item, and one slot (0x80 = 1) that names the piece with weight 100 (0x8C); the word the row changed is that count of slots, not a chance (0x558517; scratch/drops_reading.md).</t>
         </is>
       </c>
       <c r="K1361" t="inlineStr">
@@ -75986,7 +75986,7 @@
       </c>
       <c r="L1361" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -76008,14 +76008,14 @@
       </c>
       <c r="D1362" t="inlineStr">
         <is>
-          <t>equipment drop rate</t>
+          <t>equipment slot 1 weight (piece 339)</t>
         </is>
       </c>
       <c r="F1362" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1362" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H1362" t="inlineStr">
         <is>
@@ -76029,17 +76029,17 @@
       </c>
       <c r="J1362" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: the word the row means is EnemyStatusData 0x80, which is not a chance: it is how many pieces the drop draws (0x558517 allocates that many; 0 to 3 over the 516 enemies), and the chance of the drop is 0x7C, already 100 for these bosses (16 for Garasha and Ryoma). 5 is outside what the game holds. To decide: the count (3 at most), or nothing. Was: Rare equipment drop rate gently raised from 2% to 5%.</t>
+          <t>The fixed pieces of common enemies fall 2 to 4.5% of the time; seven fall under 2%, this one 0.80%: chance of the equipment drop 16 (0x7C) times its weight 5 of 100 (0x558570 - 0x5585a8). Raised to the lowest weight that gives 2%: 2.06%. The weights of the other slots are not touched. Reading: scratch/drops_reading.md, checked on 2026-10-11.</t>
         </is>
       </c>
       <c r="K1362" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="L1362" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>built</t>
         </is>
       </c>
     </row>
@@ -76082,7 +76082,7 @@
       </c>
       <c r="J1363" t="inlineStr">
         <is>
-          <t>Blocked on 2026-10-11: the word the row means is EnemyStatusData 0x80, which is not a chance: it is how many pieces the drop draws (0x558517 allocates that many; 0 to 3 over the 516 enemies), and the chance of the drop is 0x7C, already 100 for these bosses (16 for Garasha and Ryoma). 5 is outside what the game holds. To decide: the count (3 at most), or nothing. Was: Rare equipment drop rate gently raised from 2% to 5%.</t>
+          <t>Dropped on 2026-10-11: the word the row changed is the count of slots. The Sudarshana of Ryoma falls 3.2% of the time (chance 16, weight 20 of 100), which is what a fixed piece of a common enemy falls at across the game (2 to 4.5%).</t>
         </is>
       </c>
       <c r="K1363" t="inlineStr">
@@ -76092,7 +76092,7 @@
       </c>
       <c r="L1363" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -81158,6 +81158,324 @@
         </is>
       </c>
       <c r="L1457" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>P079</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>212 Cat's Eye</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>equipment slot 1 weight (piece 656)</t>
+        </is>
+      </c>
+      <c r="F1458" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1458" t="n">
+        <v>17</v>
+      </c>
+      <c r="H1458" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1458" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1458" t="inlineStr">
+        <is>
+          <t>The fixed pieces of common enemies fall 2 to 4.5% of the time; seven fall under 2%, this one 0.91%: chance of the equipment drop 13 (0x7C) times its weight 7 of 100 (0x558570 - 0x5585a8). Raised to the lowest weight that gives 2%: 2.01%. The weights of the other slots are not touched. Reading: scratch/drops_reading.md, checked on 2026-10-11.</t>
+        </is>
+      </c>
+      <c r="K1458" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1458" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>P080</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>732 Knuckle Saint</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>equipment slot 2 weight (piece 761)</t>
+        </is>
+      </c>
+      <c r="F1459" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1459" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1459" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1459" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1459" t="inlineStr">
+        <is>
+          <t>The fixed pieces of common enemies fall 2 to 4.5% of the time; seven fall under 2%, this one 0.90%: chance of the equipment drop 15 (0x7C) times its weight 6 of 100 (0x558570 - 0x5585a8). Raised to the lowest weight that gives 2%: 2.06%. The weights of the other slots are not touched. Reading: scratch/drops_reading.md, checked on 2026-10-11.</t>
+        </is>
+      </c>
+      <c r="K1459" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1459" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>P081</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>236 Thor</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>equipment slot 1 weight (piece 223)</t>
+        </is>
+      </c>
+      <c r="F1460" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1460" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1460" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1460" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1460" t="inlineStr">
+        <is>
+          <t>The fixed pieces of common enemies fall 2 to 4.5% of the time; seven fall under 2%, this one 1.02%: chance of the equipment drop 17 (0x7C) times its weight 6 of 100 (0x558570 - 0x5585a8). Raised to the lowest weight that gives 2%: 2.09%. The weights of the other slots are not touched. Reading: scratch/drops_reading.md, checked on 2026-10-11.</t>
+        </is>
+      </c>
+      <c r="K1460" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1460" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>P082</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>236 Thor</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>equipment slot 2 weight (piece 764)</t>
+        </is>
+      </c>
+      <c r="F1461" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1461" t="n">
+        <v>14</v>
+      </c>
+      <c r="H1461" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1461" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1461" t="inlineStr">
+        <is>
+          <t>The fixed pieces of common enemies fall 2 to 4.5% of the time; seven fall under 2%, this one 1.36%: chance of the equipment drop 17 (0x7C) times its weight 8 of 100 (0x558570 - 0x5585a8). Raised to the lowest weight that gives 2%: 2.09%. The weights of the other slots are not touched. Reading: scratch/drops_reading.md, checked on 2026-10-11.</t>
+        </is>
+      </c>
+      <c r="K1461" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1461" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>P083</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>933 Peach Jam</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>equipment slot 1 weight (piece 643)</t>
+        </is>
+      </c>
+      <c r="F1462" t="n">
+        <v>15</v>
+      </c>
+      <c r="G1462" t="n">
+        <v>29</v>
+      </c>
+      <c r="H1462" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1462" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1462" t="inlineStr">
+        <is>
+          <t>The fixed pieces of common enemies fall 2 to 4.5% of the time; seven fall under 2%, this one 1.20%: chance of the equipment drop 8 (0x7C) times its weight 15 of 100 (0x558570 - 0x5585a8). Raised to the lowest weight that gives 2%: 2.04%. The weights of the other slots are not touched. Reading: scratch/drops_reading.md, checked on 2026-10-11.</t>
+        </is>
+      </c>
+      <c r="K1462" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1462" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>P084</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>65 Shanina</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>equipment slot 2 weight (piece 340)</t>
+        </is>
+      </c>
+      <c r="F1463" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1463" t="n">
+        <v>9</v>
+      </c>
+      <c r="H1463" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1463" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1463" t="inlineStr">
+        <is>
+          <t>The fixed pieces of common enemies fall 2 to 4.5% of the time; seven fall under 2%, this one 1.50%: chance of the equipment drop 25 (0x7C) times its weight 6 of 100 (0x558570 - 0x5585a8). Raised to the lowest weight that gives 2%: 2.18%. The weights of the other slots are not touched. Reading: scratch/drops_reading.md, checked on 2026-10-11.</t>
+        </is>
+      </c>
+      <c r="K1463" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1463" t="inlineStr">
         <is>
           <t>built</t>
         </is>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1463"/>
+  <dimension ref="A1:L1474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81481,6 +81481,619 @@
         </is>
       </c>
     </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>W045</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>356 Tantou</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>upgrade rate</t>
+        </is>
+      </c>
+      <c r="F1464" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G1464" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H1464" t="inlineStr">
+        <is>
+          <t>L14</t>
+        </is>
+      </c>
+      <c r="I1464" t="inlineStr">
+        <is>
+          <t>F04, J27</t>
+        </is>
+      </c>
+      <c r="J1464" t="inlineStr">
+        <is>
+          <t>Proposed 2026-10-11 (classes slow at their stage: Assassin, Treasure Hunter, Kunoichi). The light blades gain 1.0 - 1.3 ATK a forge level, the swords, axes and katanas 1.6 - 3.2; damage is attack less defence (FORMULAS 2.4), so at C30 a Kunoichi (ATK 133 against a boss of DEF 162) deals 11 with a plain blow and the Treasure Hunter 4 at C40. Lever L14, as the Whip (W005)</t>
+        </is>
+      </c>
+      <c r="K1464" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1464" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>Y001</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>Technique 79 Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1465" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1465" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G1465" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H1465" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1465" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="J1465" t="inlineStr">
+        <is>
+          <t>Proposed 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level</t>
+        </is>
+      </c>
+      <c r="K1465" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1465" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>Y002</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>Technique 79 Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1466" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1466" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G1466" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H1466" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1466" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="J1466" t="inlineStr">
+        <is>
+          <t>Proposed 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level</t>
+        </is>
+      </c>
+      <c r="K1466" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1466" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>Y003</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>Technique 79 Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1467" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1467" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G1467" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H1467" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1467" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="J1467" t="inlineStr">
+        <is>
+          <t>Proposed 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level</t>
+        </is>
+      </c>
+      <c r="K1467" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1467" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>Y004</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>Technique 79 Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1468" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1468" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G1468" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H1468" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1468" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="J1468" t="inlineStr">
+        <is>
+          <t>Proposed 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level</t>
+        </is>
+      </c>
+      <c r="K1468" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1468" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>Y005</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>Technique 79 Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1469" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1469" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G1469" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H1469" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1469" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="J1469" t="inlineStr">
+        <is>
+          <t>Proposed 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level</t>
+        </is>
+      </c>
+      <c r="K1469" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1469" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>Y006</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>Technique 79 Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1470" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1470" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G1470" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H1470" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1470" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="J1470" t="inlineStr">
+        <is>
+          <t>Proposed 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level</t>
+        </is>
+      </c>
+      <c r="K1470" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1470" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>Y007</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>Technique 79 Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1471" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1471" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G1471" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H1471" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1471" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="J1471" t="inlineStr">
+        <is>
+          <t>Proposed 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level</t>
+        </is>
+      </c>
+      <c r="K1471" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1471" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>Y008</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>Technique 79 Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1472" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1472" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G1472" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H1472" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1472" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="J1472" t="inlineStr">
+        <is>
+          <t>Proposed 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level</t>
+        </is>
+      </c>
+      <c r="K1472" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1472" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>Y009</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>Technique 79 Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1473" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1473" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G1473" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H1473" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1473" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="J1473" t="inlineStr">
+        <is>
+          <t>Proposed 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level</t>
+        </is>
+      </c>
+      <c r="K1473" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1473" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>Y010</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>Technique 79 Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>effect 26 (power)</t>
+        </is>
+      </c>
+      <c r="E1474" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1474" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G1474" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H1474" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1474" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="J1474" t="inlineStr">
+        <is>
+          <t>Proposed 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level</t>
+        </is>
+      </c>
+      <c r="K1474" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1474" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -81520,7 +81520,7 @@
       </c>
       <c r="J1464" t="inlineStr">
         <is>
-          <t>Proposed 2026-10-11 (classes slow at their stage: Assassin, Treasure Hunter, Kunoichi). The light blades gain 1.0 - 1.3 ATK a forge level, the swords, axes and katanas 1.6 - 3.2; damage is attack less defence (FORMULAS 2.4), so at C30 a Kunoichi (ATK 133 against a boss of DEF 162) deals 11 with a plain blow and the Treasure Hunter 4 at C40. Lever L14, as the Whip (W005)</t>
+          <t>Decided by the user on 2026-10-11 (classes slow at their stage: Assassin, Treasure Hunter, Kunoichi). The light blades gain 1.0 - 1.3 ATK a forge level, the swords, axes and katanas 1.6 - 3.2; damage is attack less defence (FORMULAS 2.4), so at C30 a Kunoichi (ATK 133 against a boss of DEF 162) deals 11 with a plain blow and the Treasure Hunter 4 at C40. Lever L14, as the Whip (W005). Only the Tantou, the blade of the Kunoichi from level 30: with it at twice its rate she goes from 1.31 to 1.10 of the median attacker at C22, C30, C34, C40 and the difficulty curve does not move (37 of 44 within, 7 easier); the Dagger and the Kukri at twice theirs make 17 bosses easier, the reference party holding a Treasure Hunter</t>
         </is>
       </c>
       <c r="K1464" t="inlineStr">
@@ -81530,7 +81530,7 @@
       </c>
       <c r="L1464" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>built</t>
         </is>
       </c>
     </row>
@@ -81571,12 +81571,12 @@
       </c>
       <c r="I1465" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>T05 (every class at its stage; no row of the register names the Trickster)</t>
         </is>
       </c>
       <c r="J1465" t="inlineStr">
         <is>
-          <t>Proposed 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level</t>
+          <t>Decided by the user on 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level. Measured: the Trickster from 1.19 and 1.22 to 1.11 and 1.15 by its two routes; +0.15 gives 1.08 and 1.14 and shortens the fights of the reference party of chapters 15 - 27 by 10 - 15%, so +0.10 is kept</t>
         </is>
       </c>
       <c r="K1465" t="inlineStr">
@@ -81586,7 +81586,7 @@
       </c>
       <c r="L1465" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>built</t>
         </is>
       </c>
     </row>
@@ -81627,12 +81627,12 @@
       </c>
       <c r="I1466" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>T05 (every class at its stage; no row of the register names the Trickster)</t>
         </is>
       </c>
       <c r="J1466" t="inlineStr">
         <is>
-          <t>Proposed 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level</t>
+          <t>Decided by the user on 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level. Measured: the Trickster from 1.19 and 1.22 to 1.11 and 1.15 by its two routes; +0.15 gives 1.08 and 1.14 and shortens the fights of the reference party of chapters 15 - 27 by 10 - 15%, so +0.10 is kept</t>
         </is>
       </c>
       <c r="K1466" t="inlineStr">
@@ -81642,7 +81642,7 @@
       </c>
       <c r="L1466" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>built</t>
         </is>
       </c>
     </row>
@@ -81683,12 +81683,12 @@
       </c>
       <c r="I1467" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>T05 (every class at its stage; no row of the register names the Trickster)</t>
         </is>
       </c>
       <c r="J1467" t="inlineStr">
         <is>
-          <t>Proposed 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level</t>
+          <t>Decided by the user on 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level. Measured: the Trickster from 1.19 and 1.22 to 1.11 and 1.15 by its two routes; +0.15 gives 1.08 and 1.14 and shortens the fights of the reference party of chapters 15 - 27 by 10 - 15%, so +0.10 is kept</t>
         </is>
       </c>
       <c r="K1467" t="inlineStr">
@@ -81698,7 +81698,7 @@
       </c>
       <c r="L1467" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>built</t>
         </is>
       </c>
     </row>
@@ -81739,12 +81739,12 @@
       </c>
       <c r="I1468" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>T05 (every class at its stage; no row of the register names the Trickster)</t>
         </is>
       </c>
       <c r="J1468" t="inlineStr">
         <is>
-          <t>Proposed 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level</t>
+          <t>Decided by the user on 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level. Measured: the Trickster from 1.19 and 1.22 to 1.11 and 1.15 by its two routes; +0.15 gives 1.08 and 1.14 and shortens the fights of the reference party of chapters 15 - 27 by 10 - 15%, so +0.10 is kept</t>
         </is>
       </c>
       <c r="K1468" t="inlineStr">
@@ -81754,7 +81754,7 @@
       </c>
       <c r="L1468" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>built</t>
         </is>
       </c>
     </row>
@@ -81795,12 +81795,12 @@
       </c>
       <c r="I1469" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>T05 (every class at its stage; no row of the register names the Trickster)</t>
         </is>
       </c>
       <c r="J1469" t="inlineStr">
         <is>
-          <t>Proposed 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level</t>
+          <t>Decided by the user on 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level. Measured: the Trickster from 1.19 and 1.22 to 1.11 and 1.15 by its two routes; +0.15 gives 1.08 and 1.14 and shortens the fights of the reference party of chapters 15 - 27 by 10 - 15%, so +0.10 is kept</t>
         </is>
       </c>
       <c r="K1469" t="inlineStr">
@@ -81810,7 +81810,7 @@
       </c>
       <c r="L1469" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>built</t>
         </is>
       </c>
     </row>
@@ -81851,12 +81851,12 @@
       </c>
       <c r="I1470" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>T05 (every class at its stage; no row of the register names the Trickster)</t>
         </is>
       </c>
       <c r="J1470" t="inlineStr">
         <is>
-          <t>Proposed 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level</t>
+          <t>Decided by the user on 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level. Measured: the Trickster from 1.19 and 1.22 to 1.11 and 1.15 by its two routes; +0.15 gives 1.08 and 1.14 and shortens the fights of the reference party of chapters 15 - 27 by 10 - 15%, so +0.10 is kept</t>
         </is>
       </c>
       <c r="K1470" t="inlineStr">
@@ -81866,7 +81866,7 @@
       </c>
       <c r="L1470" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>built</t>
         </is>
       </c>
     </row>
@@ -81907,12 +81907,12 @@
       </c>
       <c r="I1471" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>T05 (every class at its stage; no row of the register names the Trickster)</t>
         </is>
       </c>
       <c r="J1471" t="inlineStr">
         <is>
-          <t>Proposed 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level</t>
+          <t>Decided by the user on 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level. Measured: the Trickster from 1.19 and 1.22 to 1.11 and 1.15 by its two routes; +0.15 gives 1.08 and 1.14 and shortens the fights of the reference party of chapters 15 - 27 by 10 - 15%, so +0.10 is kept</t>
         </is>
       </c>
       <c r="K1471" t="inlineStr">
@@ -81922,7 +81922,7 @@
       </c>
       <c r="L1471" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>built</t>
         </is>
       </c>
     </row>
@@ -81963,12 +81963,12 @@
       </c>
       <c r="I1472" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>T05 (every class at its stage; no row of the register names the Trickster)</t>
         </is>
       </c>
       <c r="J1472" t="inlineStr">
         <is>
-          <t>Proposed 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level</t>
+          <t>Decided by the user on 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level. Measured: the Trickster from 1.19 and 1.22 to 1.11 and 1.15 by its two routes; +0.15 gives 1.08 and 1.14 and shortens the fights of the reference party of chapters 15 - 27 by 10 - 15%, so +0.10 is kept</t>
         </is>
       </c>
       <c r="K1472" t="inlineStr">
@@ -81978,7 +81978,7 @@
       </c>
       <c r="L1472" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>built</t>
         </is>
       </c>
     </row>
@@ -82019,12 +82019,12 @@
       </c>
       <c r="I1473" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>T05 (every class at its stage; no row of the register names the Trickster)</t>
         </is>
       </c>
       <c r="J1473" t="inlineStr">
         <is>
-          <t>Proposed 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level</t>
+          <t>Decided by the user on 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level. Measured: the Trickster from 1.19 and 1.22 to 1.11 and 1.15 by its two routes; +0.15 gives 1.08 and 1.14 and shortens the fights of the reference party of chapters 15 - 27 by 10 - 15%, so +0.10 is kept</t>
         </is>
       </c>
       <c r="K1473" t="inlineStr">
@@ -82034,7 +82034,7 @@
       </c>
       <c r="L1473" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>built</t>
         </is>
       </c>
     </row>
@@ -82075,12 +82075,12 @@
       </c>
       <c r="I1474" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>T05 (every class at its stage; no row of the register names the Trickster)</t>
         </is>
       </c>
       <c r="J1474" t="inlineStr">
         <is>
-          <t>Proposed 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level</t>
+          <t>Decided by the user on 2026-10-11 (the Trickster is 19 - 22% slower than the median attacker at C10, C13, C18): Danger Shoot dealt about 120 a use where Fireball and Frost Slash dealt 155 - 160; the same amount added at every level. Measured: the Trickster from 1.19 and 1.22 to 1.11 and 1.15 by its two routes; +0.15 gives 1.08 and 1.14 and shortens the fights of the reference party of chapters 15 - 27 by 10 - 15%, so +0.10 is kept</t>
         </is>
       </c>
       <c r="K1474" t="inlineStr">
@@ -82090,7 +82090,7 @@
       </c>
       <c r="L1474" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>built</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1474"/>
+  <dimension ref="A1:L1480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5829,7 +5829,7 @@
         <v>30</v>
       </c>
       <c r="G96" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla | Decided 2026-10-11 (the Spieler at the base stage): Danger Shoot is her one attack and its first level cost 27 TP, more than the 20 - 25 TP she has at levels 3 - 5, so she could not use it once (the level a skill is used at is the level it was raised to)</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5885,7 +5885,7 @@
         <v>33</v>
       </c>
       <c r="G97" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla | Decided 2026-10-11 (the Spieler at the base stage): Danger Shoot is her one attack and its first level cost 27 TP, more than the 20 - 25 TP she has at levels 3 - 5, so she could not use it once (the level a skill is used at is the level it was raised to)</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5941,7 +5941,7 @@
         <v>36</v>
       </c>
       <c r="G98" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla | Decided 2026-10-11 (the Spieler at the base stage): Danger Shoot is her one attack and its first level cost 27 TP, more than the 20 - 25 TP she has at levels 3 - 5, so she could not use it once (the level a skill is used at is the level it was raised to)</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5997,7 +5997,7 @@
         <v>40</v>
       </c>
       <c r="G99" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla | Decided 2026-10-11 (the Spieler at the base stage): Danger Shoot is her one attack and its first level cost 27 TP, more than the 20 - 25 TP she has at levels 3 - 5, so she could not use it once (the level a skill is used at is the level it was raised to)</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6053,7 +6053,7 @@
         <v>44</v>
       </c>
       <c r="G100" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla | Decided 2026-10-11 (the Spieler at the base stage): Danger Shoot is her one attack and its first level cost 27 TP, more than the 20 - 25 TP she has at levels 3 - 5, so she could not use it once (the level a skill is used at is the level it was raised to)</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6109,7 +6109,7 @@
         <v>48</v>
       </c>
       <c r="G101" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla | Decided 2026-10-11 (the Spieler at the base stage): Danger Shoot is her one attack and its first level cost 27 TP, more than the 20 - 25 TP she has at levels 3 - 5, so she could not use it once (the level a skill is used at is the level it was raised to)</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6165,7 +6165,7 @@
         <v>52</v>
       </c>
       <c r="G102" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla | Decided 2026-10-11 (the Spieler at the base stage): Danger Shoot is her one attack and its first level cost 27 TP, more than the 20 - 25 TP she has at levels 3 - 5, so she could not use it once (the level a skill is used at is the level it was raised to)</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6221,7 +6221,7 @@
         <v>56</v>
       </c>
       <c r="G103" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla | Decided 2026-10-11 (the Spieler at the base stage): Danger Shoot is her one attack and its first level cost 27 TP, more than the 20 - 25 TP she has at levels 3 - 5, so she could not use it once (the level a skill is used at is the level it was raised to)</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla</t>
+          <t>A little: power per TP at the top level brought toward 70% of level 1, no cost lowered by more than a quarter (it was 59%); the rise of the cost above level 1 scaled by one factor, never above vanilla | Decided 2026-10-11 (the Spieler at the base stage): Danger Shoot is her one attack and its first level cost 27 TP, more than the 20 - 25 TP she has at levels 3 - 5, so she could not use it once (the level a skill is used at is the level it was raised to)</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -82089,6 +82089,343 @@
         </is>
       </c>
       <c r="L1474" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>P085</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>17 Odin</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>steal flag (0x3C bit 15)</t>
+        </is>
+      </c>
+      <c r="F1475" t="inlineStr">
+        <is>
+          <t>0x66ed</t>
+        </is>
+      </c>
+      <c r="G1475" t="inlineStr">
+        <is>
+          <t>0xe6ed</t>
+        </is>
+      </c>
+      <c r="H1475" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I1475" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1475" t="inlineStr">
+        <is>
+          <t>Decided by the user on 2026-10-11: the only four enemies of the random battles Item Steal does not work on (levels 96 - 98, two unique pieces each, 3.9 - 5.4% a kill). With the bit a steal that succeeds draws among their drops as for the other 348 (FORMULAS 12.16)</t>
+        </is>
+      </c>
+      <c r="K1475" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1475" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>P086</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>40 Myrddin</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>steal flag (0x3C bit 15)</t>
+        </is>
+      </c>
+      <c r="F1476" t="inlineStr">
+        <is>
+          <t>0x6e75</t>
+        </is>
+      </c>
+      <c r="G1476" t="inlineStr">
+        <is>
+          <t>0xee75</t>
+        </is>
+      </c>
+      <c r="H1476" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I1476" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1476" t="inlineStr">
+        <is>
+          <t>Decided by the user on 2026-10-11: the only four enemies of the random battles Item Steal does not work on (levels 96 - 98, two unique pieces each, 3.9 - 5.4% a kill). With the bit a steal that succeeds draws among their drops as for the other 348 (FORMULAS 12.16)</t>
+        </is>
+      </c>
+      <c r="K1476" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1476" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>P087</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>144 Asmodeus</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>steal flag (0x3C bit 15)</t>
+        </is>
+      </c>
+      <c r="F1477" t="inlineStr">
+        <is>
+          <t>0x76fd</t>
+        </is>
+      </c>
+      <c r="G1477" t="inlineStr">
+        <is>
+          <t>0xf6fd</t>
+        </is>
+      </c>
+      <c r="H1477" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I1477" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1477" t="inlineStr">
+        <is>
+          <t>Decided by the user on 2026-10-11: the only four enemies of the random battles Item Steal does not work on (levels 96 - 98, two unique pieces each, 3.9 - 5.4% a kill). With the bit a steal that succeeds draws among their drops as for the other 348 (FORMULAS 12.16)</t>
+        </is>
+      </c>
+      <c r="K1477" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1477" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>P088</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>444 Carmilla</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>steal flag (0x3C bit 15)</t>
+        </is>
+      </c>
+      <c r="F1478" t="inlineStr">
+        <is>
+          <t>0x67fd</t>
+        </is>
+      </c>
+      <c r="G1478" t="inlineStr">
+        <is>
+          <t>0xe7fd</t>
+        </is>
+      </c>
+      <c r="H1478" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I1478" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="J1478" t="inlineStr">
+        <is>
+          <t>Decided by the user on 2026-10-11: the only four enemies of the random battles Item Steal does not work on (levels 96 - 98, two unique pieces each, 3.9 - 5.4% a kill). With the bit a steal that succeeds draws among their drops as for the other 348 (FORMULAS 12.16)</t>
+        </is>
+      </c>
+      <c r="K1478" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1478" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>Y011</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>Technique 79 Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>TP cost</t>
+        </is>
+      </c>
+      <c r="E1479" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1479" t="n">
+        <v>27</v>
+      </c>
+      <c r="G1479" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1479" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1479" t="inlineStr">
+        <is>
+          <t>T05 (every class at its stage)</t>
+        </is>
+      </c>
+      <c r="J1479" t="inlineStr">
+        <is>
+          <t>Decided 2026-10-11 (the Spieler at the base stage): Danger Shoot is her one attack and its first level cost 27 TP, more than the 20 - 25 TP she has at levels 3 - 5, so she could not use it once (the level a skill is used at is the level it was raised to)</t>
+        </is>
+      </c>
+      <c r="K1479" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1479" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>W046</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>53 Dagger</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>ATK (base)</t>
+        </is>
+      </c>
+      <c r="F1480" t="n">
+        <v>14</v>
+      </c>
+      <c r="G1480" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1480" t="inlineStr">
+        <is>
+          <t>L14</t>
+        </is>
+      </c>
+      <c r="I1480" t="inlineStr">
+        <is>
+          <t>T05 (every class at its stage)</t>
+        </is>
+      </c>
+      <c r="J1480" t="inlineStr">
+        <is>
+          <t>Decided 2026-10-11 (the Scout with a dagger at the base stage, 9 - 13% of the damage of the party): the Dagger holds 14 ATK where the Shortsword holds 20 and the Short Bow 27; at levels 5 - 9 the forge adds little</t>
+        </is>
+      </c>
+      <c r="K1480" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1480" t="inlineStr">
         <is>
           <t>built</t>
         </is>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1480"/>
+  <dimension ref="A1:L1482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82431,6 +82431,112 @@
         </is>
       </c>
     </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>G116</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>958 Demiurge (C40)</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1481" t="n">
+        <v>24000</v>
+      </c>
+      <c r="G1481" t="n">
+        <v>28800</v>
+      </c>
+      <c r="H1481" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1481" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1481" t="inlineStr">
+        <is>
+          <t>The final boss, an exception decided by the user on 2026-10-11: on the variant the fight lasted 25.1 where vanilla lasts 35.5 and was won 95% of the time against 88%; with the HP of both forms x1.20 it lasts 34.2 and is won 95%. The condition of the gentle fit is set aside for this boss: Anti-Meta-Plus was under the floor of 50% before the change (45%) and goes to 38% (0% in vanilla), Juggernaut-Plus stands at the floor (50%), Mage-Heavy at 72% (40 battles each). x1.30 passes the length of vanilla and takes two more parties under the floor</t>
+        </is>
+      </c>
+      <c r="K1481" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1481" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>G117</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>961 Atialuco (C40)</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F1482" t="n">
+        <v>21800</v>
+      </c>
+      <c r="G1482" t="n">
+        <v>26160</v>
+      </c>
+      <c r="H1482" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1482" t="inlineStr">
+        <is>
+          <t>R08, R10</t>
+        </is>
+      </c>
+      <c r="J1482" t="inlineStr">
+        <is>
+          <t>The final boss, an exception decided by the user on 2026-10-11: on the variant the fight lasted 25.1 where vanilla lasts 35.5 and was won 95% of the time against 88%; with the HP of both forms x1.20 it lasts 34.2 and is won 95%. The condition of the gentle fit is set aside for this boss: Anti-Meta-Plus was under the floor of 50% before the change (45%) and goes to 38% (0% in vanilla), Juggernaut-Plus stands at the floor (50%), Mage-Heavy at 72% (40 battles each). x1.30 passes the length of vanilla and takes two more parties under the floor</t>
+        </is>
+      </c>
+      <c r="K1482" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1482" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1482"/>
+  <dimension ref="A1:L1487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82537,6 +82537,286 @@
         </is>
       </c>
     </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>W047</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>Passive 271 Support Shot</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>effect 260</t>
+        </is>
+      </c>
+      <c r="E1483" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1483" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G1483" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H1483" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1483" t="inlineStr">
+        <is>
+          <t>F52</t>
+        </is>
+      </c>
+      <c r="J1483" t="inlineStr">
+        <is>
+          <t>Decided 2026-10-11 (the user: raise it to a reasonable level): Support Shot fires only after a plain attack of another member, and at 4 - 12% the reference party with and without it was the same inside the noise (C22, C30, C34, C40). At 10 - 30% a Sniper beside members who strike plainly adds a shot to about one of their attacks in three; beside a party that spends TP every turn it stays what it was</t>
+        </is>
+      </c>
+      <c r="K1483" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1483" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>W048</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>Passive 271 Support Shot</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>effect 260</t>
+        </is>
+      </c>
+      <c r="E1484" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1484" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G1484" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H1484" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1484" t="inlineStr">
+        <is>
+          <t>F52</t>
+        </is>
+      </c>
+      <c r="J1484" t="inlineStr">
+        <is>
+          <t>Decided 2026-10-11 (the user: raise it to a reasonable level): Support Shot fires only after a plain attack of another member, and at 4 - 12% the reference party with and without it was the same inside the noise (C22, C30, C34, C40). At 10 - 30% a Sniper beside members who strike plainly adds a shot to about one of their attacks in three; beside a party that spends TP every turn it stays what it was</t>
+        </is>
+      </c>
+      <c r="K1484" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1484" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>W049</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>Passive 271 Support Shot</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>effect 260</t>
+        </is>
+      </c>
+      <c r="E1485" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1485" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G1485" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H1485" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1485" t="inlineStr">
+        <is>
+          <t>F52</t>
+        </is>
+      </c>
+      <c r="J1485" t="inlineStr">
+        <is>
+          <t>Decided 2026-10-11 (the user: raise it to a reasonable level): Support Shot fires only after a plain attack of another member, and at 4 - 12% the reference party with and without it was the same inside the noise (C22, C30, C34, C40). At 10 - 30% a Sniper beside members who strike plainly adds a shot to about one of their attacks in three; beside a party that spends TP every turn it stays what it was</t>
+        </is>
+      </c>
+      <c r="K1485" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1485" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>W050</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>Passive 271 Support Shot</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>effect 260</t>
+        </is>
+      </c>
+      <c r="E1486" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1486" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1486" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H1486" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1486" t="inlineStr">
+        <is>
+          <t>F52</t>
+        </is>
+      </c>
+      <c r="J1486" t="inlineStr">
+        <is>
+          <t>Decided 2026-10-11 (the user: raise it to a reasonable level): Support Shot fires only after a plain attack of another member, and at 4 - 12% the reference party with and without it was the same inside the noise (C22, C30, C34, C40). At 10 - 30% a Sniper beside members who strike plainly adds a shot to about one of their attacks in three; beside a party that spends TP every turn it stays what it was</t>
+        </is>
+      </c>
+      <c r="K1486" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1486" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>W051</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>Passive 271 Support Shot</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>effect 260</t>
+        </is>
+      </c>
+      <c r="E1487" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1487" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G1487" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H1487" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="I1487" t="inlineStr">
+        <is>
+          <t>F52</t>
+        </is>
+      </c>
+      <c r="J1487" t="inlineStr">
+        <is>
+          <t>Decided 2026-10-11 (the user: raise it to a reasonable level): Support Shot fires only after a plain attack of another member, and at 4 - 12% the reference party with and without it was the same inside the noise (C22, C30, C34, C40). At 10 - 30% a Sniper beside members who strike plainly adds a shot to about one of their attacks in three; beside a party that spends TP every turn it stays what it was</t>
+        </is>
+      </c>
+      <c r="K1487" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L1487" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -26451,7 +26451,7 @@
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>A good draw pays for the TP of the skill. The chances of the outcomes (executable, L37) are not touched; the empty outcome, the 666 damage and the money ones stay</t>
+          <t>Dropped on 2026-10-11 (the user): the outcome strikes one unit of the battle at random, members of the party included (target code 15), so a larger value is a larger risk, not a better draw; it stays at level x 10. Was: A good draw pays for the TP of the skill. The chances of the outcomes (executable, L37) are not touched; the empty outcome, the 666 damage and the money ones stay</t>
         </is>
       </c>
       <c r="K464" t="inlineStr">
@@ -26461,7 +26461,7 @@
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t>built</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1487"/>
+  <dimension ref="A1:L1499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82817,6 +82817,646 @@
         </is>
       </c>
     </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>E213</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>921 Hell's Angel (P28)</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>res</t>
+        </is>
+      </c>
+      <c r="F1488" t="n">
+        <v>407</v>
+      </c>
+      <c r="G1488" t="n">
+        <v>366</v>
+      </c>
+      <c r="H1488" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1488" t="inlineStr">
+        <is>
+          <t>J02</t>
+        </is>
+      </c>
+      <c r="J1488" t="inlineStr">
+        <is>
+          <t>Row J02 (decided 2026-10-09: lower a little what walls magic off at the superbosses, keeping their flavour; the user, 2026-10-12: without abuse, the postgame stays hard, the mages keep some of their power). At the six fights where the best option of the mage was under that of the Dark Lord, RES of every enemy times 0.9; the elemental resistances are left alone (lowering them raises the elemental strikes of the Dark Lord as much as the spells: measured, the mage stays at 50 - 84%). The mage beside the Dark Lord there: P28 51%, P29 73%, P30 50%, P33 84%, P50 54%, P51 51% before, P28 59%, P29 95%, P30 80%, P33 104%, P50 70%, P51 57% after</t>
+        </is>
+      </c>
+      <c r="K1488" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L1488" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>E214</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>992 Panagia (P33)</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>res</t>
+        </is>
+      </c>
+      <c r="F1489" t="n">
+        <v>556</v>
+      </c>
+      <c r="G1489" t="n">
+        <v>500</v>
+      </c>
+      <c r="H1489" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1489" t="inlineStr">
+        <is>
+          <t>J02</t>
+        </is>
+      </c>
+      <c r="J1489" t="inlineStr">
+        <is>
+          <t>Row J02 (decided 2026-10-09: lower a little what walls magic off at the superbosses, keeping their flavour; the user, 2026-10-12: without abuse, the postgame stays hard, the mages keep some of their power). At the six fights where the best option of the mage was under that of the Dark Lord, RES of every enemy times 0.9; the elemental resistances are left alone (lowering them raises the elemental strikes of the Dark Lord as much as the spells: measured, the mage stays at 50 - 84%). The mage beside the Dark Lord there: P28 51%, P29 73%, P30 50%, P33 84%, P50 54%, P51 51% before, P28 59%, P29 95%, P30 80%, P33 104%, P50 70%, P51 57% after</t>
+        </is>
+      </c>
+      <c r="K1489" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L1489" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>E215</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>972 Tenerezza (P30)</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>res</t>
+        </is>
+      </c>
+      <c r="F1490" t="n">
+        <v>548</v>
+      </c>
+      <c r="G1490" t="n">
+        <v>493</v>
+      </c>
+      <c r="H1490" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1490" t="inlineStr">
+        <is>
+          <t>J02</t>
+        </is>
+      </c>
+      <c r="J1490" t="inlineStr">
+        <is>
+          <t>Row J02 (decided 2026-10-09: lower a little what walls magic off at the superbosses, keeping their flavour; the user, 2026-10-12: without abuse, the postgame stays hard, the mages keep some of their power). At the six fights where the best option of the mage was under that of the Dark Lord, RES of every enemy times 0.9; the elemental resistances are left alone (lowering them raises the elemental strikes of the Dark Lord as much as the spells: measured, the mage stays at 50 - 84%). The mage beside the Dark Lord there: P28 51%, P29 73%, P30 50%, P33 84%, P50 54%, P51 51% before, P28 59%, P29 95%, P30 80%, P33 104%, P50 70%, P51 57% after</t>
+        </is>
+      </c>
+      <c r="K1490" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L1490" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>E216</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>975 Lolo (P30)</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>res</t>
+        </is>
+      </c>
+      <c r="F1491" t="n">
+        <v>666</v>
+      </c>
+      <c r="G1491" t="n">
+        <v>599</v>
+      </c>
+      <c r="H1491" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1491" t="inlineStr">
+        <is>
+          <t>J02</t>
+        </is>
+      </c>
+      <c r="J1491" t="inlineStr">
+        <is>
+          <t>Row J02 (decided 2026-10-09: lower a little what walls magic off at the superbosses, keeping their flavour; the user, 2026-10-12: without abuse, the postgame stays hard, the mages keep some of their power). At the six fights where the best option of the mage was under that of the Dark Lord, RES of every enemy times 0.9; the elemental resistances are left alone (lowering them raises the elemental strikes of the Dark Lord as much as the spells: measured, the mage stays at 50 - 84%). The mage beside the Dark Lord there: P28 51%, P29 73%, P30 50%, P33 84%, P50 54%, P51 51% before, P28 59%, P29 95%, P30 80%, P33 104%, P50 70%, P51 57% after</t>
+        </is>
+      </c>
+      <c r="K1491" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L1491" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>E217</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>993 Panagia (P33)</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>res</t>
+        </is>
+      </c>
+      <c r="F1492" t="n">
+        <v>532</v>
+      </c>
+      <c r="G1492" t="n">
+        <v>478</v>
+      </c>
+      <c r="H1492" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1492" t="inlineStr">
+        <is>
+          <t>J02</t>
+        </is>
+      </c>
+      <c r="J1492" t="inlineStr">
+        <is>
+          <t>Row J02 (decided 2026-10-09: lower a little what walls magic off at the superbosses, keeping their flavour; the user, 2026-10-12: without abuse, the postgame stays hard, the mages keep some of their power). At the six fights where the best option of the mage was under that of the Dark Lord, RES of every enemy times 0.9; the elemental resistances are left alone (lowering them raises the elemental strikes of the Dark Lord as much as the spells: measured, the mage stays at 50 - 84%). The mage beside the Dark Lord there: P28 51%, P29 73%, P30 50%, P33 84%, P50 54%, P51 51% before, P28 59%, P29 95%, P30 80%, P33 104%, P50 70%, P51 57% after</t>
+        </is>
+      </c>
+      <c r="K1492" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L1492" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>E218</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>996 Radiant Being (P33)</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>res</t>
+        </is>
+      </c>
+      <c r="F1493" t="n">
+        <v>431</v>
+      </c>
+      <c r="G1493" t="n">
+        <v>387</v>
+      </c>
+      <c r="H1493" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1493" t="inlineStr">
+        <is>
+          <t>J02</t>
+        </is>
+      </c>
+      <c r="J1493" t="inlineStr">
+        <is>
+          <t>Row J02 (decided 2026-10-09: lower a little what walls magic off at the superbosses, keeping their flavour; the user, 2026-10-12: without abuse, the postgame stays hard, the mages keep some of their power). At the six fights where the best option of the mage was under that of the Dark Lord, RES of every enemy times 0.9; the elemental resistances are left alone (lowering them raises the elemental strikes of the Dark Lord as much as the spells: measured, the mage stays at 50 - 84%). The mage beside the Dark Lord there: P28 51%, P29 73%, P30 50%, P33 84%, P50 54%, P51 51% before, P28 59%, P29 95%, P30 80%, P33 104%, P50 70%, P51 57% after</t>
+        </is>
+      </c>
+      <c r="K1493" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L1493" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>E219</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>973 Tenerezza (P50)</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>res</t>
+        </is>
+      </c>
+      <c r="F1494" t="n">
+        <v>1648</v>
+      </c>
+      <c r="G1494" t="n">
+        <v>1483</v>
+      </c>
+      <c r="H1494" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1494" t="inlineStr">
+        <is>
+          <t>J02</t>
+        </is>
+      </c>
+      <c r="J1494" t="inlineStr">
+        <is>
+          <t>Row J02 (decided 2026-10-09: lower a little what walls magic off at the superbosses, keeping their flavour; the user, 2026-10-12: without abuse, the postgame stays hard, the mages keep some of their power). At the six fights where the best option of the mage was under that of the Dark Lord, RES of every enemy times 0.9; the elemental resistances are left alone (lowering them raises the elemental strikes of the Dark Lord as much as the spells: measured, the mage stays at 50 - 84%). The mage beside the Dark Lord there: P28 51%, P29 73%, P30 50%, P33 84%, P50 54%, P51 51% before, P28 59%, P29 95%, P30 80%, P33 104%, P50 70%, P51 57% after</t>
+        </is>
+      </c>
+      <c r="K1494" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L1494" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>E220</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>976 Lolo (P50)</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>res</t>
+        </is>
+      </c>
+      <c r="F1495" t="n">
+        <v>745</v>
+      </c>
+      <c r="G1495" t="n">
+        <v>670</v>
+      </c>
+      <c r="H1495" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1495" t="inlineStr">
+        <is>
+          <t>J02</t>
+        </is>
+      </c>
+      <c r="J1495" t="inlineStr">
+        <is>
+          <t>Row J02 (decided 2026-10-09: lower a little what walls magic off at the superbosses, keeping their flavour; the user, 2026-10-12: without abuse, the postgame stays hard, the mages keep some of their power). At the six fights where the best option of the mage was under that of the Dark Lord, RES of every enemy times 0.9; the elemental resistances are left alone (lowering them raises the elemental strikes of the Dark Lord as much as the spells: measured, the mage stays at 50 - 84%). The mage beside the Dark Lord there: P28 51%, P29 73%, P30 50%, P33 84%, P50 54%, P51 51% before, P28 59%, P29 95%, P30 80%, P33 104%, P50 70%, P51 57% after</t>
+        </is>
+      </c>
+      <c r="K1495" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L1495" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>E221</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>985 Samson (P51)</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>res</t>
+        </is>
+      </c>
+      <c r="F1496" t="n">
+        <v>972</v>
+      </c>
+      <c r="G1496" t="n">
+        <v>874</v>
+      </c>
+      <c r="H1496" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1496" t="inlineStr">
+        <is>
+          <t>J02</t>
+        </is>
+      </c>
+      <c r="J1496" t="inlineStr">
+        <is>
+          <t>Row J02 (decided 2026-10-09: lower a little what walls magic off at the superbosses, keeping their flavour; the user, 2026-10-12: without abuse, the postgame stays hard, the mages keep some of their power). At the six fights where the best option of the mage was under that of the Dark Lord, RES of every enemy times 0.9; the elemental resistances are left alone (lowering them raises the elemental strikes of the Dark Lord as much as the spells: measured, the mage stays at 50 - 84%). The mage beside the Dark Lord there: P28 51%, P29 73%, P30 50%, P33 84%, P50 54%, P51 51% before, P28 59%, P29 95%, P30 80%, P33 104%, P50 70%, P51 57% after</t>
+        </is>
+      </c>
+      <c r="K1496" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L1496" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>E222</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>979 Magna Meretrix (P51)</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>res</t>
+        </is>
+      </c>
+      <c r="F1497" t="n">
+        <v>1298</v>
+      </c>
+      <c r="G1497" t="n">
+        <v>1168</v>
+      </c>
+      <c r="H1497" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1497" t="inlineStr">
+        <is>
+          <t>J02</t>
+        </is>
+      </c>
+      <c r="J1497" t="inlineStr">
+        <is>
+          <t>Row J02 (decided 2026-10-09: lower a little what walls magic off at the superbosses, keeping their flavour; the user, 2026-10-12: without abuse, the postgame stays hard, the mages keep some of their power). At the six fights where the best option of the mage was under that of the Dark Lord, RES of every enemy times 0.9; the elemental resistances are left alone (lowering them raises the elemental strikes of the Dark Lord as much as the spells: measured, the mage stays at 50 - 84%). The mage beside the Dark Lord there: P28 51%, P29 73%, P30 50%, P33 84%, P50 54%, P51 51% before, P28 59%, P29 95%, P30 80%, P33 104%, P50 70%, P51 57% after</t>
+        </is>
+      </c>
+      <c r="K1497" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L1497" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>E223</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>982 Adon (P51)</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>res</t>
+        </is>
+      </c>
+      <c r="F1498" t="n">
+        <v>844</v>
+      </c>
+      <c r="G1498" t="n">
+        <v>759</v>
+      </c>
+      <c r="H1498" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="I1498" t="inlineStr">
+        <is>
+          <t>J02</t>
+        </is>
+      </c>
+      <c r="J1498" t="inlineStr">
+        <is>
+          <t>Row J02 (decided 2026-10-09: lower a little what walls magic off at the superbosses, keeping their flavour; the user, 2026-10-12: without abuse, the postgame stays hard, the mages keep some of their power). At the six fights where the best option of the mage was under that of the Dark Lord, RES of every enemy times 0.9; the elemental resistances are left alone (lowering them raises the elemental strikes of the Dark Lord as much as the spells: measured, the mage stays at 50 - 84%). The mage beside the Dark Lord there: P28 51%, P29 73%, P30 50%, P33 84%, P50 54%, P51 51% before, P28 59%, P29 95%, P30 80%, P33 104%, P50 70%, P51 57% after</t>
+        </is>
+      </c>
+      <c r="K1498" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L1498" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>P089</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>sealbooks</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>Grand Sealbook [Molle] (0829)</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>secondary enchantment</t>
+        </is>
+      </c>
+      <c r="F1499" t="inlineStr">
+        <is>
+          <t>ench_cnt=1 (262 only)</t>
+        </is>
+      </c>
+      <c r="G1499" t="inlineStr">
+        <is>
+          <t>ench_cnt=2 (262 Escape probability UP, 270 Gain more EXP from higher-level enemies)</t>
+        </is>
+      </c>
+      <c r="H1499" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1499" t="inlineStr">
+        <is>
+          <t>U01</t>
+        </is>
+      </c>
+      <c r="J1499" t="inlineStr">
+        <is>
+          <t>The user, 2026-10-12: the piece that raises the EXP factors of B4 comes late (the Grand Sealbook of Dragon Papi, level 44); he wants the same effect around level 20 - 30, on one unique thing that is neither farmed nor stolen, without filling the game with such pieces. Molle is a boss of the story at level 23 and its grand sealbook, made once from it, held only "Escape probability UP". The book of Dragon Papi keeps its own</t>
+        </is>
+      </c>
+      <c r="K1499" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L1499" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1499"/>
+  <dimension ref="A1:L1500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83443,7 +83443,7 @@
       </c>
       <c r="J1499" t="inlineStr">
         <is>
-          <t>The user, 2026-10-12: the piece that raises the EXP factors of B4 comes late (the Grand Sealbook of Dragon Papi, level 44); he wants the same effect around level 20 - 30, on one unique thing that is neither farmed nor stolen, without filling the game with such pieces. Molle is a boss of the story at level 23 and its grand sealbook, made once from it, held only "Escape probability UP". The book of Dragon Papi keeps its own</t>
+          <t>Dropped on 2026-10-12 (the user): the effect goes on an accessory, not on a sealbook; the book of Molle is as in vanilla. Was: The user, 2026-10-12: the piece that raises the EXP factors of B4 comes late (the Grand Sealbook of Dragon Papi, level 44); he wants the same effect around level 20 - 30, on one unique thing that is neither farmed nor stolen, without filling the game with such pieces. Molle is a boss of the story at level 23 and its grand sealbook, made once from it, held only "Escape probability UP". The book of Dragon Papi keeps its own</t>
         </is>
       </c>
       <c r="K1499" t="inlineStr">
@@ -83452,6 +83452,59 @@
         </is>
       </c>
       <c r="L1499" t="inlineStr">
+        <is>
+          <t>dropped</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>P090</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>732 Bathroom Slippers</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>Enchant 2 (0x64)</t>
+        </is>
+      </c>
+      <c r="F1500" t="n">
+        <v>33</v>
+      </c>
+      <c r="G1500" t="n">
+        <v>270</v>
+      </c>
+      <c r="H1500" t="inlineStr">
+        <is>
+          <t>L15</t>
+        </is>
+      </c>
+      <c r="I1500" t="inlineStr">
+        <is>
+          <t>U01</t>
+        </is>
+      </c>
+      <c r="J1500" t="inlineStr">
+        <is>
+          <t>The user, 2026-10-12: the piece that raises the EXP factors of B4 comes late (the Grand Sealbook of Dragon Papi, level 44); he wants the same effect earlier on one unique accessory that is neither farmed nor stolen, without filling the game with such pieces. The Bathroom Slippers are the reward of quest rank 3, given once, wearable by every class; they keep "Nullify poison" and give up "Physical defense UP" (enchantment 33), the count of innate enchantments staying as it is (lever L15)</t>
+        </is>
+      </c>
+      <c r="K1500" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L1500" t="inlineStr">
         <is>
           <t>built</t>
         </is>

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -39827,7 +39827,7 @@
         <v>-0.04</v>
       </c>
       <c r="G702" t="n">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="H702" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length</t>
+          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length | 2026-10-12 (the user: raise the Etoile more, without making her a Diva): times 1.5 again. As the one support of the Meta party she won 50% / 88% / 67% at C30 / C34 / C38 and wins 68% / 98% / 82% with it; C36 (10%) and the last boss (0%) stay out of her reach, they ask for a heal she does not have, nor with Primevil. Beside a Diva the party gains at most 14 points (C38), nothing elsewhere: scratch/audit_2026-10-11/etoile_trial.py</t>
         </is>
       </c>
       <c r="K702" t="inlineStr">
@@ -39883,7 +39883,7 @@
         <v>-0.06</v>
       </c>
       <c r="G703" t="n">
-        <v>-0.09</v>
+        <v>-0.14</v>
       </c>
       <c r="H703" t="inlineStr">
         <is>
@@ -39897,7 +39897,7 @@
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length</t>
+          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length | 2026-10-12 (the user: raise the Etoile more, without making her a Diva): times 1.5 again. As the one support of the Meta party she won 50% / 88% / 67% at C30 / C34 / C38 and wins 68% / 98% / 82% with it; C36 (10%) and the last boss (0%) stay out of her reach, they ask for a heal she does not have, nor with Primevil. Beside a Diva the party gains at most 14 points (C38), nothing elsewhere: scratch/audit_2026-10-11/etoile_trial.py</t>
         </is>
       </c>
       <c r="K703" t="inlineStr">
@@ -39939,7 +39939,7 @@
         <v>-0.08</v>
       </c>
       <c r="G704" t="n">
-        <v>-0.12</v>
+        <v>-0.18</v>
       </c>
       <c r="H704" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
       </c>
       <c r="J704" t="inlineStr">
         <is>
-          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length</t>
+          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length | 2026-10-12 (the user: raise the Etoile more, without making her a Diva): times 1.5 again. As the one support of the Meta party she won 50% / 88% / 67% at C30 / C34 / C38 and wins 68% / 98% / 82% with it; C36 (10%) and the last boss (0%) stay out of her reach, they ask for a heal she does not have, nor with Primevil. Beside a Diva the party gains at most 14 points (C38), nothing elsewhere: scratch/audit_2026-10-11/etoile_trial.py</t>
         </is>
       </c>
       <c r="K704" t="inlineStr">
@@ -39995,7 +39995,7 @@
         <v>-0.1</v>
       </c>
       <c r="G705" t="n">
-        <v>-0.15</v>
+        <v>-0.22</v>
       </c>
       <c r="H705" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length</t>
+          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length | 2026-10-12 (the user: raise the Etoile more, without making her a Diva): times 1.5 again. As the one support of the Meta party she won 50% / 88% / 67% at C30 / C34 / C38 and wins 68% / 98% / 82% with it; C36 (10%) and the last boss (0%) stay out of her reach, they ask for a heal she does not have, nor with Primevil. Beside a Diva the party gains at most 14 points (C38), nothing elsewhere: scratch/audit_2026-10-11/etoile_trial.py</t>
         </is>
       </c>
       <c r="K705" t="inlineStr">
@@ -40051,7 +40051,7 @@
         <v>-0.11</v>
       </c>
       <c r="G706" t="n">
-        <v>-0.17</v>
+        <v>-0.26</v>
       </c>
       <c r="H706" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
       </c>
       <c r="J706" t="inlineStr">
         <is>
-          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length</t>
+          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length | 2026-10-12 (the user: raise the Etoile more, without making her a Diva): times 1.5 again. As the one support of the Meta party she won 50% / 88% / 67% at C30 / C34 / C38 and wins 68% / 98% / 82% with it; C36 (10%) and the last boss (0%) stay out of her reach, they ask for a heal she does not have, nor with Primevil. Beside a Diva the party gains at most 14 points (C38), nothing elsewhere: scratch/audit_2026-10-11/etoile_trial.py</t>
         </is>
       </c>
       <c r="K706" t="inlineStr">
@@ -40107,7 +40107,7 @@
         <v>-0.12</v>
       </c>
       <c r="G707" t="n">
-        <v>-0.18</v>
+        <v>-0.27</v>
       </c>
       <c r="H707" t="inlineStr">
         <is>
@@ -40121,7 +40121,7 @@
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length</t>
+          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length | 2026-10-12 (the user: raise the Etoile more, without making her a Diva): times 1.5 again. As the one support of the Meta party she won 50% / 88% / 67% at C30 / C34 / C38 and wins 68% / 98% / 82% with it; C36 (10%) and the last boss (0%) stay out of her reach, they ask for a heal she does not have, nor with Primevil. Beside a Diva the party gains at most 14 points (C38), nothing elsewhere: scratch/audit_2026-10-11/etoile_trial.py</t>
         </is>
       </c>
       <c r="K707" t="inlineStr">
@@ -40163,7 +40163,7 @@
         <v>-0.13</v>
       </c>
       <c r="G708" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="H708" t="inlineStr">
         <is>
@@ -40177,7 +40177,7 @@
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length</t>
+          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length | 2026-10-12 (the user: raise the Etoile more, without making her a Diva): times 1.5 again. As the one support of the Meta party she won 50% / 88% / 67% at C30 / C34 / C38 and wins 68% / 98% / 82% with it; C36 (10%) and the last boss (0%) stay out of her reach, they ask for a heal she does not have, nor with Primevil. Beside a Diva the party gains at most 14 points (C38), nothing elsewhere: scratch/audit_2026-10-11/etoile_trial.py</t>
         </is>
       </c>
       <c r="K708" t="inlineStr">
@@ -40219,7 +40219,7 @@
         <v>-0.14</v>
       </c>
       <c r="G709" t="n">
-        <v>-0.21</v>
+        <v>-0.32</v>
       </c>
       <c r="H709" t="inlineStr">
         <is>
@@ -40233,7 +40233,7 @@
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length</t>
+          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length | 2026-10-12 (the user: raise the Etoile more, without making her a Diva): times 1.5 again. As the one support of the Meta party she won 50% / 88% / 67% at C30 / C34 / C38 and wins 68% / 98% / 82% with it; C36 (10%) and the last boss (0%) stay out of her reach, they ask for a heal she does not have, nor with Primevil. Beside a Diva the party gains at most 14 points (C38), nothing elsewhere: scratch/audit_2026-10-11/etoile_trial.py</t>
         </is>
       </c>
       <c r="K709" t="inlineStr">
@@ -40275,7 +40275,7 @@
         <v>-0.15</v>
       </c>
       <c r="G710" t="n">
-        <v>-0.23</v>
+        <v>-0.35</v>
       </c>
       <c r="H710" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length</t>
+          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length | 2026-10-12 (the user: raise the Etoile more, without making her a Diva): times 1.5 again. As the one support of the Meta party she won 50% / 88% / 67% at C30 / C34 / C38 and wins 68% / 98% / 82% with it; C36 (10%) and the last boss (0%) stay out of her reach, they ask for a heal she does not have, nor with Primevil. Beside a Diva the party gains at most 14 points (C38), nothing elsewhere: scratch/audit_2026-10-11/etoile_trial.py</t>
         </is>
       </c>
       <c r="K710" t="inlineStr">
@@ -40331,7 +40331,7 @@
         <v>-0.16</v>
       </c>
       <c r="G711" t="n">
-        <v>-0.24</v>
+        <v>-0.36</v>
       </c>
       <c r="H711" t="inlineStr">
         <is>
@@ -40345,7 +40345,7 @@
       </c>
       <c r="J711" t="inlineStr">
         <is>
-          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length</t>
+          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length | 2026-10-12 (the user: raise the Etoile more, without making her a Diva): times 1.5 again. As the one support of the Meta party she won 50% / 88% / 67% at C30 / C34 / C38 and wins 68% / 98% / 82% with it; C36 (10%) and the last boss (0%) stay out of her reach, they ask for a heal she does not have, nor with Primevil. Beside a Diva the party gains at most 14 points (C38), nothing elsewhere: scratch/audit_2026-10-11/etoile_trial.py</t>
         </is>
       </c>
       <c r="K711" t="inlineStr">
@@ -42067,7 +42067,7 @@
         <v>-0.05</v>
       </c>
       <c r="G742" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="H742" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
       </c>
       <c r="J742" t="inlineStr">
         <is>
-          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length</t>
+          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length | 2026-10-12 (the user: raise the Etoile more, without making her a Diva): times 1.5 again. As the one support of the Meta party she won 50% / 88% / 67% at C30 / C34 / C38 and wins 68% / 98% / 82% with it; C36 (10%) and the last boss (0%) stay out of her reach, they ask for a heal she does not have, nor with Primevil. Beside a Diva the party gains at most 14 points (C38), nothing elsewhere: scratch/audit_2026-10-11/etoile_trial.py</t>
         </is>
       </c>
       <c r="K742" t="inlineStr">
@@ -42123,7 +42123,7 @@
         <v>-0.06</v>
       </c>
       <c r="G743" t="n">
-        <v>-0.09</v>
+        <v>-0.14</v>
       </c>
       <c r="H743" t="inlineStr">
         <is>
@@ -42137,7 +42137,7 @@
       </c>
       <c r="J743" t="inlineStr">
         <is>
-          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length</t>
+          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length | 2026-10-12 (the user: raise the Etoile more, without making her a Diva): times 1.5 again. As the one support of the Meta party she won 50% / 88% / 67% at C30 / C34 / C38 and wins 68% / 98% / 82% with it; C36 (10%) and the last boss (0%) stay out of her reach, they ask for a heal she does not have, nor with Primevil. Beside a Diva the party gains at most 14 points (C38), nothing elsewhere: scratch/audit_2026-10-11/etoile_trial.py</t>
         </is>
       </c>
       <c r="K743" t="inlineStr">
@@ -42179,7 +42179,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="G744" t="n">
-        <v>-0.1</v>
+        <v>-0.15</v>
       </c>
       <c r="H744" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
       </c>
       <c r="J744" t="inlineStr">
         <is>
-          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length</t>
+          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length | 2026-10-12 (the user: raise the Etoile more, without making her a Diva): times 1.5 again. As the one support of the Meta party she won 50% / 88% / 67% at C30 / C34 / C38 and wins 68% / 98% / 82% with it; C36 (10%) and the last boss (0%) stay out of her reach, they ask for a heal she does not have, nor with Primevil. Beside a Diva the party gains at most 14 points (C38), nothing elsewhere: scratch/audit_2026-10-11/etoile_trial.py</t>
         </is>
       </c>
       <c r="K744" t="inlineStr">
@@ -42235,7 +42235,7 @@
         <v>-0.08</v>
       </c>
       <c r="G745" t="n">
-        <v>-0.12</v>
+        <v>-0.18</v>
       </c>
       <c r="H745" t="inlineStr">
         <is>
@@ -42249,7 +42249,7 @@
       </c>
       <c r="J745" t="inlineStr">
         <is>
-          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length</t>
+          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length | 2026-10-12 (the user: raise the Etoile more, without making her a Diva): times 1.5 again. As the one support of the Meta party she won 50% / 88% / 67% at C30 / C34 / C38 and wins 68% / 98% / 82% with it; C36 (10%) and the last boss (0%) stay out of her reach, they ask for a heal she does not have, nor with Primevil. Beside a Diva the party gains at most 14 points (C38), nothing elsewhere: scratch/audit_2026-10-11/etoile_trial.py</t>
         </is>
       </c>
       <c r="K745" t="inlineStr">
@@ -42291,7 +42291,7 @@
         <v>-0.09</v>
       </c>
       <c r="G746" t="n">
-        <v>-0.14</v>
+        <v>-0.21</v>
       </c>
       <c r="H746" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
       </c>
       <c r="J746" t="inlineStr">
         <is>
-          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length</t>
+          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length | 2026-10-12 (the user: raise the Etoile more, without making her a Diva): times 1.5 again. As the one support of the Meta party she won 50% / 88% / 67% at C30 / C34 / C38 and wins 68% / 98% / 82% with it; C36 (10%) and the last boss (0%) stay out of her reach, they ask for a heal she does not have, nor with Primevil. Beside a Diva the party gains at most 14 points (C38), nothing elsewhere: scratch/audit_2026-10-11/etoile_trial.py</t>
         </is>
       </c>
       <c r="K746" t="inlineStr">
@@ -42347,7 +42347,7 @@
         <v>-0.1</v>
       </c>
       <c r="G747" t="n">
-        <v>-0.15</v>
+        <v>-0.22</v>
       </c>
       <c r="H747" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
       </c>
       <c r="J747" t="inlineStr">
         <is>
-          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length</t>
+          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length | 2026-10-12 (the user: raise the Etoile more, without making her a Diva): times 1.5 again. As the one support of the Meta party she won 50% / 88% / 67% at C30 / C34 / C38 and wins 68% / 98% / 82% with it; C36 (10%) and the last boss (0%) stay out of her reach, they ask for a heal she does not have, nor with Primevil. Beside a Diva the party gains at most 14 points (C38), nothing elsewhere: scratch/audit_2026-10-11/etoile_trial.py</t>
         </is>
       </c>
       <c r="K747" t="inlineStr">
@@ -42403,7 +42403,7 @@
         <v>-0.11</v>
       </c>
       <c r="G748" t="n">
-        <v>-0.17</v>
+        <v>-0.26</v>
       </c>
       <c r="H748" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
       </c>
       <c r="J748" t="inlineStr">
         <is>
-          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length</t>
+          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length | 2026-10-12 (the user: raise the Etoile more, without making her a Diva): times 1.5 again. As the one support of the Meta party she won 50% / 88% / 67% at C30 / C34 / C38 and wins 68% / 98% / 82% with it; C36 (10%) and the last boss (0%) stay out of her reach, they ask for a heal she does not have, nor with Primevil. Beside a Diva the party gains at most 14 points (C38), nothing elsewhere: scratch/audit_2026-10-11/etoile_trial.py</t>
         </is>
       </c>
       <c r="K748" t="inlineStr">
@@ -42459,7 +42459,7 @@
         <v>-0.12</v>
       </c>
       <c r="G749" t="n">
-        <v>-0.18</v>
+        <v>-0.27</v>
       </c>
       <c r="H749" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
       </c>
       <c r="J749" t="inlineStr">
         <is>
-          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length</t>
+          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length | 2026-10-12 (the user: raise the Etoile more, without making her a Diva): times 1.5 again. As the one support of the Meta party she won 50% / 88% / 67% at C30 / C34 / C38 and wins 68% / 98% / 82% with it; C36 (10%) and the last boss (0%) stay out of her reach, they ask for a heal she does not have, nor with Primevil. Beside a Diva the party gains at most 14 points (C38), nothing elsewhere: scratch/audit_2026-10-11/etoile_trial.py</t>
         </is>
       </c>
       <c r="K749" t="inlineStr">
@@ -42515,7 +42515,7 @@
         <v>-0.13</v>
       </c>
       <c r="G750" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="H750" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
       </c>
       <c r="J750" t="inlineStr">
         <is>
-          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length</t>
+          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length | 2026-10-12 (the user: raise the Etoile more, without making her a Diva): times 1.5 again. As the one support of the Meta party she won 50% / 88% / 67% at C30 / C34 / C38 and wins 68% / 98% / 82% with it; C36 (10%) and the last boss (0%) stay out of her reach, they ask for a heal she does not have, nor with Primevil. Beside a Diva the party gains at most 14 points (C38), nothing elsewhere: scratch/audit_2026-10-11/etoile_trial.py</t>
         </is>
       </c>
       <c r="K750" t="inlineStr">
@@ -42571,7 +42571,7 @@
         <v>-0.14</v>
       </c>
       <c r="G751" t="n">
-        <v>-0.21</v>
+        <v>-0.32</v>
       </c>
       <c r="H751" t="inlineStr">
         <is>
@@ -42585,7 +42585,7 @@
       </c>
       <c r="J751" t="inlineStr">
         <is>
-          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length</t>
+          <t>Debuffs x1.5, so that a debuff pays back the turn it costs within its length | 2026-10-12 (the user: raise the Etoile more, without making her a Diva): times 1.5 again. As the one support of the Meta party she won 50% / 88% / 67% at C30 / C34 / C38 and wins 68% / 98% / 82% with it; C36 (10%) and the last boss (0%) stay out of her reach, they ask for a heal she does not have, nor with Primevil. Beside a Diva the party gains at most 14 points (C38), nothing elsewhere: scratch/audit_2026-10-11/etoile_trial.py</t>
         </is>
       </c>
       <c r="K751" t="inlineStr">

--- a/mod_project/data_tables/balance_changes.xlsx
+++ b/mod_project/data_tables/balance_changes.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1500"/>
+  <dimension ref="A1:L1503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83510,6 +83510,165 @@
         </is>
       </c>
     </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>Y012</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>items</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>19 Magical Fruit</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>effect 1 value (TP to one member)</t>
+        </is>
+      </c>
+      <c r="F1501" t="n">
+        <v>25</v>
+      </c>
+      <c r="G1501" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1501" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1501" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="J1501" t="inlineStr">
+        <is>
+          <t>The user, 2026-10-12 (row F01: no party without the Maid line wins from C30 on): a fifth more TP from the fruit, not a new cut of TP costs, which would move every party. Measured before it: the Meta party with a Bishop for its Diva wins 2% at C30 and C34 with 8 fruit of 50 TP, 50% with 24, 100% with TP at will; C36 and the last boss do not turn on TP. The Maid keeps her part; without her the fights are won with effort and a bag of fruit</t>
+        </is>
+      </c>
+      <c r="K1501" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L1501" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>Y013</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>items</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>20 Fairy Apple</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>effect 1 value (TP to one member)</t>
+        </is>
+      </c>
+      <c r="F1502" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1502" t="n">
+        <v>60</v>
+      </c>
+      <c r="H1502" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1502" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="J1502" t="inlineStr">
+        <is>
+          <t>The user, 2026-10-12 (row F01: no party without the Maid line wins from C30 on): a fifth more TP from the fruit, not a new cut of TP costs, which would move every party. Measured before it: the Meta party with a Bishop for its Diva wins 2% at C30 and C34 with 8 fruit of 50 TP, 50% with 24, 100% with TP at will; C36 and the last boss do not turn on TP. The Maid keeps her part; without her the fights are won with effort and a bag of fruit</t>
+        </is>
+      </c>
+      <c r="K1502" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L1502" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>Y014</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>items</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>21 Golden Apple</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>effect 1 value (TP to one member)</t>
+        </is>
+      </c>
+      <c r="F1503" t="n">
+        <v>100</v>
+      </c>
+      <c r="G1503" t="n">
+        <v>120</v>
+      </c>
+      <c r="H1503" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="I1503" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="J1503" t="inlineStr">
+        <is>
+          <t>The user, 2026-10-12 (row F01: no party without the Maid line wins from C30 on): a fifth more TP from the fruit, not a new cut of TP costs, which would move every party. Measured before it: the Meta party with a Bishop for its Diva wins 2% at C30 and C34 with 8 fruit of 50 TP, 50% with 24, 100% with TP at will; C36 and the last boss do not turn on TP. The Maid keeps her part; without her the fights are won with effort and a bag of fruit</t>
+        </is>
+      </c>
+      <c r="K1503" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L1503" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
